--- a/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
+++ b/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
@@ -3,10 +3,11 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2625" yWindow="1965" windowWidth="21600" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4875" yWindow="1785" windowWidth="21600" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="_RarityConfig" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -524,11 +525,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
@@ -545,11 +544,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="4">
@@ -563,11 +560,9 @@
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -581,11 +576,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n">
-        <v>8.970000000000001</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="6">
@@ -599,11 +592,9 @@
           <t>Special Illustration Rare</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>1440</v>
-      </c>
+      <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n">
-        <v>40.46</v>
+        <v>39.96</v>
       </c>
     </row>
     <row r="7">
@@ -617,11 +608,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n">
-        <v>0.83</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="8">
@@ -635,11 +624,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9">
@@ -653,11 +640,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n">
-        <v>0.98</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="10">
@@ -671,11 +656,9 @@
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -689,11 +672,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n">
-        <v>5.81</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="12">
@@ -707,11 +688,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="13">
@@ -725,11 +704,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="14">
@@ -743,11 +720,9 @@
           <t>Hyper Rare</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>900</v>
-      </c>
+      <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n">
-        <v>5.24</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="15">
@@ -761,11 +736,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="16">
@@ -779,11 +752,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="17">
@@ -797,11 +768,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="18">
@@ -815,11 +784,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="19">
@@ -833,11 +800,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n">
-        <v>3.61</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="20">
@@ -851,11 +816,9 @@
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="21">
@@ -869,11 +832,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n">
-        <v>13.45</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="22">
@@ -887,11 +848,9 @@
           <t>Special Illustration Rare</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
-        <v>1440</v>
-      </c>
+      <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n">
-        <v>70.53</v>
+        <v>69.04000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -905,11 +864,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="24">
@@ -923,11 +880,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n">
-        <v>37.23</v>
+        <v>37.68</v>
       </c>
     </row>
     <row r="25">
@@ -941,11 +896,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="26">
@@ -959,11 +912,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="27">
@@ -977,11 +928,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n">
-        <v>9.65</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="28">
@@ -995,11 +944,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n">
-        <v>1.01</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="29">
@@ -1013,11 +960,9 @@
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>5.13</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="30">
@@ -1031,11 +976,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="n">
-        <v>30.95</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="31">
@@ -1049,11 +992,9 @@
           <t>Special Illustration Rare</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>1440</v>
-      </c>
+      <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="n">
-        <v>208.89</v>
+        <v>204.44</v>
       </c>
     </row>
     <row r="32">
@@ -1067,11 +1008,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="33">
@@ -1085,11 +1024,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="n">
-        <v>49.26</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="34">
@@ -1103,11 +1040,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="35">
@@ -1121,11 +1056,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n">
-        <v>33.43</v>
+        <v>32.05</v>
       </c>
     </row>
     <row r="36">
@@ -1139,11 +1072,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="37">
@@ -1157,11 +1088,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="38">
@@ -1175,9 +1104,7 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="n">
         <v>0.15</v>
       </c>
@@ -1193,11 +1120,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="40">
@@ -1211,11 +1136,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C40" s="3" t="n"/>
       <c r="D40" s="3" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="41">
@@ -1229,11 +1152,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="42">
@@ -1247,11 +1168,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="n">
-        <v>3.9</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="43">
@@ -1265,11 +1184,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="44">
@@ -1283,11 +1200,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C44" s="3" t="n"/>
       <c r="D44" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="45">
@@ -1301,11 +1216,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="n">
-        <v>1.06</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1319,11 +1232,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="47">
@@ -1337,11 +1248,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C47" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C47" s="3" t="n"/>
       <c r="D47" s="3" t="n">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="48">
@@ -1355,11 +1264,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C48" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C48" s="3" t="n"/>
       <c r="D48" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="49">
@@ -1373,11 +1280,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C49" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C49" s="3" t="n"/>
       <c r="D49" s="3" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="50">
@@ -1391,11 +1296,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C50" s="3" t="n"/>
       <c r="D50" s="3" t="n">
-        <v>26.7</v>
+        <v>25.72</v>
       </c>
     </row>
     <row r="51">
@@ -1409,11 +1312,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C51" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C51" s="3" t="n"/>
       <c r="D51" s="3" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="52">
@@ -1427,9 +1328,7 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C52" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C52" s="3" t="n"/>
       <c r="D52" s="3" t="n">
         <v>0.18</v>
       </c>
@@ -1445,9 +1344,7 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C53" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C53" s="3" t="n"/>
       <c r="D53" s="3" t="n">
         <v>0.15</v>
       </c>
@@ -1463,9 +1360,7 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C54" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C54" s="3" t="n"/>
       <c r="D54" s="3" t="n">
         <v>0.16</v>
       </c>
@@ -1481,11 +1376,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C55" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C55" s="3" t="n"/>
       <c r="D55" s="3" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="56">
@@ -1499,11 +1392,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C56" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C56" s="3" t="n"/>
       <c r="D56" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="57">
@@ -1517,11 +1408,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C57" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C57" s="3" t="n"/>
       <c r="D57" s="3" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="58">
@@ -1535,11 +1424,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C58" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C58" s="3" t="n"/>
       <c r="D58" s="3" t="n">
-        <v>2.23</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="59">
@@ -1553,11 +1440,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C59" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C59" s="3" t="n"/>
       <c r="D59" s="3" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="60">
@@ -1571,11 +1456,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C60" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C60" s="3" t="n"/>
       <c r="D60" s="3" t="n">
-        <v>1.19</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -1589,11 +1472,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C61" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C61" s="3" t="n"/>
       <c r="D61" s="3" t="n">
-        <v>7.76</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="62">
@@ -1607,11 +1488,9 @@
           <t>Special Illustration Rare</t>
         </is>
       </c>
-      <c r="C62" s="3" t="n">
-        <v>1440</v>
-      </c>
+      <c r="C62" s="3" t="n"/>
       <c r="D62" s="3" t="n">
-        <v>15.77</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="63">
@@ -1625,11 +1504,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C63" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C63" s="3" t="n"/>
       <c r="D63" s="3" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="64">
@@ -1643,11 +1520,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C64" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C64" s="3" t="n"/>
       <c r="D64" s="3" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="65">
@@ -1661,11 +1536,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C65" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C65" s="3" t="n"/>
       <c r="D65" s="3" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="66">
@@ -1679,11 +1552,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C66" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C66" s="3" t="n"/>
       <c r="D66" s="3" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="67">
@@ -1697,11 +1568,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C67" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C67" s="3" t="n"/>
       <c r="D67" s="3" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="68">
@@ -1715,11 +1584,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C68" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C68" s="3" t="n"/>
       <c r="D68" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="69">
@@ -1733,11 +1600,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C69" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C69" s="3" t="n"/>
       <c r="D69" s="3" t="n">
-        <v>2.99</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="70">
@@ -1751,9 +1616,7 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C70" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C70" s="3" t="n"/>
       <c r="D70" s="3" t="n">
         <v>0.14</v>
       </c>
@@ -1769,11 +1632,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C71" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C71" s="3" t="n"/>
       <c r="D71" s="3" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="72">
@@ -1787,11 +1648,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C72" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C72" s="3" t="n"/>
       <c r="D72" s="3" t="n">
-        <v>4.57</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="73">
@@ -1805,11 +1664,9 @@
           <t>Special Illustration Rare</t>
         </is>
       </c>
-      <c r="C73" s="3" t="n">
-        <v>1440</v>
-      </c>
+      <c r="C73" s="3" t="n"/>
       <c r="D73" s="3" t="n">
-        <v>15.06</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="74">
@@ -1823,11 +1680,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C74" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C74" s="3" t="n"/>
       <c r="D74" s="3" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="75">
@@ -1841,11 +1696,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C75" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C75" s="3" t="n"/>
       <c r="D75" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="76">
@@ -1859,11 +1712,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C76" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C76" s="3" t="n"/>
       <c r="D76" s="3" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="77">
@@ -1877,11 +1728,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C77" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C77" s="3" t="n"/>
       <c r="D77" s="3" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="78">
@@ -1895,11 +1744,9 @@
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="C78" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="C78" s="3" t="n"/>
       <c r="D78" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="79">
@@ -1913,11 +1760,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C79" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C79" s="3" t="n"/>
       <c r="D79" s="3" t="n">
-        <v>6.55</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="80">
@@ -1931,11 +1776,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C80" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C80" s="3" t="n"/>
       <c r="D80" s="3" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="81">
@@ -1949,11 +1792,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C81" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C81" s="3" t="n"/>
       <c r="D81" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="82">
@@ -1967,11 +1808,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C82" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C82" s="3" t="n"/>
       <c r="D82" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="83">
@@ -1985,9 +1824,7 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C83" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C83" s="3" t="n"/>
       <c r="D83" s="3" t="n">
         <v>0.2</v>
       </c>
@@ -2003,11 +1840,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C84" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C84" s="3" t="n"/>
       <c r="D84" s="3" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="85">
@@ -2021,11 +1856,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C85" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C85" s="3" t="n"/>
       <c r="D85" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="86">
@@ -2039,11 +1872,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C86" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C86" s="3" t="n"/>
       <c r="D86" s="3" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2057,11 +1888,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C87" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C87" s="3" t="n"/>
       <c r="D87" s="3" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="88">
@@ -2075,11 +1904,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C88" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C88" s="3" t="n"/>
       <c r="D88" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="89">
@@ -2093,11 +1920,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C89" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C89" s="3" t="n"/>
       <c r="D89" s="3" t="n">
-        <v>2.56</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="90">
@@ -2111,11 +1936,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C90" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C90" s="3" t="n"/>
       <c r="D90" s="3" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="91">
@@ -2129,11 +1952,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C91" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C91" s="3" t="n"/>
       <c r="D91" s="3" t="n">
-        <v>29.73</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="92">
@@ -2147,9 +1968,7 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C92" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C92" s="3" t="n"/>
       <c r="D92" s="3" t="n">
         <v>0.19</v>
       </c>
@@ -2165,11 +1984,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C93" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C93" s="3" t="n"/>
       <c r="D93" s="3" t="n">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="94">
@@ -2183,11 +2000,9 @@
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="C94" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="C94" s="3" t="n"/>
       <c r="D94" s="3" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="95">
@@ -2201,11 +2016,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C95" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C95" s="3" t="n"/>
       <c r="D95" s="3" t="n">
-        <v>5.22</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="96">
@@ -2219,11 +2032,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C96" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C96" s="3" t="n"/>
       <c r="D96" s="3" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="97">
@@ -2237,11 +2048,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C97" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C97" s="3" t="n"/>
       <c r="D97" s="3" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="98">
@@ -2255,11 +2064,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C98" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C98" s="3" t="n"/>
       <c r="D98" s="3" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="99">
@@ -2273,11 +2080,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C99" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C99" s="3" t="n"/>
       <c r="D99" s="3" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="100">
@@ -2291,11 +2096,9 @@
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="C100" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="C100" s="3" t="n"/>
       <c r="D100" s="3" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="101">
@@ -2309,11 +2112,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C101" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C101" s="3" t="n"/>
       <c r="D101" s="3" t="n">
-        <v>6.58</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="102">
@@ -2327,11 +2128,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C102" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C102" s="3" t="n"/>
       <c r="D102" s="3" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="103">
@@ -2345,11 +2144,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C103" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C103" s="3" t="n"/>
       <c r="D103" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="104">
@@ -2363,11 +2160,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C104" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C104" s="3" t="n"/>
       <c r="D104" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="105">
@@ -2381,11 +2176,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C105" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C105" s="3" t="n"/>
       <c r="D105" s="3" t="n">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="106">
@@ -2399,11 +2192,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C106" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C106" s="3" t="n"/>
       <c r="D106" s="3" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="107">
@@ -2417,11 +2208,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C107" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C107" s="3" t="n"/>
       <c r="D107" s="3" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="108">
@@ -2435,9 +2224,7 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C108" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C108" s="3" t="n"/>
       <c r="D108" s="3" t="n">
         <v>0.6</v>
       </c>
@@ -2453,11 +2240,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C109" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C109" s="3" t="n"/>
       <c r="D109" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="110">
@@ -2471,11 +2256,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C110" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C110" s="3" t="n"/>
       <c r="D110" s="3" t="n">
-        <v>12.04</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="111">
@@ -2489,11 +2272,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C111" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C111" s="3" t="n"/>
       <c r="D111" s="3" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="112">
@@ -2507,11 +2288,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C112" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C112" s="3" t="n"/>
       <c r="D112" s="3" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="113">
@@ -2525,11 +2304,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C113" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C113" s="3" t="n"/>
       <c r="D113" s="3" t="n">
-        <v>2.07</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="114">
@@ -2543,11 +2320,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C114" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C114" s="3" t="n"/>
       <c r="D114" s="3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="115">
@@ -2561,9 +2336,7 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C115" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C115" s="3" t="n"/>
       <c r="D115" s="3" t="n">
         <v>0.14</v>
       </c>
@@ -2579,11 +2352,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C116" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C116" s="3" t="n"/>
       <c r="D116" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="117">
@@ -2597,11 +2368,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C117" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C117" s="3" t="n"/>
       <c r="D117" s="3" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="118">
@@ -2615,9 +2384,7 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C118" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C118" s="3" t="n"/>
       <c r="D118" s="3" t="n">
         <v>0.17</v>
       </c>
@@ -2633,11 +2400,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C119" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C119" s="3" t="n"/>
       <c r="D119" s="3" t="n">
-        <v>2.71</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="120">
@@ -2651,11 +2416,9 @@
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="C120" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="C120" s="3" t="n"/>
       <c r="D120" s="3" t="n">
-        <v>7.31</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="121">
@@ -2669,11 +2432,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C121" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C121" s="3" t="n"/>
       <c r="D121" s="3" t="n">
-        <v>19.15</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="122">
@@ -2687,11 +2448,9 @@
           <t>Hyper Rare</t>
         </is>
       </c>
-      <c r="C122" s="3" t="n">
-        <v>900</v>
-      </c>
+      <c r="C122" s="3" t="n"/>
       <c r="D122" s="3" t="n">
-        <v>12.33</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="123">
@@ -2705,11 +2464,9 @@
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="C123" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="C123" s="3" t="n"/>
       <c r="D123" s="3" t="n">
-        <v>11</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="124">
@@ -2723,11 +2480,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C124" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C124" s="3" t="n"/>
       <c r="D124" s="3" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="125">
@@ -2741,11 +2496,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C125" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C125" s="3" t="n"/>
       <c r="D125" s="3" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="126">
@@ -2759,11 +2512,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C126" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C126" s="3" t="n"/>
       <c r="D126" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="127">
@@ -2777,11 +2528,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C127" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C127" s="3" t="n"/>
       <c r="D127" s="3" t="n">
-        <v>7</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="128">
@@ -2795,11 +2544,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C128" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C128" s="3" t="n"/>
       <c r="D128" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="129">
@@ -2813,11 +2560,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C129" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C129" s="3" t="n"/>
       <c r="D129" s="3" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="130">
@@ -2831,11 +2576,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C130" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C130" s="3" t="n"/>
       <c r="D130" s="3" t="n">
-        <v>10.76</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="131">
@@ -2849,11 +2592,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C131" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C131" s="3" t="n"/>
       <c r="D131" s="3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="132">
@@ -2867,11 +2608,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C132" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C132" s="3" t="n"/>
       <c r="D132" s="3" t="n">
-        <v>2.57</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="133">
@@ -2885,11 +2624,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C133" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C133" s="3" t="n"/>
       <c r="D133" s="3" t="n">
-        <v>2.79</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="134">
@@ -2903,11 +2640,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C134" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C134" s="3" t="n"/>
       <c r="D134" s="3" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="135">
@@ -2921,11 +2656,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C135" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C135" s="3" t="n"/>
       <c r="D135" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="136">
@@ -2939,11 +2672,9 @@
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="C136" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="C136" s="3" t="n"/>
       <c r="D136" s="3" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="137">
@@ -2957,11 +2688,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C137" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C137" s="3" t="n"/>
       <c r="D137" s="3" t="n">
-        <v>9.210000000000001</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="138">
@@ -2975,11 +2704,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C138" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C138" s="3" t="n"/>
       <c r="D138" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="139">
@@ -2993,11 +2720,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C139" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C139" s="3" t="n"/>
       <c r="D139" s="3" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="140">
@@ -3011,11 +2736,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C140" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C140" s="3" t="n"/>
       <c r="D140" s="3" t="n">
-        <v>6.55</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="141">
@@ -3029,11 +2752,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C141" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C141" s="3" t="n"/>
       <c r="D141" s="3" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="142">
@@ -3047,11 +2768,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C142" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C142" s="3" t="n"/>
       <c r="D142" s="3" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="143">
@@ -3065,11 +2784,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C143" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C143" s="3" t="n"/>
       <c r="D143" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="144">
@@ -3083,9 +2800,7 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C144" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C144" s="3" t="n"/>
       <c r="D144" s="3" t="n">
         <v>0.12</v>
       </c>
@@ -3101,11 +2816,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C145" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C145" s="3" t="n"/>
       <c r="D145" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="146">
@@ -3119,11 +2832,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C146" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C146" s="3" t="n"/>
       <c r="D146" s="3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="147">
@@ -3137,11 +2848,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C147" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C147" s="3" t="n"/>
       <c r="D147" s="3" t="n">
-        <v>4.52</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="148">
@@ -3155,11 +2864,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C148" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C148" s="3" t="n"/>
       <c r="D148" s="3" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="149">
@@ -3173,11 +2880,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C149" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C149" s="3" t="n"/>
       <c r="D149" s="3" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="150">
@@ -3191,11 +2896,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C150" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C150" s="3" t="n"/>
       <c r="D150" s="3" t="n">
-        <v>31.52</v>
+        <v>31.45</v>
       </c>
     </row>
     <row r="151">
@@ -3209,11 +2912,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C151" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C151" s="3" t="n"/>
       <c r="D151" s="3" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="152">
@@ -3227,11 +2928,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C152" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C152" s="3" t="n"/>
       <c r="D152" s="3" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="153">
@@ -3245,11 +2944,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C153" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C153" s="3" t="n"/>
       <c r="D153" s="3" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="154">
@@ -3263,11 +2960,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C154" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C154" s="3" t="n"/>
       <c r="D154" s="3" t="n">
-        <v>17.7</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="155">
@@ -3281,11 +2976,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C155" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C155" s="3" t="n"/>
       <c r="D155" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="156">
@@ -3299,11 +2992,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C156" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C156" s="3" t="n"/>
       <c r="D156" s="3" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="157">
@@ -3317,9 +3008,7 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C157" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C157" s="3" t="n"/>
       <c r="D157" s="3" t="n">
         <v>0.11</v>
       </c>
@@ -3335,9 +3024,7 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C158" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C158" s="3" t="n"/>
       <c r="D158" s="3" t="n">
         <v>0.15</v>
       </c>
@@ -3353,11 +3040,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C159" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C159" s="3" t="n"/>
       <c r="D159" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="160">
@@ -3371,11 +3056,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C160" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C160" s="3" t="n"/>
       <c r="D160" s="3" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="161">
@@ -3389,11 +3072,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C161" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C161" s="3" t="n"/>
       <c r="D161" s="3" t="n">
-        <v>25.21</v>
+        <v>21.01</v>
       </c>
     </row>
     <row r="162">
@@ -3407,11 +3088,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C162" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C162" s="3" t="n"/>
       <c r="D162" s="3" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="163">
@@ -3425,11 +3104,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C163" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C163" s="3" t="n"/>
       <c r="D163" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="164">
@@ -3443,9 +3120,7 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C164" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C164" s="3" t="n"/>
       <c r="D164" s="3" t="n">
         <v>0.18</v>
       </c>
@@ -3461,11 +3136,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C165" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C165" s="3" t="n"/>
       <c r="D165" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="166">
@@ -3479,11 +3152,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C166" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C166" s="3" t="n"/>
       <c r="D166" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="167">
@@ -3497,11 +3168,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C167" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C167" s="3" t="n"/>
       <c r="D167" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="168">
@@ -3515,11 +3184,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C168" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C168" s="3" t="n"/>
       <c r="D168" s="3" t="n">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="169">
@@ -3533,11 +3200,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C169" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C169" s="3" t="n"/>
       <c r="D169" s="3" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="170">
@@ -3551,11 +3216,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C170" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C170" s="3" t="n"/>
       <c r="D170" s="3" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="171">
@@ -3569,11 +3232,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C171" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C171" s="3" t="n"/>
       <c r="D171" s="3" t="n">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="172">
@@ -3587,11 +3248,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C172" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C172" s="3" t="n"/>
       <c r="D172" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="173">
@@ -3605,11 +3264,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C173" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C173" s="3" t="n"/>
       <c r="D173" s="3" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="174">
@@ -3623,11 +3280,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C174" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C174" s="3" t="n"/>
       <c r="D174" s="3" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="175">
@@ -3641,11 +3296,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C175" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C175" s="3" t="n"/>
       <c r="D175" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="176">
@@ -3659,9 +3312,7 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C176" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C176" s="3" t="n"/>
       <c r="D176" s="3" t="n">
         <v>0.18</v>
       </c>
@@ -3677,11 +3328,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C177" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C177" s="3" t="n"/>
       <c r="D177" s="3" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="178">
@@ -3695,11 +3344,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C178" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C178" s="3" t="n"/>
       <c r="D178" s="3" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="179">
@@ -3713,11 +3360,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C179" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C179" s="3" t="n"/>
       <c r="D179" s="3" t="n">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="180">
@@ -3731,11 +3376,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C180" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C180" s="3" t="n"/>
       <c r="D180" s="3" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="181">
@@ -3749,11 +3392,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C181" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C181" s="3" t="n"/>
       <c r="D181" s="3" t="n">
-        <v>45.81</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="182">
@@ -3767,11 +3408,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C182" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C182" s="3" t="n"/>
       <c r="D182" s="3" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="183">
@@ -3785,11 +3424,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C183" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C183" s="3" t="n"/>
       <c r="D183" s="3" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="184">
@@ -3803,11 +3440,9 @@
           <t>Hyper Rare</t>
         </is>
       </c>
-      <c r="C184" s="3" t="n">
-        <v>900</v>
-      </c>
+      <c r="C184" s="3" t="n"/>
       <c r="D184" s="3" t="n">
-        <v>3.22</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="185">
@@ -3821,9 +3456,7 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C185" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C185" s="3" t="n"/>
       <c r="D185" s="3" t="n">
         <v>0.16</v>
       </c>
@@ -3839,11 +3472,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C186" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C186" s="3" t="n"/>
       <c r="D186" s="3" t="n">
-        <v>8.390000000000001</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="187">
@@ -3857,11 +3488,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C187" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C187" s="3" t="n"/>
       <c r="D187" s="3" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="188">
@@ -3875,11 +3504,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C188" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C188" s="3" t="n"/>
       <c r="D188" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="189">
@@ -3893,11 +3520,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C189" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C189" s="3" t="n"/>
       <c r="D189" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="190">
@@ -3911,11 +3536,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C190" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C190" s="3" t="n"/>
       <c r="D190" s="3" t="n">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="191">
@@ -3929,11 +3552,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C191" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C191" s="3" t="n"/>
       <c r="D191" s="3" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="192">
@@ -3947,11 +3568,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C192" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C192" s="3" t="n"/>
       <c r="D192" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="193">
@@ -3965,11 +3584,9 @@
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="C193" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="C193" s="3" t="n"/>
       <c r="D193" s="3" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="194">
@@ -3983,11 +3600,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C194" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C194" s="3" t="n"/>
       <c r="D194" s="3" t="n">
-        <v>11.52</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="195">
@@ -4001,11 +3616,9 @@
           <t>Special Illustration Rare</t>
         </is>
       </c>
-      <c r="C195" s="3" t="n">
-        <v>1440</v>
-      </c>
+      <c r="C195" s="3" t="n"/>
       <c r="D195" s="3" t="n">
-        <v>63.82</v>
+        <v>64.23999999999999</v>
       </c>
     </row>
     <row r="196">
@@ -4019,9 +3632,7 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C196" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C196" s="3" t="n"/>
       <c r="D196" s="3" t="n">
         <v>0.15</v>
       </c>
@@ -4037,11 +3648,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C197" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C197" s="3" t="n"/>
       <c r="D197" s="3" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="198">
@@ -4055,11 +3664,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C198" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C198" s="3" t="n"/>
       <c r="D198" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="199">
@@ -4073,11 +3680,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C199" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C199" s="3" t="n"/>
       <c r="D199" s="3" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="200">
@@ -4091,11 +3696,9 @@
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="C200" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="C200" s="3" t="n"/>
       <c r="D200" s="3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="201">
@@ -4109,11 +3712,9 @@
           <t>Illustration Rare</t>
         </is>
       </c>
-      <c r="C201" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C201" s="3" t="n"/>
       <c r="D201" s="3" t="n">
-        <v>29.17</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="202">
@@ -4127,11 +3728,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C202" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C202" s="3" t="n"/>
       <c r="D202" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="203">
@@ -4145,11 +3744,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C203" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C203" s="3" t="n"/>
       <c r="D203" s="3" t="n">
-        <v>2.69</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="204">
@@ -4163,11 +3760,9 @@
           <t>Rare</t>
         </is>
       </c>
-      <c r="C204" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="C204" s="3" t="n"/>
       <c r="D204" s="3" t="n">
-        <v>0.77</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="205">
@@ -4181,11 +3776,9 @@
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="C205" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="C205" s="3" t="n"/>
       <c r="D205" s="3" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="206">
@@ -4199,11 +3792,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C206" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C206" s="3" t="n"/>
       <c r="D206" s="3" t="n">
-        <v>6.67</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="207">
@@ -4217,11 +3808,9 @@
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="C207" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="C207" s="3" t="n"/>
       <c r="D207" s="3" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="208">
@@ -4235,11 +3824,9 @@
           <t>Ultra Rare</t>
         </is>
       </c>
-      <c r="C208" s="3" t="n">
-        <v>161</v>
-      </c>
+      <c r="C208" s="3" t="n"/>
       <c r="D208" s="3" t="n">
-        <v>8.15</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="209">
@@ -4253,11 +3840,9 @@
           <t>Special Illustration Rare</t>
         </is>
       </c>
-      <c r="C209" s="3" t="n">
-        <v>1440</v>
-      </c>
+      <c r="C209" s="3" t="n"/>
       <c r="D209" s="3" t="n">
-        <v>53.44</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="210">
@@ -4271,11 +3856,9 @@
           <t>Common</t>
         </is>
       </c>
-      <c r="C210" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="C210" s="3" t="n"/>
       <c r="D210" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="211">
@@ -5134,4 +4717,40 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32.28515625" customWidth="1" min="1" max="1"/>
+    <col width="27.5703125" customWidth="1" min="2" max="2"/>
+    <col width="29.140625" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rarity Name (Column A)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull Rate (1/X) (Column B) </t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Notes (Column C - optional)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
+++ b/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4875" yWindow="1785" windowWidth="21600" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4725" yWindow="4215" windowWidth="21600" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -445,10 +445,9 @@
   <dimension ref="A1:K353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39.6" customWidth="1" min="1" max="1"/>
+    <col width="39.5703125" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="4"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="33.5703125" customWidth="1" min="5" max="5"/>
     <col width="32.42578125" customWidth="1" min="6" max="7"/>
     <col width="39.42578125" customWidth="1" min="8" max="8"/>
@@ -4725,12 +4724,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:G210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32.28515625" customWidth="1" min="1" max="1"/>
-    <col width="27.5703125" customWidth="1" min="2" max="2"/>
-    <col width="29.140625" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32.4" customWidth="1" min="2" max="2"/>
+    <col width="32.4" customWidth="1" min="3" max="3"/>
+    <col width="39.6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4749,6 +4749,3852 @@
           <t>Notes (Column C - optional)</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Card Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Price ($)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Rarity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Pull Rate (1/X)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>66</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Abra</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>62</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Aerodactyl</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Alakazam ex - 065/165</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Alakazam ex - 188/165</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>248</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Alakazam ex - 201/165</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>39.96</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>188</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Antique Dome Fossil</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>225</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Antique Helix Fossil</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hyper Rare </t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>154</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Antique Old Amber</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Arbok ex - 024/165</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Arbok ex - 185/165</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Arcanine</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Articuno</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Basic Psychic Energy - 207/165</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Beedrill</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Bellsprout</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Big Air Balloon</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Bill's Transfer - 156/165</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Bill's Transfer - 194/165</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Blastoise ex - 009/165</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Blastoise ex - 184/165</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Blastoise ex - 200/165</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>69.68000000000001</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Bulbasaur - 001/165</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Bulbasaur - 166/165</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>37.68</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Butterfree</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Caterpie - 010/165</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Caterpie - 172/165</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Chansey</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Charizard ex - 006/165</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Charizard ex - 183/165</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>30.96</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Charizard ex - 199/165</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>204.44</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Charmander - 004/165</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Charmander - 168/165</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Charmeleon - 005/165</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Charmeleon - 169/165</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Clefable</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Clefairy</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Cloyster</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Cubone</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Cycling Road</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Daisy's Help - 158/165</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Daisy's Help - 195/165</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Dewgong</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Diglett</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Ditto</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Ditto - 132/165 (Non-Holo)</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Dodrio</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Doduo</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Dragonair - 148/165</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Dragonair - 181/165</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Dragonite</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Dratini</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Drowzee</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Dugtrio</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Eevee</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Ekans</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Electabuzz</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Electrode</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Energy Sticker</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Erika's Invitation - 160/165</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Erika's Invitation - 196/165</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Erika's Invitation - 203/165</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Exeggcute</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Exeggutor</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Farfetch'd</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Fearow</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Flareon</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Gastly</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Gengar</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Geodude</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Giovanni's Charisma - 161/165</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Giovanni's Charisma - 197/165</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Giovanni's Charisma - 204/165</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Gloom</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Golbat</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Goldeen</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Golduck</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Golem ex - 076/165</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Golem ex - 189/165</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Grabber</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Graveler</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Grimer</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Growlithe</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Gyarados</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Haunter</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Hitmonchan</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Hitmonlee</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Horsea</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Hypno</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Ivysaur - 002/165</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Ivysaur - 167/165</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Jigglypuff</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Jolteon</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Jynx ex - 124/165</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Jynx ex - 191/165</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Kabuto</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Kabutops</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Kadabra</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Kakuna</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Kangaskhan ex - 115/165</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Kangaskhan ex - 190/165</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Kingler</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Koffing</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Krabby</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Lapras</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Leftovers</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Lickitung</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Machamp</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Machoke - 067/165</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Machoke - 177/165</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Machop</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Magikarp</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Magmar</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Magnemite</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Magneton</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Mankey</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Marowak</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>Meowth</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Metapod</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Mew ex - 151/165</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Mew ex - 193/165</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Mew ex - 205/165</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Mew ex - 205/165 (151 Metal Card)</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Mewtwo</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Moltres</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Mr. Mime - 122/165</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>Mr. Mime - 179/165</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Muk</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Nidoking - 034/165</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Nidoking - 174/165</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Nidoqueen</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Nidoran F</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Nidoran M</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Nidorina</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Nidorino</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Ninetales ex - 038/165</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Ninetales ex - 186/165</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Oddish</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Omanyte - 138/165</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Omanyte - 180/165</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Omastar</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Onix</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Paras</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Parasect</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Persian</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Pidgeot</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Pidgeotto</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Pidgey</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Pikachu - 025/165</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Pikachu - 173/165</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Pinsir</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Poliwag</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Poliwhirl - 061/165</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Poliwhirl - 176/165</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Poliwrath</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Ponyta</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Porygon</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Primeape</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Protective Goggles</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Psyduck - 054/165</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Psyduck - 175/165</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Raichu</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Rapidash</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Raticate</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Rattata</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Rhydon</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Rhyhorn</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Rigid Band</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Sandshrew</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Sandslash</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Scyther</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Seadra</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Seaking</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Seel</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Shellder</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Slowbro</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>Slowpoke</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>Snorlax</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>Spearow</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Squirtle - 007/165</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Squirtle - 170/165</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Starmie</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Staryu</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>Switch - 206/165</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Tangela - 114/165</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>Tangela - 178/165</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Tauros</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Tentacool</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>Tentacruel</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Vaporeon</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>Venomoth</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Venonat</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>Venusaur ex - 003/165</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>Venusaur ex - 182/165</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>Venusaur ex - 198/165</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>64.23999999999999</v>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>Victreebel</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>Vileplume</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Voltorb</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>Vulpix</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>Wartortle - 008/165</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>Wartortle - 171/165</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>30.13</v>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Weedle</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Weepinbell</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Weezing</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Wigglytuff ex - 040/165</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Wigglytuff ex - 187/165</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Zapdos ex - 145/165</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Zapdos ex - 192/165</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>Zapdos ex - 202/165</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Zubat</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v>66</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
+++ b/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1350" yWindow="2325" windowWidth="21600" windowHeight="11385" tabRatio="797" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-27375" yWindow="90" windowWidth="25260" windowHeight="11385" tabRatio="797" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$N$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$K$210</definedName>
   </definedNames>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,10 +41,15 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,16 +58,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -90,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -114,6 +139,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -481,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1263"/>
+  <dimension ref="A1:K1263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39.6" customWidth="1" min="1" max="1"/>
@@ -493,9 +530,6 @@
     <col width="33.5703125" customWidth="1" min="7" max="8"/>
     <col width="32.42578125" customWidth="1" min="9" max="10"/>
     <col width="39.42578125" customWidth="1" min="11" max="11"/>
-    <col width="16.85546875" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -554,21 +588,6 @@
           <t>Current Market Price of ETB Promo Card</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>EV Component</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Total EV</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>EVR</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -585,21 +604,21 @@
         <v>46</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0.15</v>
       </c>
       <c r="F2" s="3">
-        <f>IF(B2="common", 4, IF(B2="uncommon", 3, IF(B2="rare", 1.22, 1)))</f>
+        <f>IF(B2="common", 4, IF(B2="uncommon", 3, IF(B2="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
       <c r="G2">
-        <f>SUMPRODUCT(F2:F210, D2:D210/ C2:C210)</f>
+        <f>SUM(H2:H10)</f>
         <v/>
       </c>
       <c r="H2">
-        <f>SUMPRODUCT((B2:B210="Common") * D2:D210 * F2:F210 / C2:C210)</f>
+        <f>SUMPRODUCT((B2:B217="Common") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
       <c r="I2" s="3" t="n">
@@ -627,21 +646,17 @@
         <v>21</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="F3" s="3">
-        <f>IF(B3="common", 4, IF(B3="uncommon", 3, IF(B3="rare", 1.22, 1)))</f>
-        <v/>
-      </c>
-      <c r="G3">
-        <f>SUM(H2:H9)</f>
+        <f>IF(B3="common", 4, IF(B3="uncommon", 3, IF(B3="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
       <c r="H3">
-        <f>SUMPRODUCT((B2:B210="Uncommon") * D2:D210 * F2:F210 / C2:C210)</f>
+        <f>SUMPRODUCT((B2:B217="Uncommon") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
     </row>
@@ -660,11 +675,11 @@
         <v>90</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.74</v>
+        <v>1.12</v>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3">
-        <f>IF(B4="common", 4, IF(B4="uncommon", 3, IF(B4="rare", 1.22, 1)))</f>
+        <f>IF(B4="common", 4, IF(B4="uncommon", 3, IF(B4="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
       <c r="H4">
@@ -687,15 +702,15 @@
         <v>248</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7.64</v>
+        <v>7.46</v>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3">
-        <f>IF(B5="common", 4, IF(B5="uncommon", 3, IF(B5="rare", 1.22, 1)))</f>
+        <f>IF(B5="common", 4, IF(B5="uncommon", 3, IF(B5="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
       <c r="H5">
-        <f>SUMPRODUCT((B2:B210="Double Rare") * D2:D210 * F2:F210 / C2:C210)</f>
+        <f>SUMPRODUCT((B2:B217="Double Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
     </row>
@@ -714,11 +729,11 @@
         <v>225</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>39.98</v>
+        <v>43.34</v>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3">
-        <f>IF(B6="common", 4, IF(B6="uncommon", 3, IF(B6="rare", 1.22, 1)))</f>
+        <f>IF(B6="common", 4, IF(B6="uncommon", 3, IF(B6="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
       <c r="H6">
@@ -741,17 +756,17 @@
         <v>46</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.64</v>
       </c>
       <c r="F7" s="3">
-        <f>IF(B7="common", 4, IF(B7="uncommon", 3, IF(B7="rare", 1.22, 1)))</f>
+        <f>IF(B7="common", 4, IF(B7="uncommon", 3, IF(B7="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
       <c r="H7">
-        <f>SUMPRODUCT((B2:B210="Illustration Rare") * D2:D210 * F2:F210 / C2:C210)</f>
+        <f>SUMPRODUCT((B2:B217="Illustration Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
     </row>
@@ -770,17 +785,17 @@
         <v>46</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1.39</v>
+        <v>1.06</v>
       </c>
       <c r="F8" s="3">
-        <f>IF(B8="common", 4, IF(B8="uncommon", 3, IF(B8="rare", 1.22, 1)))</f>
+        <f>IF(B8="common", 4, IF(B8="uncommon", 3, IF(B8="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
       <c r="H8">
-        <f>SUMPRODUCT((B2:B210="Special Illustration Rare") * D2:D210 * F2:F210 / C2:C210)</f>
+        <f>SUMPRODUCT((B2:B217="Special Illustration Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
     </row>
@@ -799,17 +814,17 @@
         <v>46</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="F9" s="3">
-        <f>IF(B9="common", 4, IF(B9="uncommon", 3, IF(B9="rare", 1.22, 1)))</f>
+        <f>IF(B9="common", 4, IF(B9="uncommon", 3, IF(B9="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
       <c r="H9">
-        <f>SUMPRODUCT((B2:B210="Ultra Rare") * D2:D210 * F2:F210 / C2:C210)</f>
+        <f>SUMPRODUCT((B2:B217="Ultra Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
     </row>
@@ -828,11 +843,15 @@
         <v>90</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3">
-        <f>IF(B10="common", 4, IF(B10="uncommon", 3, IF(B10="rare", 1.22, 1)))</f>
+        <f>IF(B10="common", 4, IF(B10="uncommon", 3, IF(B10="rare", 1.74127216869152, 1)))</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>1.88 * SUMPRODUCT((C2:C217&lt;&gt;"") * (E2:E217&lt;&gt;"") * (E2:E217 / C2:C217))</f>
         <v/>
       </c>
     </row>
@@ -851,11 +870,11 @@
         <v>248</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.46</v>
+        <v>4.89</v>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3">
-        <f>IF(B11="common", 4, IF(B11="uncommon", 3, IF(B11="rare", 1.22, 1)))</f>
+        <f>IF(B11="common", 4, IF(B11="uncommon", 3, IF(B11="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -874,13 +893,13 @@
         <v>33</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="F12" s="3">
-        <f>IF(B12="common", 4, IF(B12="uncommon", 3, IF(B12="rare", 1.22, 1)))</f>
+        <f>IF(B12="common", 4, IF(B12="uncommon", 3, IF(B12="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -899,13 +918,13 @@
         <v>21</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
       <c r="F13" s="3">
-        <f>IF(B13="common", 4, IF(B13="uncommon", 3, IF(B13="rare", 1.22, 1)))</f>
+        <f>IF(B13="common", 4, IF(B13="uncommon", 3, IF(B13="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -924,11 +943,11 @@
         <v>154</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5.36</v>
+        <v>4.95</v>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3">
-        <f>IF(B14="common", 4, IF(B14="uncommon", 3, IF(B14="rare", 1.22, 1)))</f>
+        <f>IF(B14="common", 4, IF(B14="uncommon", 3, IF(B14="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -947,13 +966,13 @@
         <v>21</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="F15" s="3">
-        <f>IF(B15="common", 4, IF(B15="uncommon", 3, IF(B15="rare", 1.22, 1)))</f>
+        <f>IF(B15="common", 4, IF(B15="uncommon", 3, IF(B15="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -972,13 +991,13 @@
         <v>46</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0.14</v>
       </c>
       <c r="F16" s="3">
-        <f>IF(B16="common", 4, IF(B16="uncommon", 3, IF(B16="rare", 1.22, 1)))</f>
+        <f>IF(B16="common", 4, IF(B16="uncommon", 3, IF(B16="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -997,13 +1016,13 @@
         <v>33</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="F17" s="3">
-        <f>IF(B17="common", 4, IF(B17="uncommon", 3, IF(B17="rare", 1.22, 1)))</f>
+        <f>IF(B17="common", 4, IF(B17="uncommon", 3, IF(B17="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1022,13 +1041,13 @@
         <v>33</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="F18" s="3">
-        <f>IF(B18="common", 4, IF(B18="uncommon", 3, IF(B18="rare", 1.22, 1)))</f>
+        <f>IF(B18="common", 4, IF(B18="uncommon", 3, IF(B18="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1047,11 +1066,11 @@
         <v>248</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3">
-        <f>IF(B19="common", 4, IF(B19="uncommon", 3, IF(B19="rare", 1.22, 1)))</f>
+        <f>IF(B19="common", 4, IF(B19="uncommon", 3, IF(B19="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1070,11 +1089,11 @@
         <v>90</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.66</v>
+        <v>1.18</v>
       </c>
       <c r="E20" s="3" t="inlineStr"/>
       <c r="F20" s="3">
-        <f>IF(B20="common", 4, IF(B20="uncommon", 3, IF(B20="rare", 1.22, 1)))</f>
+        <f>IF(B20="common", 4, IF(B20="uncommon", 3, IF(B20="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1093,11 +1112,11 @@
         <v>248</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14.54</v>
+        <v>14.89</v>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3">
-        <f>IF(B21="common", 4, IF(B21="uncommon", 3, IF(B21="rare", 1.22, 1)))</f>
+        <f>IF(B21="common", 4, IF(B21="uncommon", 3, IF(B21="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1116,11 +1135,11 @@
         <v>225</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>70.20999999999999</v>
+        <v>73.55</v>
       </c>
       <c r="E22" s="3" t="inlineStr"/>
       <c r="F22" s="3">
-        <f>IF(B22="common", 4, IF(B22="uncommon", 3, IF(B22="rare", 1.22, 1)))</f>
+        <f>IF(B22="common", 4, IF(B22="uncommon", 3, IF(B22="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1139,13 +1158,13 @@
         <v>46</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="F23" s="3">
-        <f>IF(B23="common", 4, IF(B23="uncommon", 3, IF(B23="rare", 1.22, 1)))</f>
+        <f>IF(B23="common", 4, IF(B23="uncommon", 3, IF(B23="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1164,11 +1183,11 @@
         <v>188</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>37.17</v>
+        <v>37.52</v>
       </c>
       <c r="E24" s="3" t="inlineStr"/>
       <c r="F24" s="3">
-        <f>IF(B24="common", 4, IF(B24="uncommon", 3, IF(B24="rare", 1.22, 1)))</f>
+        <f>IF(B24="common", 4, IF(B24="uncommon", 3, IF(B24="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1187,13 +1206,13 @@
         <v>33</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="F25" s="3">
-        <f>IF(B25="common", 4, IF(B25="uncommon", 3, IF(B25="rare", 1.22, 1)))</f>
+        <f>IF(B25="common", 4, IF(B25="uncommon", 3, IF(B25="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1212,13 +1231,13 @@
         <v>46</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="F26" s="3">
-        <f>IF(B26="common", 4, IF(B26="uncommon", 3, IF(B26="rare", 1.22, 1)))</f>
+        <f>IF(B26="common", 4, IF(B26="uncommon", 3, IF(B26="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1237,11 +1256,11 @@
         <v>188</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>9.66</v>
+        <v>9.56</v>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3">
-        <f>IF(B27="common", 4, IF(B27="uncommon", 3, IF(B27="rare", 1.22, 1)))</f>
+        <f>IF(B27="common", 4, IF(B27="uncommon", 3, IF(B27="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1260,13 +1279,13 @@
         <v>21</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
       <c r="F28" s="3">
-        <f>IF(B28="common", 4, IF(B28="uncommon", 3, IF(B28="rare", 1.22, 1)))</f>
+        <f>IF(B28="common", 4, IF(B28="uncommon", 3, IF(B28="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1285,11 +1304,11 @@
         <v>90</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.54</v>
+        <v>4.71</v>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3">
-        <f>IF(B29="common", 4, IF(B29="uncommon", 3, IF(B29="rare", 1.22, 1)))</f>
+        <f>IF(B29="common", 4, IF(B29="uncommon", 3, IF(B29="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1308,11 +1327,11 @@
         <v>248</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>29.54</v>
+        <v>31.27</v>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3">
-        <f>IF(B30="common", 4, IF(B30="uncommon", 3, IF(B30="rare", 1.22, 1)))</f>
+        <f>IF(B30="common", 4, IF(B30="uncommon", 3, IF(B30="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1331,11 +1350,11 @@
         <v>225</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>210.03</v>
+        <v>210.14</v>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3">
-        <f>IF(B31="common", 4, IF(B31="uncommon", 3, IF(B31="rare", 1.22, 1)))</f>
+        <f>IF(B31="common", 4, IF(B31="uncommon", 3, IF(B31="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1354,13 +1373,13 @@
         <v>46</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>0.19</v>
       </c>
       <c r="F32" s="3">
-        <f>IF(B32="common", 4, IF(B32="uncommon", 3, IF(B32="rare", 1.22, 1)))</f>
+        <f>IF(B32="common", 4, IF(B32="uncommon", 3, IF(B32="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1379,11 +1398,11 @@
         <v>188</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>46.71</v>
+        <v>52.06</v>
       </c>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3">
-        <f>IF(B33="common", 4, IF(B33="uncommon", 3, IF(B33="rare", 1.22, 1)))</f>
+        <f>IF(B33="common", 4, IF(B33="uncommon", 3, IF(B33="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1405,10 +1424,10 @@
         <v>0.1</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="F34" s="3">
-        <f>IF(B34="common", 4, IF(B34="uncommon", 3, IF(B34="rare", 1.22, 1)))</f>
+        <f>IF(B34="common", 4, IF(B34="uncommon", 3, IF(B34="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1427,11 +1446,11 @@
         <v>188</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>32.96</v>
+        <v>34.86</v>
       </c>
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3">
-        <f>IF(B35="common", 4, IF(B35="uncommon", 3, IF(B35="rare", 1.22, 1)))</f>
+        <f>IF(B35="common", 4, IF(B35="uncommon", 3, IF(B35="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1450,13 +1469,13 @@
         <v>33</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="F36" s="3">
-        <f>IF(B36="common", 4, IF(B36="uncommon", 3, IF(B36="rare", 1.22, 1)))</f>
+        <f>IF(B36="common", 4, IF(B36="uncommon", 3, IF(B36="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1475,13 +1494,13 @@
         <v>46</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="F37" s="3">
-        <f>IF(B37="common", 4, IF(B37="uncommon", 3, IF(B37="rare", 1.22, 1)))</f>
+        <f>IF(B37="common", 4, IF(B37="uncommon", 3, IF(B37="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1500,13 +1519,13 @@
         <v>33</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F38" s="3">
-        <f>IF(B38="common", 4, IF(B38="uncommon", 3, IF(B38="rare", 1.22, 1)))</f>
+        <f>IF(B38="common", 4, IF(B38="uncommon", 3, IF(B38="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1525,13 +1544,13 @@
         <v>46</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="F39" s="3">
-        <f>IF(B39="common", 4, IF(B39="uncommon", 3, IF(B39="rare", 1.22, 1)))</f>
+        <f>IF(B39="common", 4, IF(B39="uncommon", 3, IF(B39="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1550,13 +1569,13 @@
         <v>33</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="F40" s="3">
-        <f>IF(B40="common", 4, IF(B40="uncommon", 3, IF(B40="rare", 1.22, 1)))</f>
+        <f>IF(B40="common", 4, IF(B40="uncommon", 3, IF(B40="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1578,10 +1597,10 @@
         <v>0.09</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="F41" s="3">
-        <f>IF(B41="common", 4, IF(B41="uncommon", 3, IF(B41="rare", 1.22, 1)))</f>
+        <f>IF(B41="common", 4, IF(B41="uncommon", 3, IF(B41="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1600,11 +1619,11 @@
         <v>248</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>3.42</v>
+        <v>4.04</v>
       </c>
       <c r="E42" s="3" t="inlineStr"/>
       <c r="F42" s="3">
-        <f>IF(B42="common", 4, IF(B42="uncommon", 3, IF(B42="rare", 1.22, 1)))</f>
+        <f>IF(B42="common", 4, IF(B42="uncommon", 3, IF(B42="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1626,10 +1645,10 @@
         <v>0.06</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F43" s="3">
-        <f>IF(B43="common", 4, IF(B43="uncommon", 3, IF(B43="rare", 1.22, 1)))</f>
+        <f>IF(B43="common", 4, IF(B43="uncommon", 3, IF(B43="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1651,10 +1670,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="F44" s="3">
-        <f>IF(B44="common", 4, IF(B44="uncommon", 3, IF(B44="rare", 1.22, 1)))</f>
+        <f>IF(B44="common", 4, IF(B44="uncommon", 3, IF(B44="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1673,13 +1692,13 @@
         <v>21</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.84</v>
+        <v>0.64</v>
       </c>
       <c r="F45" s="3">
-        <f>IF(B45="common", 4, IF(B45="uncommon", 3, IF(B45="rare", 1.22, 1)))</f>
+        <f>IF(B45="common", 4, IF(B45="uncommon", 3, IF(B45="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1698,11 +1717,11 @@
         <v>21</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="E46" s="3" t="inlineStr"/>
       <c r="F46" s="3">
-        <f>IF(B46="common", 4, IF(B46="uncommon", 3, IF(B46="rare", 1.22, 1)))</f>
+        <f>IF(B46="common", 4, IF(B46="uncommon", 3, IF(B46="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1724,10 +1743,10 @@
         <v>0.14</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="F47" s="3">
-        <f>IF(B47="common", 4, IF(B47="uncommon", 3, IF(B47="rare", 1.22, 1)))</f>
+        <f>IF(B47="common", 4, IF(B47="uncommon", 3, IF(B47="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1749,10 +1768,10 @@
         <v>0.06</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="F48" s="3">
-        <f>IF(B48="common", 4, IF(B48="uncommon", 3, IF(B48="rare", 1.22, 1)))</f>
+        <f>IF(B48="common", 4, IF(B48="uncommon", 3, IF(B48="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1774,10 +1793,10 @@
         <v>0.11</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="F49" s="3">
-        <f>IF(B49="common", 4, IF(B49="uncommon", 3, IF(B49="rare", 1.22, 1)))</f>
+        <f>IF(B49="common", 4, IF(B49="uncommon", 3, IF(B49="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1796,11 +1815,11 @@
         <v>188</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>22.83</v>
+        <v>25.78</v>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="3">
-        <f>IF(B50="common", 4, IF(B50="uncommon", 3, IF(B50="rare", 1.22, 1)))</f>
+        <f>IF(B50="common", 4, IF(B50="uncommon", 3, IF(B50="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1819,13 +1838,13 @@
         <v>21</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="F51" s="3">
-        <f>IF(B51="common", 4, IF(B51="uncommon", 3, IF(B51="rare", 1.22, 1)))</f>
+        <f>IF(B51="common", 4, IF(B51="uncommon", 3, IF(B51="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1844,13 +1863,13 @@
         <v>46</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="F52" s="3">
-        <f>IF(B52="common", 4, IF(B52="uncommon", 3, IF(B52="rare", 1.22, 1)))</f>
+        <f>IF(B52="common", 4, IF(B52="uncommon", 3, IF(B52="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1869,13 +1888,13 @@
         <v>46</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F53" s="3">
-        <f>IF(B53="common", 4, IF(B53="uncommon", 3, IF(B53="rare", 1.22, 1)))</f>
+        <f>IF(B53="common", 4, IF(B53="uncommon", 3, IF(B53="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1897,10 +1916,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.31</v>
+        <v>0.13</v>
       </c>
       <c r="F54" s="3">
-        <f>IF(B54="common", 4, IF(B54="uncommon", 3, IF(B54="rare", 1.22, 1)))</f>
+        <f>IF(B54="common", 4, IF(B54="uncommon", 3, IF(B54="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1919,13 +1938,13 @@
         <v>46</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="F55" s="3">
-        <f>IF(B55="common", 4, IF(B55="uncommon", 3, IF(B55="rare", 1.22, 1)))</f>
+        <f>IF(B55="common", 4, IF(B55="uncommon", 3, IF(B55="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1944,13 +1963,13 @@
         <v>46</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="F56" s="3">
-        <f>IF(B56="common", 4, IF(B56="uncommon", 3, IF(B56="rare", 1.22, 1)))</f>
+        <f>IF(B56="common", 4, IF(B56="uncommon", 3, IF(B56="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1969,13 +1988,13 @@
         <v>46</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="F57" s="3">
-        <f>IF(B57="common", 4, IF(B57="uncommon", 3, IF(B57="rare", 1.22, 1)))</f>
+        <f>IF(B57="common", 4, IF(B57="uncommon", 3, IF(B57="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -1997,10 +2016,10 @@
         <v>0.13</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="F58" s="3">
-        <f>IF(B58="common", 4, IF(B58="uncommon", 3, IF(B58="rare", 1.22, 1)))</f>
+        <f>IF(B58="common", 4, IF(B58="uncommon", 3, IF(B58="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2019,13 +2038,13 @@
         <v>33</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="F59" s="3">
-        <f>IF(B59="common", 4, IF(B59="uncommon", 3, IF(B59="rare", 1.22, 1)))</f>
+        <f>IF(B59="common", 4, IF(B59="uncommon", 3, IF(B59="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2044,13 +2063,13 @@
         <v>33</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="F60" s="3">
-        <f>IF(B60="common", 4, IF(B60="uncommon", 3, IF(B60="rare", 1.22, 1)))</f>
+        <f>IF(B60="common", 4, IF(B60="uncommon", 3, IF(B60="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2069,11 +2088,11 @@
         <v>248</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>6.39</v>
+        <v>6.99</v>
       </c>
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3">
-        <f>IF(B61="common", 4, IF(B61="uncommon", 3, IF(B61="rare", 1.22, 1)))</f>
+        <f>IF(B61="common", 4, IF(B61="uncommon", 3, IF(B61="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2092,11 +2111,11 @@
         <v>225</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>14.75</v>
+        <v>14.98</v>
       </c>
       <c r="E62" s="3" t="inlineStr"/>
       <c r="F62" s="3">
-        <f>IF(B62="common", 4, IF(B62="uncommon", 3, IF(B62="rare", 1.22, 1)))</f>
+        <f>IF(B62="common", 4, IF(B62="uncommon", 3, IF(B62="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2118,10 +2137,10 @@
         <v>0.05</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="F63" s="3">
-        <f>IF(B63="common", 4, IF(B63="uncommon", 3, IF(B63="rare", 1.22, 1)))</f>
+        <f>IF(B63="common", 4, IF(B63="uncommon", 3, IF(B63="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2140,13 +2159,13 @@
         <v>33</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="F64" s="3">
-        <f>IF(B64="common", 4, IF(B64="uncommon", 3, IF(B64="rare", 1.22, 1)))</f>
+        <f>IF(B64="common", 4, IF(B64="uncommon", 3, IF(B64="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2165,13 +2184,13 @@
         <v>46</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F65" s="3">
-        <f>IF(B65="common", 4, IF(B65="uncommon", 3, IF(B65="rare", 1.22, 1)))</f>
+        <f>IF(B65="common", 4, IF(B65="uncommon", 3, IF(B65="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2190,13 +2209,13 @@
         <v>33</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="F66" s="3">
-        <f>IF(B66="common", 4, IF(B66="uncommon", 3, IF(B66="rare", 1.22, 1)))</f>
+        <f>IF(B66="common", 4, IF(B66="uncommon", 3, IF(B66="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2215,13 +2234,13 @@
         <v>21</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="F67" s="3">
-        <f>IF(B67="common", 4, IF(B67="uncommon", 3, IF(B67="rare", 1.22, 1)))</f>
+        <f>IF(B67="common", 4, IF(B67="uncommon", 3, IF(B67="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2240,13 +2259,13 @@
         <v>46</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="F68" s="3">
-        <f>IF(B68="common", 4, IF(B68="uncommon", 3, IF(B68="rare", 1.22, 1)))</f>
+        <f>IF(B68="common", 4, IF(B68="uncommon", 3, IF(B68="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2265,13 +2284,13 @@
         <v>21</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.38</v>
+        <v>0.27</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="F69" s="3">
-        <f>IF(B69="common", 4, IF(B69="uncommon", 3, IF(B69="rare", 1.22, 1)))</f>
+        <f>IF(B69="common", 4, IF(B69="uncommon", 3, IF(B69="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2296,7 +2315,7 @@
         <v>0.15</v>
       </c>
       <c r="F70" s="3">
-        <f>IF(B70="common", 4, IF(B70="uncommon", 3, IF(B70="rare", 1.22, 1)))</f>
+        <f>IF(B70="common", 4, IF(B70="uncommon", 3, IF(B70="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2315,13 +2334,13 @@
         <v>33</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="F71" s="3">
-        <f>IF(B71="common", 4, IF(B71="uncommon", 3, IF(B71="rare", 1.22, 1)))</f>
+        <f>IF(B71="common", 4, IF(B71="uncommon", 3, IF(B71="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2340,11 +2359,11 @@
         <v>248</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>4.81</v>
+        <v>4.99</v>
       </c>
       <c r="E72" s="3" t="inlineStr"/>
       <c r="F72" s="3">
-        <f>IF(B72="common", 4, IF(B72="uncommon", 3, IF(B72="rare", 1.22, 1)))</f>
+        <f>IF(B72="common", 4, IF(B72="uncommon", 3, IF(B72="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2363,11 +2382,11 @@
         <v>225</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>13.81</v>
+        <v>15.6</v>
       </c>
       <c r="E73" s="3" t="inlineStr"/>
       <c r="F73" s="3">
-        <f>IF(B73="common", 4, IF(B73="uncommon", 3, IF(B73="rare", 1.22, 1)))</f>
+        <f>IF(B73="common", 4, IF(B73="uncommon", 3, IF(B73="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2386,13 +2405,13 @@
         <v>33</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="F74" s="3">
-        <f>IF(B74="common", 4, IF(B74="uncommon", 3, IF(B74="rare", 1.22, 1)))</f>
+        <f>IF(B74="common", 4, IF(B74="uncommon", 3, IF(B74="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2417,7 +2436,7 @@
         <v>0.18</v>
       </c>
       <c r="F75" s="3">
-        <f>IF(B75="common", 4, IF(B75="uncommon", 3, IF(B75="rare", 1.22, 1)))</f>
+        <f>IF(B75="common", 4, IF(B75="uncommon", 3, IF(B75="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2436,13 +2455,13 @@
         <v>46</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F76" s="3">
-        <f>IF(B76="common", 4, IF(B76="uncommon", 3, IF(B76="rare", 1.22, 1)))</f>
+        <f>IF(B76="common", 4, IF(B76="uncommon", 3, IF(B76="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2461,13 +2480,13 @@
         <v>33</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="F77" s="3">
-        <f>IF(B77="common", 4, IF(B77="uncommon", 3, IF(B77="rare", 1.22, 1)))</f>
+        <f>IF(B77="common", 4, IF(B77="uncommon", 3, IF(B77="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2486,11 +2505,11 @@
         <v>90</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="E78" s="3" t="inlineStr"/>
       <c r="F78" s="3">
-        <f>IF(B78="common", 4, IF(B78="uncommon", 3, IF(B78="rare", 1.22, 1)))</f>
+        <f>IF(B78="common", 4, IF(B78="uncommon", 3, IF(B78="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2509,11 +2528,11 @@
         <v>248</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>5.64</v>
+        <v>5.18</v>
       </c>
       <c r="E79" s="3" t="inlineStr"/>
       <c r="F79" s="3">
-        <f>IF(B79="common", 4, IF(B79="uncommon", 3, IF(B79="rare", 1.22, 1)))</f>
+        <f>IF(B79="common", 4, IF(B79="uncommon", 3, IF(B79="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2532,13 +2551,13 @@
         <v>33</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="F80" s="3">
-        <f>IF(B80="common", 4, IF(B80="uncommon", 3, IF(B80="rare", 1.22, 1)))</f>
+        <f>IF(B80="common", 4, IF(B80="uncommon", 3, IF(B80="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2557,13 +2576,13 @@
         <v>33</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F81" s="3">
-        <f>IF(B81="common", 4, IF(B81="uncommon", 3, IF(B81="rare", 1.22, 1)))</f>
+        <f>IF(B81="common", 4, IF(B81="uncommon", 3, IF(B81="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2582,13 +2601,13 @@
         <v>46</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F82" s="3">
-        <f>IF(B82="common", 4, IF(B82="uncommon", 3, IF(B82="rare", 1.22, 1)))</f>
+        <f>IF(B82="common", 4, IF(B82="uncommon", 3, IF(B82="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2607,13 +2626,13 @@
         <v>46</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="F83" s="3">
-        <f>IF(B83="common", 4, IF(B83="uncommon", 3, IF(B83="rare", 1.22, 1)))</f>
+        <f>IF(B83="common", 4, IF(B83="uncommon", 3, IF(B83="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2632,13 +2651,13 @@
         <v>21</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="F84" s="3">
-        <f>IF(B84="common", 4, IF(B84="uncommon", 3, IF(B84="rare", 1.22, 1)))</f>
+        <f>IF(B84="common", 4, IF(B84="uncommon", 3, IF(B84="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2660,10 +2679,10 @@
         <v>0.1</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="F85" s="3">
-        <f>IF(B85="common", 4, IF(B85="uncommon", 3, IF(B85="rare", 1.22, 1)))</f>
+        <f>IF(B85="common", 4, IF(B85="uncommon", 3, IF(B85="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2682,13 +2701,13 @@
         <v>33</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="F86" s="3">
-        <f>IF(B86="common", 4, IF(B86="uncommon", 3, IF(B86="rare", 1.22, 1)))</f>
+        <f>IF(B86="common", 4, IF(B86="uncommon", 3, IF(B86="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2710,10 +2729,10 @@
         <v>0.08</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>1.46</v>
+        <v>1.12</v>
       </c>
       <c r="F87" s="3">
-        <f>IF(B87="common", 4, IF(B87="uncommon", 3, IF(B87="rare", 1.22, 1)))</f>
+        <f>IF(B87="common", 4, IF(B87="uncommon", 3, IF(B87="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2732,13 +2751,13 @@
         <v>46</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F88" s="3">
-        <f>IF(B88="common", 4, IF(B88="uncommon", 3, IF(B88="rare", 1.22, 1)))</f>
+        <f>IF(B88="common", 4, IF(B88="uncommon", 3, IF(B88="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2757,13 +2776,13 @@
         <v>33</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="F89" s="3">
-        <f>IF(B89="common", 4, IF(B89="uncommon", 3, IF(B89="rare", 1.22, 1)))</f>
+        <f>IF(B89="common", 4, IF(B89="uncommon", 3, IF(B89="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2782,13 +2801,13 @@
         <v>33</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="F90" s="3">
-        <f>IF(B90="common", 4, IF(B90="uncommon", 3, IF(B90="rare", 1.22, 1)))</f>
+        <f>IF(B90="common", 4, IF(B90="uncommon", 3, IF(B90="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2807,11 +2826,11 @@
         <v>188</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>26.54</v>
+        <v>26.26</v>
       </c>
       <c r="E91" s="3" t="inlineStr"/>
       <c r="F91" s="3">
-        <f>IF(B91="common", 4, IF(B91="uncommon", 3, IF(B91="rare", 1.22, 1)))</f>
+        <f>IF(B91="common", 4, IF(B91="uncommon", 3, IF(B91="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2830,13 +2849,13 @@
         <v>46</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0.22</v>
       </c>
       <c r="F92" s="3">
-        <f>IF(B92="common", 4, IF(B92="uncommon", 3, IF(B92="rare", 1.22, 1)))</f>
+        <f>IF(B92="common", 4, IF(B92="uncommon", 3, IF(B92="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2855,13 +2874,13 @@
         <v>21</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>1.66</v>
+        <v>2.24</v>
       </c>
       <c r="F93" s="3">
-        <f>IF(B93="common", 4, IF(B93="uncommon", 3, IF(B93="rare", 1.22, 1)))</f>
+        <f>IF(B93="common", 4, IF(B93="uncommon", 3, IF(B93="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2880,11 +2899,11 @@
         <v>90</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E94" s="3" t="inlineStr"/>
       <c r="F94" s="3">
-        <f>IF(B94="common", 4, IF(B94="uncommon", 3, IF(B94="rare", 1.22, 1)))</f>
+        <f>IF(B94="common", 4, IF(B94="uncommon", 3, IF(B94="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2903,11 +2922,11 @@
         <v>248</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>4.76</v>
+        <v>5.3</v>
       </c>
       <c r="E95" s="3" t="inlineStr"/>
       <c r="F95" s="3">
-        <f>IF(B95="common", 4, IF(B95="uncommon", 3, IF(B95="rare", 1.22, 1)))</f>
+        <f>IF(B95="common", 4, IF(B95="uncommon", 3, IF(B95="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2926,13 +2945,13 @@
         <v>33</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="F96" s="3">
-        <f>IF(B96="common", 4, IF(B96="uncommon", 3, IF(B96="rare", 1.22, 1)))</f>
+        <f>IF(B96="common", 4, IF(B96="uncommon", 3, IF(B96="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2954,10 +2973,10 @@
         <v>0.13</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="F97" s="3">
-        <f>IF(B97="common", 4, IF(B97="uncommon", 3, IF(B97="rare", 1.22, 1)))</f>
+        <f>IF(B97="common", 4, IF(B97="uncommon", 3, IF(B97="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -2976,13 +2995,13 @@
         <v>33</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="F98" s="3">
-        <f>IF(B98="common", 4, IF(B98="uncommon", 3, IF(B98="rare", 1.22, 1)))</f>
+        <f>IF(B98="common", 4, IF(B98="uncommon", 3, IF(B98="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3001,13 +3020,13 @@
         <v>46</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="F99" s="3">
-        <f>IF(B99="common", 4, IF(B99="uncommon", 3, IF(B99="rare", 1.22, 1)))</f>
+        <f>IF(B99="common", 4, IF(B99="uncommon", 3, IF(B99="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3026,11 +3045,11 @@
         <v>90</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="E100" s="3" t="inlineStr"/>
       <c r="F100" s="3">
-        <f>IF(B100="common", 4, IF(B100="uncommon", 3, IF(B100="rare", 1.22, 1)))</f>
+        <f>IF(B100="common", 4, IF(B100="uncommon", 3, IF(B100="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3049,11 +3068,11 @@
         <v>248</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>5.53</v>
+        <v>5.8</v>
       </c>
       <c r="E101" s="3" t="inlineStr"/>
       <c r="F101" s="3">
-        <f>IF(B101="common", 4, IF(B101="uncommon", 3, IF(B101="rare", 1.22, 1)))</f>
+        <f>IF(B101="common", 4, IF(B101="uncommon", 3, IF(B101="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3072,13 +3091,13 @@
         <v>33</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="F102" s="3">
-        <f>IF(B102="common", 4, IF(B102="uncommon", 3, IF(B102="rare", 1.22, 1)))</f>
+        <f>IF(B102="common", 4, IF(B102="uncommon", 3, IF(B102="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3100,10 +3119,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="F103" s="3">
-        <f>IF(B103="common", 4, IF(B103="uncommon", 3, IF(B103="rare", 1.22, 1)))</f>
+        <f>IF(B103="common", 4, IF(B103="uncommon", 3, IF(B103="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3122,13 +3141,13 @@
         <v>46</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="F104" s="3">
-        <f>IF(B104="common", 4, IF(B104="uncommon", 3, IF(B104="rare", 1.22, 1)))</f>
+        <f>IF(B104="common", 4, IF(B104="uncommon", 3, IF(B104="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3150,10 +3169,10 @@
         <v>0.08</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="F105" s="3">
-        <f>IF(B105="common", 4, IF(B105="uncommon", 3, IF(B105="rare", 1.22, 1)))</f>
+        <f>IF(B105="common", 4, IF(B105="uncommon", 3, IF(B105="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3172,13 +3191,13 @@
         <v>33</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="F106" s="3">
-        <f>IF(B106="common", 4, IF(B106="uncommon", 3, IF(B106="rare", 1.22, 1)))</f>
+        <f>IF(B106="common", 4, IF(B106="uncommon", 3, IF(B106="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3197,13 +3216,13 @@
         <v>46</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F107" s="3">
-        <f>IF(B107="common", 4, IF(B107="uncommon", 3, IF(B107="rare", 1.22, 1)))</f>
+        <f>IF(B107="common", 4, IF(B107="uncommon", 3, IF(B107="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3222,13 +3241,13 @@
         <v>21</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="F108" s="3">
-        <f>IF(B108="common", 4, IF(B108="uncommon", 3, IF(B108="rare", 1.22, 1)))</f>
+        <f>IF(B108="common", 4, IF(B108="uncommon", 3, IF(B108="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3247,13 +3266,13 @@
         <v>33</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="F109" s="3">
-        <f>IF(B109="common", 4, IF(B109="uncommon", 3, IF(B109="rare", 1.22, 1)))</f>
+        <f>IF(B109="common", 4, IF(B109="uncommon", 3, IF(B109="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3272,11 +3291,11 @@
         <v>188</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>10.04</v>
+        <v>11.24</v>
       </c>
       <c r="E110" s="3" t="inlineStr"/>
       <c r="F110" s="3">
-        <f>IF(B110="common", 4, IF(B110="uncommon", 3, IF(B110="rare", 1.22, 1)))</f>
+        <f>IF(B110="common", 4, IF(B110="uncommon", 3, IF(B110="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3298,10 +3317,10 @@
         <v>0.06</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="F111" s="3">
-        <f>IF(B111="common", 4, IF(B111="uncommon", 3, IF(B111="rare", 1.22, 1)))</f>
+        <f>IF(B111="common", 4, IF(B111="uncommon", 3, IF(B111="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3320,13 +3339,13 @@
         <v>46</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="F112" s="3">
-        <f>IF(B112="common", 4, IF(B112="uncommon", 3, IF(B112="rare", 1.22, 1)))</f>
+        <f>IF(B112="common", 4, IF(B112="uncommon", 3, IF(B112="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3345,13 +3364,13 @@
         <v>46</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>1.26</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F113" s="3">
-        <f>IF(B113="common", 4, IF(B113="uncommon", 3, IF(B113="rare", 1.22, 1)))</f>
+        <f>IF(B113="common", 4, IF(B113="uncommon", 3, IF(B113="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3370,13 +3389,13 @@
         <v>46</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>0.15</v>
       </c>
       <c r="F114" s="3">
-        <f>IF(B114="common", 4, IF(B114="uncommon", 3, IF(B114="rare", 1.22, 1)))</f>
+        <f>IF(B114="common", 4, IF(B114="uncommon", 3, IF(B114="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3395,13 +3414,13 @@
         <v>33</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="F115" s="3">
-        <f>IF(B115="common", 4, IF(B115="uncommon", 3, IF(B115="rare", 1.22, 1)))</f>
+        <f>IF(B115="common", 4, IF(B115="uncommon", 3, IF(B115="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3420,13 +3439,13 @@
         <v>46</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F116" s="3">
-        <f>IF(B116="common", 4, IF(B116="uncommon", 3, IF(B116="rare", 1.22, 1)))</f>
+        <f>IF(B116="common", 4, IF(B116="uncommon", 3, IF(B116="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3445,13 +3464,13 @@
         <v>21</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>0.71</v>
+        <v>0.54</v>
       </c>
       <c r="F117" s="3">
-        <f>IF(B117="common", 4, IF(B117="uncommon", 3, IF(B117="rare", 1.22, 1)))</f>
+        <f>IF(B117="common", 4, IF(B117="uncommon", 3, IF(B117="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3470,13 +3489,13 @@
         <v>46</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F118" s="3">
-        <f>IF(B118="common", 4, IF(B118="uncommon", 3, IF(B118="rare", 1.22, 1)))</f>
+        <f>IF(B118="common", 4, IF(B118="uncommon", 3, IF(B118="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3495,13 +3514,13 @@
         <v>46</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="F119" s="3">
-        <f>IF(B119="common", 4, IF(B119="uncommon", 3, IF(B119="rare", 1.22, 1)))</f>
+        <f>IF(B119="common", 4, IF(B119="uncommon", 3, IF(B119="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3520,11 +3539,11 @@
         <v>90</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>6.89</v>
+        <v>7.21</v>
       </c>
       <c r="E120" s="3" t="inlineStr"/>
       <c r="F120" s="3">
-        <f>IF(B120="common", 4, IF(B120="uncommon", 3, IF(B120="rare", 1.22, 1)))</f>
+        <f>IF(B120="common", 4, IF(B120="uncommon", 3, IF(B120="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3543,11 +3562,11 @@
         <v>248</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>18.01</v>
+        <v>19.11</v>
       </c>
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3">
-        <f>IF(B121="common", 4, IF(B121="uncommon", 3, IF(B121="rare", 1.22, 1)))</f>
+        <f>IF(B121="common", 4, IF(B121="uncommon", 3, IF(B121="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3566,11 +3585,11 @@
         <v>154</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>13.15</v>
+        <v>13.27</v>
       </c>
       <c r="E122" s="3" t="inlineStr"/>
       <c r="F122" s="3">
-        <f>IF(B122="common", 4, IF(B122="uncommon", 3, IF(B122="rare", 1.22, 1)))</f>
+        <f>IF(B122="common", 4, IF(B122="uncommon", 3, IF(B122="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3589,11 +3608,11 @@
         <v>90</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>9.84</v>
+        <v>9.75</v>
       </c>
       <c r="E123" s="3" t="inlineStr"/>
       <c r="F123" s="3">
-        <f>IF(B123="common", 4, IF(B123="uncommon", 3, IF(B123="rare", 1.22, 1)))</f>
+        <f>IF(B123="common", 4, IF(B123="uncommon", 3, IF(B123="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3612,13 +3631,13 @@
         <v>21</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="F124" s="3">
-        <f>IF(B124="common", 4, IF(B124="uncommon", 3, IF(B124="rare", 1.22, 1)))</f>
+        <f>IF(B124="common", 4, IF(B124="uncommon", 3, IF(B124="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3637,13 +3656,13 @@
         <v>21</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>1.01</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F125" s="3">
-        <f>IF(B125="common", 4, IF(B125="uncommon", 3, IF(B125="rare", 1.22, 1)))</f>
+        <f>IF(B125="common", 4, IF(B125="uncommon", 3, IF(B125="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3662,13 +3681,13 @@
         <v>21</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="F126" s="3">
-        <f>IF(B126="common", 4, IF(B126="uncommon", 3, IF(B126="rare", 1.22, 1)))</f>
+        <f>IF(B126="common", 4, IF(B126="uncommon", 3, IF(B126="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3687,11 +3706,11 @@
         <v>188</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>6.68</v>
+        <v>5.79</v>
       </c>
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3">
-        <f>IF(B127="common", 4, IF(B127="uncommon", 3, IF(B127="rare", 1.22, 1)))</f>
+        <f>IF(B127="common", 4, IF(B127="uncommon", 3, IF(B127="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3710,13 +3729,13 @@
         <v>33</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="F128" s="3">
-        <f>IF(B128="common", 4, IF(B128="uncommon", 3, IF(B128="rare", 1.22, 1)))</f>
+        <f>IF(B128="common", 4, IF(B128="uncommon", 3, IF(B128="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3735,13 +3754,13 @@
         <v>21</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F129" s="3">
-        <f>IF(B129="common", 4, IF(B129="uncommon", 3, IF(B129="rare", 1.22, 1)))</f>
+        <f>IF(B129="common", 4, IF(B129="uncommon", 3, IF(B129="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3760,11 +3779,11 @@
         <v>188</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>10.45</v>
+        <v>9.58</v>
       </c>
       <c r="E130" s="3" t="inlineStr"/>
       <c r="F130" s="3">
-        <f>IF(B130="common", 4, IF(B130="uncommon", 3, IF(B130="rare", 1.22, 1)))</f>
+        <f>IF(B130="common", 4, IF(B130="uncommon", 3, IF(B130="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3783,13 +3802,13 @@
         <v>33</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="F131" s="3">
-        <f>IF(B131="common", 4, IF(B131="uncommon", 3, IF(B131="rare", 1.22, 1)))</f>
+        <f>IF(B131="common", 4, IF(B131="uncommon", 3, IF(B131="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3808,13 +3827,13 @@
         <v>46</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="F132" s="3">
-        <f>IF(B132="common", 4, IF(B132="uncommon", 3, IF(B132="rare", 1.22, 1)))</f>
+        <f>IF(B132="common", 4, IF(B132="uncommon", 3, IF(B132="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3833,13 +3852,13 @@
         <v>46</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>2.12</v>
+        <v>1.56</v>
       </c>
       <c r="F133" s="3">
-        <f>IF(B133="common", 4, IF(B133="uncommon", 3, IF(B133="rare", 1.22, 1)))</f>
+        <f>IF(B133="common", 4, IF(B133="uncommon", 3, IF(B133="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3861,10 +3880,10 @@
         <v>0.08</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="F134" s="3">
-        <f>IF(B134="common", 4, IF(B134="uncommon", 3, IF(B134="rare", 1.22, 1)))</f>
+        <f>IF(B134="common", 4, IF(B134="uncommon", 3, IF(B134="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3883,13 +3902,13 @@
         <v>33</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="F135" s="3">
-        <f>IF(B135="common", 4, IF(B135="uncommon", 3, IF(B135="rare", 1.22, 1)))</f>
+        <f>IF(B135="common", 4, IF(B135="uncommon", 3, IF(B135="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3908,11 +3927,11 @@
         <v>90</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>0.59</v>
+        <v>0.83</v>
       </c>
       <c r="E136" s="3" t="inlineStr"/>
       <c r="F136" s="3">
-        <f>IF(B136="common", 4, IF(B136="uncommon", 3, IF(B136="rare", 1.22, 1)))</f>
+        <f>IF(B136="common", 4, IF(B136="uncommon", 3, IF(B136="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3931,11 +3950,11 @@
         <v>248</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>9.24</v>
+        <v>7.87</v>
       </c>
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3">
-        <f>IF(B137="common", 4, IF(B137="uncommon", 3, IF(B137="rare", 1.22, 1)))</f>
+        <f>IF(B137="common", 4, IF(B137="uncommon", 3, IF(B137="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3954,13 +3973,13 @@
         <v>46</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="F138" s="3">
-        <f>IF(B138="common", 4, IF(B138="uncommon", 3, IF(B138="rare", 1.22, 1)))</f>
+        <f>IF(B138="common", 4, IF(B138="uncommon", 3, IF(B138="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -3979,13 +3998,13 @@
         <v>33</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="F139" s="3">
-        <f>IF(B139="common", 4, IF(B139="uncommon", 3, IF(B139="rare", 1.22, 1)))</f>
+        <f>IF(B139="common", 4, IF(B139="uncommon", 3, IF(B139="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4004,11 +4023,11 @@
         <v>188</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>7.26</v>
+        <v>8</v>
       </c>
       <c r="E140" s="3" t="inlineStr"/>
       <c r="F140" s="3">
-        <f>IF(B140="common", 4, IF(B140="uncommon", 3, IF(B140="rare", 1.22, 1)))</f>
+        <f>IF(B140="common", 4, IF(B140="uncommon", 3, IF(B140="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4027,13 +4046,13 @@
         <v>21</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="F141" s="3">
-        <f>IF(B141="common", 4, IF(B141="uncommon", 3, IF(B141="rare", 1.22, 1)))</f>
+        <f>IF(B141="common", 4, IF(B141="uncommon", 3, IF(B141="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4052,13 +4071,13 @@
         <v>33</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="F142" s="3">
-        <f>IF(B142="common", 4, IF(B142="uncommon", 3, IF(B142="rare", 1.22, 1)))</f>
+        <f>IF(B142="common", 4, IF(B142="uncommon", 3, IF(B142="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4077,13 +4096,13 @@
         <v>46</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E143" s="3" t="n">
         <v>0.16</v>
       </c>
       <c r="F143" s="3">
-        <f>IF(B143="common", 4, IF(B143="uncommon", 3, IF(B143="rare", 1.22, 1)))</f>
+        <f>IF(B143="common", 4, IF(B143="uncommon", 3, IF(B143="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4102,13 +4121,13 @@
         <v>33</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="F144" s="3">
-        <f>IF(B144="common", 4, IF(B144="uncommon", 3, IF(B144="rare", 1.22, 1)))</f>
+        <f>IF(B144="common", 4, IF(B144="uncommon", 3, IF(B144="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4127,13 +4146,13 @@
         <v>33</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="F145" s="3">
-        <f>IF(B145="common", 4, IF(B145="uncommon", 3, IF(B145="rare", 1.22, 1)))</f>
+        <f>IF(B145="common", 4, IF(B145="uncommon", 3, IF(B145="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4152,13 +4171,13 @@
         <v>33</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="F146" s="3">
-        <f>IF(B146="common", 4, IF(B146="uncommon", 3, IF(B146="rare", 1.22, 1)))</f>
+        <f>IF(B146="common", 4, IF(B146="uncommon", 3, IF(B146="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4177,13 +4196,13 @@
         <v>46</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>3.16</v>
+        <v>2.19</v>
       </c>
       <c r="F147" s="3">
-        <f>IF(B147="common", 4, IF(B147="uncommon", 3, IF(B147="rare", 1.22, 1)))</f>
+        <f>IF(B147="common", 4, IF(B147="uncommon", 3, IF(B147="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4202,13 +4221,13 @@
         <v>46</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="F148" s="3">
-        <f>IF(B148="common", 4, IF(B148="uncommon", 3, IF(B148="rare", 1.22, 1)))</f>
+        <f>IF(B148="common", 4, IF(B148="uncommon", 3, IF(B148="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4230,10 +4249,10 @@
         <v>0.1</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="F149" s="3">
-        <f>IF(B149="common", 4, IF(B149="uncommon", 3, IF(B149="rare", 1.22, 1)))</f>
+        <f>IF(B149="common", 4, IF(B149="uncommon", 3, IF(B149="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4252,11 +4271,11 @@
         <v>188</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>28.19</v>
+        <v>28.89</v>
       </c>
       <c r="E150" s="3" t="inlineStr"/>
       <c r="F150" s="3">
-        <f>IF(B150="common", 4, IF(B150="uncommon", 3, IF(B150="rare", 1.22, 1)))</f>
+        <f>IF(B150="common", 4, IF(B150="uncommon", 3, IF(B150="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4275,13 +4294,13 @@
         <v>33</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="F151" s="3">
-        <f>IF(B151="common", 4, IF(B151="uncommon", 3, IF(B151="rare", 1.22, 1)))</f>
+        <f>IF(B151="common", 4, IF(B151="uncommon", 3, IF(B151="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4303,10 +4322,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="F152" s="3">
-        <f>IF(B152="common", 4, IF(B152="uncommon", 3, IF(B152="rare", 1.22, 1)))</f>
+        <f>IF(B152="common", 4, IF(B152="uncommon", 3, IF(B152="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4328,10 +4347,10 @@
         <v>0.1</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="F153" s="3">
-        <f>IF(B153="common", 4, IF(B153="uncommon", 3, IF(B153="rare", 1.22, 1)))</f>
+        <f>IF(B153="common", 4, IF(B153="uncommon", 3, IF(B153="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4350,11 +4369,11 @@
         <v>188</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>15.76</v>
+        <v>18.96</v>
       </c>
       <c r="E154" s="3" t="inlineStr"/>
       <c r="F154" s="3">
-        <f>IF(B154="common", 4, IF(B154="uncommon", 3, IF(B154="rare", 1.22, 1)))</f>
+        <f>IF(B154="common", 4, IF(B154="uncommon", 3, IF(B154="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4373,13 +4392,13 @@
         <v>33</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F155" s="3">
-        <f>IF(B155="common", 4, IF(B155="uncommon", 3, IF(B155="rare", 1.22, 1)))</f>
+        <f>IF(B155="common", 4, IF(B155="uncommon", 3, IF(B155="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4398,13 +4417,13 @@
         <v>46</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="F156" s="3">
-        <f>IF(B156="common", 4, IF(B156="uncommon", 3, IF(B156="rare", 1.22, 1)))</f>
+        <f>IF(B156="common", 4, IF(B156="uncommon", 3, IF(B156="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4423,13 +4442,13 @@
         <v>46</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="F157" s="3">
-        <f>IF(B157="common", 4, IF(B157="uncommon", 3, IF(B157="rare", 1.22, 1)))</f>
+        <f>IF(B157="common", 4, IF(B157="uncommon", 3, IF(B157="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4448,13 +4467,13 @@
         <v>33</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="F158" s="3">
-        <f>IF(B158="common", 4, IF(B158="uncommon", 3, IF(B158="rare", 1.22, 1)))</f>
+        <f>IF(B158="common", 4, IF(B158="uncommon", 3, IF(B158="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4473,13 +4492,13 @@
         <v>33</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="F159" s="3">
-        <f>IF(B159="common", 4, IF(B159="uncommon", 3, IF(B159="rare", 1.22, 1)))</f>
+        <f>IF(B159="common", 4, IF(B159="uncommon", 3, IF(B159="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4498,13 +4517,13 @@
         <v>46</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>0.34</v>
+        <v>0.22</v>
       </c>
       <c r="F160" s="3">
-        <f>IF(B160="common", 4, IF(B160="uncommon", 3, IF(B160="rare", 1.22, 1)))</f>
+        <f>IF(B160="common", 4, IF(B160="uncommon", 3, IF(B160="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4523,11 +4542,11 @@
         <v>188</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>20.61</v>
+        <v>21.1</v>
       </c>
       <c r="E161" s="3" t="inlineStr"/>
       <c r="F161" s="3">
-        <f>IF(B161="common", 4, IF(B161="uncommon", 3, IF(B161="rare", 1.22, 1)))</f>
+        <f>IF(B161="common", 4, IF(B161="uncommon", 3, IF(B161="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4549,10 +4568,10 @@
         <v>0.14</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
       <c r="F162" s="3">
-        <f>IF(B162="common", 4, IF(B162="uncommon", 3, IF(B162="rare", 1.22, 1)))</f>
+        <f>IF(B162="common", 4, IF(B162="uncommon", 3, IF(B162="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4574,10 +4593,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="F163" s="3">
-        <f>IF(B163="common", 4, IF(B163="uncommon", 3, IF(B163="rare", 1.22, 1)))</f>
+        <f>IF(B163="common", 4, IF(B163="uncommon", 3, IF(B163="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4596,13 +4615,13 @@
         <v>33</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E164" s="3" t="n">
         <v>0.17</v>
       </c>
       <c r="F164" s="3">
-        <f>IF(B164="common", 4, IF(B164="uncommon", 3, IF(B164="rare", 1.22, 1)))</f>
+        <f>IF(B164="common", 4, IF(B164="uncommon", 3, IF(B164="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4624,10 +4643,10 @@
         <v>0.06</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="F165" s="3">
-        <f>IF(B165="common", 4, IF(B165="uncommon", 3, IF(B165="rare", 1.22, 1)))</f>
+        <f>IF(B165="common", 4, IF(B165="uncommon", 3, IF(B165="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4646,13 +4665,13 @@
         <v>33</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F166" s="3">
-        <f>IF(B166="common", 4, IF(B166="uncommon", 3, IF(B166="rare", 1.22, 1)))</f>
+        <f>IF(B166="common", 4, IF(B166="uncommon", 3, IF(B166="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4671,13 +4690,13 @@
         <v>46</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F167" s="3">
-        <f>IF(B167="common", 4, IF(B167="uncommon", 3, IF(B167="rare", 1.22, 1)))</f>
+        <f>IF(B167="common", 4, IF(B167="uncommon", 3, IF(B167="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4696,13 +4715,13 @@
         <v>33</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>1.43</v>
+        <v>1.08</v>
       </c>
       <c r="F168" s="3">
-        <f>IF(B168="common", 4, IF(B168="uncommon", 3, IF(B168="rare", 1.22, 1)))</f>
+        <f>IF(B168="common", 4, IF(B168="uncommon", 3, IF(B168="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4721,13 +4740,13 @@
         <v>46</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F169" s="3">
-        <f>IF(B169="common", 4, IF(B169="uncommon", 3, IF(B169="rare", 1.22, 1)))</f>
+        <f>IF(B169="common", 4, IF(B169="uncommon", 3, IF(B169="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4746,13 +4765,13 @@
         <v>33</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F170" s="3">
-        <f>IF(B170="common", 4, IF(B170="uncommon", 3, IF(B170="rare", 1.22, 1)))</f>
+        <f>IF(B170="common", 4, IF(B170="uncommon", 3, IF(B170="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4771,13 +4790,13 @@
         <v>33</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="F171" s="3">
-        <f>IF(B171="common", 4, IF(B171="uncommon", 3, IF(B171="rare", 1.22, 1)))</f>
+        <f>IF(B171="common", 4, IF(B171="uncommon", 3, IF(B171="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4796,13 +4815,13 @@
         <v>33</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E172" s="3" t="n">
         <v>0.14</v>
       </c>
       <c r="F172" s="3">
-        <f>IF(B172="common", 4, IF(B172="uncommon", 3, IF(B172="rare", 1.22, 1)))</f>
+        <f>IF(B172="common", 4, IF(B172="uncommon", 3, IF(B172="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4821,13 +4840,13 @@
         <v>33</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>1.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F173" s="3">
-        <f>IF(B173="common", 4, IF(B173="uncommon", 3, IF(B173="rare", 1.22, 1)))</f>
+        <f>IF(B173="common", 4, IF(B173="uncommon", 3, IF(B173="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4849,10 +4868,10 @@
         <v>0.08</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="F174" s="3">
-        <f>IF(B174="common", 4, IF(B174="uncommon", 3, IF(B174="rare", 1.22, 1)))</f>
+        <f>IF(B174="common", 4, IF(B174="uncommon", 3, IF(B174="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4874,10 +4893,10 @@
         <v>0.06</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F175" s="3">
-        <f>IF(B175="common", 4, IF(B175="uncommon", 3, IF(B175="rare", 1.22, 1)))</f>
+        <f>IF(B175="common", 4, IF(B175="uncommon", 3, IF(B175="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4896,13 +4915,13 @@
         <v>33</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="F176" s="3">
-        <f>IF(B176="common", 4, IF(B176="uncommon", 3, IF(B176="rare", 1.22, 1)))</f>
+        <f>IF(B176="common", 4, IF(B176="uncommon", 3, IF(B176="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4921,13 +4940,13 @@
         <v>46</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="F177" s="3">
-        <f>IF(B177="common", 4, IF(B177="uncommon", 3, IF(B177="rare", 1.22, 1)))</f>
+        <f>IF(B177="common", 4, IF(B177="uncommon", 3, IF(B177="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4946,13 +4965,13 @@
         <v>33</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>1.96</v>
+        <v>1.27</v>
       </c>
       <c r="F178" s="3">
-        <f>IF(B178="common", 4, IF(B178="uncommon", 3, IF(B178="rare", 1.22, 1)))</f>
+        <f>IF(B178="common", 4, IF(B178="uncommon", 3, IF(B178="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4971,13 +4990,13 @@
         <v>46</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="F179" s="3">
-        <f>IF(B179="common", 4, IF(B179="uncommon", 3, IF(B179="rare", 1.22, 1)))</f>
+        <f>IF(B179="common", 4, IF(B179="uncommon", 3, IF(B179="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -4996,13 +5015,13 @@
         <v>46</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="F180" s="3">
-        <f>IF(B180="common", 4, IF(B180="uncommon", 3, IF(B180="rare", 1.22, 1)))</f>
+        <f>IF(B180="common", 4, IF(B180="uncommon", 3, IF(B180="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5021,11 +5040,11 @@
         <v>188</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>45.51</v>
+        <v>46.05</v>
       </c>
       <c r="E181" s="3" t="inlineStr"/>
       <c r="F181" s="3">
-        <f>IF(B181="common", 4, IF(B181="uncommon", 3, IF(B181="rare", 1.22, 1)))</f>
+        <f>IF(B181="common", 4, IF(B181="uncommon", 3, IF(B181="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5044,13 +5063,13 @@
         <v>21</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="F182" s="3">
-        <f>IF(B182="common", 4, IF(B182="uncommon", 3, IF(B182="rare", 1.22, 1)))</f>
+        <f>IF(B182="common", 4, IF(B182="uncommon", 3, IF(B182="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5069,13 +5088,13 @@
         <v>46</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="F183" s="3">
-        <f>IF(B183="common", 4, IF(B183="uncommon", 3, IF(B183="rare", 1.22, 1)))</f>
+        <f>IF(B183="common", 4, IF(B183="uncommon", 3, IF(B183="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5094,11 +5113,11 @@
         <v>154</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="E184" s="3" t="inlineStr"/>
       <c r="F184" s="3">
-        <f>IF(B184="common", 4, IF(B184="uncommon", 3, IF(B184="rare", 1.22, 1)))</f>
+        <f>IF(B184="common", 4, IF(B184="uncommon", 3, IF(B184="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5117,13 +5136,13 @@
         <v>46</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F185" s="3">
-        <f>IF(B185="common", 4, IF(B185="uncommon", 3, IF(B185="rare", 1.22, 1)))</f>
+        <f>IF(B185="common", 4, IF(B185="uncommon", 3, IF(B185="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5142,11 +5161,11 @@
         <v>188</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>7.57</v>
+        <v>7.68</v>
       </c>
       <c r="E186" s="3" t="inlineStr"/>
       <c r="F186" s="3">
-        <f>IF(B186="common", 4, IF(B186="uncommon", 3, IF(B186="rare", 1.22, 1)))</f>
+        <f>IF(B186="common", 4, IF(B186="uncommon", 3, IF(B186="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5165,13 +5184,13 @@
         <v>33</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="F187" s="3">
-        <f>IF(B187="common", 4, IF(B187="uncommon", 3, IF(B187="rare", 1.22, 1)))</f>
+        <f>IF(B187="common", 4, IF(B187="uncommon", 3, IF(B187="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5190,13 +5209,13 @@
         <v>46</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="F188" s="3">
-        <f>IF(B188="common", 4, IF(B188="uncommon", 3, IF(B188="rare", 1.22, 1)))</f>
+        <f>IF(B188="common", 4, IF(B188="uncommon", 3, IF(B188="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5215,13 +5234,13 @@
         <v>33</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F189" s="3">
-        <f>IF(B189="common", 4, IF(B189="uncommon", 3, IF(B189="rare", 1.22, 1)))</f>
+        <f>IF(B189="common", 4, IF(B189="uncommon", 3, IF(B189="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5243,10 +5262,10 @@
         <v>0.28</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="F190" s="3">
-        <f>IF(B190="common", 4, IF(B190="uncommon", 3, IF(B190="rare", 1.22, 1)))</f>
+        <f>IF(B190="common", 4, IF(B190="uncommon", 3, IF(B190="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5268,10 +5287,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="F191" s="3">
-        <f>IF(B191="common", 4, IF(B191="uncommon", 3, IF(B191="rare", 1.22, 1)))</f>
+        <f>IF(B191="common", 4, IF(B191="uncommon", 3, IF(B191="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5290,13 +5309,13 @@
         <v>46</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E192" s="3" t="n">
         <v>0.14</v>
       </c>
       <c r="F192" s="3">
-        <f>IF(B192="common", 4, IF(B192="uncommon", 3, IF(B192="rare", 1.22, 1)))</f>
+        <f>IF(B192="common", 4, IF(B192="uncommon", 3, IF(B192="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5315,11 +5334,11 @@
         <v>90</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="E193" s="3" t="inlineStr"/>
       <c r="F193" s="3">
-        <f>IF(B193="common", 4, IF(B193="uncommon", 3, IF(B193="rare", 1.22, 1)))</f>
+        <f>IF(B193="common", 4, IF(B193="uncommon", 3, IF(B193="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5338,11 +5357,11 @@
         <v>248</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>11.85</v>
+        <v>11.82</v>
       </c>
       <c r="E194" s="3" t="inlineStr"/>
       <c r="F194" s="3">
-        <f>IF(B194="common", 4, IF(B194="uncommon", 3, IF(B194="rare", 1.22, 1)))</f>
+        <f>IF(B194="common", 4, IF(B194="uncommon", 3, IF(B194="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5361,11 +5380,11 @@
         <v>225</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>66.20999999999999</v>
+        <v>68.69</v>
       </c>
       <c r="E195" s="3" t="inlineStr"/>
       <c r="F195" s="3">
-        <f>IF(B195="common", 4, IF(B195="uncommon", 3, IF(B195="rare", 1.22, 1)))</f>
+        <f>IF(B195="common", 4, IF(B195="uncommon", 3, IF(B195="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5387,10 +5406,10 @@
         <v>0.05</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="F196" s="3">
-        <f>IF(B196="common", 4, IF(B196="uncommon", 3, IF(B196="rare", 1.22, 1)))</f>
+        <f>IF(B196="common", 4, IF(B196="uncommon", 3, IF(B196="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5409,13 +5428,13 @@
         <v>21</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="F197" s="3">
-        <f>IF(B197="common", 4, IF(B197="uncommon", 3, IF(B197="rare", 1.22, 1)))</f>
+        <f>IF(B197="common", 4, IF(B197="uncommon", 3, IF(B197="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5434,13 +5453,13 @@
         <v>46</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F198" s="3">
-        <f>IF(B198="common", 4, IF(B198="uncommon", 3, IF(B198="rare", 1.22, 1)))</f>
+        <f>IF(B198="common", 4, IF(B198="uncommon", 3, IF(B198="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5459,13 +5478,13 @@
         <v>46</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="F199" s="3">
-        <f>IF(B199="common", 4, IF(B199="uncommon", 3, IF(B199="rare", 1.22, 1)))</f>
+        <f>IF(B199="common", 4, IF(B199="uncommon", 3, IF(B199="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5487,10 +5506,10 @@
         <v>0.12</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F200" s="3">
-        <f>IF(B200="common", 4, IF(B200="uncommon", 3, IF(B200="rare", 1.22, 1)))</f>
+        <f>IF(B200="common", 4, IF(B200="uncommon", 3, IF(B200="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5509,11 +5528,11 @@
         <v>188</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>29.75</v>
+        <v>30.34</v>
       </c>
       <c r="E201" s="3" t="inlineStr"/>
       <c r="F201" s="3">
-        <f>IF(B201="common", 4, IF(B201="uncommon", 3, IF(B201="rare", 1.22, 1)))</f>
+        <f>IF(B201="common", 4, IF(B201="uncommon", 3, IF(B201="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5532,13 +5551,13 @@
         <v>46</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="F202" s="3">
-        <f>IF(B202="common", 4, IF(B202="uncommon", 3, IF(B202="rare", 1.22, 1)))</f>
+        <f>IF(B202="common", 4, IF(B202="uncommon", 3, IF(B202="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5557,13 +5576,13 @@
         <v>46</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="F203" s="3">
-        <f>IF(B203="common", 4, IF(B203="uncommon", 3, IF(B203="rare", 1.22, 1)))</f>
+        <f>IF(B203="common", 4, IF(B203="uncommon", 3, IF(B203="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5582,13 +5601,13 @@
         <v>21</v>
       </c>
       <c r="D204" s="3" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="F204" s="3">
-        <f>IF(B204="common", 4, IF(B204="uncommon", 3, IF(B204="rare", 1.22, 1)))</f>
+        <f>IF(B204="common", 4, IF(B204="uncommon", 3, IF(B204="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5607,11 +5626,11 @@
         <v>90</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="E205" s="3" t="inlineStr"/>
       <c r="F205" s="3">
-        <f>IF(B205="common", 4, IF(B205="uncommon", 3, IF(B205="rare", 1.22, 1)))</f>
+        <f>IF(B205="common", 4, IF(B205="uncommon", 3, IF(B205="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5630,11 +5649,11 @@
         <v>248</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>6.95</v>
+        <v>7.9</v>
       </c>
       <c r="E206" s="3" t="inlineStr"/>
       <c r="F206" s="3">
-        <f>IF(B206="common", 4, IF(B206="uncommon", 3, IF(B206="rare", 1.22, 1)))</f>
+        <f>IF(B206="common", 4, IF(B206="uncommon", 3, IF(B206="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5653,11 +5672,11 @@
         <v>90</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="E207" s="3" t="inlineStr"/>
       <c r="F207" s="3">
-        <f>IF(B207="common", 4, IF(B207="uncommon", 3, IF(B207="rare", 1.22, 1)))</f>
+        <f>IF(B207="common", 4, IF(B207="uncommon", 3, IF(B207="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5676,11 +5695,11 @@
         <v>248</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>7.9</v>
+        <v>8.06</v>
       </c>
       <c r="E208" s="3" t="inlineStr"/>
       <c r="F208" s="3">
-        <f>IF(B208="common", 4, IF(B208="uncommon", 3, IF(B208="rare", 1.22, 1)))</f>
+        <f>IF(B208="common", 4, IF(B208="uncommon", 3, IF(B208="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5699,11 +5718,11 @@
         <v>225</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>52.05</v>
+        <v>55.36</v>
       </c>
       <c r="E209" s="3" t="inlineStr"/>
       <c r="F209" s="3">
-        <f>IF(B209="common", 4, IF(B209="uncommon", 3, IF(B209="rare", 1.22, 1)))</f>
+        <f>IF(B209="common", 4, IF(B209="uncommon", 3, IF(B209="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5725,10 +5744,10 @@
         <v>0.06</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="F210" s="3">
-        <f>IF(B210="common", 4, IF(B210="uncommon", 3, IF(B210="rare", 1.22, 1)))</f>
+        <f>IF(B210="common", 4, IF(B210="uncommon", 3, IF(B210="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5753,7 +5772,7 @@
         <v>0.59</v>
       </c>
       <c r="F211" s="3">
-        <f>IF(B211="common", 4, IF(B211="uncommon", 3, IF(B211="rare", 1.22, 1)))</f>
+        <f>IF(B211="common", 4, IF(B211="uncommon", 3, IF(B211="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5776,7 +5795,7 @@
       </c>
       <c r="E212" s="3" t="n"/>
       <c r="F212" s="3">
-        <f>IF(B212="common", 4, IF(B212="uncommon", 3, IF(B212="rare", 1.22, 1)))</f>
+        <f>IF(B212="common", 4, IF(B212="uncommon", 3, IF(B212="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5799,7 +5818,7 @@
       </c>
       <c r="E213" s="3" t="n"/>
       <c r="F213" s="3">
-        <f>IF(B213="common", 4, IF(B213="uncommon", 3, IF(B213="rare", 1.22, 1)))</f>
+        <f>IF(B213="common", 4, IF(B213="uncommon", 3, IF(B213="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5822,7 +5841,7 @@
       </c>
       <c r="E214" s="3" t="n"/>
       <c r="F214" s="3">
-        <f>IF(B214="common", 4, IF(B214="uncommon", 3, IF(B214="rare", 1.22, 1)))</f>
+        <f>IF(B214="common", 4, IF(B214="uncommon", 3, IF(B214="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5845,7 +5864,7 @@
       </c>
       <c r="E215" s="3" t="n"/>
       <c r="F215" s="3">
-        <f>IF(B215="common", 4, IF(B215="uncommon", 3, IF(B215="rare", 1.22, 1)))</f>
+        <f>IF(B215="common", 4, IF(B215="uncommon", 3, IF(B215="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5868,7 +5887,7 @@
       </c>
       <c r="E216" s="3" t="n"/>
       <c r="F216" s="3">
-        <f>IF(B216="common", 4, IF(B216="uncommon", 3, IF(B216="rare", 1.22, 1)))</f>
+        <f>IF(B216="common", 4, IF(B216="uncommon", 3, IF(B216="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -5893,7 +5912,7 @@
         <v>0.14</v>
       </c>
       <c r="F217" s="3">
-        <f>IF(B217="common", 4, IF(B217="uncommon", 3, IF(B217="rare", 1.22, 1)))</f>
+        <f>IF(B217="common", 4, IF(B217="uncommon", 3, IF(B217="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
     </row>
@@ -12441,7 +12460,7 @@
       <c r="E1263" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N210"/>
+  <autoFilter ref="A1:K210"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12452,7 +12471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12460,194 +12479,224 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>ev_common_total</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
-        <v>0.1093478260869565</v>
+      <c r="B2" s="11" t="n">
+        <v>0.1123913043478261</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ev_uncommon_total</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
-        <v>0.1560606060606061</v>
+      <c r="B3" s="11" t="n">
+        <v>0.1696969696969697</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>ev_rare_total</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
-        <v>0.2604761904761905</v>
+      <c r="B4" s="11" t="n">
+        <v>0.2695238095238095</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>ev_double_rare_total</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>0.3288888888888888</v>
+      <c r="B5" s="11" t="n">
+        <v>0.3478888888888889</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>ev_pokeball_total</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>ev_master_ball_total</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>ev_hyper_rare_total</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>0.1356493506493506</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B8" s="11" t="n">
+        <v>0.1349350649350649</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>ev_ultra_rare_total</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>0.6429435483870968</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="B9" s="11" t="n">
+        <v>0.6597580645161291</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>ev_SIR_total</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>2.301644444444444</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B10" s="11" t="n">
+        <v>2.366622222222222</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>ev_IR_total</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
-        <v>1.902606382978723</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="B11" s="11" t="n">
+        <v>1.987606382978723</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>ev_reverse_total</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
-        <v>3.066667607754564</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B12" s="11" t="n">
+        <v>2.824572746094485</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>reverse_multiplier</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B13" s="11" t="n">
         <v>1.879338061465721</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>rare_multiplier</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B14" s="10" t="n">
         <v>1.741272168691524</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>ev_total_for_hits</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
-        <v>4.982843726459615</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="B15" s="11" t="n">
+        <v>5.14892173465214</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>ev_hits_total</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
-        <v>5.311732615348505</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="B16" s="11" t="n">
+        <v>5.496810623541029</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>total_ev</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
-        <v>12.43417083607831</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="B17" s="11" t="n">
+        <v>11.07690299510566</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>net_value</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
-        <v>1.544170836078312</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B18" s="11" t="n">
+        <v>0.1869029951056582</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>roi</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
-        <v>0.1417971382992023</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="B19" s="12" t="n">
+        <v>0.01716280946792081</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>roi_percent</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
-        <v>13.17971382992023</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>hit_prob_pct</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
+      <c r="B20" s="12" t="n">
+        <v>0.7162809467920814</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>no_hit_probability_percentage</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>68.32877110235633</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>hit_probability_percentage</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
         <v>31.67122889764367</v>
       </c>
     </row>

--- a/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
+++ b/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-27375" yWindow="90" windowWidth="25260" windowHeight="11385" tabRatio="797" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3450" yWindow="825" windowWidth="25260" windowHeight="11385" tabRatio="797" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -138,6 +138,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -148,6 +151,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -597,7 +603,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -607,7 +613,7 @@
         <v>0.06</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F2" s="3">
         <f>IF(B2="common", 4, IF(B2="uncommon", 3, IF(B2="rare", 1.74127216869152, 1)))</f>
@@ -639,17 +645,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="F3" s="3">
         <f>IF(B3="common", 4, IF(B3="uncommon", 3, IF(B3="rare", 1.74127216869152, 1)))</f>
@@ -668,14 +674,14 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
         <v>90</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3">
@@ -683,7 +689,7 @@
         <v/>
       </c>
       <c r="H4">
-        <f>SUMPRODUCT((B2:B210="Rare") * D2:D210 * F2:F210 / C2:C210)</f>
+        <f>0.792892156862745*SUMPRODUCT((B2:B217="Rare") * D2:D217 / C2:C217)</f>
         <v/>
       </c>
     </row>
@@ -695,14 +701,14 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7.46</v>
+        <v>7.37</v>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3">
@@ -710,7 +716,7 @@
         <v/>
       </c>
       <c r="H5">
-        <f>SUMPRODUCT((B2:B217="Double Rare") * D2:D217 * F2:F217 / C2:C217)</f>
+        <f>1.88541666666666* SUMPRODUCT((C2:C217&lt;&gt;"") * (E2:E217&lt;&gt;"") * (E2:E217 / C2:C217))</f>
         <v/>
       </c>
     </row>
@@ -722,14 +728,14 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Special Illustration Rare</t>
+          <t>special illustration rare</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
         <v>225</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>43.34</v>
+        <v>43.91</v>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3">
@@ -737,7 +743,7 @@
         <v/>
       </c>
       <c r="H6">
-        <f>SUMPRODUCT((B2:B210="Hyper Rare") * D2:D210 * F2:F210 / C2:C210)</f>
+        <f>SUMPRODUCT((B2:B217="Illustration Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
     </row>
@@ -749,7 +755,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -759,14 +765,14 @@
         <v>0.08</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="F7" s="3">
         <f>IF(B7="common", 4, IF(B7="uncommon", 3, IF(B7="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
       <c r="H7">
-        <f>SUMPRODUCT((B2:B217="Illustration Rare") * D2:D217 * F2:F217 / C2:C217)</f>
+        <f>SUMPRODUCT((B2:B217="Special Illustration Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
     </row>
@@ -778,24 +784,24 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="F8" s="3">
         <f>IF(B8="common", 4, IF(B8="uncommon", 3, IF(B8="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
       <c r="H8">
-        <f>SUMPRODUCT((B2:B217="Special Illustration Rare") * D2:D217 * F2:F217 / C2:C217)</f>
+        <f>SUMPRODUCT((B2:B217="Double Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
     </row>
@@ -807,24 +813,24 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="F9" s="3">
         <f>IF(B9="common", 4, IF(B9="uncommon", 3, IF(B9="rare", 1.74127216869152, 1)))</f>
         <v/>
       </c>
       <c r="H9">
-        <f>SUMPRODUCT((B2:B217="Ultra Rare") * D2:D217 * F2:F217 / C2:C217)</f>
+        <f>SUMPRODUCT((B2:B217="Hyper Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
     </row>
@@ -836,14 +842,14 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
         <v>90</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3">
@@ -851,7 +857,7 @@
         <v/>
       </c>
       <c r="H10">
-        <f>1.88 * SUMPRODUCT((C2:C217&lt;&gt;"") * (E2:E217&lt;&gt;"") * (E2:E217 / C2:C217))</f>
+        <f>SUMPRODUCT((B2:B217="Ultra Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
     </row>
@@ -863,14 +869,14 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.89</v>
+        <v>4.98</v>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3">
@@ -886,17 +892,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F12" s="3">
         <f>IF(B12="common", 4, IF(B12="uncommon", 3, IF(B12="rare", 1.74127216869152, 1)))</f>
@@ -911,17 +917,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="F13" s="3">
         <f>IF(B13="common", 4, IF(B13="uncommon", 3, IF(B13="rare", 1.74127216869152, 1)))</f>
@@ -936,14 +942,14 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Hyper Rare</t>
+          <t>hyper rare</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
         <v>154</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3">
@@ -959,7 +965,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -984,7 +990,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -994,7 +1000,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F16" s="3">
         <f>IF(B16="common", 4, IF(B16="uncommon", 3, IF(B16="rare", 1.74127216869152, 1)))</f>
@@ -1009,17 +1015,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="F17" s="3">
         <f>IF(B17="common", 4, IF(B17="uncommon", 3, IF(B17="rare", 1.74127216869152, 1)))</f>
@@ -1034,7 +1040,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1044,7 +1050,7 @@
         <v>0.12</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="F18" s="3">
         <f>IF(B18="common", 4, IF(B18="uncommon", 3, IF(B18="rare", 1.74127216869152, 1)))</f>
@@ -1059,14 +1065,14 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3">
@@ -1082,14 +1088,14 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>90</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.18</v>
+        <v>0.96</v>
       </c>
       <c r="E20" s="3" t="inlineStr"/>
       <c r="F20" s="3">
@@ -1105,14 +1111,14 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14.89</v>
+        <v>14.5</v>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3">
@@ -1128,14 +1134,14 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Special Illustration Rare</t>
+          <t>special illustration rare</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>225</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>73.55</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E22" s="3" t="inlineStr"/>
       <c r="F22" s="3">
@@ -1151,17 +1157,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="F23" s="3">
         <f>IF(B23="common", 4, IF(B23="uncommon", 3, IF(B23="rare", 1.74127216869152, 1)))</f>
@@ -1176,14 +1182,14 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>37.52</v>
+        <v>37.01</v>
       </c>
       <c r="E24" s="3" t="inlineStr"/>
       <c r="F24" s="3">
@@ -1199,7 +1205,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -1209,7 +1215,7 @@
         <v>0.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F25" s="3">
         <f>IF(B25="common", 4, IF(B25="uncommon", 3, IF(B25="rare", 1.74127216869152, 1)))</f>
@@ -1224,14 +1230,14 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>0.21</v>
@@ -1249,14 +1255,14 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>9.56</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3">
@@ -1272,17 +1278,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F28" s="3">
         <f>IF(B28="common", 4, IF(B28="uncommon", 3, IF(B28="rare", 1.74127216869152, 1)))</f>
@@ -1297,14 +1303,14 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
         <v>90</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.71</v>
+        <v>5.05</v>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3">
@@ -1320,14 +1326,14 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>31.27</v>
+        <v>31.25</v>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3">
@@ -1343,14 +1349,14 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Special Illustration Rare</t>
+          <t>special illustration rare</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
         <v>225</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>210.14</v>
+        <v>214.14</v>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3">
@@ -1366,14 +1372,14 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>0.19</v>
@@ -1391,14 +1397,14 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>52.06</v>
+        <v>51.42</v>
       </c>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3">
@@ -1414,7 +1420,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -1424,7 +1430,7 @@
         <v>0.1</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="F34" s="3">
         <f>IF(B34="common", 4, IF(B34="uncommon", 3, IF(B34="rare", 1.74127216869152, 1)))</f>
@@ -1439,14 +1445,14 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>34.86</v>
+        <v>34.16</v>
       </c>
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3">
@@ -1462,7 +1468,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -1487,7 +1493,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -1512,17 +1518,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F38" s="3">
         <f>IF(B38="common", 4, IF(B38="uncommon", 3, IF(B38="rare", 1.74127216869152, 1)))</f>
@@ -1537,17 +1543,17 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F39" s="3">
         <f>IF(B39="common", 4, IF(B39="uncommon", 3, IF(B39="rare", 1.74127216869152, 1)))</f>
@@ -1562,17 +1568,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="F40" s="3">
         <f>IF(B40="common", 4, IF(B40="uncommon", 3, IF(B40="rare", 1.74127216869152, 1)))</f>
@@ -1587,17 +1593,17 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="F41" s="3">
         <f>IF(B41="common", 4, IF(B41="uncommon", 3, IF(B41="rare", 1.74127216869152, 1)))</f>
@@ -1612,14 +1618,14 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>4.04</v>
+        <v>3.92</v>
       </c>
       <c r="E42" s="3" t="inlineStr"/>
       <c r="F42" s="3">
@@ -1635,17 +1641,17 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F43" s="3">
         <f>IF(B43="common", 4, IF(B43="uncommon", 3, IF(B43="rare", 1.74127216869152, 1)))</f>
@@ -1660,14 +1666,14 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>0.15</v>
@@ -1685,17 +1691,17 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="F45" s="3">
         <f>IF(B45="common", 4, IF(B45="uncommon", 3, IF(B45="rare", 1.74127216869152, 1)))</f>
@@ -1710,14 +1716,14 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
       <c r="E46" s="3" t="inlineStr"/>
       <c r="F46" s="3">
@@ -1733,17 +1739,17 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="F47" s="3">
         <f>IF(B47="common", 4, IF(B47="uncommon", 3, IF(B47="rare", 1.74127216869152, 1)))</f>
@@ -1758,7 +1764,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -1783,17 +1789,17 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="F49" s="3">
         <f>IF(B49="common", 4, IF(B49="uncommon", 3, IF(B49="rare", 1.74127216869152, 1)))</f>
@@ -1808,14 +1814,14 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>25.78</v>
+        <v>25.53</v>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="3">
@@ -1831,17 +1837,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="F51" s="3">
         <f>IF(B51="common", 4, IF(B51="uncommon", 3, IF(B51="rare", 1.74127216869152, 1)))</f>
@@ -1856,17 +1862,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F52" s="3">
         <f>IF(B52="common", 4, IF(B52="uncommon", 3, IF(B52="rare", 1.74127216869152, 1)))</f>
@@ -1881,7 +1887,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -1891,7 +1897,7 @@
         <v>0.05</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F53" s="3">
         <f>IF(B53="common", 4, IF(B53="uncommon", 3, IF(B53="rare", 1.74127216869152, 1)))</f>
@@ -1906,7 +1912,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -1931,17 +1937,17 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="F55" s="3">
         <f>IF(B55="common", 4, IF(B55="uncommon", 3, IF(B55="rare", 1.74127216869152, 1)))</f>
@@ -1956,7 +1962,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -1966,7 +1972,7 @@
         <v>0.05</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F56" s="3">
         <f>IF(B56="common", 4, IF(B56="uncommon", 3, IF(B56="rare", 1.74127216869152, 1)))</f>
@@ -1981,7 +1987,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -1991,7 +1997,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="F57" s="3">
         <f>IF(B57="common", 4, IF(B57="uncommon", 3, IF(B57="rare", 1.74127216869152, 1)))</f>
@@ -2006,7 +2012,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -2016,7 +2022,7 @@
         <v>0.13</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="F58" s="3">
         <f>IF(B58="common", 4, IF(B58="uncommon", 3, IF(B58="rare", 1.74127216869152, 1)))</f>
@@ -2031,7 +2037,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -2041,7 +2047,7 @@
         <v>0.16</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="F59" s="3">
         <f>IF(B59="common", 4, IF(B59="uncommon", 3, IF(B59="rare", 1.74127216869152, 1)))</f>
@@ -2056,17 +2062,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="F60" s="3">
         <f>IF(B60="common", 4, IF(B60="uncommon", 3, IF(B60="rare", 1.74127216869152, 1)))</f>
@@ -2081,14 +2087,14 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>6.99</v>
+        <v>6.92</v>
       </c>
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3">
@@ -2104,14 +2110,14 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Special Illustration Rare</t>
+          <t>special illustration rare</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
         <v>225</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>14.98</v>
+        <v>14.48</v>
       </c>
       <c r="E62" s="3" t="inlineStr"/>
       <c r="F62" s="3">
@@ -2127,7 +2133,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
@@ -2152,7 +2158,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
@@ -2162,7 +2168,7 @@
         <v>0.1</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="F64" s="3">
         <f>IF(B64="common", 4, IF(B64="uncommon", 3, IF(B64="rare", 1.74127216869152, 1)))</f>
@@ -2177,7 +2183,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -2187,7 +2193,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="F65" s="3">
         <f>IF(B65="common", 4, IF(B65="uncommon", 3, IF(B65="rare", 1.74127216869152, 1)))</f>
@@ -2202,17 +2208,17 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F66" s="3">
         <f>IF(B66="common", 4, IF(B66="uncommon", 3, IF(B66="rare", 1.74127216869152, 1)))</f>
@@ -2227,14 +2233,14 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>1.08</v>
@@ -2252,14 +2258,14 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E68" s="3" t="n">
         <v>0.18</v>
@@ -2277,17 +2283,17 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="F69" s="3">
         <f>IF(B69="common", 4, IF(B69="uncommon", 3, IF(B69="rare", 1.74127216869152, 1)))</f>
@@ -2302,7 +2308,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
@@ -2327,17 +2333,17 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="F71" s="3">
         <f>IF(B71="common", 4, IF(B71="uncommon", 3, IF(B71="rare", 1.74127216869152, 1)))</f>
@@ -2352,14 +2358,14 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>4.99</v>
+        <v>5.05</v>
       </c>
       <c r="E72" s="3" t="inlineStr"/>
       <c r="F72" s="3">
@@ -2375,14 +2381,14 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Special Illustration Rare</t>
+          <t>special illustration rare</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
         <v>225</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>15.6</v>
+        <v>13.93</v>
       </c>
       <c r="E73" s="3" t="inlineStr"/>
       <c r="F73" s="3">
@@ -2398,14 +2404,14 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>0.21</v>
@@ -2423,7 +2429,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -2448,17 +2454,17 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F76" s="3">
         <f>IF(B76="common", 4, IF(B76="uncommon", 3, IF(B76="rare", 1.74127216869152, 1)))</f>
@@ -2473,7 +2479,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -2498,14 +2504,14 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
         <v>90</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="E78" s="3" t="inlineStr"/>
       <c r="F78" s="3">
@@ -2521,14 +2527,14 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>5.18</v>
+        <v>4.83</v>
       </c>
       <c r="E79" s="3" t="inlineStr"/>
       <c r="F79" s="3">
@@ -2544,17 +2550,17 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="F80" s="3">
         <f>IF(B80="common", 4, IF(B80="uncommon", 3, IF(B80="rare", 1.74127216869152, 1)))</f>
@@ -2569,7 +2575,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
@@ -2594,14 +2600,14 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E82" s="3" t="n">
         <v>0.15</v>
@@ -2619,7 +2625,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
@@ -2644,17 +2650,17 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="F84" s="3">
         <f>IF(B84="common", 4, IF(B84="uncommon", 3, IF(B84="rare", 1.74127216869152, 1)))</f>
@@ -2669,17 +2675,17 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F85" s="3">
         <f>IF(B85="common", 4, IF(B85="uncommon", 3, IF(B85="rare", 1.74127216869152, 1)))</f>
@@ -2694,17 +2700,17 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="F86" s="3">
         <f>IF(B86="common", 4, IF(B86="uncommon", 3, IF(B86="rare", 1.74127216869152, 1)))</f>
@@ -2719,17 +2725,17 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="F87" s="3">
         <f>IF(B87="common", 4, IF(B87="uncommon", 3, IF(B87="rare", 1.74127216869152, 1)))</f>
@@ -2744,7 +2750,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
@@ -2754,7 +2760,7 @@
         <v>0.06</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F88" s="3">
         <f>IF(B88="common", 4, IF(B88="uncommon", 3, IF(B88="rare", 1.74127216869152, 1)))</f>
@@ -2769,7 +2775,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
@@ -2779,7 +2785,7 @@
         <v>0.1</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="F89" s="3">
         <f>IF(B89="common", 4, IF(B89="uncommon", 3, IF(B89="rare", 1.74127216869152, 1)))</f>
@@ -2794,7 +2800,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
@@ -2819,14 +2825,14 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>26.26</v>
+        <v>26.78</v>
       </c>
       <c r="E91" s="3" t="inlineStr"/>
       <c r="F91" s="3">
@@ -2842,17 +2848,17 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="F92" s="3">
         <f>IF(B92="common", 4, IF(B92="uncommon", 3, IF(B92="rare", 1.74127216869152, 1)))</f>
@@ -2867,17 +2873,17 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="F93" s="3">
         <f>IF(B93="common", 4, IF(B93="uncommon", 3, IF(B93="rare", 1.74127216869152, 1)))</f>
@@ -2892,14 +2898,14 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C94" s="3" t="n">
         <v>90</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="E94" s="3" t="inlineStr"/>
       <c r="F94" s="3">
@@ -2915,14 +2921,14 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>5.3</v>
+        <v>5.09</v>
       </c>
       <c r="E95" s="3" t="inlineStr"/>
       <c r="F95" s="3">
@@ -2938,7 +2944,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
@@ -2948,7 +2954,7 @@
         <v>0.09</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="F96" s="3">
         <f>IF(B96="common", 4, IF(B96="uncommon", 3, IF(B96="rare", 1.74127216869152, 1)))</f>
@@ -2963,17 +2969,17 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="F97" s="3">
         <f>IF(B97="common", 4, IF(B97="uncommon", 3, IF(B97="rare", 1.74127216869152, 1)))</f>
@@ -2988,17 +2994,17 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F98" s="3">
         <f>IF(B98="common", 4, IF(B98="uncommon", 3, IF(B98="rare", 1.74127216869152, 1)))</f>
@@ -3013,7 +3019,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
@@ -3023,7 +3029,7 @@
         <v>0.1</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="F99" s="3">
         <f>IF(B99="common", 4, IF(B99="uncommon", 3, IF(B99="rare", 1.74127216869152, 1)))</f>
@@ -3038,14 +3044,14 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
         <v>90</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="E100" s="3" t="inlineStr"/>
       <c r="F100" s="3">
@@ -3061,14 +3067,14 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>5.8</v>
+        <v>5.55</v>
       </c>
       <c r="E101" s="3" t="inlineStr"/>
       <c r="F101" s="3">
@@ -3084,17 +3090,17 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C102" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="F102" s="3">
         <f>IF(B102="common", 4, IF(B102="uncommon", 3, IF(B102="rare", 1.74127216869152, 1)))</f>
@@ -3109,7 +3115,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
@@ -3134,7 +3140,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
@@ -3159,7 +3165,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
@@ -3169,7 +3175,7 @@
         <v>0.08</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="F105" s="3">
         <f>IF(B105="common", 4, IF(B105="uncommon", 3, IF(B105="rare", 1.74127216869152, 1)))</f>
@@ -3184,17 +3190,17 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="F106" s="3">
         <f>IF(B106="common", 4, IF(B106="uncommon", 3, IF(B106="rare", 1.74127216869152, 1)))</f>
@@ -3209,17 +3215,17 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F107" s="3">
         <f>IF(B107="common", 4, IF(B107="uncommon", 3, IF(B107="rare", 1.74127216869152, 1)))</f>
@@ -3234,17 +3240,17 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="F108" s="3">
         <f>IF(B108="common", 4, IF(B108="uncommon", 3, IF(B108="rare", 1.74127216869152, 1)))</f>
@@ -3259,17 +3265,17 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F109" s="3">
         <f>IF(B109="common", 4, IF(B109="uncommon", 3, IF(B109="rare", 1.74127216869152, 1)))</f>
@@ -3284,14 +3290,14 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>11.24</v>
+        <v>11.22</v>
       </c>
       <c r="E110" s="3" t="inlineStr"/>
       <c r="F110" s="3">
@@ -3307,17 +3313,17 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="F111" s="3">
         <f>IF(B111="common", 4, IF(B111="uncommon", 3, IF(B111="rare", 1.74127216869152, 1)))</f>
@@ -3332,7 +3338,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
@@ -3342,7 +3348,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="F112" s="3">
         <f>IF(B112="common", 4, IF(B112="uncommon", 3, IF(B112="rare", 1.74127216869152, 1)))</f>
@@ -3357,14 +3363,14 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E113" s="3" t="n">
         <v>0.9399999999999999</v>
@@ -3382,7 +3388,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
@@ -3392,7 +3398,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F114" s="3">
         <f>IF(B114="common", 4, IF(B114="uncommon", 3, IF(B114="rare", 1.74127216869152, 1)))</f>
@@ -3407,14 +3413,14 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0.13</v>
@@ -3432,14 +3438,14 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0.13</v>
@@ -3457,7 +3463,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
@@ -3467,7 +3473,7 @@
         <v>0.16</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="F117" s="3">
         <f>IF(B117="common", 4, IF(B117="uncommon", 3, IF(B117="rare", 1.74127216869152, 1)))</f>
@@ -3482,7 +3488,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
@@ -3492,7 +3498,7 @@
         <v>0.06</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F118" s="3">
         <f>IF(B118="common", 4, IF(B118="uncommon", 3, IF(B118="rare", 1.74127216869152, 1)))</f>
@@ -3507,17 +3513,17 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="F119" s="3">
         <f>IF(B119="common", 4, IF(B119="uncommon", 3, IF(B119="rare", 1.74127216869152, 1)))</f>
@@ -3532,14 +3538,14 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
         <v>90</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>7.21</v>
+        <v>6.62</v>
       </c>
       <c r="E120" s="3" t="inlineStr"/>
       <c r="F120" s="3">
@@ -3555,14 +3561,14 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>19.11</v>
+        <v>18.71</v>
       </c>
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3">
@@ -3578,14 +3584,14 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Hyper Rare</t>
+          <t>hyper rare</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
         <v>154</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>13.27</v>
+        <v>13.41</v>
       </c>
       <c r="E122" s="3" t="inlineStr"/>
       <c r="F122" s="3">
@@ -3601,14 +3607,14 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
         <v>90</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>9.75</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E123" s="3" t="inlineStr"/>
       <c r="F123" s="3">
@@ -3624,17 +3630,17 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="F124" s="3">
         <f>IF(B124="common", 4, IF(B124="uncommon", 3, IF(B124="rare", 1.74127216869152, 1)))</f>
@@ -3649,7 +3655,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
@@ -3659,7 +3665,7 @@
         <v>0.21</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="F125" s="3">
         <f>IF(B125="common", 4, IF(B125="uncommon", 3, IF(B125="rare", 1.74127216869152, 1)))</f>
@@ -3674,7 +3680,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
@@ -3699,14 +3705,14 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C127" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>5.79</v>
+        <v>5.49</v>
       </c>
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3">
@@ -3722,14 +3728,14 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>0.22</v>
@@ -3747,7 +3753,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
@@ -3757,7 +3763,7 @@
         <v>0.19</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="F129" s="3">
         <f>IF(B129="common", 4, IF(B129="uncommon", 3, IF(B129="rare", 1.74127216869152, 1)))</f>
@@ -3772,14 +3778,14 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>9.58</v>
+        <v>9.9</v>
       </c>
       <c r="E130" s="3" t="inlineStr"/>
       <c r="F130" s="3">
@@ -3795,7 +3801,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
@@ -3805,7 +3811,7 @@
         <v>0.06</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="F131" s="3">
         <f>IF(B131="common", 4, IF(B131="uncommon", 3, IF(B131="rare", 1.74127216869152, 1)))</f>
@@ -3820,17 +3826,17 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="F132" s="3">
         <f>IF(B132="common", 4, IF(B132="uncommon", 3, IF(B132="rare", 1.74127216869152, 1)))</f>
@@ -3845,17 +3851,17 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="F133" s="3">
         <f>IF(B133="common", 4, IF(B133="uncommon", 3, IF(B133="rare", 1.74127216869152, 1)))</f>
@@ -3870,14 +3876,14 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C134" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0.19</v>
@@ -3895,17 +3901,17 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="F135" s="3">
         <f>IF(B135="common", 4, IF(B135="uncommon", 3, IF(B135="rare", 1.74127216869152, 1)))</f>
@@ -3920,14 +3926,14 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
         <v>90</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="E136" s="3" t="inlineStr"/>
       <c r="F136" s="3">
@@ -3943,14 +3949,14 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>7.87</v>
+        <v>6.83</v>
       </c>
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3">
@@ -3966,7 +3972,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
@@ -3976,7 +3982,7 @@
         <v>0.08</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="F138" s="3">
         <f>IF(B138="common", 4, IF(B138="uncommon", 3, IF(B138="rare", 1.74127216869152, 1)))</f>
@@ -3991,7 +3997,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
@@ -4001,7 +4007,7 @@
         <v>0.06</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="F139" s="3">
         <f>IF(B139="common", 4, IF(B139="uncommon", 3, IF(B139="rare", 1.74127216869152, 1)))</f>
@@ -4016,14 +4022,14 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C140" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>8</v>
+        <v>7.85</v>
       </c>
       <c r="E140" s="3" t="inlineStr"/>
       <c r="F140" s="3">
@@ -4039,14 +4045,14 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E141" s="3" t="n">
         <v>0.59</v>
@@ -4064,7 +4070,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C142" s="3" t="n">
@@ -4074,7 +4080,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="F142" s="3">
         <f>IF(B142="common", 4, IF(B142="uncommon", 3, IF(B142="rare", 1.74127216869152, 1)))</f>
@@ -4089,7 +4095,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C143" s="3" t="n">
@@ -4114,7 +4120,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
@@ -4124,7 +4130,7 @@
         <v>0.1</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="F144" s="3">
         <f>IF(B144="common", 4, IF(B144="uncommon", 3, IF(B144="rare", 1.74127216869152, 1)))</f>
@@ -4139,17 +4145,17 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="F145" s="3">
         <f>IF(B145="common", 4, IF(B145="uncommon", 3, IF(B145="rare", 1.74127216869152, 1)))</f>
@@ -4164,7 +4170,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C146" s="3" t="n">
@@ -4174,7 +4180,7 @@
         <v>0.06</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F146" s="3">
         <f>IF(B146="common", 4, IF(B146="uncommon", 3, IF(B146="rare", 1.74127216869152, 1)))</f>
@@ -4189,17 +4195,17 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C147" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="F147" s="3">
         <f>IF(B147="common", 4, IF(B147="uncommon", 3, IF(B147="rare", 1.74127216869152, 1)))</f>
@@ -4214,7 +4220,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
@@ -4224,7 +4230,7 @@
         <v>0.09</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="F148" s="3">
         <f>IF(B148="common", 4, IF(B148="uncommon", 3, IF(B148="rare", 1.74127216869152, 1)))</f>
@@ -4239,7 +4245,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C149" s="3" t="n">
@@ -4249,7 +4255,7 @@
         <v>0.1</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="F149" s="3">
         <f>IF(B149="common", 4, IF(B149="uncommon", 3, IF(B149="rare", 1.74127216869152, 1)))</f>
@@ -4264,14 +4270,14 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C150" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>28.89</v>
+        <v>28.78</v>
       </c>
       <c r="E150" s="3" t="inlineStr"/>
       <c r="F150" s="3">
@@ -4287,17 +4293,17 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="F151" s="3">
         <f>IF(B151="common", 4, IF(B151="uncommon", 3, IF(B151="rare", 1.74127216869152, 1)))</f>
@@ -4312,7 +4318,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
@@ -4322,7 +4328,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F152" s="3">
         <f>IF(B152="common", 4, IF(B152="uncommon", 3, IF(B152="rare", 1.74127216869152, 1)))</f>
@@ -4337,17 +4343,17 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="F153" s="3">
         <f>IF(B153="common", 4, IF(B153="uncommon", 3, IF(B153="rare", 1.74127216869152, 1)))</f>
@@ -4362,14 +4368,14 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>18.96</v>
+        <v>19.64</v>
       </c>
       <c r="E154" s="3" t="inlineStr"/>
       <c r="F154" s="3">
@@ -4385,7 +4391,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C155" s="3" t="n">
@@ -4410,7 +4416,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
@@ -4420,7 +4426,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="F156" s="3">
         <f>IF(B156="common", 4, IF(B156="uncommon", 3, IF(B156="rare", 1.74127216869152, 1)))</f>
@@ -4435,14 +4441,14 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C157" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E157" s="3" t="n">
         <v>0.17</v>
@@ -4460,7 +4466,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
@@ -4470,7 +4476,7 @@
         <v>0.09</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F158" s="3">
         <f>IF(B158="common", 4, IF(B158="uncommon", 3, IF(B158="rare", 1.74127216869152, 1)))</f>
@@ -4485,17 +4491,17 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C159" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="F159" s="3">
         <f>IF(B159="common", 4, IF(B159="uncommon", 3, IF(B159="rare", 1.74127216869152, 1)))</f>
@@ -4510,7 +4516,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C160" s="3" t="n">
@@ -4535,14 +4541,14 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C161" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>21.1</v>
+        <v>20.45</v>
       </c>
       <c r="E161" s="3" t="inlineStr"/>
       <c r="F161" s="3">
@@ -4558,17 +4564,17 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C162" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="F162" s="3">
         <f>IF(B162="common", 4, IF(B162="uncommon", 3, IF(B162="rare", 1.74127216869152, 1)))</f>
@@ -4583,7 +4589,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
@@ -4593,7 +4599,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="F163" s="3">
         <f>IF(B163="common", 4, IF(B163="uncommon", 3, IF(B163="rare", 1.74127216869152, 1)))</f>
@@ -4608,7 +4614,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C164" s="3" t="n">
@@ -4633,7 +4639,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C165" s="3" t="n">
@@ -4643,7 +4649,7 @@
         <v>0.06</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="F165" s="3">
         <f>IF(B165="common", 4, IF(B165="uncommon", 3, IF(B165="rare", 1.74127216869152, 1)))</f>
@@ -4658,17 +4664,17 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="F166" s="3">
         <f>IF(B166="common", 4, IF(B166="uncommon", 3, IF(B166="rare", 1.74127216869152, 1)))</f>
@@ -4683,7 +4689,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
@@ -4693,7 +4699,7 @@
         <v>0.06</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F167" s="3">
         <f>IF(B167="common", 4, IF(B167="uncommon", 3, IF(B167="rare", 1.74127216869152, 1)))</f>
@@ -4708,17 +4714,17 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C168" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="F168" s="3">
         <f>IF(B168="common", 4, IF(B168="uncommon", 3, IF(B168="rare", 1.74127216869152, 1)))</f>
@@ -4733,17 +4739,17 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="F169" s="3">
         <f>IF(B169="common", 4, IF(B169="uncommon", 3, IF(B169="rare", 1.74127216869152, 1)))</f>
@@ -4758,7 +4764,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
@@ -4768,7 +4774,7 @@
         <v>0.08</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="F170" s="3">
         <f>IF(B170="common", 4, IF(B170="uncommon", 3, IF(B170="rare", 1.74127216869152, 1)))</f>
@@ -4783,7 +4789,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
@@ -4793,7 +4799,7 @@
         <v>0.11</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="F171" s="3">
         <f>IF(B171="common", 4, IF(B171="uncommon", 3, IF(B171="rare", 1.74127216869152, 1)))</f>
@@ -4808,7 +4814,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
@@ -4818,7 +4824,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F172" s="3">
         <f>IF(B172="common", 4, IF(B172="uncommon", 3, IF(B172="rare", 1.74127216869152, 1)))</f>
@@ -4833,7 +4839,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
@@ -4858,7 +4864,7 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
@@ -4883,7 +4889,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
@@ -4893,7 +4899,7 @@
         <v>0.06</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F175" s="3">
         <f>IF(B175="common", 4, IF(B175="uncommon", 3, IF(B175="rare", 1.74127216869152, 1)))</f>
@@ -4908,7 +4914,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
@@ -4933,7 +4939,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
@@ -4943,7 +4949,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="F177" s="3">
         <f>IF(B177="common", 4, IF(B177="uncommon", 3, IF(B177="rare", 1.74127216869152, 1)))</f>
@@ -4958,7 +4964,7 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
@@ -4968,7 +4974,7 @@
         <v>0.16</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="F178" s="3">
         <f>IF(B178="common", 4, IF(B178="uncommon", 3, IF(B178="rare", 1.74127216869152, 1)))</f>
@@ -4983,7 +4989,7 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
@@ -4993,7 +4999,7 @@
         <v>0.06</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F179" s="3">
         <f>IF(B179="common", 4, IF(B179="uncommon", 3, IF(B179="rare", 1.74127216869152, 1)))</f>
@@ -5008,7 +5014,7 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
@@ -5018,7 +5024,7 @@
         <v>0.11</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="F180" s="3">
         <f>IF(B180="common", 4, IF(B180="uncommon", 3, IF(B180="rare", 1.74127216869152, 1)))</f>
@@ -5033,14 +5039,14 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>46.05</v>
+        <v>45.09</v>
       </c>
       <c r="E181" s="3" t="inlineStr"/>
       <c r="F181" s="3">
@@ -5056,17 +5062,17 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="F182" s="3">
         <f>IF(B182="common", 4, IF(B182="uncommon", 3, IF(B182="rare", 1.74127216869152, 1)))</f>
@@ -5081,7 +5087,7 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
@@ -5106,14 +5112,14 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Hyper Rare</t>
+          <t>hyper rare</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
         <v>154</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>2.56</v>
+        <v>2.93</v>
       </c>
       <c r="E184" s="3" t="inlineStr"/>
       <c r="F184" s="3">
@@ -5129,17 +5135,17 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C185" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="F185" s="3">
         <f>IF(B185="common", 4, IF(B185="uncommon", 3, IF(B185="rare", 1.74127216869152, 1)))</f>
@@ -5154,14 +5160,14 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>7.68</v>
+        <v>7.56</v>
       </c>
       <c r="E186" s="3" t="inlineStr"/>
       <c r="F186" s="3">
@@ -5177,17 +5183,17 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C187" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="F187" s="3">
         <f>IF(B187="common", 4, IF(B187="uncommon", 3, IF(B187="rare", 1.74127216869152, 1)))</f>
@@ -5202,7 +5208,7 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C188" s="3" t="n">
@@ -5212,7 +5218,7 @@
         <v>0.06</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F188" s="3">
         <f>IF(B188="common", 4, IF(B188="uncommon", 3, IF(B188="rare", 1.74127216869152, 1)))</f>
@@ -5227,7 +5233,7 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C189" s="3" t="n">
@@ -5252,17 +5258,17 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="F190" s="3">
         <f>IF(B190="common", 4, IF(B190="uncommon", 3, IF(B190="rare", 1.74127216869152, 1)))</f>
@@ -5277,7 +5283,7 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
@@ -5287,7 +5293,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="F191" s="3">
         <f>IF(B191="common", 4, IF(B191="uncommon", 3, IF(B191="rare", 1.74127216869152, 1)))</f>
@@ -5302,7 +5308,7 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
@@ -5327,14 +5333,14 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
         <v>90</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>0.77</v>
+        <v>0.95</v>
       </c>
       <c r="E193" s="3" t="inlineStr"/>
       <c r="F193" s="3">
@@ -5350,14 +5356,14 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>11.82</v>
+        <v>11.58</v>
       </c>
       <c r="E194" s="3" t="inlineStr"/>
       <c r="F194" s="3">
@@ -5373,14 +5379,14 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Special Illustration Rare</t>
+          <t>special illustration rare</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
         <v>225</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>68.69</v>
+        <v>67.88</v>
       </c>
       <c r="E195" s="3" t="inlineStr"/>
       <c r="F195" s="3">
@@ -5396,7 +5402,7 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
@@ -5406,7 +5412,7 @@
         <v>0.05</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F196" s="3">
         <f>IF(B196="common", 4, IF(B196="uncommon", 3, IF(B196="rare", 1.74127216869152, 1)))</f>
@@ -5421,17 +5427,17 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C197" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="F197" s="3">
         <f>IF(B197="common", 4, IF(B197="uncommon", 3, IF(B197="rare", 1.74127216869152, 1)))</f>
@@ -5446,7 +5452,7 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
@@ -5456,7 +5462,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F198" s="3">
         <f>IF(B198="common", 4, IF(B198="uncommon", 3, IF(B198="rare", 1.74127216869152, 1)))</f>
@@ -5471,7 +5477,7 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
@@ -5481,7 +5487,7 @@
         <v>0.09</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="F199" s="3">
         <f>IF(B199="common", 4, IF(B199="uncommon", 3, IF(B199="rare", 1.74127216869152, 1)))</f>
@@ -5496,17 +5502,17 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>uncommon</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
         <v>33</v>
       </c>
       <c r="D200" s="3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="F200" s="3">
         <f>IF(B200="common", 4, IF(B200="uncommon", 3, IF(B200="rare", 1.74127216869152, 1)))</f>
@@ -5521,14 +5527,14 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>illustration rare</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
         <v>188</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>30.34</v>
+        <v>29.96</v>
       </c>
       <c r="E201" s="3" t="inlineStr"/>
       <c r="F201" s="3">
@@ -5544,7 +5550,7 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
@@ -5554,7 +5560,7 @@
         <v>0.06</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="F202" s="3">
         <f>IF(B202="common", 4, IF(B202="uncommon", 3, IF(B202="rare", 1.74127216869152, 1)))</f>
@@ -5569,17 +5575,17 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
         <v>46</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="F203" s="3">
         <f>IF(B203="common", 4, IF(B203="uncommon", 3, IF(B203="rare", 1.74127216869152, 1)))</f>
@@ -5594,17 +5600,17 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D204" s="3" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="F204" s="3">
         <f>IF(B204="common", 4, IF(B204="uncommon", 3, IF(B204="rare", 1.74127216869152, 1)))</f>
@@ -5619,14 +5625,14 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
         <v>90</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="E205" s="3" t="inlineStr"/>
       <c r="F205" s="3">
@@ -5642,14 +5648,14 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>7.9</v>
+        <v>7.25</v>
       </c>
       <c r="E206" s="3" t="inlineStr"/>
       <c r="F206" s="3">
@@ -5665,14 +5671,14 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
         <v>90</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="E207" s="3" t="inlineStr"/>
       <c r="F207" s="3">
@@ -5688,14 +5694,14 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
         <v>248</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>8.06</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="E208" s="3" t="inlineStr"/>
       <c r="F208" s="3">
@@ -5711,14 +5717,14 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Special Illustration Rare</t>
+          <t>special illustration rare</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
         <v>225</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>55.36</v>
+        <v>55.64</v>
       </c>
       <c r="E209" s="3" t="inlineStr"/>
       <c r="F209" s="3">
@@ -5734,7 +5740,7 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
@@ -5759,7 +5765,7 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
@@ -5784,7 +5790,7 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
@@ -5807,7 +5813,7 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
@@ -5830,7 +5836,7 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>double rare</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
@@ -5853,7 +5859,7 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>ultra rare</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
@@ -5876,7 +5882,7 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>Special Illustration Rare</t>
+          <t>special illustration rare</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
@@ -5899,7 +5905,7 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
@@ -12479,225 +12485,225 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>ev_common_total</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n">
-        <v>0.1123913043478261</v>
+      <c r="B2" s="12" t="n">
+        <v>0.451304347826087</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>ev_uncommon_total</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n">
-        <v>0.1696969696969697</v>
+      <c r="B3" s="12" t="n">
+        <v>0.5090909090909091</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>ev_rare_total</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
-        <v>0.2695238095238095</v>
+      <c r="B4" s="12" t="n">
+        <v>0.213703314659197</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>ev_reverse_total</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>5.313106295878034</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>ev_ace_spec_total</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>ev_pokeball_total</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>ev_master_ball_total</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>ev_IR_total</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>1.96968085106383</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>ev_SIR_total</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>2.372933333333333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>ev_double_rare_total</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
-        <v>0.3478888888888889</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>ev_pokeball_total</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>ev_master_ball_total</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="B11" s="12" t="n">
+        <v>0.3439999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>ev_hyper_rare_total</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
-        <v>0.1349350649350649</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="B12" s="12" t="n">
+        <v>0.1366233766233766</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>ev_ultra_rare_total</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
-        <v>0.6597580645161291</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>ev_SIR_total</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>2.366622222222222</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>ev_IR_total</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>1.987606382978723</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>ev_reverse_total</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="n">
-        <v>2.824572746094485</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="B13" s="12" t="n">
+        <v>0.6449596774193548</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>reverse_multiplier</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
-        <v>1.879338061465721</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="n">
+        <v>1.885416666666667</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>rare_multiplier</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
-        <v>1.741272168691524</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>ev_total_for_hits</t>
-        </is>
-      </c>
       <c r="B15" s="11" t="n">
-        <v>5.14892173465214</v>
+        <v>0.7928921568627451</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>ev_hits_total</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
-        <v>5.496810623541029</v>
+      <c r="B16" s="12" t="n">
+        <v>5.468197238439894</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>total_ev</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
-        <v>11.07690299510566</v>
+      <c r="B17" s="12" t="n">
+        <v>11.95540210589412</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>net_value</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
-        <v>0.1869029951056582</v>
+      <c r="B18" s="12" t="n">
+        <v>1.065402105894121</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>roi</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
-        <v>0.01716280946792081</v>
+      <c r="B19" s="13" t="n">
+        <v>1.097833067575218</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>roi_percent</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
-        <v>0.7162809467920814</v>
+      <c r="B20" s="14" t="n">
+        <v>0.09783306757521772</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>no_hit_probability_percentage</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
-        <v>68.32877110235633</v>
+      <c r="B21" s="14" t="n">
+        <v>0.6832877110235632</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>hit_probability_percentage</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
-        <v>31.67122889764367</v>
+      <c r="B22" s="14" t="n">
+        <v>0.3167122889764367</v>
       </c>
     </row>
   </sheetData>

--- a/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
+++ b/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
@@ -524,18 +524,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1263"/>
+  <dimension ref="A1:T1263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39.6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="4"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="24.7109375" customWidth="1" min="6" max="6"/>
-    <col width="33.5703125" customWidth="1" min="7" max="8"/>
-    <col width="32.42578125" customWidth="1" min="9" max="10"/>
+    <col width="30" customWidth="1" min="2" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="39.140625" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="50.28515625" customWidth="1" min="8" max="8"/>
+    <col width="28.85546875" customWidth="1" min="9" max="9"/>
+    <col width="23.7109375" customWidth="1" min="10" max="10"/>
     <col width="39.42578125" customWidth="1" min="11" max="11"/>
+    <col width="20.7109375" customWidth="1" min="12" max="12"/>
+    <col width="21.85546875" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -546,24 +550,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Price ($)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Reverse Variant Price ($)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Rarity</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Pull Rate (1/X)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Price ($)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Variant Price ($)</t>
-        </is>
-      </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Copies In Pack</t>
@@ -571,27 +575,37 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Category Sums</t>
+          <t>EV Total</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Category Evs</t>
+          <t>EV Breakdown</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Current Market Pack Price</t>
+          <t>Pack Price</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Current ETB Market Price</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Current Market Price of ETB Promo Card</t>
+          <t>ETB Price</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>ETB Promo Card Price</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Booster Box Price</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Special Collection Price</t>
         </is>
       </c>
     </row>
@@ -601,29 +615,26 @@
           <t>Abra</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F2" s="3">
-        <f>IF(B2="common", 4, IF(B2="uncommon", 3, IF(B2="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
-      <c r="G2">
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3">
         <f>SUM(H2:H10)</f>
         <v/>
       </c>
-      <c r="H2">
+      <c r="H2" s="3">
         <f>SUMPRODUCT((B2:B217="Common") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
@@ -636,6 +647,12 @@
       <c r="K2" s="3" t="n">
         <v>5.6</v>
       </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="Q2" s="3" t="n"/>
+      <c r="R2" s="3" t="n"/>
+      <c r="S2" s="3" t="n"/>
+      <c r="T2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -643,28 +660,34 @@
           <t>Aerodactyl</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="F3" s="3">
-        <f>IF(B3="common", 4, IF(B3="uncommon", 3, IF(B3="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
-      <c r="H3">
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3">
         <f>SUMPRODUCT((B2:B217="Uncommon") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -672,26 +695,32 @@
           <t>Alakazam ex - 065/165</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>double rare</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3">
-        <f>IF(B4="common", 4, IF(B4="uncommon", 3, IF(B4="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
-      <c r="H4">
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3">
         <f>0.792892156862745*SUMPRODUCT((B2:B217="Rare") * D2:D217 / C2:C217)</f>
         <v/>
       </c>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -699,26 +728,32 @@
           <t>Alakazam ex - 188/165</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3">
-        <f>IF(B5="common", 4, IF(B5="uncommon", 3, IF(B5="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
-      <c r="H5">
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3">
         <f>1.88541666666666* SUMPRODUCT((C2:C217&lt;&gt;"") * (E2:E217&lt;&gt;"") * (E2:E217 / C2:C217))</f>
         <v/>
       </c>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -726,26 +761,32 @@
           <t>Alakazam ex - 201/165</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="3" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>special illustration rare</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>43.91</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3">
-        <f>IF(B6="common", 4, IF(B6="uncommon", 3, IF(B6="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
-      <c r="H6">
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3">
         <f>SUMPRODUCT((B2:B217="Illustration Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -753,28 +794,34 @@
           <t>Antique Dome Fossil</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="F7" s="3">
-        <f>IF(B7="common", 4, IF(B7="uncommon", 3, IF(B7="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
-      <c r="H7">
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3">
         <f>SUMPRODUCT((B2:B217="Special Illustration Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -782,28 +829,34 @@
           <t>Antique Helix Fossil</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D8" s="3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F8" s="3">
-        <f>IF(B8="common", 4, IF(B8="uncommon", 3, IF(B8="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
-      <c r="H8">
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3">
         <f>SUMPRODUCT((B2:B217="Double Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -811,28 +864,34 @@
           <t>Antique Old Amber</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="F9" s="3">
-        <f>IF(B9="common", 4, IF(B9="uncommon", 3, IF(B9="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
-      <c r="H9">
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3">
         <f>SUMPRODUCT((B2:B217="Hyper Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -840,26 +899,32 @@
           <t>Arbok ex - 024/165</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>double rare</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3">
-        <f>IF(B10="common", 4, IF(B10="uncommon", 3, IF(B10="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
-      <c r="H10">
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3">
         <f>SUMPRODUCT((B2:B217="Ultra Rare") * D2:D217 * F2:F217 / C2:C217)</f>
         <v/>
       </c>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="3" t="n"/>
+      <c r="T10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -867,22 +932,29 @@
           <t>Arbok ex - 185/165</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="3" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3">
-        <f>IF(B11="common", 4, IF(B11="uncommon", 3, IF(B11="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -890,24 +962,31 @@
           <t>Arcanine</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F12" s="3">
-        <f>IF(B12="common", 4, IF(B12="uncommon", 3, IF(B12="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="Q12" s="3" t="n"/>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -915,24 +994,31 @@
           <t>Articuno</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D13" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="F13" s="3">
-        <f>IF(B13="common", 4, IF(B13="uncommon", 3, IF(B13="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -940,22 +1026,29 @@
           <t>Basic Psychic Energy - 207/165</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="3" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>hyper rare</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3">
-        <f>IF(B14="common", 4, IF(B14="uncommon", 3, IF(B14="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="Q14" s="3" t="n"/>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="3" t="n"/>
+      <c r="T14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -963,24 +1056,31 @@
           <t>Beedrill</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F15" s="3">
-        <f>IF(B15="common", 4, IF(B15="uncommon", 3, IF(B15="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="Q15" s="3" t="n"/>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="3" t="n"/>
+      <c r="T15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -988,24 +1088,31 @@
           <t>Bellsprout</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F16" s="3">
-        <f>IF(B16="common", 4, IF(B16="uncommon", 3, IF(B16="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="Q16" s="3" t="n"/>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1013,24 +1120,31 @@
           <t>Big Air Balloon</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D17" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="F17" s="3">
-        <f>IF(B17="common", 4, IF(B17="uncommon", 3, IF(B17="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="Q17" s="3" t="n"/>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1038,24 +1152,31 @@
           <t>Bill's Transfer - 156/165</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="F18" s="3">
-        <f>IF(B18="common", 4, IF(B18="uncommon", 3, IF(B18="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="Q18" s="3" t="n"/>
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" s="3" t="n"/>
+      <c r="T18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1063,22 +1184,29 @@
           <t>Bill's Transfer - 194/165</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D19" s="3" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3">
-        <f>IF(B19="common", 4, IF(B19="uncommon", 3, IF(B19="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="Q19" s="3" t="n"/>
+      <c r="R19" s="3" t="n"/>
+      <c r="S19" s="3" t="n"/>
+      <c r="T19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1086,22 +1214,29 @@
           <t>Blastoise ex - 009/165</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>double rare</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3">
-        <f>IF(B20="common", 4, IF(B20="uncommon", 3, IF(B20="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="Q20" s="3" t="n"/>
+      <c r="R20" s="3" t="n"/>
+      <c r="S20" s="3" t="n"/>
+      <c r="T20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1109,22 +1244,29 @@
           <t>Blastoise ex - 184/165</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="3" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3">
-        <f>IF(B21="common", 4, IF(B21="uncommon", 3, IF(B21="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
+      <c r="R21" s="3" t="n"/>
+      <c r="S21" s="3" t="n"/>
+      <c r="T21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1132,22 +1274,29 @@
           <t>Blastoise ex - 200/165</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="3" t="n">
+        <v>71.38</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>special illustration rare</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3">
-        <f>IF(B22="common", 4, IF(B22="uncommon", 3, IF(B22="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="Q22" s="3" t="n"/>
+      <c r="R22" s="3" t="n"/>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1155,24 +1304,31 @@
           <t>Bulbasaur - 001/165</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D23" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F23" s="3">
-        <f>IF(B23="common", 4, IF(B23="uncommon", 3, IF(B23="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
+      <c r="T23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1180,22 +1336,29 @@
           <t>Bulbasaur - 166/165</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="3" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>37.01</v>
-      </c>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3">
-        <f>IF(B24="common", 4, IF(B24="uncommon", 3, IF(B24="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="Q24" s="3" t="n"/>
+      <c r="R24" s="3" t="n"/>
+      <c r="S24" s="3" t="n"/>
+      <c r="T24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1203,24 +1366,31 @@
           <t>Butterfree</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D25" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F25" s="3">
-        <f>IF(B25="common", 4, IF(B25="uncommon", 3, IF(B25="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="Q25" s="3" t="n"/>
+      <c r="R25" s="3" t="n"/>
+      <c r="S25" s="3" t="n"/>
+      <c r="T25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1228,24 +1398,31 @@
           <t>Caterpie - 010/165</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F26" s="3">
-        <f>IF(B26="common", 4, IF(B26="uncommon", 3, IF(B26="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
+      <c r="Q26" s="3" t="n"/>
+      <c r="R26" s="3" t="n"/>
+      <c r="S26" s="3" t="n"/>
+      <c r="T26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1253,22 +1430,29 @@
           <t>Caterpie - 172/165</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="3" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D27" s="3" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3">
-        <f>IF(B27="common", 4, IF(B27="uncommon", 3, IF(B27="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="Q27" s="3" t="n"/>
+      <c r="R27" s="3" t="n"/>
+      <c r="S27" s="3" t="n"/>
+      <c r="T27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1276,24 +1460,31 @@
           <t>Chansey</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D28" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="F28" s="3">
-        <f>IF(B28="common", 4, IF(B28="uncommon", 3, IF(B28="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="Q28" s="3" t="n"/>
+      <c r="R28" s="3" t="n"/>
+      <c r="S28" s="3" t="n"/>
+      <c r="T28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1301,22 +1492,29 @@
           <t>Charizard ex - 006/165</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="3" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>double rare</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D29" s="3" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3">
-        <f>IF(B29="common", 4, IF(B29="uncommon", 3, IF(B29="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="Q29" s="3" t="n"/>
+      <c r="R29" s="3" t="n"/>
+      <c r="S29" s="3" t="n"/>
+      <c r="T29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1324,22 +1522,29 @@
           <t>Charizard ex - 183/165</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="3" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D30" s="3" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="3">
-        <f>IF(B30="common", 4, IF(B30="uncommon", 3, IF(B30="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="Q30" s="3" t="n"/>
+      <c r="R30" s="3" t="n"/>
+      <c r="S30" s="3" t="n"/>
+      <c r="T30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1347,22 +1552,29 @@
           <t>Charizard ex - 199/165</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="3" t="n">
+        <v>212.94</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>special illustration rare</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>214.14</v>
-      </c>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3">
-        <f>IF(B31="common", 4, IF(B31="uncommon", 3, IF(B31="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="Q31" s="3" t="n"/>
+      <c r="R31" s="3" t="n"/>
+      <c r="S31" s="3" t="n"/>
+      <c r="T31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1370,24 +1582,31 @@
           <t>Charmander - 004/165</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="F32" s="3">
-        <f>IF(B32="common", 4, IF(B32="uncommon", 3, IF(B32="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
+      <c r="Q32" s="3" t="n"/>
+      <c r="R32" s="3" t="n"/>
+      <c r="S32" s="3" t="n"/>
+      <c r="T32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1395,22 +1614,29 @@
           <t>Charmander - 168/165</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="3" t="n">
+        <v>51.89</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D33" s="3" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3">
-        <f>IF(B33="common", 4, IF(B33="uncommon", 3, IF(B33="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="Q33" s="3" t="n"/>
+      <c r="R33" s="3" t="n"/>
+      <c r="S33" s="3" t="n"/>
+      <c r="T33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1418,24 +1644,31 @@
           <t>Charmeleon - 005/165</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D34" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="F34" s="3">
-        <f>IF(B34="common", 4, IF(B34="uncommon", 3, IF(B34="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n"/>
+      <c r="Q34" s="3" t="n"/>
+      <c r="R34" s="3" t="n"/>
+      <c r="S34" s="3" t="n"/>
+      <c r="T34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1443,22 +1676,29 @@
           <t>Charmeleon - 169/165</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="3" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D35" s="3" t="n">
-        <v>34.16</v>
-      </c>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3">
-        <f>IF(B35="common", 4, IF(B35="uncommon", 3, IF(B35="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="Q35" s="3" t="n"/>
+      <c r="R35" s="3" t="n"/>
+      <c r="S35" s="3" t="n"/>
+      <c r="T35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1466,24 +1706,31 @@
           <t>Clefable</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D36" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="F36" s="3">
-        <f>IF(B36="common", 4, IF(B36="uncommon", 3, IF(B36="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="n"/>
+      <c r="L36" s="3" t="n"/>
+      <c r="M36" s="3" t="n"/>
+      <c r="Q36" s="3" t="n"/>
+      <c r="R36" s="3" t="n"/>
+      <c r="S36" s="3" t="n"/>
+      <c r="T36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1491,24 +1738,31 @@
           <t>Clefairy</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D37" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F37" s="3">
-        <f>IF(B37="common", 4, IF(B37="uncommon", 3, IF(B37="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
+      <c r="Q37" s="3" t="n"/>
+      <c r="R37" s="3" t="n"/>
+      <c r="S37" s="3" t="n"/>
+      <c r="T37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1516,24 +1770,31 @@
           <t>Cloyster</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D38" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F38" s="3">
-        <f>IF(B38="common", 4, IF(B38="uncommon", 3, IF(B38="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+      <c r="I38" s="3" t="n"/>
+      <c r="J38" s="3" t="n"/>
+      <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="n"/>
+      <c r="Q38" s="3" t="n"/>
+      <c r="R38" s="3" t="n"/>
+      <c r="S38" s="3" t="n"/>
+      <c r="T38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1541,24 +1802,31 @@
           <t>Cubone</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D39" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F39" s="3">
-        <f>IF(B39="common", 4, IF(B39="uncommon", 3, IF(B39="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="Q39" s="3" t="n"/>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="3" t="n"/>
+      <c r="T39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1566,24 +1834,31 @@
           <t>Cycling Road</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D40" s="3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="F40" s="3">
-        <f>IF(B40="common", 4, IF(B40="uncommon", 3, IF(B40="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="3" t="n"/>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="n"/>
+      <c r="Q40" s="3" t="n"/>
+      <c r="R40" s="3" t="n"/>
+      <c r="S40" s="3" t="n"/>
+      <c r="T40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1591,24 +1866,31 @@
           <t>Daisy's Help - 158/165</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D41" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="F41" s="3">
-        <f>IF(B41="common", 4, IF(B41="uncommon", 3, IF(B41="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="Q41" s="3" t="n"/>
+      <c r="R41" s="3" t="n"/>
+      <c r="S41" s="3" t="n"/>
+      <c r="T41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -1616,22 +1898,29 @@
           <t>Daisy's Help - 195/165</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D42" s="3" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3">
-        <f>IF(B42="common", 4, IF(B42="uncommon", 3, IF(B42="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="L42" s="3" t="n"/>
+      <c r="M42" s="3" t="n"/>
+      <c r="Q42" s="3" t="n"/>
+      <c r="R42" s="3" t="n"/>
+      <c r="S42" s="3" t="n"/>
+      <c r="T42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1639,24 +1928,31 @@
           <t>Dewgong</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D43" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F43" s="3">
-        <f>IF(B43="common", 4, IF(B43="uncommon", 3, IF(B43="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="L43" s="3" t="n"/>
+      <c r="M43" s="3" t="n"/>
+      <c r="Q43" s="3" t="n"/>
+      <c r="R43" s="3" t="n"/>
+      <c r="S43" s="3" t="n"/>
+      <c r="T43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1664,24 +1960,31 @@
           <t>Diglett</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D44" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F44" s="3">
-        <f>IF(B44="common", 4, IF(B44="uncommon", 3, IF(B44="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="n"/>
+      <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
+      <c r="R44" s="3" t="n"/>
+      <c r="S44" s="3" t="n"/>
+      <c r="T44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1689,24 +1992,31 @@
           <t>Ditto</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D45" s="3" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="F45" s="3">
-        <f>IF(B45="common", 4, IF(B45="uncommon", 3, IF(B45="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="3" t="n"/>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n"/>
+      <c r="Q45" s="3" t="n"/>
+      <c r="R45" s="3" t="n"/>
+      <c r="S45" s="3" t="n"/>
+      <c r="T45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1714,22 +2024,29 @@
           <t>Ditto - 132/165 (Non-Holo)</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D46" s="3" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3">
-        <f>IF(B46="common", 4, IF(B46="uncommon", 3, IF(B46="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="n"/>
+      <c r="L46" s="3" t="n"/>
+      <c r="M46" s="3" t="n"/>
+      <c r="Q46" s="3" t="n"/>
+      <c r="R46" s="3" t="n"/>
+      <c r="S46" s="3" t="n"/>
+      <c r="T46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1737,24 +2054,31 @@
           <t>Dodrio</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D47" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="F47" s="3">
-        <f>IF(B47="common", 4, IF(B47="uncommon", 3, IF(B47="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="n"/>
+      <c r="L47" s="3" t="n"/>
+      <c r="M47" s="3" t="n"/>
+      <c r="Q47" s="3" t="n"/>
+      <c r="R47" s="3" t="n"/>
+      <c r="S47" s="3" t="n"/>
+      <c r="T47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1762,24 +2086,31 @@
           <t>Doduo</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D48" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="F48" s="3">
-        <f>IF(B48="common", 4, IF(B48="uncommon", 3, IF(B48="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="3" t="n"/>
+      <c r="L48" s="3" t="n"/>
+      <c r="M48" s="3" t="n"/>
+      <c r="Q48" s="3" t="n"/>
+      <c r="R48" s="3" t="n"/>
+      <c r="S48" s="3" t="n"/>
+      <c r="T48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -1787,24 +2118,31 @@
           <t>Dragonair - 148/165</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D49" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="F49" s="3">
-        <f>IF(B49="common", 4, IF(B49="uncommon", 3, IF(B49="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+      <c r="I49" s="3" t="n"/>
+      <c r="J49" s="3" t="n"/>
+      <c r="L49" s="3" t="n"/>
+      <c r="M49" s="3" t="n"/>
+      <c r="Q49" s="3" t="n"/>
+      <c r="R49" s="3" t="n"/>
+      <c r="S49" s="3" t="n"/>
+      <c r="T49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -1812,22 +2150,29 @@
           <t>Dragonair - 181/165</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="3" t="n">
+        <v>24.61</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr"/>
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D50" s="3" t="n">
-        <v>25.53</v>
-      </c>
-      <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" s="3">
-        <f>IF(B50="common", 4, IF(B50="uncommon", 3, IF(B50="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+      <c r="I50" s="3" t="n"/>
+      <c r="J50" s="3" t="n"/>
+      <c r="L50" s="3" t="n"/>
+      <c r="M50" s="3" t="n"/>
+      <c r="Q50" s="3" t="n"/>
+      <c r="R50" s="3" t="n"/>
+      <c r="S50" s="3" t="n"/>
+      <c r="T50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1835,24 +2180,31 @@
           <t>Dragonite</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D51" s="3" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F51" s="3">
-        <f>IF(B51="common", 4, IF(B51="uncommon", 3, IF(B51="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="n"/>
+      <c r="L51" s="3" t="n"/>
+      <c r="M51" s="3" t="n"/>
+      <c r="Q51" s="3" t="n"/>
+      <c r="R51" s="3" t="n"/>
+      <c r="S51" s="3" t="n"/>
+      <c r="T51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1860,24 +2212,31 @@
           <t>Dratini</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D52" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F52" s="3">
-        <f>IF(B52="common", 4, IF(B52="uncommon", 3, IF(B52="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="3" t="n"/>
+      <c r="L52" s="3" t="n"/>
+      <c r="M52" s="3" t="n"/>
+      <c r="Q52" s="3" t="n"/>
+      <c r="R52" s="3" t="n"/>
+      <c r="S52" s="3" t="n"/>
+      <c r="T52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1885,24 +2244,31 @@
           <t>Drowzee</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D53" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F53" s="3">
-        <f>IF(B53="common", 4, IF(B53="uncommon", 3, IF(B53="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
+      <c r="J53" s="3" t="n"/>
+      <c r="L53" s="3" t="n"/>
+      <c r="M53" s="3" t="n"/>
+      <c r="Q53" s="3" t="n"/>
+      <c r="R53" s="3" t="n"/>
+      <c r="S53" s="3" t="n"/>
+      <c r="T53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1910,24 +2276,31 @@
           <t>Dugtrio</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D54" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F54" s="3">
-        <f>IF(B54="common", 4, IF(B54="uncommon", 3, IF(B54="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="n"/>
+      <c r="L54" s="3" t="n"/>
+      <c r="M54" s="3" t="n"/>
+      <c r="Q54" s="3" t="n"/>
+      <c r="R54" s="3" t="n"/>
+      <c r="S54" s="3" t="n"/>
+      <c r="T54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1935,24 +2308,31 @@
           <t>Eevee</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D55" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F55" s="3">
-        <f>IF(B55="common", 4, IF(B55="uncommon", 3, IF(B55="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="n"/>
+      <c r="L55" s="3" t="n"/>
+      <c r="M55" s="3" t="n"/>
+      <c r="Q55" s="3" t="n"/>
+      <c r="R55" s="3" t="n"/>
+      <c r="S55" s="3" t="n"/>
+      <c r="T55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -1960,24 +2340,31 @@
           <t>Ekans</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D56" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="F56" s="3">
-        <f>IF(B56="common", 4, IF(B56="uncommon", 3, IF(B56="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="3" t="n"/>
+      <c r="L56" s="3" t="n"/>
+      <c r="M56" s="3" t="n"/>
+      <c r="Q56" s="3" t="n"/>
+      <c r="R56" s="3" t="n"/>
+      <c r="S56" s="3" t="n"/>
+      <c r="T56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -1985,24 +2372,31 @@
           <t>Electabuzz</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D57" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="F57" s="3">
-        <f>IF(B57="common", 4, IF(B57="uncommon", 3, IF(B57="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" s="3" t="n"/>
+      <c r="L57" s="3" t="n"/>
+      <c r="M57" s="3" t="n"/>
+      <c r="Q57" s="3" t="n"/>
+      <c r="R57" s="3" t="n"/>
+      <c r="S57" s="3" t="n"/>
+      <c r="T57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -2010,24 +2404,31 @@
           <t>Electrode</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D58" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="F58" s="3">
-        <f>IF(B58="common", 4, IF(B58="uncommon", 3, IF(B58="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+      <c r="I58" s="3" t="n"/>
+      <c r="J58" s="3" t="n"/>
+      <c r="L58" s="3" t="n"/>
+      <c r="M58" s="3" t="n"/>
+      <c r="Q58" s="3" t="n"/>
+      <c r="R58" s="3" t="n"/>
+      <c r="S58" s="3" t="n"/>
+      <c r="T58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -2035,24 +2436,31 @@
           <t>Energy Sticker</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="E59" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D59" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="F59" s="3">
-        <f>IF(B59="common", 4, IF(B59="uncommon", 3, IF(B59="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+      <c r="I59" s="3" t="n"/>
+      <c r="J59" s="3" t="n"/>
+      <c r="L59" s="3" t="n"/>
+      <c r="M59" s="3" t="n"/>
+      <c r="Q59" s="3" t="n"/>
+      <c r="R59" s="3" t="n"/>
+      <c r="S59" s="3" t="n"/>
+      <c r="T59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -2060,24 +2468,31 @@
           <t>Erika's Invitation - 160/165</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="E60" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D60" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F60" s="3">
-        <f>IF(B60="common", 4, IF(B60="uncommon", 3, IF(B60="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+      <c r="I60" s="3" t="n"/>
+      <c r="J60" s="3" t="n"/>
+      <c r="L60" s="3" t="n"/>
+      <c r="M60" s="3" t="n"/>
+      <c r="Q60" s="3" t="n"/>
+      <c r="R60" s="3" t="n"/>
+      <c r="S60" s="3" t="n"/>
+      <c r="T60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -2085,22 +2500,29 @@
           <t>Erika's Invitation - 196/165</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="3" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="E61" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D61" s="3" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3">
-        <f>IF(B61="common", 4, IF(B61="uncommon", 3, IF(B61="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
+      <c r="J61" s="3" t="n"/>
+      <c r="L61" s="3" t="n"/>
+      <c r="M61" s="3" t="n"/>
+      <c r="Q61" s="3" t="n"/>
+      <c r="R61" s="3" t="n"/>
+      <c r="S61" s="3" t="n"/>
+      <c r="T61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -2108,22 +2530,29 @@
           <t>Erika's Invitation - 203/165</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="3" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>special illustration rare</t>
         </is>
       </c>
-      <c r="C62" s="3" t="n">
+      <c r="E62" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="D62" s="3" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="E62" s="3" t="inlineStr"/>
-      <c r="F62" s="3">
-        <f>IF(B62="common", 4, IF(B62="uncommon", 3, IF(B62="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="3" t="n"/>
+      <c r="J62" s="3" t="n"/>
+      <c r="L62" s="3" t="n"/>
+      <c r="M62" s="3" t="n"/>
+      <c r="Q62" s="3" t="n"/>
+      <c r="R62" s="3" t="n"/>
+      <c r="S62" s="3" t="n"/>
+      <c r="T62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -2131,24 +2560,31 @@
           <t>Exeggcute</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="E63" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D63" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F63" s="3">
-        <f>IF(B63="common", 4, IF(B63="uncommon", 3, IF(B63="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+      <c r="I63" s="3" t="n"/>
+      <c r="J63" s="3" t="n"/>
+      <c r="L63" s="3" t="n"/>
+      <c r="M63" s="3" t="n"/>
+      <c r="Q63" s="3" t="n"/>
+      <c r="R63" s="3" t="n"/>
+      <c r="S63" s="3" t="n"/>
+      <c r="T63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -2156,24 +2592,31 @@
           <t>Exeggutor</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C64" s="3" t="n">
+      <c r="E64" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D64" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="F64" s="3">
-        <f>IF(B64="common", 4, IF(B64="uncommon", 3, IF(B64="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+      <c r="I64" s="3" t="n"/>
+      <c r="J64" s="3" t="n"/>
+      <c r="L64" s="3" t="n"/>
+      <c r="M64" s="3" t="n"/>
+      <c r="Q64" s="3" t="n"/>
+      <c r="R64" s="3" t="n"/>
+      <c r="S64" s="3" t="n"/>
+      <c r="T64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2181,24 +2624,31 @@
           <t>Farfetch'd</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C65" s="3" t="n">
+      <c r="E65" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D65" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F65" s="3">
-        <f>IF(B65="common", 4, IF(B65="uncommon", 3, IF(B65="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+      <c r="I65" s="3" t="n"/>
+      <c r="J65" s="3" t="n"/>
+      <c r="L65" s="3" t="n"/>
+      <c r="M65" s="3" t="n"/>
+      <c r="Q65" s="3" t="n"/>
+      <c r="R65" s="3" t="n"/>
+      <c r="S65" s="3" t="n"/>
+      <c r="T65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -2206,24 +2656,31 @@
           <t>Fearow</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="E66" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D66" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F66" s="3">
-        <f>IF(B66="common", 4, IF(B66="uncommon", 3, IF(B66="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+      <c r="I66" s="3" t="n"/>
+      <c r="J66" s="3" t="n"/>
+      <c r="L66" s="3" t="n"/>
+      <c r="M66" s="3" t="n"/>
+      <c r="Q66" s="3" t="n"/>
+      <c r="R66" s="3" t="n"/>
+      <c r="S66" s="3" t="n"/>
+      <c r="T66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2231,24 +2688,31 @@
           <t>Flareon</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C67" s="3" t="n">
+      <c r="E67" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D67" s="3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="F67" s="3">
-        <f>IF(B67="common", 4, IF(B67="uncommon", 3, IF(B67="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+      <c r="I67" s="3" t="n"/>
+      <c r="J67" s="3" t="n"/>
+      <c r="L67" s="3" t="n"/>
+      <c r="M67" s="3" t="n"/>
+      <c r="Q67" s="3" t="n"/>
+      <c r="R67" s="3" t="n"/>
+      <c r="S67" s="3" t="n"/>
+      <c r="T67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -2256,24 +2720,31 @@
           <t>Gastly</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="E68" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D68" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F68" s="3">
-        <f>IF(B68="common", 4, IF(B68="uncommon", 3, IF(B68="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+      <c r="I68" s="3" t="n"/>
+      <c r="J68" s="3" t="n"/>
+      <c r="L68" s="3" t="n"/>
+      <c r="M68" s="3" t="n"/>
+      <c r="Q68" s="3" t="n"/>
+      <c r="R68" s="3" t="n"/>
+      <c r="S68" s="3" t="n"/>
+      <c r="T68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -2281,24 +2752,31 @@
           <t>Gengar</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="E69" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D69" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="F69" s="3">
-        <f>IF(B69="common", 4, IF(B69="uncommon", 3, IF(B69="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+      <c r="I69" s="3" t="n"/>
+      <c r="J69" s="3" t="n"/>
+      <c r="L69" s="3" t="n"/>
+      <c r="M69" s="3" t="n"/>
+      <c r="Q69" s="3" t="n"/>
+      <c r="R69" s="3" t="n"/>
+      <c r="S69" s="3" t="n"/>
+      <c r="T69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -2306,24 +2784,31 @@
           <t>Geodude</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="E70" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D70" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F70" s="3">
-        <f>IF(B70="common", 4, IF(B70="uncommon", 3, IF(B70="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+      <c r="I70" s="3" t="n"/>
+      <c r="J70" s="3" t="n"/>
+      <c r="L70" s="3" t="n"/>
+      <c r="M70" s="3" t="n"/>
+      <c r="Q70" s="3" t="n"/>
+      <c r="R70" s="3" t="n"/>
+      <c r="S70" s="3" t="n"/>
+      <c r="T70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -2331,24 +2816,31 @@
           <t>Giovanni's Charisma - 161/165</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C71" s="3" t="n">
+      <c r="E71" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D71" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="F71" s="3">
-        <f>IF(B71="common", 4, IF(B71="uncommon", 3, IF(B71="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+      <c r="I71" s="3" t="n"/>
+      <c r="J71" s="3" t="n"/>
+      <c r="L71" s="3" t="n"/>
+      <c r="M71" s="3" t="n"/>
+      <c r="Q71" s="3" t="n"/>
+      <c r="R71" s="3" t="n"/>
+      <c r="S71" s="3" t="n"/>
+      <c r="T71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -2356,22 +2848,29 @@
           <t>Giovanni's Charisma - 197/165</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" s="3" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr"/>
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C72" s="3" t="n">
+      <c r="E72" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D72" s="3" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E72" s="3" t="inlineStr"/>
-      <c r="F72" s="3">
-        <f>IF(B72="common", 4, IF(B72="uncommon", 3, IF(B72="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+      <c r="I72" s="3" t="n"/>
+      <c r="J72" s="3" t="n"/>
+      <c r="L72" s="3" t="n"/>
+      <c r="M72" s="3" t="n"/>
+      <c r="Q72" s="3" t="n"/>
+      <c r="R72" s="3" t="n"/>
+      <c r="S72" s="3" t="n"/>
+      <c r="T72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -2379,22 +2878,29 @@
           <t>Giovanni's Charisma - 204/165</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" s="3" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>special illustration rare</t>
         </is>
       </c>
-      <c r="C73" s="3" t="n">
+      <c r="E73" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="D73" s="3" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="E73" s="3" t="inlineStr"/>
-      <c r="F73" s="3">
-        <f>IF(B73="common", 4, IF(B73="uncommon", 3, IF(B73="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+      <c r="I73" s="3" t="n"/>
+      <c r="J73" s="3" t="n"/>
+      <c r="L73" s="3" t="n"/>
+      <c r="M73" s="3" t="n"/>
+      <c r="Q73" s="3" t="n"/>
+      <c r="R73" s="3" t="n"/>
+      <c r="S73" s="3" t="n"/>
+      <c r="T73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -2402,24 +2908,31 @@
           <t>Gloom</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C74" s="3" t="n">
+      <c r="E74" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D74" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F74" s="3">
-        <f>IF(B74="common", 4, IF(B74="uncommon", 3, IF(B74="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="3" t="n"/>
+      <c r="L74" s="3" t="n"/>
+      <c r="M74" s="3" t="n"/>
+      <c r="Q74" s="3" t="n"/>
+      <c r="R74" s="3" t="n"/>
+      <c r="S74" s="3" t="n"/>
+      <c r="T74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2427,24 +2940,31 @@
           <t>Golbat</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C75" s="3" t="n">
+      <c r="E75" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D75" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F75" s="3">
-        <f>IF(B75="common", 4, IF(B75="uncommon", 3, IF(B75="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="3" t="n"/>
+      <c r="J75" s="3" t="n"/>
+      <c r="L75" s="3" t="n"/>
+      <c r="M75" s="3" t="n"/>
+      <c r="Q75" s="3" t="n"/>
+      <c r="R75" s="3" t="n"/>
+      <c r="S75" s="3" t="n"/>
+      <c r="T75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -2452,24 +2972,31 @@
           <t>Goldeen</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C76" s="3" t="n">
+      <c r="E76" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D76" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F76" s="3">
-        <f>IF(B76="common", 4, IF(B76="uncommon", 3, IF(B76="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+      <c r="I76" s="3" t="n"/>
+      <c r="J76" s="3" t="n"/>
+      <c r="L76" s="3" t="n"/>
+      <c r="M76" s="3" t="n"/>
+      <c r="Q76" s="3" t="n"/>
+      <c r="R76" s="3" t="n"/>
+      <c r="S76" s="3" t="n"/>
+      <c r="T76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -2477,24 +3004,31 @@
           <t>Golduck</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="E77" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D77" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F77" s="3">
-        <f>IF(B77="common", 4, IF(B77="uncommon", 3, IF(B77="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+      <c r="I77" s="3" t="n"/>
+      <c r="J77" s="3" t="n"/>
+      <c r="L77" s="3" t="n"/>
+      <c r="M77" s="3" t="n"/>
+      <c r="Q77" s="3" t="n"/>
+      <c r="R77" s="3" t="n"/>
+      <c r="S77" s="3" t="n"/>
+      <c r="T77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -2502,22 +3036,29 @@
           <t>Golem ex - 076/165</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" s="3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="C78" s="3" t="inlineStr"/>
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>double rare</t>
         </is>
       </c>
-      <c r="C78" s="3" t="n">
+      <c r="E78" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D78" s="3" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E78" s="3" t="inlineStr"/>
-      <c r="F78" s="3">
-        <f>IF(B78="common", 4, IF(B78="uncommon", 3, IF(B78="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+      <c r="I78" s="3" t="n"/>
+      <c r="J78" s="3" t="n"/>
+      <c r="L78" s="3" t="n"/>
+      <c r="M78" s="3" t="n"/>
+      <c r="Q78" s="3" t="n"/>
+      <c r="R78" s="3" t="n"/>
+      <c r="S78" s="3" t="n"/>
+      <c r="T78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -2525,22 +3066,29 @@
           <t>Golem ex - 189/165</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" s="3" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="C79" s="3" t="inlineStr"/>
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C79" s="3" t="n">
+      <c r="E79" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D79" s="3" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="E79" s="3" t="inlineStr"/>
-      <c r="F79" s="3">
-        <f>IF(B79="common", 4, IF(B79="uncommon", 3, IF(B79="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="L79" s="3" t="n"/>
+      <c r="M79" s="3" t="n"/>
+      <c r="Q79" s="3" t="n"/>
+      <c r="R79" s="3" t="n"/>
+      <c r="S79" s="3" t="n"/>
+      <c r="T79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -2548,24 +3096,31 @@
           <t>Grabber</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B80" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C80" s="3" t="n">
+      <c r="E80" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D80" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="F80" s="3">
-        <f>IF(B80="common", 4, IF(B80="uncommon", 3, IF(B80="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+      <c r="I80" s="3" t="n"/>
+      <c r="J80" s="3" t="n"/>
+      <c r="L80" s="3" t="n"/>
+      <c r="M80" s="3" t="n"/>
+      <c r="Q80" s="3" t="n"/>
+      <c r="R80" s="3" t="n"/>
+      <c r="S80" s="3" t="n"/>
+      <c r="T80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -2573,24 +3128,31 @@
           <t>Graveler</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B81" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C81" s="3" t="n">
+      <c r="E81" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D81" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F81" s="3">
-        <f>IF(B81="common", 4, IF(B81="uncommon", 3, IF(B81="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F81" s="3" t="n"/>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+      <c r="I81" s="3" t="n"/>
+      <c r="J81" s="3" t="n"/>
+      <c r="L81" s="3" t="n"/>
+      <c r="M81" s="3" t="n"/>
+      <c r="Q81" s="3" t="n"/>
+      <c r="R81" s="3" t="n"/>
+      <c r="S81" s="3" t="n"/>
+      <c r="T81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -2598,24 +3160,31 @@
           <t>Grimer</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B82" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C82" s="3" t="n">
+      <c r="E82" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D82" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F82" s="3">
-        <f>IF(B82="common", 4, IF(B82="uncommon", 3, IF(B82="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F82" s="3" t="n"/>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+      <c r="I82" s="3" t="n"/>
+      <c r="J82" s="3" t="n"/>
+      <c r="L82" s="3" t="n"/>
+      <c r="M82" s="3" t="n"/>
+      <c r="Q82" s="3" t="n"/>
+      <c r="R82" s="3" t="n"/>
+      <c r="S82" s="3" t="n"/>
+      <c r="T82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -2623,24 +3192,31 @@
           <t>Growlithe</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B83" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C83" s="3" t="n">
+      <c r="E83" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D83" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F83" s="3">
-        <f>IF(B83="common", 4, IF(B83="uncommon", 3, IF(B83="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F83" s="3" t="n"/>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+      <c r="I83" s="3" t="n"/>
+      <c r="J83" s="3" t="n"/>
+      <c r="L83" s="3" t="n"/>
+      <c r="M83" s="3" t="n"/>
+      <c r="Q83" s="3" t="n"/>
+      <c r="R83" s="3" t="n"/>
+      <c r="S83" s="3" t="n"/>
+      <c r="T83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -2648,24 +3224,31 @@
           <t>Gyarados</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B84" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C84" s="3" t="n">
+      <c r="E84" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D84" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F84" s="3">
-        <f>IF(B84="common", 4, IF(B84="uncommon", 3, IF(B84="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F84" s="3" t="n"/>
+      <c r="G84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
+      <c r="I84" s="3" t="n"/>
+      <c r="J84" s="3" t="n"/>
+      <c r="L84" s="3" t="n"/>
+      <c r="M84" s="3" t="n"/>
+      <c r="Q84" s="3" t="n"/>
+      <c r="R84" s="3" t="n"/>
+      <c r="S84" s="3" t="n"/>
+      <c r="T84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -2673,24 +3256,31 @@
           <t>Haunter</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C85" s="3" t="n">
+      <c r="E85" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D85" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F85" s="3">
-        <f>IF(B85="common", 4, IF(B85="uncommon", 3, IF(B85="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F85" s="3" t="n"/>
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="3" t="n"/>
+      <c r="I85" s="3" t="n"/>
+      <c r="J85" s="3" t="n"/>
+      <c r="L85" s="3" t="n"/>
+      <c r="M85" s="3" t="n"/>
+      <c r="Q85" s="3" t="n"/>
+      <c r="R85" s="3" t="n"/>
+      <c r="S85" s="3" t="n"/>
+      <c r="T85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -2698,24 +3288,31 @@
           <t>Hitmonchan</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B86" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C86" s="3" t="n">
+      <c r="E86" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D86" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F86" s="3">
-        <f>IF(B86="common", 4, IF(B86="uncommon", 3, IF(B86="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F86" s="3" t="n"/>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
+      <c r="I86" s="3" t="n"/>
+      <c r="J86" s="3" t="n"/>
+      <c r="L86" s="3" t="n"/>
+      <c r="M86" s="3" t="n"/>
+      <c r="Q86" s="3" t="n"/>
+      <c r="R86" s="3" t="n"/>
+      <c r="S86" s="3" t="n"/>
+      <c r="T86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -2723,24 +3320,31 @@
           <t>Hitmonlee</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B87" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C87" s="3" t="n">
+      <c r="E87" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D87" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="F87" s="3">
-        <f>IF(B87="common", 4, IF(B87="uncommon", 3, IF(B87="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F87" s="3" t="n"/>
+      <c r="G87" s="3" t="n"/>
+      <c r="H87" s="3" t="n"/>
+      <c r="I87" s="3" t="n"/>
+      <c r="J87" s="3" t="n"/>
+      <c r="L87" s="3" t="n"/>
+      <c r="M87" s="3" t="n"/>
+      <c r="Q87" s="3" t="n"/>
+      <c r="R87" s="3" t="n"/>
+      <c r="S87" s="3" t="n"/>
+      <c r="T87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -2748,24 +3352,31 @@
           <t>Horsea</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B88" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C88" s="3" t="n">
+      <c r="E88" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D88" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F88" s="3">
-        <f>IF(B88="common", 4, IF(B88="uncommon", 3, IF(B88="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+      <c r="I88" s="3" t="n"/>
+      <c r="J88" s="3" t="n"/>
+      <c r="L88" s="3" t="n"/>
+      <c r="M88" s="3" t="n"/>
+      <c r="Q88" s="3" t="n"/>
+      <c r="R88" s="3" t="n"/>
+      <c r="S88" s="3" t="n"/>
+      <c r="T88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -2773,24 +3384,31 @@
           <t>Hypno</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B89" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C89" s="3" t="n">
+      <c r="E89" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D89" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="F89" s="3">
-        <f>IF(B89="common", 4, IF(B89="uncommon", 3, IF(B89="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="n"/>
+      <c r="I89" s="3" t="n"/>
+      <c r="J89" s="3" t="n"/>
+      <c r="L89" s="3" t="n"/>
+      <c r="M89" s="3" t="n"/>
+      <c r="Q89" s="3" t="n"/>
+      <c r="R89" s="3" t="n"/>
+      <c r="S89" s="3" t="n"/>
+      <c r="T89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -2798,24 +3416,31 @@
           <t>Ivysaur - 002/165</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B90" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C90" s="3" t="n">
+      <c r="E90" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D90" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="F90" s="3">
-        <f>IF(B90="common", 4, IF(B90="uncommon", 3, IF(B90="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F90" s="3" t="n"/>
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+      <c r="I90" s="3" t="n"/>
+      <c r="J90" s="3" t="n"/>
+      <c r="L90" s="3" t="n"/>
+      <c r="M90" s="3" t="n"/>
+      <c r="Q90" s="3" t="n"/>
+      <c r="R90" s="3" t="n"/>
+      <c r="S90" s="3" t="n"/>
+      <c r="T90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -2823,22 +3448,29 @@
           <t>Ivysaur - 167/165</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B91" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="C91" s="3" t="inlineStr"/>
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C91" s="3" t="n">
+      <c r="E91" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D91" s="3" t="n">
-        <v>26.78</v>
-      </c>
-      <c r="E91" s="3" t="inlineStr"/>
-      <c r="F91" s="3">
-        <f>IF(B91="common", 4, IF(B91="uncommon", 3, IF(B91="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F91" s="3" t="n"/>
+      <c r="G91" s="3" t="n"/>
+      <c r="H91" s="3" t="n"/>
+      <c r="I91" s="3" t="n"/>
+      <c r="J91" s="3" t="n"/>
+      <c r="L91" s="3" t="n"/>
+      <c r="M91" s="3" t="n"/>
+      <c r="Q91" s="3" t="n"/>
+      <c r="R91" s="3" t="n"/>
+      <c r="S91" s="3" t="n"/>
+      <c r="T91" s="3" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -2846,24 +3478,31 @@
           <t>Jigglypuff</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B92" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C92" s="3" t="n">
+      <c r="E92" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D92" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F92" s="3">
-        <f>IF(B92="common", 4, IF(B92="uncommon", 3, IF(B92="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F92" s="3" t="n"/>
+      <c r="G92" s="3" t="n"/>
+      <c r="H92" s="3" t="n"/>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="3" t="n"/>
+      <c r="L92" s="3" t="n"/>
+      <c r="M92" s="3" t="n"/>
+      <c r="Q92" s="3" t="n"/>
+      <c r="R92" s="3" t="n"/>
+      <c r="S92" s="3" t="n"/>
+      <c r="T92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -2871,24 +3510,31 @@
           <t>Jolteon</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B93" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C93" s="3" t="n">
+      <c r="E93" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D93" s="3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="F93" s="3">
-        <f>IF(B93="common", 4, IF(B93="uncommon", 3, IF(B93="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F93" s="3" t="n"/>
+      <c r="G93" s="3" t="n"/>
+      <c r="H93" s="3" t="n"/>
+      <c r="I93" s="3" t="n"/>
+      <c r="J93" s="3" t="n"/>
+      <c r="L93" s="3" t="n"/>
+      <c r="M93" s="3" t="n"/>
+      <c r="Q93" s="3" t="n"/>
+      <c r="R93" s="3" t="n"/>
+      <c r="S93" s="3" t="n"/>
+      <c r="T93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -2896,22 +3542,29 @@
           <t>Jynx ex - 124/165</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B94" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="C94" s="3" t="inlineStr"/>
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>double rare</t>
         </is>
       </c>
-      <c r="C94" s="3" t="n">
+      <c r="E94" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D94" s="3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E94" s="3" t="inlineStr"/>
-      <c r="F94" s="3">
-        <f>IF(B94="common", 4, IF(B94="uncommon", 3, IF(B94="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F94" s="3" t="n"/>
+      <c r="G94" s="3" t="n"/>
+      <c r="H94" s="3" t="n"/>
+      <c r="I94" s="3" t="n"/>
+      <c r="J94" s="3" t="n"/>
+      <c r="L94" s="3" t="n"/>
+      <c r="M94" s="3" t="n"/>
+      <c r="Q94" s="3" t="n"/>
+      <c r="R94" s="3" t="n"/>
+      <c r="S94" s="3" t="n"/>
+      <c r="T94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -2919,22 +3572,29 @@
           <t>Jynx ex - 191/165</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" s="3" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="C95" s="3" t="inlineStr"/>
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C95" s="3" t="n">
+      <c r="E95" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D95" s="3" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="E95" s="3" t="inlineStr"/>
-      <c r="F95" s="3">
-        <f>IF(B95="common", 4, IF(B95="uncommon", 3, IF(B95="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F95" s="3" t="n"/>
+      <c r="G95" s="3" t="n"/>
+      <c r="H95" s="3" t="n"/>
+      <c r="I95" s="3" t="n"/>
+      <c r="J95" s="3" t="n"/>
+      <c r="L95" s="3" t="n"/>
+      <c r="M95" s="3" t="n"/>
+      <c r="Q95" s="3" t="n"/>
+      <c r="R95" s="3" t="n"/>
+      <c r="S95" s="3" t="n"/>
+      <c r="T95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -2942,24 +3602,31 @@
           <t>Kabuto</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B96" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C96" s="3" t="n">
+      <c r="E96" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D96" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="F96" s="3">
-        <f>IF(B96="common", 4, IF(B96="uncommon", 3, IF(B96="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F96" s="3" t="n"/>
+      <c r="G96" s="3" t="n"/>
+      <c r="H96" s="3" t="n"/>
+      <c r="I96" s="3" t="n"/>
+      <c r="J96" s="3" t="n"/>
+      <c r="L96" s="3" t="n"/>
+      <c r="M96" s="3" t="n"/>
+      <c r="Q96" s="3" t="n"/>
+      <c r="R96" s="3" t="n"/>
+      <c r="S96" s="3" t="n"/>
+      <c r="T96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -2967,24 +3634,31 @@
           <t>Kabutops</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B97" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C97" s="3" t="n">
+      <c r="E97" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D97" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="F97" s="3">
-        <f>IF(B97="common", 4, IF(B97="uncommon", 3, IF(B97="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F97" s="3" t="n"/>
+      <c r="G97" s="3" t="n"/>
+      <c r="H97" s="3" t="n"/>
+      <c r="I97" s="3" t="n"/>
+      <c r="J97" s="3" t="n"/>
+      <c r="L97" s="3" t="n"/>
+      <c r="M97" s="3" t="n"/>
+      <c r="Q97" s="3" t="n"/>
+      <c r="R97" s="3" t="n"/>
+      <c r="S97" s="3" t="n"/>
+      <c r="T97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -2992,24 +3666,31 @@
           <t>Kadabra</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B98" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C98" s="3" t="n">
+      <c r="E98" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D98" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="F98" s="3">
-        <f>IF(B98="common", 4, IF(B98="uncommon", 3, IF(B98="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F98" s="3" t="n"/>
+      <c r="G98" s="3" t="n"/>
+      <c r="H98" s="3" t="n"/>
+      <c r="I98" s="3" t="n"/>
+      <c r="J98" s="3" t="n"/>
+      <c r="L98" s="3" t="n"/>
+      <c r="M98" s="3" t="n"/>
+      <c r="Q98" s="3" t="n"/>
+      <c r="R98" s="3" t="n"/>
+      <c r="S98" s="3" t="n"/>
+      <c r="T98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -3017,24 +3698,31 @@
           <t>Kakuna</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B99" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C99" s="3" t="n">
+      <c r="E99" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D99" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F99" s="3">
-        <f>IF(B99="common", 4, IF(B99="uncommon", 3, IF(B99="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F99" s="3" t="n"/>
+      <c r="G99" s="3" t="n"/>
+      <c r="H99" s="3" t="n"/>
+      <c r="I99" s="3" t="n"/>
+      <c r="J99" s="3" t="n"/>
+      <c r="L99" s="3" t="n"/>
+      <c r="M99" s="3" t="n"/>
+      <c r="Q99" s="3" t="n"/>
+      <c r="R99" s="3" t="n"/>
+      <c r="S99" s="3" t="n"/>
+      <c r="T99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -3042,22 +3730,29 @@
           <t>Kangaskhan ex - 115/165</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B100" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="C100" s="3" t="inlineStr"/>
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>double rare</t>
         </is>
       </c>
-      <c r="C100" s="3" t="n">
+      <c r="E100" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D100" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E100" s="3" t="inlineStr"/>
-      <c r="F100" s="3">
-        <f>IF(B100="common", 4, IF(B100="uncommon", 3, IF(B100="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F100" s="3" t="n"/>
+      <c r="G100" s="3" t="n"/>
+      <c r="H100" s="3" t="n"/>
+      <c r="I100" s="3" t="n"/>
+      <c r="J100" s="3" t="n"/>
+      <c r="L100" s="3" t="n"/>
+      <c r="M100" s="3" t="n"/>
+      <c r="Q100" s="3" t="n"/>
+      <c r="R100" s="3" t="n"/>
+      <c r="S100" s="3" t="n"/>
+      <c r="T100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -3065,22 +3760,29 @@
           <t>Kangaskhan ex - 190/165</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B101" s="3" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="C101" s="3" t="inlineStr"/>
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C101" s="3" t="n">
+      <c r="E101" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D101" s="3" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="E101" s="3" t="inlineStr"/>
-      <c r="F101" s="3">
-        <f>IF(B101="common", 4, IF(B101="uncommon", 3, IF(B101="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F101" s="3" t="n"/>
+      <c r="G101" s="3" t="n"/>
+      <c r="H101" s="3" t="n"/>
+      <c r="I101" s="3" t="n"/>
+      <c r="J101" s="3" t="n"/>
+      <c r="L101" s="3" t="n"/>
+      <c r="M101" s="3" t="n"/>
+      <c r="Q101" s="3" t="n"/>
+      <c r="R101" s="3" t="n"/>
+      <c r="S101" s="3" t="n"/>
+      <c r="T101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -3088,24 +3790,31 @@
           <t>Kingler</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B102" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C102" s="3" t="n">
+      <c r="E102" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D102" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F102" s="3">
-        <f>IF(B102="common", 4, IF(B102="uncommon", 3, IF(B102="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="3" t="n"/>
+      <c r="H102" s="3" t="n"/>
+      <c r="I102" s="3" t="n"/>
+      <c r="J102" s="3" t="n"/>
+      <c r="L102" s="3" t="n"/>
+      <c r="M102" s="3" t="n"/>
+      <c r="Q102" s="3" t="n"/>
+      <c r="R102" s="3" t="n"/>
+      <c r="S102" s="3" t="n"/>
+      <c r="T102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -3113,24 +3822,31 @@
           <t>Koffing</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B103" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C103" s="3" t="n">
+      <c r="E103" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D103" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F103" s="3">
-        <f>IF(B103="common", 4, IF(B103="uncommon", 3, IF(B103="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F103" s="3" t="n"/>
+      <c r="G103" s="3" t="n"/>
+      <c r="H103" s="3" t="n"/>
+      <c r="I103" s="3" t="n"/>
+      <c r="J103" s="3" t="n"/>
+      <c r="L103" s="3" t="n"/>
+      <c r="M103" s="3" t="n"/>
+      <c r="Q103" s="3" t="n"/>
+      <c r="R103" s="3" t="n"/>
+      <c r="S103" s="3" t="n"/>
+      <c r="T103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -3138,24 +3854,31 @@
           <t>Krabby</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B104" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C104" s="3" t="n">
+      <c r="E104" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D104" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F104" s="3">
-        <f>IF(B104="common", 4, IF(B104="uncommon", 3, IF(B104="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F104" s="3" t="n"/>
+      <c r="G104" s="3" t="n"/>
+      <c r="H104" s="3" t="n"/>
+      <c r="I104" s="3" t="n"/>
+      <c r="J104" s="3" t="n"/>
+      <c r="L104" s="3" t="n"/>
+      <c r="M104" s="3" t="n"/>
+      <c r="Q104" s="3" t="n"/>
+      <c r="R104" s="3" t="n"/>
+      <c r="S104" s="3" t="n"/>
+      <c r="T104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -3163,24 +3886,31 @@
           <t>Lapras</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B105" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C105" s="3" t="n">
+      <c r="E105" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D105" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="F105" s="3">
-        <f>IF(B105="common", 4, IF(B105="uncommon", 3, IF(B105="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F105" s="3" t="n"/>
+      <c r="G105" s="3" t="n"/>
+      <c r="H105" s="3" t="n"/>
+      <c r="I105" s="3" t="n"/>
+      <c r="J105" s="3" t="n"/>
+      <c r="L105" s="3" t="n"/>
+      <c r="M105" s="3" t="n"/>
+      <c r="Q105" s="3" t="n"/>
+      <c r="R105" s="3" t="n"/>
+      <c r="S105" s="3" t="n"/>
+      <c r="T105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
@@ -3188,24 +3918,31 @@
           <t>Leftovers</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B106" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C106" s="3" t="n">
+      <c r="E106" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D106" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E106" s="3" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="F106" s="3">
-        <f>IF(B106="common", 4, IF(B106="uncommon", 3, IF(B106="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F106" s="3" t="n"/>
+      <c r="G106" s="3" t="n"/>
+      <c r="H106" s="3" t="n"/>
+      <c r="I106" s="3" t="n"/>
+      <c r="J106" s="3" t="n"/>
+      <c r="L106" s="3" t="n"/>
+      <c r="M106" s="3" t="n"/>
+      <c r="Q106" s="3" t="n"/>
+      <c r="R106" s="3" t="n"/>
+      <c r="S106" s="3" t="n"/>
+      <c r="T106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -3213,24 +3950,31 @@
           <t>Lickitung</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B107" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C107" s="3" t="n">
+      <c r="E107" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D107" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F107" s="3">
-        <f>IF(B107="common", 4, IF(B107="uncommon", 3, IF(B107="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F107" s="3" t="n"/>
+      <c r="G107" s="3" t="n"/>
+      <c r="H107" s="3" t="n"/>
+      <c r="I107" s="3" t="n"/>
+      <c r="J107" s="3" t="n"/>
+      <c r="L107" s="3" t="n"/>
+      <c r="M107" s="3" t="n"/>
+      <c r="Q107" s="3" t="n"/>
+      <c r="R107" s="3" t="n"/>
+      <c r="S107" s="3" t="n"/>
+      <c r="T107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -3238,24 +3982,31 @@
           <t>Machamp</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B108" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C108" s="3" t="n">
+      <c r="E108" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D108" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="F108" s="3">
-        <f>IF(B108="common", 4, IF(B108="uncommon", 3, IF(B108="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F108" s="3" t="n"/>
+      <c r="G108" s="3" t="n"/>
+      <c r="H108" s="3" t="n"/>
+      <c r="I108" s="3" t="n"/>
+      <c r="J108" s="3" t="n"/>
+      <c r="L108" s="3" t="n"/>
+      <c r="M108" s="3" t="n"/>
+      <c r="Q108" s="3" t="n"/>
+      <c r="R108" s="3" t="n"/>
+      <c r="S108" s="3" t="n"/>
+      <c r="T108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -3263,24 +4014,31 @@
           <t>Machoke - 067/165</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B109" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C109" s="3" t="n">
+      <c r="E109" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D109" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F109" s="3">
-        <f>IF(B109="common", 4, IF(B109="uncommon", 3, IF(B109="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F109" s="3" t="n"/>
+      <c r="G109" s="3" t="n"/>
+      <c r="H109" s="3" t="n"/>
+      <c r="I109" s="3" t="n"/>
+      <c r="J109" s="3" t="n"/>
+      <c r="L109" s="3" t="n"/>
+      <c r="M109" s="3" t="n"/>
+      <c r="Q109" s="3" t="n"/>
+      <c r="R109" s="3" t="n"/>
+      <c r="S109" s="3" t="n"/>
+      <c r="T109" s="3" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -3288,22 +4046,29 @@
           <t>Machoke - 177/165</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B110" s="3" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="C110" s="3" t="inlineStr"/>
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C110" s="3" t="n">
+      <c r="E110" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D110" s="3" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="E110" s="3" t="inlineStr"/>
-      <c r="F110" s="3">
-        <f>IF(B110="common", 4, IF(B110="uncommon", 3, IF(B110="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F110" s="3" t="n"/>
+      <c r="G110" s="3" t="n"/>
+      <c r="H110" s="3" t="n"/>
+      <c r="I110" s="3" t="n"/>
+      <c r="J110" s="3" t="n"/>
+      <c r="L110" s="3" t="n"/>
+      <c r="M110" s="3" t="n"/>
+      <c r="Q110" s="3" t="n"/>
+      <c r="R110" s="3" t="n"/>
+      <c r="S110" s="3" t="n"/>
+      <c r="T110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -3311,24 +4076,31 @@
           <t>Machop</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B111" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C111" s="3" t="n">
+      <c r="E111" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D111" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F111" s="3">
-        <f>IF(B111="common", 4, IF(B111="uncommon", 3, IF(B111="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F111" s="3" t="n"/>
+      <c r="G111" s="3" t="n"/>
+      <c r="H111" s="3" t="n"/>
+      <c r="I111" s="3" t="n"/>
+      <c r="J111" s="3" t="n"/>
+      <c r="L111" s="3" t="n"/>
+      <c r="M111" s="3" t="n"/>
+      <c r="Q111" s="3" t="n"/>
+      <c r="R111" s="3" t="n"/>
+      <c r="S111" s="3" t="n"/>
+      <c r="T111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -3336,24 +4108,31 @@
           <t>Magikarp</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B112" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C112" s="3" t="n">
+      <c r="E112" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D112" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="F112" s="3">
-        <f>IF(B112="common", 4, IF(B112="uncommon", 3, IF(B112="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F112" s="3" t="n"/>
+      <c r="G112" s="3" t="n"/>
+      <c r="H112" s="3" t="n"/>
+      <c r="I112" s="3" t="n"/>
+      <c r="J112" s="3" t="n"/>
+      <c r="L112" s="3" t="n"/>
+      <c r="M112" s="3" t="n"/>
+      <c r="Q112" s="3" t="n"/>
+      <c r="R112" s="3" t="n"/>
+      <c r="S112" s="3" t="n"/>
+      <c r="T112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -3361,24 +4140,31 @@
           <t>Magmar</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B113" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C113" s="3" t="n">
+      <c r="E113" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D113" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F113" s="3">
-        <f>IF(B113="common", 4, IF(B113="uncommon", 3, IF(B113="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F113" s="3" t="n"/>
+      <c r="G113" s="3" t="n"/>
+      <c r="H113" s="3" t="n"/>
+      <c r="I113" s="3" t="n"/>
+      <c r="J113" s="3" t="n"/>
+      <c r="L113" s="3" t="n"/>
+      <c r="M113" s="3" t="n"/>
+      <c r="Q113" s="3" t="n"/>
+      <c r="R113" s="3" t="n"/>
+      <c r="S113" s="3" t="n"/>
+      <c r="T113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -3386,24 +4172,31 @@
           <t>Magnemite</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B114" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C114" s="3" t="n">
+      <c r="E114" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D114" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F114" s="3">
-        <f>IF(B114="common", 4, IF(B114="uncommon", 3, IF(B114="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F114" s="3" t="n"/>
+      <c r="G114" s="3" t="n"/>
+      <c r="H114" s="3" t="n"/>
+      <c r="I114" s="3" t="n"/>
+      <c r="J114" s="3" t="n"/>
+      <c r="L114" s="3" t="n"/>
+      <c r="M114" s="3" t="n"/>
+      <c r="Q114" s="3" t="n"/>
+      <c r="R114" s="3" t="n"/>
+      <c r="S114" s="3" t="n"/>
+      <c r="T114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -3411,24 +4204,31 @@
           <t>Magneton</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B115" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C115" s="3" t="n">
+      <c r="E115" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D115" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F115" s="3">
-        <f>IF(B115="common", 4, IF(B115="uncommon", 3, IF(B115="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F115" s="3" t="n"/>
+      <c r="G115" s="3" t="n"/>
+      <c r="H115" s="3" t="n"/>
+      <c r="I115" s="3" t="n"/>
+      <c r="J115" s="3" t="n"/>
+      <c r="L115" s="3" t="n"/>
+      <c r="M115" s="3" t="n"/>
+      <c r="Q115" s="3" t="n"/>
+      <c r="R115" s="3" t="n"/>
+      <c r="S115" s="3" t="n"/>
+      <c r="T115" s="3" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -3436,24 +4236,31 @@
           <t>Mankey</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B116" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C116" s="3" t="n">
+      <c r="E116" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D116" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F116" s="3">
-        <f>IF(B116="common", 4, IF(B116="uncommon", 3, IF(B116="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F116" s="3" t="n"/>
+      <c r="G116" s="3" t="n"/>
+      <c r="H116" s="3" t="n"/>
+      <c r="I116" s="3" t="n"/>
+      <c r="J116" s="3" t="n"/>
+      <c r="L116" s="3" t="n"/>
+      <c r="M116" s="3" t="n"/>
+      <c r="Q116" s="3" t="n"/>
+      <c r="R116" s="3" t="n"/>
+      <c r="S116" s="3" t="n"/>
+      <c r="T116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -3461,24 +4268,31 @@
           <t>Marowak</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B117" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C117" s="3" t="n">
+      <c r="E117" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D117" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F117" s="3">
-        <f>IF(B117="common", 4, IF(B117="uncommon", 3, IF(B117="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F117" s="3" t="n"/>
+      <c r="G117" s="3" t="n"/>
+      <c r="H117" s="3" t="n"/>
+      <c r="I117" s="3" t="n"/>
+      <c r="J117" s="3" t="n"/>
+      <c r="L117" s="3" t="n"/>
+      <c r="M117" s="3" t="n"/>
+      <c r="Q117" s="3" t="n"/>
+      <c r="R117" s="3" t="n"/>
+      <c r="S117" s="3" t="n"/>
+      <c r="T117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -3486,24 +4300,31 @@
           <t>Meowth</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B118" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C118" s="3" t="n">
+      <c r="E118" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D118" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F118" s="3">
-        <f>IF(B118="common", 4, IF(B118="uncommon", 3, IF(B118="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F118" s="3" t="n"/>
+      <c r="G118" s="3" t="n"/>
+      <c r="H118" s="3" t="n"/>
+      <c r="I118" s="3" t="n"/>
+      <c r="J118" s="3" t="n"/>
+      <c r="L118" s="3" t="n"/>
+      <c r="M118" s="3" t="n"/>
+      <c r="Q118" s="3" t="n"/>
+      <c r="R118" s="3" t="n"/>
+      <c r="S118" s="3" t="n"/>
+      <c r="T118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -3511,24 +4332,31 @@
           <t>Metapod</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B119" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C119" s="3" t="n">
+      <c r="E119" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D119" s="3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="F119" s="3">
-        <f>IF(B119="common", 4, IF(B119="uncommon", 3, IF(B119="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F119" s="3" t="n"/>
+      <c r="G119" s="3" t="n"/>
+      <c r="H119" s="3" t="n"/>
+      <c r="I119" s="3" t="n"/>
+      <c r="J119" s="3" t="n"/>
+      <c r="L119" s="3" t="n"/>
+      <c r="M119" s="3" t="n"/>
+      <c r="Q119" s="3" t="n"/>
+      <c r="R119" s="3" t="n"/>
+      <c r="S119" s="3" t="n"/>
+      <c r="T119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -3536,22 +4364,29 @@
           <t>Mew ex - 151/165</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B120" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C120" s="3" t="inlineStr"/>
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>double rare</t>
         </is>
       </c>
-      <c r="C120" s="3" t="n">
+      <c r="E120" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D120" s="3" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="E120" s="3" t="inlineStr"/>
-      <c r="F120" s="3">
-        <f>IF(B120="common", 4, IF(B120="uncommon", 3, IF(B120="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F120" s="3" t="n"/>
+      <c r="G120" s="3" t="n"/>
+      <c r="H120" s="3" t="n"/>
+      <c r="I120" s="3" t="n"/>
+      <c r="J120" s="3" t="n"/>
+      <c r="L120" s="3" t="n"/>
+      <c r="M120" s="3" t="n"/>
+      <c r="Q120" s="3" t="n"/>
+      <c r="R120" s="3" t="n"/>
+      <c r="S120" s="3" t="n"/>
+      <c r="T120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -3559,22 +4394,29 @@
           <t>Mew ex - 193/165</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B121" s="3" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="C121" s="3" t="inlineStr"/>
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C121" s="3" t="n">
+      <c r="E121" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D121" s="3" t="n">
-        <v>18.71</v>
-      </c>
-      <c r="E121" s="3" t="inlineStr"/>
-      <c r="F121" s="3">
-        <f>IF(B121="common", 4, IF(B121="uncommon", 3, IF(B121="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F121" s="3" t="n"/>
+      <c r="G121" s="3" t="n"/>
+      <c r="H121" s="3" t="n"/>
+      <c r="I121" s="3" t="n"/>
+      <c r="J121" s="3" t="n"/>
+      <c r="L121" s="3" t="n"/>
+      <c r="M121" s="3" t="n"/>
+      <c r="Q121" s="3" t="n"/>
+      <c r="R121" s="3" t="n"/>
+      <c r="S121" s="3" t="n"/>
+      <c r="T121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -3582,22 +4424,29 @@
           <t>Mew ex - 205/165</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B122" s="3" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="C122" s="3" t="inlineStr"/>
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>hyper rare</t>
         </is>
       </c>
-      <c r="C122" s="3" t="n">
+      <c r="E122" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="D122" s="3" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="E122" s="3" t="inlineStr"/>
-      <c r="F122" s="3">
-        <f>IF(B122="common", 4, IF(B122="uncommon", 3, IF(B122="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F122" s="3" t="n"/>
+      <c r="G122" s="3" t="n"/>
+      <c r="H122" s="3" t="n"/>
+      <c r="I122" s="3" t="n"/>
+      <c r="J122" s="3" t="n"/>
+      <c r="L122" s="3" t="n"/>
+      <c r="M122" s="3" t="n"/>
+      <c r="Q122" s="3" t="n"/>
+      <c r="R122" s="3" t="n"/>
+      <c r="S122" s="3" t="n"/>
+      <c r="T122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -3605,22 +4454,29 @@
           <t>Mew ex - 205/165 (151 Metal Card)</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B123" s="3" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="C123" s="3" t="inlineStr"/>
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>double rare</t>
         </is>
       </c>
-      <c r="C123" s="3" t="n">
+      <c r="E123" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D123" s="3" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="E123" s="3" t="inlineStr"/>
-      <c r="F123" s="3">
-        <f>IF(B123="common", 4, IF(B123="uncommon", 3, IF(B123="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F123" s="3" t="n"/>
+      <c r="G123" s="3" t="n"/>
+      <c r="H123" s="3" t="n"/>
+      <c r="I123" s="3" t="n"/>
+      <c r="J123" s="3" t="n"/>
+      <c r="L123" s="3" t="n"/>
+      <c r="M123" s="3" t="n"/>
+      <c r="Q123" s="3" t="n"/>
+      <c r="R123" s="3" t="n"/>
+      <c r="S123" s="3" t="n"/>
+      <c r="T123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -3628,24 +4484,31 @@
           <t>Mewtwo</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B124" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C124" s="3" t="n">
+      <c r="E124" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D124" s="3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="F124" s="3">
-        <f>IF(B124="common", 4, IF(B124="uncommon", 3, IF(B124="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F124" s="3" t="n"/>
+      <c r="G124" s="3" t="n"/>
+      <c r="H124" s="3" t="n"/>
+      <c r="I124" s="3" t="n"/>
+      <c r="J124" s="3" t="n"/>
+      <c r="L124" s="3" t="n"/>
+      <c r="M124" s="3" t="n"/>
+      <c r="Q124" s="3" t="n"/>
+      <c r="R124" s="3" t="n"/>
+      <c r="S124" s="3" t="n"/>
+      <c r="T124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -3653,24 +4516,31 @@
           <t>Moltres</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B125" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C125" s="3" t="n">
+      <c r="E125" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D125" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="F125" s="3">
-        <f>IF(B125="common", 4, IF(B125="uncommon", 3, IF(B125="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F125" s="3" t="n"/>
+      <c r="G125" s="3" t="n"/>
+      <c r="H125" s="3" t="n"/>
+      <c r="I125" s="3" t="n"/>
+      <c r="J125" s="3" t="n"/>
+      <c r="L125" s="3" t="n"/>
+      <c r="M125" s="3" t="n"/>
+      <c r="Q125" s="3" t="n"/>
+      <c r="R125" s="3" t="n"/>
+      <c r="S125" s="3" t="n"/>
+      <c r="T125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -3678,24 +4548,31 @@
           <t>Mr. Mime - 122/165</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B126" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C126" s="3" t="n">
+      <c r="E126" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D126" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="F126" s="3">
-        <f>IF(B126="common", 4, IF(B126="uncommon", 3, IF(B126="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F126" s="3" t="n"/>
+      <c r="G126" s="3" t="n"/>
+      <c r="H126" s="3" t="n"/>
+      <c r="I126" s="3" t="n"/>
+      <c r="J126" s="3" t="n"/>
+      <c r="L126" s="3" t="n"/>
+      <c r="M126" s="3" t="n"/>
+      <c r="Q126" s="3" t="n"/>
+      <c r="R126" s="3" t="n"/>
+      <c r="S126" s="3" t="n"/>
+      <c r="T126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -3703,22 +4580,29 @@
           <t>Mr. Mime - 179/165</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B127" s="3" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="C127" s="3" t="inlineStr"/>
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C127" s="3" t="n">
+      <c r="E127" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D127" s="3" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="E127" s="3" t="inlineStr"/>
-      <c r="F127" s="3">
-        <f>IF(B127="common", 4, IF(B127="uncommon", 3, IF(B127="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F127" s="3" t="n"/>
+      <c r="G127" s="3" t="n"/>
+      <c r="H127" s="3" t="n"/>
+      <c r="I127" s="3" t="n"/>
+      <c r="J127" s="3" t="n"/>
+      <c r="L127" s="3" t="n"/>
+      <c r="M127" s="3" t="n"/>
+      <c r="Q127" s="3" t="n"/>
+      <c r="R127" s="3" t="n"/>
+      <c r="S127" s="3" t="n"/>
+      <c r="T127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -3726,24 +4610,31 @@
           <t>Muk</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B128" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C128" s="3" t="n">
+      <c r="E128" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D128" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F128" s="3">
-        <f>IF(B128="common", 4, IF(B128="uncommon", 3, IF(B128="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F128" s="3" t="n"/>
+      <c r="G128" s="3" t="n"/>
+      <c r="H128" s="3" t="n"/>
+      <c r="I128" s="3" t="n"/>
+      <c r="J128" s="3" t="n"/>
+      <c r="L128" s="3" t="n"/>
+      <c r="M128" s="3" t="n"/>
+      <c r="Q128" s="3" t="n"/>
+      <c r="R128" s="3" t="n"/>
+      <c r="S128" s="3" t="n"/>
+      <c r="T128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -3751,24 +4642,31 @@
           <t>Nidoking - 034/165</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B129" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C129" s="3" t="n">
+      <c r="E129" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D129" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="F129" s="3">
-        <f>IF(B129="common", 4, IF(B129="uncommon", 3, IF(B129="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F129" s="3" t="n"/>
+      <c r="G129" s="3" t="n"/>
+      <c r="H129" s="3" t="n"/>
+      <c r="I129" s="3" t="n"/>
+      <c r="J129" s="3" t="n"/>
+      <c r="L129" s="3" t="n"/>
+      <c r="M129" s="3" t="n"/>
+      <c r="Q129" s="3" t="n"/>
+      <c r="R129" s="3" t="n"/>
+      <c r="S129" s="3" t="n"/>
+      <c r="T129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -3776,22 +4674,29 @@
           <t>Nidoking - 174/165</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B130" s="3" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="C130" s="3" t="inlineStr"/>
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C130" s="3" t="n">
+      <c r="E130" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D130" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E130" s="3" t="inlineStr"/>
-      <c r="F130" s="3">
-        <f>IF(B130="common", 4, IF(B130="uncommon", 3, IF(B130="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="3" t="n"/>
+      <c r="H130" s="3" t="n"/>
+      <c r="I130" s="3" t="n"/>
+      <c r="J130" s="3" t="n"/>
+      <c r="L130" s="3" t="n"/>
+      <c r="M130" s="3" t="n"/>
+      <c r="Q130" s="3" t="n"/>
+      <c r="R130" s="3" t="n"/>
+      <c r="S130" s="3" t="n"/>
+      <c r="T130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -3799,24 +4704,31 @@
           <t>Nidoqueen</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B131" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C131" s="3" t="n">
+      <c r="E131" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D131" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F131" s="3">
-        <f>IF(B131="common", 4, IF(B131="uncommon", 3, IF(B131="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F131" s="3" t="n"/>
+      <c r="G131" s="3" t="n"/>
+      <c r="H131" s="3" t="n"/>
+      <c r="I131" s="3" t="n"/>
+      <c r="J131" s="3" t="n"/>
+      <c r="L131" s="3" t="n"/>
+      <c r="M131" s="3" t="n"/>
+      <c r="Q131" s="3" t="n"/>
+      <c r="R131" s="3" t="n"/>
+      <c r="S131" s="3" t="n"/>
+      <c r="T131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -3824,24 +4736,31 @@
           <t>Nidoran F</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B132" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C132" s="3" t="n">
+      <c r="E132" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D132" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="F132" s="3">
-        <f>IF(B132="common", 4, IF(B132="uncommon", 3, IF(B132="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F132" s="3" t="n"/>
+      <c r="G132" s="3" t="n"/>
+      <c r="H132" s="3" t="n"/>
+      <c r="I132" s="3" t="n"/>
+      <c r="J132" s="3" t="n"/>
+      <c r="L132" s="3" t="n"/>
+      <c r="M132" s="3" t="n"/>
+      <c r="Q132" s="3" t="n"/>
+      <c r="R132" s="3" t="n"/>
+      <c r="S132" s="3" t="n"/>
+      <c r="T132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -3849,24 +4768,31 @@
           <t>Nidoran M</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr">
+      <c r="B133" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C133" s="3" t="n">
+      <c r="E133" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D133" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="F133" s="3">
-        <f>IF(B133="common", 4, IF(B133="uncommon", 3, IF(B133="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F133" s="3" t="n"/>
+      <c r="G133" s="3" t="n"/>
+      <c r="H133" s="3" t="n"/>
+      <c r="I133" s="3" t="n"/>
+      <c r="J133" s="3" t="n"/>
+      <c r="L133" s="3" t="n"/>
+      <c r="M133" s="3" t="n"/>
+      <c r="Q133" s="3" t="n"/>
+      <c r="R133" s="3" t="n"/>
+      <c r="S133" s="3" t="n"/>
+      <c r="T133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -3874,24 +4800,31 @@
           <t>Nidorina</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B134" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C134" s="3" t="n">
+      <c r="E134" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D134" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="F134" s="3">
-        <f>IF(B134="common", 4, IF(B134="uncommon", 3, IF(B134="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F134" s="3" t="n"/>
+      <c r="G134" s="3" t="n"/>
+      <c r="H134" s="3" t="n"/>
+      <c r="I134" s="3" t="n"/>
+      <c r="J134" s="3" t="n"/>
+      <c r="L134" s="3" t="n"/>
+      <c r="M134" s="3" t="n"/>
+      <c r="Q134" s="3" t="n"/>
+      <c r="R134" s="3" t="n"/>
+      <c r="S134" s="3" t="n"/>
+      <c r="T134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -3899,24 +4832,31 @@
           <t>Nidorino</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B135" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C135" s="3" t="n">
+      <c r="E135" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D135" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="F135" s="3">
-        <f>IF(B135="common", 4, IF(B135="uncommon", 3, IF(B135="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F135" s="3" t="n"/>
+      <c r="G135" s="3" t="n"/>
+      <c r="H135" s="3" t="n"/>
+      <c r="I135" s="3" t="n"/>
+      <c r="J135" s="3" t="n"/>
+      <c r="L135" s="3" t="n"/>
+      <c r="M135" s="3" t="n"/>
+      <c r="Q135" s="3" t="n"/>
+      <c r="R135" s="3" t="n"/>
+      <c r="S135" s="3" t="n"/>
+      <c r="T135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -3924,22 +4864,29 @@
           <t>Ninetales ex - 038/165</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B136" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C136" s="3" t="inlineStr"/>
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>double rare</t>
         </is>
       </c>
-      <c r="C136" s="3" t="n">
+      <c r="E136" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D136" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E136" s="3" t="inlineStr"/>
-      <c r="F136" s="3">
-        <f>IF(B136="common", 4, IF(B136="uncommon", 3, IF(B136="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F136" s="3" t="n"/>
+      <c r="G136" s="3" t="n"/>
+      <c r="H136" s="3" t="n"/>
+      <c r="I136" s="3" t="n"/>
+      <c r="J136" s="3" t="n"/>
+      <c r="L136" s="3" t="n"/>
+      <c r="M136" s="3" t="n"/>
+      <c r="Q136" s="3" t="n"/>
+      <c r="R136" s="3" t="n"/>
+      <c r="S136" s="3" t="n"/>
+      <c r="T136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -3947,22 +4894,29 @@
           <t>Ninetales ex - 186/165</t>
         </is>
       </c>
-      <c r="B137" s="3" t="inlineStr">
+      <c r="B137" s="3" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="C137" s="3" t="inlineStr"/>
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C137" s="3" t="n">
+      <c r="E137" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D137" s="3" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="E137" s="3" t="inlineStr"/>
-      <c r="F137" s="3">
-        <f>IF(B137="common", 4, IF(B137="uncommon", 3, IF(B137="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F137" s="3" t="n"/>
+      <c r="G137" s="3" t="n"/>
+      <c r="H137" s="3" t="n"/>
+      <c r="I137" s="3" t="n"/>
+      <c r="J137" s="3" t="n"/>
+      <c r="L137" s="3" t="n"/>
+      <c r="M137" s="3" t="n"/>
+      <c r="Q137" s="3" t="n"/>
+      <c r="R137" s="3" t="n"/>
+      <c r="S137" s="3" t="n"/>
+      <c r="T137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -3970,24 +4924,31 @@
           <t>Oddish</t>
         </is>
       </c>
-      <c r="B138" s="3" t="inlineStr">
+      <c r="B138" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C138" s="3" t="n">
+      <c r="E138" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D138" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F138" s="3">
-        <f>IF(B138="common", 4, IF(B138="uncommon", 3, IF(B138="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F138" s="3" t="n"/>
+      <c r="G138" s="3" t="n"/>
+      <c r="H138" s="3" t="n"/>
+      <c r="I138" s="3" t="n"/>
+      <c r="J138" s="3" t="n"/>
+      <c r="L138" s="3" t="n"/>
+      <c r="M138" s="3" t="n"/>
+      <c r="Q138" s="3" t="n"/>
+      <c r="R138" s="3" t="n"/>
+      <c r="S138" s="3" t="n"/>
+      <c r="T138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -3995,24 +4956,31 @@
           <t>Omanyte - 138/165</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B139" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C139" s="3" t="n">
+      <c r="E139" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D139" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="F139" s="3">
-        <f>IF(B139="common", 4, IF(B139="uncommon", 3, IF(B139="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F139" s="3" t="n"/>
+      <c r="G139" s="3" t="n"/>
+      <c r="H139" s="3" t="n"/>
+      <c r="I139" s="3" t="n"/>
+      <c r="J139" s="3" t="n"/>
+      <c r="L139" s="3" t="n"/>
+      <c r="M139" s="3" t="n"/>
+      <c r="Q139" s="3" t="n"/>
+      <c r="R139" s="3" t="n"/>
+      <c r="S139" s="3" t="n"/>
+      <c r="T139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -4020,22 +4988,29 @@
           <t>Omanyte - 180/165</t>
         </is>
       </c>
-      <c r="B140" s="3" t="inlineStr">
+      <c r="B140" s="3" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="C140" s="3" t="inlineStr"/>
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C140" s="3" t="n">
+      <c r="E140" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D140" s="3" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="E140" s="3" t="inlineStr"/>
-      <c r="F140" s="3">
-        <f>IF(B140="common", 4, IF(B140="uncommon", 3, IF(B140="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F140" s="3" t="n"/>
+      <c r="G140" s="3" t="n"/>
+      <c r="H140" s="3" t="n"/>
+      <c r="I140" s="3" t="n"/>
+      <c r="J140" s="3" t="n"/>
+      <c r="L140" s="3" t="n"/>
+      <c r="M140" s="3" t="n"/>
+      <c r="Q140" s="3" t="n"/>
+      <c r="R140" s="3" t="n"/>
+      <c r="S140" s="3" t="n"/>
+      <c r="T140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -4043,24 +5018,31 @@
           <t>Omastar</t>
         </is>
       </c>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B141" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C141" s="3" t="n">
+      <c r="E141" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D141" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="F141" s="3">
-        <f>IF(B141="common", 4, IF(B141="uncommon", 3, IF(B141="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F141" s="3" t="n"/>
+      <c r="G141" s="3" t="n"/>
+      <c r="H141" s="3" t="n"/>
+      <c r="I141" s="3" t="n"/>
+      <c r="J141" s="3" t="n"/>
+      <c r="L141" s="3" t="n"/>
+      <c r="M141" s="3" t="n"/>
+      <c r="Q141" s="3" t="n"/>
+      <c r="R141" s="3" t="n"/>
+      <c r="S141" s="3" t="n"/>
+      <c r="T141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -4068,24 +5050,31 @@
           <t>Onix</t>
         </is>
       </c>
-      <c r="B142" s="3" t="inlineStr">
+      <c r="B142" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C142" s="3" t="n">
+      <c r="E142" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D142" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="F142" s="3">
-        <f>IF(B142="common", 4, IF(B142="uncommon", 3, IF(B142="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F142" s="3" t="n"/>
+      <c r="G142" s="3" t="n"/>
+      <c r="H142" s="3" t="n"/>
+      <c r="I142" s="3" t="n"/>
+      <c r="J142" s="3" t="n"/>
+      <c r="L142" s="3" t="n"/>
+      <c r="M142" s="3" t="n"/>
+      <c r="Q142" s="3" t="n"/>
+      <c r="R142" s="3" t="n"/>
+      <c r="S142" s="3" t="n"/>
+      <c r="T142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -4093,24 +5082,31 @@
           <t>Paras</t>
         </is>
       </c>
-      <c r="B143" s="3" t="inlineStr">
+      <c r="B143" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C143" s="3" t="n">
+      <c r="E143" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D143" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F143" s="3">
-        <f>IF(B143="common", 4, IF(B143="uncommon", 3, IF(B143="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F143" s="3" t="n"/>
+      <c r="G143" s="3" t="n"/>
+      <c r="H143" s="3" t="n"/>
+      <c r="I143" s="3" t="n"/>
+      <c r="J143" s="3" t="n"/>
+      <c r="L143" s="3" t="n"/>
+      <c r="M143" s="3" t="n"/>
+      <c r="Q143" s="3" t="n"/>
+      <c r="R143" s="3" t="n"/>
+      <c r="S143" s="3" t="n"/>
+      <c r="T143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -4118,24 +5114,31 @@
           <t>Parasect</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="B144" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C144" s="3" t="n">
+      <c r="E144" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D144" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F144" s="3">
-        <f>IF(B144="common", 4, IF(B144="uncommon", 3, IF(B144="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F144" s="3" t="n"/>
+      <c r="G144" s="3" t="n"/>
+      <c r="H144" s="3" t="n"/>
+      <c r="I144" s="3" t="n"/>
+      <c r="J144" s="3" t="n"/>
+      <c r="L144" s="3" t="n"/>
+      <c r="M144" s="3" t="n"/>
+      <c r="Q144" s="3" t="n"/>
+      <c r="R144" s="3" t="n"/>
+      <c r="S144" s="3" t="n"/>
+      <c r="T144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -4143,24 +5146,31 @@
           <t>Persian</t>
         </is>
       </c>
-      <c r="B145" s="3" t="inlineStr">
+      <c r="B145" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C145" s="3" t="n">
+      <c r="E145" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D145" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F145" s="3">
-        <f>IF(B145="common", 4, IF(B145="uncommon", 3, IF(B145="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F145" s="3" t="n"/>
+      <c r="G145" s="3" t="n"/>
+      <c r="H145" s="3" t="n"/>
+      <c r="I145" s="3" t="n"/>
+      <c r="J145" s="3" t="n"/>
+      <c r="L145" s="3" t="n"/>
+      <c r="M145" s="3" t="n"/>
+      <c r="Q145" s="3" t="n"/>
+      <c r="R145" s="3" t="n"/>
+      <c r="S145" s="3" t="n"/>
+      <c r="T145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -4168,24 +5178,31 @@
           <t>Pidgeot</t>
         </is>
       </c>
-      <c r="B146" s="3" t="inlineStr">
+      <c r="B146" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C146" s="3" t="n">
+      <c r="E146" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D146" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="F146" s="3">
-        <f>IF(B146="common", 4, IF(B146="uncommon", 3, IF(B146="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F146" s="3" t="n"/>
+      <c r="G146" s="3" t="n"/>
+      <c r="H146" s="3" t="n"/>
+      <c r="I146" s="3" t="n"/>
+      <c r="J146" s="3" t="n"/>
+      <c r="L146" s="3" t="n"/>
+      <c r="M146" s="3" t="n"/>
+      <c r="Q146" s="3" t="n"/>
+      <c r="R146" s="3" t="n"/>
+      <c r="S146" s="3" t="n"/>
+      <c r="T146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -4193,24 +5210,31 @@
           <t>Pidgeotto</t>
         </is>
       </c>
-      <c r="B147" s="3" t="inlineStr">
+      <c r="B147" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C147" s="3" t="n">
+      <c r="E147" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D147" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="F147" s="3">
-        <f>IF(B147="common", 4, IF(B147="uncommon", 3, IF(B147="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F147" s="3" t="n"/>
+      <c r="G147" s="3" t="n"/>
+      <c r="H147" s="3" t="n"/>
+      <c r="I147" s="3" t="n"/>
+      <c r="J147" s="3" t="n"/>
+      <c r="L147" s="3" t="n"/>
+      <c r="M147" s="3" t="n"/>
+      <c r="Q147" s="3" t="n"/>
+      <c r="R147" s="3" t="n"/>
+      <c r="S147" s="3" t="n"/>
+      <c r="T147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
@@ -4218,24 +5242,31 @@
           <t>Pidgey</t>
         </is>
       </c>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="B148" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C148" s="3" t="n">
+      <c r="E148" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D148" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F148" s="3">
-        <f>IF(B148="common", 4, IF(B148="uncommon", 3, IF(B148="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F148" s="3" t="n"/>
+      <c r="G148" s="3" t="n"/>
+      <c r="H148" s="3" t="n"/>
+      <c r="I148" s="3" t="n"/>
+      <c r="J148" s="3" t="n"/>
+      <c r="L148" s="3" t="n"/>
+      <c r="M148" s="3" t="n"/>
+      <c r="Q148" s="3" t="n"/>
+      <c r="R148" s="3" t="n"/>
+      <c r="S148" s="3" t="n"/>
+      <c r="T148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -4243,24 +5274,31 @@
           <t>Pikachu - 025/165</t>
         </is>
       </c>
-      <c r="B149" s="3" t="inlineStr">
+      <c r="B149" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C149" s="3" t="n">
+      <c r="E149" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D149" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E149" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="F149" s="3">
-        <f>IF(B149="common", 4, IF(B149="uncommon", 3, IF(B149="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F149" s="3" t="n"/>
+      <c r="G149" s="3" t="n"/>
+      <c r="H149" s="3" t="n"/>
+      <c r="I149" s="3" t="n"/>
+      <c r="J149" s="3" t="n"/>
+      <c r="L149" s="3" t="n"/>
+      <c r="M149" s="3" t="n"/>
+      <c r="Q149" s="3" t="n"/>
+      <c r="R149" s="3" t="n"/>
+      <c r="S149" s="3" t="n"/>
+      <c r="T149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -4268,22 +5306,29 @@
           <t>Pikachu - 173/165</t>
         </is>
       </c>
-      <c r="B150" s="3" t="inlineStr">
+      <c r="B150" s="3" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="C150" s="3" t="inlineStr"/>
+      <c r="D150" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C150" s="3" t="n">
+      <c r="E150" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D150" s="3" t="n">
-        <v>28.78</v>
-      </c>
-      <c r="E150" s="3" t="inlineStr"/>
-      <c r="F150" s="3">
-        <f>IF(B150="common", 4, IF(B150="uncommon", 3, IF(B150="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F150" s="3" t="n"/>
+      <c r="G150" s="3" t="n"/>
+      <c r="H150" s="3" t="n"/>
+      <c r="I150" s="3" t="n"/>
+      <c r="J150" s="3" t="n"/>
+      <c r="L150" s="3" t="n"/>
+      <c r="M150" s="3" t="n"/>
+      <c r="Q150" s="3" t="n"/>
+      <c r="R150" s="3" t="n"/>
+      <c r="S150" s="3" t="n"/>
+      <c r="T150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -4291,24 +5336,31 @@
           <t>Pinsir</t>
         </is>
       </c>
-      <c r="B151" s="3" t="inlineStr">
+      <c r="B151" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C151" s="3" t="n">
+      <c r="E151" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D151" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E151" s="3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="F151" s="3">
-        <f>IF(B151="common", 4, IF(B151="uncommon", 3, IF(B151="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F151" s="3" t="n"/>
+      <c r="G151" s="3" t="n"/>
+      <c r="H151" s="3" t="n"/>
+      <c r="I151" s="3" t="n"/>
+      <c r="J151" s="3" t="n"/>
+      <c r="L151" s="3" t="n"/>
+      <c r="M151" s="3" t="n"/>
+      <c r="Q151" s="3" t="n"/>
+      <c r="R151" s="3" t="n"/>
+      <c r="S151" s="3" t="n"/>
+      <c r="T151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -4316,24 +5368,31 @@
           <t>Poliwag</t>
         </is>
       </c>
-      <c r="B152" s="3" t="inlineStr">
+      <c r="B152" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C152" s="3" t="n">
+      <c r="E152" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D152" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F152" s="3">
-        <f>IF(B152="common", 4, IF(B152="uncommon", 3, IF(B152="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F152" s="3" t="n"/>
+      <c r="G152" s="3" t="n"/>
+      <c r="H152" s="3" t="n"/>
+      <c r="I152" s="3" t="n"/>
+      <c r="J152" s="3" t="n"/>
+      <c r="L152" s="3" t="n"/>
+      <c r="M152" s="3" t="n"/>
+      <c r="Q152" s="3" t="n"/>
+      <c r="R152" s="3" t="n"/>
+      <c r="S152" s="3" t="n"/>
+      <c r="T152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -4341,24 +5400,31 @@
           <t>Poliwhirl - 061/165</t>
         </is>
       </c>
-      <c r="B153" s="3" t="inlineStr">
+      <c r="B153" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C153" s="3" t="n">
+      <c r="E153" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D153" s="3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E153" s="3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="F153" s="3">
-        <f>IF(B153="common", 4, IF(B153="uncommon", 3, IF(B153="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F153" s="3" t="n"/>
+      <c r="G153" s="3" t="n"/>
+      <c r="H153" s="3" t="n"/>
+      <c r="I153" s="3" t="n"/>
+      <c r="J153" s="3" t="n"/>
+      <c r="L153" s="3" t="n"/>
+      <c r="M153" s="3" t="n"/>
+      <c r="Q153" s="3" t="n"/>
+      <c r="R153" s="3" t="n"/>
+      <c r="S153" s="3" t="n"/>
+      <c r="T153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
@@ -4366,22 +5432,29 @@
           <t>Poliwhirl - 176/165</t>
         </is>
       </c>
-      <c r="B154" s="3" t="inlineStr">
+      <c r="B154" s="3" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="C154" s="3" t="inlineStr"/>
+      <c r="D154" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C154" s="3" t="n">
+      <c r="E154" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D154" s="3" t="n">
-        <v>19.64</v>
-      </c>
-      <c r="E154" s="3" t="inlineStr"/>
-      <c r="F154" s="3">
-        <f>IF(B154="common", 4, IF(B154="uncommon", 3, IF(B154="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F154" s="3" t="n"/>
+      <c r="G154" s="3" t="n"/>
+      <c r="H154" s="3" t="n"/>
+      <c r="I154" s="3" t="n"/>
+      <c r="J154" s="3" t="n"/>
+      <c r="L154" s="3" t="n"/>
+      <c r="M154" s="3" t="n"/>
+      <c r="Q154" s="3" t="n"/>
+      <c r="R154" s="3" t="n"/>
+      <c r="S154" s="3" t="n"/>
+      <c r="T154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
@@ -4389,24 +5462,31 @@
           <t>Poliwrath</t>
         </is>
       </c>
-      <c r="B155" s="3" t="inlineStr">
+      <c r="B155" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C155" s="3" t="n">
+      <c r="E155" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D155" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E155" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F155" s="3">
-        <f>IF(B155="common", 4, IF(B155="uncommon", 3, IF(B155="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F155" s="3" t="n"/>
+      <c r="G155" s="3" t="n"/>
+      <c r="H155" s="3" t="n"/>
+      <c r="I155" s="3" t="n"/>
+      <c r="J155" s="3" t="n"/>
+      <c r="L155" s="3" t="n"/>
+      <c r="M155" s="3" t="n"/>
+      <c r="Q155" s="3" t="n"/>
+      <c r="R155" s="3" t="n"/>
+      <c r="S155" s="3" t="n"/>
+      <c r="T155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -4414,24 +5494,31 @@
           <t>Ponyta</t>
         </is>
       </c>
-      <c r="B156" s="3" t="inlineStr">
+      <c r="B156" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C156" s="3" t="n">
+      <c r="E156" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D156" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E156" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F156" s="3">
-        <f>IF(B156="common", 4, IF(B156="uncommon", 3, IF(B156="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F156" s="3" t="n"/>
+      <c r="G156" s="3" t="n"/>
+      <c r="H156" s="3" t="n"/>
+      <c r="I156" s="3" t="n"/>
+      <c r="J156" s="3" t="n"/>
+      <c r="L156" s="3" t="n"/>
+      <c r="M156" s="3" t="n"/>
+      <c r="Q156" s="3" t="n"/>
+      <c r="R156" s="3" t="n"/>
+      <c r="S156" s="3" t="n"/>
+      <c r="T156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -4439,24 +5526,31 @@
           <t>Porygon</t>
         </is>
       </c>
-      <c r="B157" s="3" t="inlineStr">
+      <c r="B157" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C157" s="3" t="n">
+      <c r="E157" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D157" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E157" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F157" s="3">
-        <f>IF(B157="common", 4, IF(B157="uncommon", 3, IF(B157="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F157" s="3" t="n"/>
+      <c r="G157" s="3" t="n"/>
+      <c r="H157" s="3" t="n"/>
+      <c r="I157" s="3" t="n"/>
+      <c r="J157" s="3" t="n"/>
+      <c r="L157" s="3" t="n"/>
+      <c r="M157" s="3" t="n"/>
+      <c r="Q157" s="3" t="n"/>
+      <c r="R157" s="3" t="n"/>
+      <c r="S157" s="3" t="n"/>
+      <c r="T157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -4464,24 +5558,31 @@
           <t>Primeape</t>
         </is>
       </c>
-      <c r="B158" s="3" t="inlineStr">
+      <c r="B158" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C158" s="3" t="n">
+      <c r="E158" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D158" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E158" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F158" s="3">
-        <f>IF(B158="common", 4, IF(B158="uncommon", 3, IF(B158="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F158" s="3" t="n"/>
+      <c r="G158" s="3" t="n"/>
+      <c r="H158" s="3" t="n"/>
+      <c r="I158" s="3" t="n"/>
+      <c r="J158" s="3" t="n"/>
+      <c r="L158" s="3" t="n"/>
+      <c r="M158" s="3" t="n"/>
+      <c r="Q158" s="3" t="n"/>
+      <c r="R158" s="3" t="n"/>
+      <c r="S158" s="3" t="n"/>
+      <c r="T158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -4489,24 +5590,31 @@
           <t>Protective Goggles</t>
         </is>
       </c>
-      <c r="B159" s="3" t="inlineStr">
+      <c r="B159" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C159" s="3" t="n">
+      <c r="E159" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D159" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F159" s="3">
-        <f>IF(B159="common", 4, IF(B159="uncommon", 3, IF(B159="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F159" s="3" t="n"/>
+      <c r="G159" s="3" t="n"/>
+      <c r="H159" s="3" t="n"/>
+      <c r="I159" s="3" t="n"/>
+      <c r="J159" s="3" t="n"/>
+      <c r="L159" s="3" t="n"/>
+      <c r="M159" s="3" t="n"/>
+      <c r="Q159" s="3" t="n"/>
+      <c r="R159" s="3" t="n"/>
+      <c r="S159" s="3" t="n"/>
+      <c r="T159" s="3" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -4514,24 +5622,31 @@
           <t>Psyduck - 054/165</t>
         </is>
       </c>
-      <c r="B160" s="3" t="inlineStr">
+      <c r="B160" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C160" s="3" t="n">
+      <c r="E160" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D160" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E160" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F160" s="3">
-        <f>IF(B160="common", 4, IF(B160="uncommon", 3, IF(B160="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F160" s="3" t="n"/>
+      <c r="G160" s="3" t="n"/>
+      <c r="H160" s="3" t="n"/>
+      <c r="I160" s="3" t="n"/>
+      <c r="J160" s="3" t="n"/>
+      <c r="L160" s="3" t="n"/>
+      <c r="M160" s="3" t="n"/>
+      <c r="Q160" s="3" t="n"/>
+      <c r="R160" s="3" t="n"/>
+      <c r="S160" s="3" t="n"/>
+      <c r="T160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -4539,22 +5654,29 @@
           <t>Psyduck - 175/165</t>
         </is>
       </c>
-      <c r="B161" s="3" t="inlineStr">
+      <c r="B161" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="C161" s="3" t="inlineStr"/>
+      <c r="D161" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C161" s="3" t="n">
+      <c r="E161" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D161" s="3" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="E161" s="3" t="inlineStr"/>
-      <c r="F161" s="3">
-        <f>IF(B161="common", 4, IF(B161="uncommon", 3, IF(B161="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F161" s="3" t="n"/>
+      <c r="G161" s="3" t="n"/>
+      <c r="H161" s="3" t="n"/>
+      <c r="I161" s="3" t="n"/>
+      <c r="J161" s="3" t="n"/>
+      <c r="L161" s="3" t="n"/>
+      <c r="M161" s="3" t="n"/>
+      <c r="Q161" s="3" t="n"/>
+      <c r="R161" s="3" t="n"/>
+      <c r="S161" s="3" t="n"/>
+      <c r="T161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
@@ -4562,24 +5684,31 @@
           <t>Raichu</t>
         </is>
       </c>
-      <c r="B162" s="3" t="inlineStr">
+      <c r="B162" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C162" s="3" t="n">
+      <c r="E162" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D162" s="3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E162" s="3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="F162" s="3">
-        <f>IF(B162="common", 4, IF(B162="uncommon", 3, IF(B162="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F162" s="3" t="n"/>
+      <c r="G162" s="3" t="n"/>
+      <c r="H162" s="3" t="n"/>
+      <c r="I162" s="3" t="n"/>
+      <c r="J162" s="3" t="n"/>
+      <c r="L162" s="3" t="n"/>
+      <c r="M162" s="3" t="n"/>
+      <c r="Q162" s="3" t="n"/>
+      <c r="R162" s="3" t="n"/>
+      <c r="S162" s="3" t="n"/>
+      <c r="T162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -4587,24 +5716,31 @@
           <t>Rapidash</t>
         </is>
       </c>
-      <c r="B163" s="3" t="inlineStr">
+      <c r="B163" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C163" s="3" t="n">
+      <c r="E163" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D163" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F163" s="3">
-        <f>IF(B163="common", 4, IF(B163="uncommon", 3, IF(B163="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F163" s="3" t="n"/>
+      <c r="G163" s="3" t="n"/>
+      <c r="H163" s="3" t="n"/>
+      <c r="I163" s="3" t="n"/>
+      <c r="J163" s="3" t="n"/>
+      <c r="L163" s="3" t="n"/>
+      <c r="M163" s="3" t="n"/>
+      <c r="Q163" s="3" t="n"/>
+      <c r="R163" s="3" t="n"/>
+      <c r="S163" s="3" t="n"/>
+      <c r="T163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -4612,24 +5748,31 @@
           <t>Raticate</t>
         </is>
       </c>
-      <c r="B164" s="3" t="inlineStr">
+      <c r="B164" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C164" s="3" t="n">
+      <c r="E164" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D164" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E164" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F164" s="3">
-        <f>IF(B164="common", 4, IF(B164="uncommon", 3, IF(B164="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F164" s="3" t="n"/>
+      <c r="G164" s="3" t="n"/>
+      <c r="H164" s="3" t="n"/>
+      <c r="I164" s="3" t="n"/>
+      <c r="J164" s="3" t="n"/>
+      <c r="L164" s="3" t="n"/>
+      <c r="M164" s="3" t="n"/>
+      <c r="Q164" s="3" t="n"/>
+      <c r="R164" s="3" t="n"/>
+      <c r="S164" s="3" t="n"/>
+      <c r="T164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -4637,24 +5780,31 @@
           <t>Rattata</t>
         </is>
       </c>
-      <c r="B165" s="3" t="inlineStr">
+      <c r="B165" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C165" s="3" t="n">
+      <c r="E165" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D165" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F165" s="3">
-        <f>IF(B165="common", 4, IF(B165="uncommon", 3, IF(B165="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F165" s="3" t="n"/>
+      <c r="G165" s="3" t="n"/>
+      <c r="H165" s="3" t="n"/>
+      <c r="I165" s="3" t="n"/>
+      <c r="J165" s="3" t="n"/>
+      <c r="L165" s="3" t="n"/>
+      <c r="M165" s="3" t="n"/>
+      <c r="Q165" s="3" t="n"/>
+      <c r="R165" s="3" t="n"/>
+      <c r="S165" s="3" t="n"/>
+      <c r="T165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -4662,24 +5812,31 @@
           <t>Rhydon</t>
         </is>
       </c>
-      <c r="B166" s="3" t="inlineStr">
+      <c r="B166" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C166" s="3" t="n">
+      <c r="E166" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D166" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F166" s="3">
-        <f>IF(B166="common", 4, IF(B166="uncommon", 3, IF(B166="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F166" s="3" t="n"/>
+      <c r="G166" s="3" t="n"/>
+      <c r="H166" s="3" t="n"/>
+      <c r="I166" s="3" t="n"/>
+      <c r="J166" s="3" t="n"/>
+      <c r="L166" s="3" t="n"/>
+      <c r="M166" s="3" t="n"/>
+      <c r="Q166" s="3" t="n"/>
+      <c r="R166" s="3" t="n"/>
+      <c r="S166" s="3" t="n"/>
+      <c r="T166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -4687,24 +5844,31 @@
           <t>Rhyhorn</t>
         </is>
       </c>
-      <c r="B167" s="3" t="inlineStr">
+      <c r="B167" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C167" s="3" t="n">
+      <c r="E167" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D167" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E167" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F167" s="3">
-        <f>IF(B167="common", 4, IF(B167="uncommon", 3, IF(B167="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F167" s="3" t="n"/>
+      <c r="G167" s="3" t="n"/>
+      <c r="H167" s="3" t="n"/>
+      <c r="I167" s="3" t="n"/>
+      <c r="J167" s="3" t="n"/>
+      <c r="L167" s="3" t="n"/>
+      <c r="M167" s="3" t="n"/>
+      <c r="Q167" s="3" t="n"/>
+      <c r="R167" s="3" t="n"/>
+      <c r="S167" s="3" t="n"/>
+      <c r="T167" s="3" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
@@ -4712,24 +5876,31 @@
           <t>Rigid Band</t>
         </is>
       </c>
-      <c r="B168" s="3" t="inlineStr">
+      <c r="B168" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C168" s="3" t="n">
+      <c r="E168" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D168" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E168" s="3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F168" s="3">
-        <f>IF(B168="common", 4, IF(B168="uncommon", 3, IF(B168="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F168" s="3" t="n"/>
+      <c r="G168" s="3" t="n"/>
+      <c r="H168" s="3" t="n"/>
+      <c r="I168" s="3" t="n"/>
+      <c r="J168" s="3" t="n"/>
+      <c r="L168" s="3" t="n"/>
+      <c r="M168" s="3" t="n"/>
+      <c r="Q168" s="3" t="n"/>
+      <c r="R168" s="3" t="n"/>
+      <c r="S168" s="3" t="n"/>
+      <c r="T168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
@@ -4737,24 +5908,31 @@
           <t>Sandshrew</t>
         </is>
       </c>
-      <c r="B169" s="3" t="inlineStr">
+      <c r="B169" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C169" s="3" t="n">
+      <c r="E169" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D169" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E169" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F169" s="3">
-        <f>IF(B169="common", 4, IF(B169="uncommon", 3, IF(B169="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F169" s="3" t="n"/>
+      <c r="G169" s="3" t="n"/>
+      <c r="H169" s="3" t="n"/>
+      <c r="I169" s="3" t="n"/>
+      <c r="J169" s="3" t="n"/>
+      <c r="L169" s="3" t="n"/>
+      <c r="M169" s="3" t="n"/>
+      <c r="Q169" s="3" t="n"/>
+      <c r="R169" s="3" t="n"/>
+      <c r="S169" s="3" t="n"/>
+      <c r="T169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -4762,24 +5940,31 @@
           <t>Sandslash</t>
         </is>
       </c>
-      <c r="B170" s="3" t="inlineStr">
+      <c r="B170" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C170" s="3" t="n">
+      <c r="E170" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D170" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E170" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F170" s="3">
-        <f>IF(B170="common", 4, IF(B170="uncommon", 3, IF(B170="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F170" s="3" t="n"/>
+      <c r="G170" s="3" t="n"/>
+      <c r="H170" s="3" t="n"/>
+      <c r="I170" s="3" t="n"/>
+      <c r="J170" s="3" t="n"/>
+      <c r="L170" s="3" t="n"/>
+      <c r="M170" s="3" t="n"/>
+      <c r="Q170" s="3" t="n"/>
+      <c r="R170" s="3" t="n"/>
+      <c r="S170" s="3" t="n"/>
+      <c r="T170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -4787,24 +5972,31 @@
           <t>Scyther</t>
         </is>
       </c>
-      <c r="B171" s="3" t="inlineStr">
+      <c r="B171" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C171" s="3" t="n">
+      <c r="E171" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D171" s="3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E171" s="3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="F171" s="3">
-        <f>IF(B171="common", 4, IF(B171="uncommon", 3, IF(B171="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F171" s="3" t="n"/>
+      <c r="G171" s="3" t="n"/>
+      <c r="H171" s="3" t="n"/>
+      <c r="I171" s="3" t="n"/>
+      <c r="J171" s="3" t="n"/>
+      <c r="L171" s="3" t="n"/>
+      <c r="M171" s="3" t="n"/>
+      <c r="Q171" s="3" t="n"/>
+      <c r="R171" s="3" t="n"/>
+      <c r="S171" s="3" t="n"/>
+      <c r="T171" s="3" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -4812,24 +6004,31 @@
           <t>Seadra</t>
         </is>
       </c>
-      <c r="B172" s="3" t="inlineStr">
+      <c r="B172" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C172" s="3" t="n">
+      <c r="E172" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D172" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E172" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F172" s="3">
-        <f>IF(B172="common", 4, IF(B172="uncommon", 3, IF(B172="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F172" s="3" t="n"/>
+      <c r="G172" s="3" t="n"/>
+      <c r="H172" s="3" t="n"/>
+      <c r="I172" s="3" t="n"/>
+      <c r="J172" s="3" t="n"/>
+      <c r="L172" s="3" t="n"/>
+      <c r="M172" s="3" t="n"/>
+      <c r="Q172" s="3" t="n"/>
+      <c r="R172" s="3" t="n"/>
+      <c r="S172" s="3" t="n"/>
+      <c r="T172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -4837,24 +6036,31 @@
           <t>Seaking</t>
         </is>
       </c>
-      <c r="B173" s="3" t="inlineStr">
+      <c r="B173" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C173" s="3" t="n">
+      <c r="E173" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D173" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E173" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F173" s="3">
-        <f>IF(B173="common", 4, IF(B173="uncommon", 3, IF(B173="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F173" s="3" t="n"/>
+      <c r="G173" s="3" t="n"/>
+      <c r="H173" s="3" t="n"/>
+      <c r="I173" s="3" t="n"/>
+      <c r="J173" s="3" t="n"/>
+      <c r="L173" s="3" t="n"/>
+      <c r="M173" s="3" t="n"/>
+      <c r="Q173" s="3" t="n"/>
+      <c r="R173" s="3" t="n"/>
+      <c r="S173" s="3" t="n"/>
+      <c r="T173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -4862,24 +6068,31 @@
           <t>Seel</t>
         </is>
       </c>
-      <c r="B174" s="3" t="inlineStr">
+      <c r="B174" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C174" s="3" t="n">
+      <c r="E174" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D174" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E174" s="3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F174" s="3">
-        <f>IF(B174="common", 4, IF(B174="uncommon", 3, IF(B174="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F174" s="3" t="n"/>
+      <c r="G174" s="3" t="n"/>
+      <c r="H174" s="3" t="n"/>
+      <c r="I174" s="3" t="n"/>
+      <c r="J174" s="3" t="n"/>
+      <c r="L174" s="3" t="n"/>
+      <c r="M174" s="3" t="n"/>
+      <c r="Q174" s="3" t="n"/>
+      <c r="R174" s="3" t="n"/>
+      <c r="S174" s="3" t="n"/>
+      <c r="T174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -4887,24 +6100,31 @@
           <t>Shellder</t>
         </is>
       </c>
-      <c r="B175" s="3" t="inlineStr">
+      <c r="B175" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C175" s="3" t="n">
+      <c r="E175" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D175" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E175" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F175" s="3">
-        <f>IF(B175="common", 4, IF(B175="uncommon", 3, IF(B175="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F175" s="3" t="n"/>
+      <c r="G175" s="3" t="n"/>
+      <c r="H175" s="3" t="n"/>
+      <c r="I175" s="3" t="n"/>
+      <c r="J175" s="3" t="n"/>
+      <c r="L175" s="3" t="n"/>
+      <c r="M175" s="3" t="n"/>
+      <c r="Q175" s="3" t="n"/>
+      <c r="R175" s="3" t="n"/>
+      <c r="S175" s="3" t="n"/>
+      <c r="T175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
@@ -4912,24 +6132,31 @@
           <t>Slowbro</t>
         </is>
       </c>
-      <c r="B176" s="3" t="inlineStr">
+      <c r="B176" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C176" s="3" t="n">
+      <c r="E176" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D176" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F176" s="3">
-        <f>IF(B176="common", 4, IF(B176="uncommon", 3, IF(B176="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F176" s="3" t="n"/>
+      <c r="G176" s="3" t="n"/>
+      <c r="H176" s="3" t="n"/>
+      <c r="I176" s="3" t="n"/>
+      <c r="J176" s="3" t="n"/>
+      <c r="L176" s="3" t="n"/>
+      <c r="M176" s="3" t="n"/>
+      <c r="Q176" s="3" t="n"/>
+      <c r="R176" s="3" t="n"/>
+      <c r="S176" s="3" t="n"/>
+      <c r="T176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -4937,24 +6164,31 @@
           <t>Slowpoke</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B177" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C177" s="3" t="n">
+      <c r="E177" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D177" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E177" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="F177" s="3">
-        <f>IF(B177="common", 4, IF(B177="uncommon", 3, IF(B177="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F177" s="3" t="n"/>
+      <c r="G177" s="3" t="n"/>
+      <c r="H177" s="3" t="n"/>
+      <c r="I177" s="3" t="n"/>
+      <c r="J177" s="3" t="n"/>
+      <c r="L177" s="3" t="n"/>
+      <c r="M177" s="3" t="n"/>
+      <c r="Q177" s="3" t="n"/>
+      <c r="R177" s="3" t="n"/>
+      <c r="S177" s="3" t="n"/>
+      <c r="T177" s="3" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -4962,24 +6196,31 @@
           <t>Snorlax</t>
         </is>
       </c>
-      <c r="B178" s="3" t="inlineStr">
+      <c r="B178" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C178" s="3" t="n">
+      <c r="E178" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D178" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E178" s="3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="F178" s="3">
-        <f>IF(B178="common", 4, IF(B178="uncommon", 3, IF(B178="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F178" s="3" t="n"/>
+      <c r="G178" s="3" t="n"/>
+      <c r="H178" s="3" t="n"/>
+      <c r="I178" s="3" t="n"/>
+      <c r="J178" s="3" t="n"/>
+      <c r="L178" s="3" t="n"/>
+      <c r="M178" s="3" t="n"/>
+      <c r="Q178" s="3" t="n"/>
+      <c r="R178" s="3" t="n"/>
+      <c r="S178" s="3" t="n"/>
+      <c r="T178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -4987,24 +6228,31 @@
           <t>Spearow</t>
         </is>
       </c>
-      <c r="B179" s="3" t="inlineStr">
+      <c r="B179" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C179" s="3" t="n">
+      <c r="E179" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D179" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E179" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F179" s="3">
-        <f>IF(B179="common", 4, IF(B179="uncommon", 3, IF(B179="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F179" s="3" t="n"/>
+      <c r="G179" s="3" t="n"/>
+      <c r="H179" s="3" t="n"/>
+      <c r="I179" s="3" t="n"/>
+      <c r="J179" s="3" t="n"/>
+      <c r="L179" s="3" t="n"/>
+      <c r="M179" s="3" t="n"/>
+      <c r="Q179" s="3" t="n"/>
+      <c r="R179" s="3" t="n"/>
+      <c r="S179" s="3" t="n"/>
+      <c r="T179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -5012,24 +6260,31 @@
           <t>Squirtle - 007/165</t>
         </is>
       </c>
-      <c r="B180" s="3" t="inlineStr">
+      <c r="B180" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C180" s="3" t="n">
+      <c r="E180" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D180" s="3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F180" s="3">
-        <f>IF(B180="common", 4, IF(B180="uncommon", 3, IF(B180="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F180" s="3" t="n"/>
+      <c r="G180" s="3" t="n"/>
+      <c r="H180" s="3" t="n"/>
+      <c r="I180" s="3" t="n"/>
+      <c r="J180" s="3" t="n"/>
+      <c r="L180" s="3" t="n"/>
+      <c r="M180" s="3" t="n"/>
+      <c r="Q180" s="3" t="n"/>
+      <c r="R180" s="3" t="n"/>
+      <c r="S180" s="3" t="n"/>
+      <c r="T180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -5037,22 +6292,29 @@
           <t>Squirtle - 170/165</t>
         </is>
       </c>
-      <c r="B181" s="3" t="inlineStr">
+      <c r="B181" s="3" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="C181" s="3" t="inlineStr"/>
+      <c r="D181" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C181" s="3" t="n">
+      <c r="E181" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D181" s="3" t="n">
-        <v>45.09</v>
-      </c>
-      <c r="E181" s="3" t="inlineStr"/>
-      <c r="F181" s="3">
-        <f>IF(B181="common", 4, IF(B181="uncommon", 3, IF(B181="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F181" s="3" t="n"/>
+      <c r="G181" s="3" t="n"/>
+      <c r="H181" s="3" t="n"/>
+      <c r="I181" s="3" t="n"/>
+      <c r="J181" s="3" t="n"/>
+      <c r="L181" s="3" t="n"/>
+      <c r="M181" s="3" t="n"/>
+      <c r="Q181" s="3" t="n"/>
+      <c r="R181" s="3" t="n"/>
+      <c r="S181" s="3" t="n"/>
+      <c r="T181" s="3" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
@@ -5060,24 +6322,31 @@
           <t>Starmie</t>
         </is>
       </c>
-      <c r="B182" s="3" t="inlineStr">
+      <c r="B182" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C182" s="3" t="n">
+      <c r="E182" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D182" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E182" s="3" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="F182" s="3">
-        <f>IF(B182="common", 4, IF(B182="uncommon", 3, IF(B182="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F182" s="3" t="n"/>
+      <c r="G182" s="3" t="n"/>
+      <c r="H182" s="3" t="n"/>
+      <c r="I182" s="3" t="n"/>
+      <c r="J182" s="3" t="n"/>
+      <c r="L182" s="3" t="n"/>
+      <c r="M182" s="3" t="n"/>
+      <c r="Q182" s="3" t="n"/>
+      <c r="R182" s="3" t="n"/>
+      <c r="S182" s="3" t="n"/>
+      <c r="T182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -5085,24 +6354,31 @@
           <t>Staryu</t>
         </is>
       </c>
-      <c r="B183" s="3" t="inlineStr">
+      <c r="B183" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C183" s="3" t="n">
+      <c r="E183" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D183" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E183" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F183" s="3">
-        <f>IF(B183="common", 4, IF(B183="uncommon", 3, IF(B183="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F183" s="3" t="n"/>
+      <c r="G183" s="3" t="n"/>
+      <c r="H183" s="3" t="n"/>
+      <c r="I183" s="3" t="n"/>
+      <c r="J183" s="3" t="n"/>
+      <c r="L183" s="3" t="n"/>
+      <c r="M183" s="3" t="n"/>
+      <c r="Q183" s="3" t="n"/>
+      <c r="R183" s="3" t="n"/>
+      <c r="S183" s="3" t="n"/>
+      <c r="T183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -5110,22 +6386,29 @@
           <t>Switch - 206/165</t>
         </is>
       </c>
-      <c r="B184" s="3" t="inlineStr">
+      <c r="B184" s="3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C184" s="3" t="inlineStr"/>
+      <c r="D184" s="3" t="inlineStr">
         <is>
           <t>hyper rare</t>
         </is>
       </c>
-      <c r="C184" s="3" t="n">
+      <c r="E184" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="D184" s="3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E184" s="3" t="inlineStr"/>
-      <c r="F184" s="3">
-        <f>IF(B184="common", 4, IF(B184="uncommon", 3, IF(B184="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F184" s="3" t="n"/>
+      <c r="G184" s="3" t="n"/>
+      <c r="H184" s="3" t="n"/>
+      <c r="I184" s="3" t="n"/>
+      <c r="J184" s="3" t="n"/>
+      <c r="L184" s="3" t="n"/>
+      <c r="M184" s="3" t="n"/>
+      <c r="Q184" s="3" t="n"/>
+      <c r="R184" s="3" t="n"/>
+      <c r="S184" s="3" t="n"/>
+      <c r="T184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -5133,24 +6416,31 @@
           <t>Tangela - 114/165</t>
         </is>
       </c>
-      <c r="B185" s="3" t="inlineStr">
+      <c r="B185" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C185" s="3" t="n">
+      <c r="E185" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D185" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E185" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F185" s="3">
-        <f>IF(B185="common", 4, IF(B185="uncommon", 3, IF(B185="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F185" s="3" t="n"/>
+      <c r="G185" s="3" t="n"/>
+      <c r="H185" s="3" t="n"/>
+      <c r="I185" s="3" t="n"/>
+      <c r="J185" s="3" t="n"/>
+      <c r="L185" s="3" t="n"/>
+      <c r="M185" s="3" t="n"/>
+      <c r="Q185" s="3" t="n"/>
+      <c r="R185" s="3" t="n"/>
+      <c r="S185" s="3" t="n"/>
+      <c r="T185" s="3" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -5158,22 +6448,29 @@
           <t>Tangela - 178/165</t>
         </is>
       </c>
-      <c r="B186" s="3" t="inlineStr">
+      <c r="B186" s="3" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="C186" s="3" t="inlineStr"/>
+      <c r="D186" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C186" s="3" t="n">
+      <c r="E186" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D186" s="3" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="E186" s="3" t="inlineStr"/>
-      <c r="F186" s="3">
-        <f>IF(B186="common", 4, IF(B186="uncommon", 3, IF(B186="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F186" s="3" t="n"/>
+      <c r="G186" s="3" t="n"/>
+      <c r="H186" s="3" t="n"/>
+      <c r="I186" s="3" t="n"/>
+      <c r="J186" s="3" t="n"/>
+      <c r="L186" s="3" t="n"/>
+      <c r="M186" s="3" t="n"/>
+      <c r="Q186" s="3" t="n"/>
+      <c r="R186" s="3" t="n"/>
+      <c r="S186" s="3" t="n"/>
+      <c r="T186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -5181,24 +6478,31 @@
           <t>Tauros</t>
         </is>
       </c>
-      <c r="B187" s="3" t="inlineStr">
+      <c r="B187" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C187" s="3" t="n">
+      <c r="E187" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D187" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E187" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F187" s="3">
-        <f>IF(B187="common", 4, IF(B187="uncommon", 3, IF(B187="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F187" s="3" t="n"/>
+      <c r="G187" s="3" t="n"/>
+      <c r="H187" s="3" t="n"/>
+      <c r="I187" s="3" t="n"/>
+      <c r="J187" s="3" t="n"/>
+      <c r="L187" s="3" t="n"/>
+      <c r="M187" s="3" t="n"/>
+      <c r="Q187" s="3" t="n"/>
+      <c r="R187" s="3" t="n"/>
+      <c r="S187" s="3" t="n"/>
+      <c r="T187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -5206,24 +6510,31 @@
           <t>Tentacool</t>
         </is>
       </c>
-      <c r="B188" s="3" t="inlineStr">
+      <c r="B188" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C188" s="3" t="n">
+      <c r="E188" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D188" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E188" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F188" s="3">
-        <f>IF(B188="common", 4, IF(B188="uncommon", 3, IF(B188="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F188" s="3" t="n"/>
+      <c r="G188" s="3" t="n"/>
+      <c r="H188" s="3" t="n"/>
+      <c r="I188" s="3" t="n"/>
+      <c r="J188" s="3" t="n"/>
+      <c r="L188" s="3" t="n"/>
+      <c r="M188" s="3" t="n"/>
+      <c r="Q188" s="3" t="n"/>
+      <c r="R188" s="3" t="n"/>
+      <c r="S188" s="3" t="n"/>
+      <c r="T188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -5231,24 +6542,31 @@
           <t>Tentacruel</t>
         </is>
       </c>
-      <c r="B189" s="3" t="inlineStr">
+      <c r="B189" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C189" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C189" s="3" t="n">
+      <c r="E189" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D189" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E189" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F189" s="3">
-        <f>IF(B189="common", 4, IF(B189="uncommon", 3, IF(B189="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F189" s="3" t="n"/>
+      <c r="G189" s="3" t="n"/>
+      <c r="H189" s="3" t="n"/>
+      <c r="I189" s="3" t="n"/>
+      <c r="J189" s="3" t="n"/>
+      <c r="L189" s="3" t="n"/>
+      <c r="M189" s="3" t="n"/>
+      <c r="Q189" s="3" t="n"/>
+      <c r="R189" s="3" t="n"/>
+      <c r="S189" s="3" t="n"/>
+      <c r="T189" s="3" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
@@ -5256,24 +6574,31 @@
           <t>Vaporeon</t>
         </is>
       </c>
-      <c r="B190" s="3" t="inlineStr">
+      <c r="B190" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C190" s="3" t="n">
+      <c r="E190" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D190" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E190" s="3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F190" s="3">
-        <f>IF(B190="common", 4, IF(B190="uncommon", 3, IF(B190="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F190" s="3" t="n"/>
+      <c r="G190" s="3" t="n"/>
+      <c r="H190" s="3" t="n"/>
+      <c r="I190" s="3" t="n"/>
+      <c r="J190" s="3" t="n"/>
+      <c r="L190" s="3" t="n"/>
+      <c r="M190" s="3" t="n"/>
+      <c r="Q190" s="3" t="n"/>
+      <c r="R190" s="3" t="n"/>
+      <c r="S190" s="3" t="n"/>
+      <c r="T190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -5281,24 +6606,31 @@
           <t>Venomoth</t>
         </is>
       </c>
-      <c r="B191" s="3" t="inlineStr">
+      <c r="B191" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C191" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C191" s="3" t="n">
+      <c r="E191" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D191" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E191" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="F191" s="3">
-        <f>IF(B191="common", 4, IF(B191="uncommon", 3, IF(B191="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F191" s="3" t="n"/>
+      <c r="G191" s="3" t="n"/>
+      <c r="H191" s="3" t="n"/>
+      <c r="I191" s="3" t="n"/>
+      <c r="J191" s="3" t="n"/>
+      <c r="L191" s="3" t="n"/>
+      <c r="M191" s="3" t="n"/>
+      <c r="Q191" s="3" t="n"/>
+      <c r="R191" s="3" t="n"/>
+      <c r="S191" s="3" t="n"/>
+      <c r="T191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -5306,24 +6638,31 @@
           <t>Venonat</t>
         </is>
       </c>
-      <c r="B192" s="3" t="inlineStr">
+      <c r="B192" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C192" s="3" t="n">
+      <c r="E192" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D192" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E192" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F192" s="3">
-        <f>IF(B192="common", 4, IF(B192="uncommon", 3, IF(B192="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F192" s="3" t="n"/>
+      <c r="G192" s="3" t="n"/>
+      <c r="H192" s="3" t="n"/>
+      <c r="I192" s="3" t="n"/>
+      <c r="J192" s="3" t="n"/>
+      <c r="L192" s="3" t="n"/>
+      <c r="M192" s="3" t="n"/>
+      <c r="Q192" s="3" t="n"/>
+      <c r="R192" s="3" t="n"/>
+      <c r="S192" s="3" t="n"/>
+      <c r="T192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -5331,22 +6670,29 @@
           <t>Venusaur ex - 003/165</t>
         </is>
       </c>
-      <c r="B193" s="3" t="inlineStr">
+      <c r="B193" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="C193" s="3" t="inlineStr"/>
+      <c r="D193" s="3" t="inlineStr">
         <is>
           <t>double rare</t>
         </is>
       </c>
-      <c r="C193" s="3" t="n">
+      <c r="E193" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D193" s="3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E193" s="3" t="inlineStr"/>
-      <c r="F193" s="3">
-        <f>IF(B193="common", 4, IF(B193="uncommon", 3, IF(B193="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F193" s="3" t="n"/>
+      <c r="G193" s="3" t="n"/>
+      <c r="H193" s="3" t="n"/>
+      <c r="I193" s="3" t="n"/>
+      <c r="J193" s="3" t="n"/>
+      <c r="L193" s="3" t="n"/>
+      <c r="M193" s="3" t="n"/>
+      <c r="Q193" s="3" t="n"/>
+      <c r="R193" s="3" t="n"/>
+      <c r="S193" s="3" t="n"/>
+      <c r="T193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -5354,22 +6700,29 @@
           <t>Venusaur ex - 182/165</t>
         </is>
       </c>
-      <c r="B194" s="3" t="inlineStr">
+      <c r="B194" s="3" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="C194" s="3" t="inlineStr"/>
+      <c r="D194" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C194" s="3" t="n">
+      <c r="E194" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D194" s="3" t="n">
-        <v>11.58</v>
-      </c>
-      <c r="E194" s="3" t="inlineStr"/>
-      <c r="F194" s="3">
-        <f>IF(B194="common", 4, IF(B194="uncommon", 3, IF(B194="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F194" s="3" t="n"/>
+      <c r="G194" s="3" t="n"/>
+      <c r="H194" s="3" t="n"/>
+      <c r="I194" s="3" t="n"/>
+      <c r="J194" s="3" t="n"/>
+      <c r="L194" s="3" t="n"/>
+      <c r="M194" s="3" t="n"/>
+      <c r="Q194" s="3" t="n"/>
+      <c r="R194" s="3" t="n"/>
+      <c r="S194" s="3" t="n"/>
+      <c r="T194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -5377,22 +6730,29 @@
           <t>Venusaur ex - 198/165</t>
         </is>
       </c>
-      <c r="B195" s="3" t="inlineStr">
+      <c r="B195" s="3" t="n">
+        <v>66.29000000000001</v>
+      </c>
+      <c r="C195" s="3" t="inlineStr"/>
+      <c r="D195" s="3" t="inlineStr">
         <is>
           <t>special illustration rare</t>
         </is>
       </c>
-      <c r="C195" s="3" t="n">
+      <c r="E195" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="D195" s="3" t="n">
-        <v>67.88</v>
-      </c>
-      <c r="E195" s="3" t="inlineStr"/>
-      <c r="F195" s="3">
-        <f>IF(B195="common", 4, IF(B195="uncommon", 3, IF(B195="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F195" s="3" t="n"/>
+      <c r="G195" s="3" t="n"/>
+      <c r="H195" s="3" t="n"/>
+      <c r="I195" s="3" t="n"/>
+      <c r="J195" s="3" t="n"/>
+      <c r="L195" s="3" t="n"/>
+      <c r="M195" s="3" t="n"/>
+      <c r="Q195" s="3" t="n"/>
+      <c r="R195" s="3" t="n"/>
+      <c r="S195" s="3" t="n"/>
+      <c r="T195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
@@ -5400,24 +6760,31 @@
           <t>Victreebel</t>
         </is>
       </c>
-      <c r="B196" s="3" t="inlineStr">
+      <c r="B196" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C196" s="3" t="n">
+      <c r="E196" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D196" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E196" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F196" s="3">
-        <f>IF(B196="common", 4, IF(B196="uncommon", 3, IF(B196="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F196" s="3" t="n"/>
+      <c r="G196" s="3" t="n"/>
+      <c r="H196" s="3" t="n"/>
+      <c r="I196" s="3" t="n"/>
+      <c r="J196" s="3" t="n"/>
+      <c r="L196" s="3" t="n"/>
+      <c r="M196" s="3" t="n"/>
+      <c r="Q196" s="3" t="n"/>
+      <c r="R196" s="3" t="n"/>
+      <c r="S196" s="3" t="n"/>
+      <c r="T196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -5425,24 +6792,31 @@
           <t>Vileplume</t>
         </is>
       </c>
-      <c r="B197" s="3" t="inlineStr">
+      <c r="B197" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C197" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C197" s="3" t="n">
+      <c r="E197" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D197" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E197" s="3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F197" s="3">
-        <f>IF(B197="common", 4, IF(B197="uncommon", 3, IF(B197="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F197" s="3" t="n"/>
+      <c r="G197" s="3" t="n"/>
+      <c r="H197" s="3" t="n"/>
+      <c r="I197" s="3" t="n"/>
+      <c r="J197" s="3" t="n"/>
+      <c r="L197" s="3" t="n"/>
+      <c r="M197" s="3" t="n"/>
+      <c r="Q197" s="3" t="n"/>
+      <c r="R197" s="3" t="n"/>
+      <c r="S197" s="3" t="n"/>
+      <c r="T197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -5450,24 +6824,31 @@
           <t>Voltorb</t>
         </is>
       </c>
-      <c r="B198" s="3" t="inlineStr">
+      <c r="B198" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C198" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C198" s="3" t="n">
+      <c r="E198" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D198" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E198" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F198" s="3">
-        <f>IF(B198="common", 4, IF(B198="uncommon", 3, IF(B198="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F198" s="3" t="n"/>
+      <c r="G198" s="3" t="n"/>
+      <c r="H198" s="3" t="n"/>
+      <c r="I198" s="3" t="n"/>
+      <c r="J198" s="3" t="n"/>
+      <c r="L198" s="3" t="n"/>
+      <c r="M198" s="3" t="n"/>
+      <c r="Q198" s="3" t="n"/>
+      <c r="R198" s="3" t="n"/>
+      <c r="S198" s="3" t="n"/>
+      <c r="T198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -5475,24 +6856,31 @@
           <t>Vulpix</t>
         </is>
       </c>
-      <c r="B199" s="3" t="inlineStr">
+      <c r="B199" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C199" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C199" s="3" t="n">
+      <c r="E199" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D199" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E199" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F199" s="3">
-        <f>IF(B199="common", 4, IF(B199="uncommon", 3, IF(B199="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F199" s="3" t="n"/>
+      <c r="G199" s="3" t="n"/>
+      <c r="H199" s="3" t="n"/>
+      <c r="I199" s="3" t="n"/>
+      <c r="J199" s="3" t="n"/>
+      <c r="L199" s="3" t="n"/>
+      <c r="M199" s="3" t="n"/>
+      <c r="Q199" s="3" t="n"/>
+      <c r="R199" s="3" t="n"/>
+      <c r="S199" s="3" t="n"/>
+      <c r="T199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -5500,24 +6888,31 @@
           <t>Wartortle - 008/165</t>
         </is>
       </c>
-      <c r="B200" s="3" t="inlineStr">
+      <c r="B200" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="C200" s="3" t="n">
+      <c r="E200" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="D200" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E200" s="3" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F200" s="3">
-        <f>IF(B200="common", 4, IF(B200="uncommon", 3, IF(B200="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F200" s="3" t="n"/>
+      <c r="G200" s="3" t="n"/>
+      <c r="H200" s="3" t="n"/>
+      <c r="I200" s="3" t="n"/>
+      <c r="J200" s="3" t="n"/>
+      <c r="L200" s="3" t="n"/>
+      <c r="M200" s="3" t="n"/>
+      <c r="Q200" s="3" t="n"/>
+      <c r="R200" s="3" t="n"/>
+      <c r="S200" s="3" t="n"/>
+      <c r="T200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -5525,22 +6920,29 @@
           <t>Wartortle - 171/165</t>
         </is>
       </c>
-      <c r="B201" s="3" t="inlineStr">
+      <c r="B201" s="3" t="n">
+        <v>28.22</v>
+      </c>
+      <c r="C201" s="3" t="inlineStr"/>
+      <c r="D201" s="3" t="inlineStr">
         <is>
           <t>illustration rare</t>
         </is>
       </c>
-      <c r="C201" s="3" t="n">
+      <c r="E201" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="D201" s="3" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="E201" s="3" t="inlineStr"/>
-      <c r="F201" s="3">
-        <f>IF(B201="common", 4, IF(B201="uncommon", 3, IF(B201="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F201" s="3" t="n"/>
+      <c r="G201" s="3" t="n"/>
+      <c r="H201" s="3" t="n"/>
+      <c r="I201" s="3" t="n"/>
+      <c r="J201" s="3" t="n"/>
+      <c r="L201" s="3" t="n"/>
+      <c r="M201" s="3" t="n"/>
+      <c r="Q201" s="3" t="n"/>
+      <c r="R201" s="3" t="n"/>
+      <c r="S201" s="3" t="n"/>
+      <c r="T201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -5548,24 +6950,31 @@
           <t>Weedle</t>
         </is>
       </c>
-      <c r="B202" s="3" t="inlineStr">
+      <c r="B202" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C202" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C202" s="3" t="n">
+      <c r="E202" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D202" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E202" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F202" s="3">
-        <f>IF(B202="common", 4, IF(B202="uncommon", 3, IF(B202="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F202" s="3" t="n"/>
+      <c r="G202" s="3" t="n"/>
+      <c r="H202" s="3" t="n"/>
+      <c r="I202" s="3" t="n"/>
+      <c r="J202" s="3" t="n"/>
+      <c r="L202" s="3" t="n"/>
+      <c r="M202" s="3" t="n"/>
+      <c r="Q202" s="3" t="n"/>
+      <c r="R202" s="3" t="n"/>
+      <c r="S202" s="3" t="n"/>
+      <c r="T202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
@@ -5573,24 +6982,31 @@
           <t>Weepinbell</t>
         </is>
       </c>
-      <c r="B203" s="3" t="inlineStr">
+      <c r="B203" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C203" s="3" t="n">
+      <c r="E203" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D203" s="3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E203" s="3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="F203" s="3">
-        <f>IF(B203="common", 4, IF(B203="uncommon", 3, IF(B203="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F203" s="3" t="n"/>
+      <c r="G203" s="3" t="n"/>
+      <c r="H203" s="3" t="n"/>
+      <c r="I203" s="3" t="n"/>
+      <c r="J203" s="3" t="n"/>
+      <c r="L203" s="3" t="n"/>
+      <c r="M203" s="3" t="n"/>
+      <c r="Q203" s="3" t="n"/>
+      <c r="R203" s="3" t="n"/>
+      <c r="S203" s="3" t="n"/>
+      <c r="T203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
@@ -5598,24 +7014,31 @@
           <t>Weezing</t>
         </is>
       </c>
-      <c r="B204" s="3" t="inlineStr">
+      <c r="B204" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C204" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="C204" s="3" t="n">
+      <c r="E204" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D204" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E204" s="3" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F204" s="3">
-        <f>IF(B204="common", 4, IF(B204="uncommon", 3, IF(B204="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F204" s="3" t="n"/>
+      <c r="G204" s="3" t="n"/>
+      <c r="H204" s="3" t="n"/>
+      <c r="I204" s="3" t="n"/>
+      <c r="J204" s="3" t="n"/>
+      <c r="L204" s="3" t="n"/>
+      <c r="M204" s="3" t="n"/>
+      <c r="Q204" s="3" t="n"/>
+      <c r="R204" s="3" t="n"/>
+      <c r="S204" s="3" t="n"/>
+      <c r="T204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -5623,22 +7046,29 @@
           <t>Wigglytuff ex - 040/165</t>
         </is>
       </c>
-      <c r="B205" s="3" t="inlineStr">
+      <c r="B205" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C205" s="3" t="inlineStr"/>
+      <c r="D205" s="3" t="inlineStr">
         <is>
           <t>double rare</t>
         </is>
       </c>
-      <c r="C205" s="3" t="n">
+      <c r="E205" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D205" s="3" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E205" s="3" t="inlineStr"/>
-      <c r="F205" s="3">
-        <f>IF(B205="common", 4, IF(B205="uncommon", 3, IF(B205="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F205" s="3" t="n"/>
+      <c r="G205" s="3" t="n"/>
+      <c r="H205" s="3" t="n"/>
+      <c r="I205" s="3" t="n"/>
+      <c r="J205" s="3" t="n"/>
+      <c r="L205" s="3" t="n"/>
+      <c r="M205" s="3" t="n"/>
+      <c r="Q205" s="3" t="n"/>
+      <c r="R205" s="3" t="n"/>
+      <c r="S205" s="3" t="n"/>
+      <c r="T205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -5646,22 +7076,29 @@
           <t>Wigglytuff ex - 187/165</t>
         </is>
       </c>
-      <c r="B206" s="3" t="inlineStr">
+      <c r="B206" s="3" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="C206" s="3" t="inlineStr"/>
+      <c r="D206" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C206" s="3" t="n">
+      <c r="E206" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D206" s="3" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="E206" s="3" t="inlineStr"/>
-      <c r="F206" s="3">
-        <f>IF(B206="common", 4, IF(B206="uncommon", 3, IF(B206="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F206" s="3" t="n"/>
+      <c r="G206" s="3" t="n"/>
+      <c r="H206" s="3" t="n"/>
+      <c r="I206" s="3" t="n"/>
+      <c r="J206" s="3" t="n"/>
+      <c r="L206" s="3" t="n"/>
+      <c r="M206" s="3" t="n"/>
+      <c r="Q206" s="3" t="n"/>
+      <c r="R206" s="3" t="n"/>
+      <c r="S206" s="3" t="n"/>
+      <c r="T206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -5669,22 +7106,29 @@
           <t>Zapdos ex - 145/165</t>
         </is>
       </c>
-      <c r="B207" s="3" t="inlineStr">
+      <c r="B207" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="C207" s="3" t="inlineStr"/>
+      <c r="D207" s="3" t="inlineStr">
         <is>
           <t>double rare</t>
         </is>
       </c>
-      <c r="C207" s="3" t="n">
+      <c r="E207" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D207" s="3" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E207" s="3" t="inlineStr"/>
-      <c r="F207" s="3">
-        <f>IF(B207="common", 4, IF(B207="uncommon", 3, IF(B207="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F207" s="3" t="n"/>
+      <c r="G207" s="3" t="n"/>
+      <c r="H207" s="3" t="n"/>
+      <c r="I207" s="3" t="n"/>
+      <c r="J207" s="3" t="n"/>
+      <c r="L207" s="3" t="n"/>
+      <c r="M207" s="3" t="n"/>
+      <c r="Q207" s="3" t="n"/>
+      <c r="R207" s="3" t="n"/>
+      <c r="S207" s="3" t="n"/>
+      <c r="T207" s="3" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -5692,22 +7136,29 @@
           <t>Zapdos ex - 192/165</t>
         </is>
       </c>
-      <c r="B208" s="3" t="inlineStr">
+      <c r="B208" s="3" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="C208" s="3" t="inlineStr"/>
+      <c r="D208" s="3" t="inlineStr">
         <is>
           <t>ultra rare</t>
         </is>
       </c>
-      <c r="C208" s="3" t="n">
+      <c r="E208" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="D208" s="3" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="E208" s="3" t="inlineStr"/>
-      <c r="F208" s="3">
-        <f>IF(B208="common", 4, IF(B208="uncommon", 3, IF(B208="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F208" s="3" t="n"/>
+      <c r="G208" s="3" t="n"/>
+      <c r="H208" s="3" t="n"/>
+      <c r="I208" s="3" t="n"/>
+      <c r="J208" s="3" t="n"/>
+      <c r="L208" s="3" t="n"/>
+      <c r="M208" s="3" t="n"/>
+      <c r="Q208" s="3" t="n"/>
+      <c r="R208" s="3" t="n"/>
+      <c r="S208" s="3" t="n"/>
+      <c r="T208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -5715,22 +7166,29 @@
           <t>Zapdos ex - 202/165</t>
         </is>
       </c>
-      <c r="B209" s="3" t="inlineStr">
+      <c r="B209" s="3" t="n">
+        <v>54.16</v>
+      </c>
+      <c r="C209" s="3" t="inlineStr"/>
+      <c r="D209" s="3" t="inlineStr">
         <is>
           <t>special illustration rare</t>
         </is>
       </c>
-      <c r="C209" s="3" t="n">
+      <c r="E209" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="D209" s="3" t="n">
-        <v>55.64</v>
-      </c>
-      <c r="E209" s="3" t="inlineStr"/>
-      <c r="F209" s="3">
-        <f>IF(B209="common", 4, IF(B209="uncommon", 3, IF(B209="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F209" s="3" t="n"/>
+      <c r="G209" s="3" t="n"/>
+      <c r="H209" s="3" t="n"/>
+      <c r="I209" s="3" t="n"/>
+      <c r="J209" s="3" t="n"/>
+      <c r="L209" s="3" t="n"/>
+      <c r="M209" s="3" t="n"/>
+      <c r="Q209" s="3" t="n"/>
+      <c r="R209" s="3" t="n"/>
+      <c r="S209" s="3" t="n"/>
+      <c r="T209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
@@ -5738,24 +7196,31 @@
           <t>Zubat</t>
         </is>
       </c>
-      <c r="B210" s="3" t="inlineStr">
+      <c r="B210" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C210" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C210" s="3" t="n">
+      <c r="E210" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="D210" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E210" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F210" s="3">
-        <f>IF(B210="common", 4, IF(B210="uncommon", 3, IF(B210="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F210" s="3" t="n"/>
+      <c r="G210" s="3" t="n"/>
+      <c r="H210" s="3" t="n"/>
+      <c r="I210" s="3" t="n"/>
+      <c r="J210" s="3" t="n"/>
+      <c r="L210" s="3" t="n"/>
+      <c r="M210" s="3" t="n"/>
+      <c r="Q210" s="3" t="n"/>
+      <c r="R210" s="3" t="n"/>
+      <c r="S210" s="3" t="n"/>
+      <c r="T210" s="3" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
@@ -5785,7 +7250,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>Wigglytuff ex - 040/165</t>
+          <t>Pack Prices:</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -5800,9 +7265,60 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="E212" s="3" t="n"/>
-      <c r="F212" s="3">
-        <f>IF(B212="common", 4, IF(B212="uncommon", 3, IF(B212="rare", 1.74127216869152, 1)))</f>
-        <v/>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>10.75</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>224.85</t>
+        </is>
+      </c>
+      <c r="H212" s="3" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="I212" s="3" t="inlineStr">
+        <is>
+          <t>261.66</t>
+        </is>
+      </c>
+      <c r="J212" s="3" t="inlineStr">
+        <is>
+          <t>224.85</t>
+        </is>
+      </c>
+      <c r="L212" s="3" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>261.66</t>
+        </is>
+      </c>
+      <c r="Q212" s="3" t="inlineStr">
+        <is>
+          <t>10.76</t>
+        </is>
+      </c>
+      <c r="R212" s="3" t="inlineStr">
+        <is>
+          <t>224.84</t>
+        </is>
+      </c>
+      <c r="S212" s="3" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="T212" s="3" t="inlineStr">
+        <is>
+          <t>261.66</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -12468,6 +13984,7 @@
   </sheetData>
   <autoFilter ref="A1:K210"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -12503,7 +14020,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>0.451304347826087</v>
+        <v>0.4469565217391304</v>
       </c>
     </row>
     <row r="3">
@@ -12513,7 +14030,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>0.5090909090909091</v>
+        <v>0.4954545454545455</v>
       </c>
     </row>
     <row r="4">
@@ -12523,7 +14040,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>0.213703314659197</v>
+        <v>0.2148360177404295</v>
       </c>
     </row>
     <row r="5">
@@ -12533,7 +14050,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>5.313106295878034</v>
+        <v>5.413358438813602</v>
       </c>
     </row>
     <row r="6">
@@ -12573,7 +14090,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1.96968085106383</v>
+        <v>1.936063829787234</v>
       </c>
     </row>
     <row r="10">
@@ -12583,7 +14100,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>2.372933333333333</v>
+        <v>2.105955555555556</v>
       </c>
     </row>
     <row r="11">
@@ -12593,7 +14110,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.3439999999999999</v>
+        <v>0.3091111111111111</v>
       </c>
     </row>
     <row r="12">
@@ -12603,7 +14120,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>0.1366233766233766</v>
+        <v>0.1363636363636364</v>
       </c>
     </row>
     <row r="13">
@@ -12613,7 +14130,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>0.6449596774193548</v>
+        <v>0.5658467741935483</v>
       </c>
     </row>
     <row r="14">
@@ -12643,7 +14160,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>5.468197238439894</v>
+        <v>5.053340907011087</v>
       </c>
     </row>
     <row r="17">
@@ -12653,7 +14170,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>11.95540210589412</v>
+        <v>11.62394643075879</v>
       </c>
     </row>
     <row r="18">
@@ -12663,7 +14180,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>1.065402105894121</v>
+        <v>0.7339464307587917</v>
       </c>
     </row>
     <row r="19">
@@ -12673,7 +14190,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1.097833067575218</v>
+        <v>1.067396366460862</v>
       </c>
     </row>
     <row r="20">
@@ -12683,7 +14200,7 @@
         </is>
       </c>
       <c r="B20" s="14" t="n">
-        <v>0.09783306757521772</v>
+        <v>0.06739636646086233</v>
       </c>
     </row>
     <row r="21">
@@ -12693,7 +14210,7 @@
         </is>
       </c>
       <c r="B21" s="14" t="n">
-        <v>0.6832877110235632</v>
+        <v>0.7075425630525005</v>
       </c>
     </row>
     <row r="22">
@@ -12703,7 +14220,7 @@
         </is>
       </c>
       <c r="B22" s="14" t="n">
-        <v>0.3167122889764367</v>
+        <v>0.2924574369474995</v>
       </c>
     </row>
   </sheetData>

--- a/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
+++ b/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
@@ -524,22 +524,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1263"/>
+  <dimension ref="A1:AX1263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39.6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="4"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="4"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="39.140625" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="50.28515625" customWidth="1" min="8" max="8"/>
-    <col width="28.85546875" customWidth="1" min="9" max="9"/>
-    <col width="23.7109375" customWidth="1" min="10" max="10"/>
-    <col width="39.42578125" customWidth="1" min="11" max="11"/>
-    <col width="20.7109375" customWidth="1" min="12" max="12"/>
-    <col width="21.85546875" customWidth="1" min="13" max="13"/>
+    <col width="51.42578125" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="67.140625" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="20.4" customWidth="1" min="12" max="12"/>
+    <col width="28.8" customWidth="1" min="13" max="13"/>
+    <col width="15.85546875" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="46" max="47"/>
+    <col width="24" customWidth="1" min="48" max="48"/>
+    <col width="20.42578125" customWidth="1" min="49" max="49"/>
+    <col width="28.85546875" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -616,10 +621,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -639,20 +644,35 @@
         <v/>
       </c>
       <c r="I2" s="3" t="n">
-        <v>10.89</v>
+        <v>10.35</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>215.18</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>5.6</v>
-      </c>
+        <v>224.93</v>
+      </c>
+      <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
+      <c r="M2" s="3" t="n">
+        <v>250.78</v>
+      </c>
       <c r="Q2" s="3" t="n"/>
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
+      <c r="Z2" s="3" t="n"/>
+      <c r="AA2" s="3" t="n"/>
+      <c r="AB2" s="3" t="n"/>
+      <c r="AC2" s="3" t="n"/>
+      <c r="AD2" s="3" t="n"/>
+      <c r="AJ2" s="3" t="n"/>
+      <c r="AK2" s="3" t="n"/>
+      <c r="AL2" s="3" t="n"/>
+      <c r="AM2" s="3" t="n"/>
+      <c r="AN2" s="3" t="n"/>
+      <c r="AT2" s="3" t="n"/>
+      <c r="AU2" s="3" t="n"/>
+      <c r="AV2" s="3" t="n"/>
+      <c r="AW2" s="3" t="n"/>
+      <c r="AX2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -661,10 +681,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.53</v>
+        <v>0.78</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -682,12 +702,28 @@
       </c>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
       <c r="Q3" s="3" t="n"/>
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
+      <c r="Z3" s="3" t="n"/>
+      <c r="AA3" s="3" t="n"/>
+      <c r="AB3" s="3" t="n"/>
+      <c r="AC3" s="3" t="n"/>
+      <c r="AD3" s="3" t="n"/>
+      <c r="AJ3" s="3" t="n"/>
+      <c r="AK3" s="3" t="n"/>
+      <c r="AL3" s="3" t="n"/>
+      <c r="AM3" s="3" t="n"/>
+      <c r="AN3" s="3" t="n"/>
+      <c r="AT3" s="3" t="n"/>
+      <c r="AU3" s="3" t="n"/>
+      <c r="AV3" s="3" t="n"/>
+      <c r="AW3" s="3" t="n"/>
+      <c r="AX3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -696,7 +732,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.93</v>
+        <v>1.02</v>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
@@ -715,12 +751,28 @@
       </c>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
+      <c r="AB4" s="3" t="n"/>
+      <c r="AC4" s="3" t="n"/>
+      <c r="AD4" s="3" t="n"/>
+      <c r="AJ4" s="3" t="n"/>
+      <c r="AK4" s="3" t="n"/>
+      <c r="AL4" s="3" t="n"/>
+      <c r="AM4" s="3" t="n"/>
+      <c r="AN4" s="3" t="n"/>
+      <c r="AT4" s="3" t="n"/>
+      <c r="AU4" s="3" t="n"/>
+      <c r="AV4" s="3" t="n"/>
+      <c r="AW4" s="3" t="n"/>
+      <c r="AX4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -729,7 +781,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
@@ -748,12 +800,28 @@
       </c>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
       <c r="Q5" s="3" t="n"/>
       <c r="R5" s="3" t="n"/>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
+      <c r="Z5" s="3" t="n"/>
+      <c r="AA5" s="3" t="n"/>
+      <c r="AB5" s="3" t="n"/>
+      <c r="AC5" s="3" t="n"/>
+      <c r="AD5" s="3" t="n"/>
+      <c r="AJ5" s="3" t="n"/>
+      <c r="AK5" s="3" t="n"/>
+      <c r="AL5" s="3" t="n"/>
+      <c r="AM5" s="3" t="n"/>
+      <c r="AN5" s="3" t="n"/>
+      <c r="AT5" s="3" t="n"/>
+      <c r="AU5" s="3" t="n"/>
+      <c r="AV5" s="3" t="n"/>
+      <c r="AW5" s="3" t="n"/>
+      <c r="AX5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -762,7 +830,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>42.11</v>
+        <v>42.53</v>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr">
@@ -781,12 +849,28 @@
       </c>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
       <c r="Q6" s="3" t="n"/>
       <c r="R6" s="3" t="n"/>
       <c r="S6" s="3" t="n"/>
       <c r="T6" s="3" t="n"/>
+      <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
+      <c r="AB6" s="3" t="n"/>
+      <c r="AC6" s="3" t="n"/>
+      <c r="AD6" s="3" t="n"/>
+      <c r="AJ6" s="3" t="n"/>
+      <c r="AK6" s="3" t="n"/>
+      <c r="AL6" s="3" t="n"/>
+      <c r="AM6" s="3" t="n"/>
+      <c r="AN6" s="3" t="n"/>
+      <c r="AT6" s="3" t="n"/>
+      <c r="AU6" s="3" t="n"/>
+      <c r="AV6" s="3" t="n"/>
+      <c r="AW6" s="3" t="n"/>
+      <c r="AX6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -798,7 +882,7 @@
         <v>0.08</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -816,12 +900,28 @@
       </c>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
       <c r="Q7" s="3" t="n"/>
       <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="n"/>
+      <c r="Z7" s="3" t="n"/>
+      <c r="AA7" s="3" t="n"/>
+      <c r="AB7" s="3" t="n"/>
+      <c r="AC7" s="3" t="n"/>
+      <c r="AD7" s="3" t="n"/>
+      <c r="AJ7" s="3" t="n"/>
+      <c r="AK7" s="3" t="n"/>
+      <c r="AL7" s="3" t="n"/>
+      <c r="AM7" s="3" t="n"/>
+      <c r="AN7" s="3" t="n"/>
+      <c r="AT7" s="3" t="n"/>
+      <c r="AU7" s="3" t="n"/>
+      <c r="AV7" s="3" t="n"/>
+      <c r="AW7" s="3" t="n"/>
+      <c r="AX7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -830,10 +930,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -851,12 +951,28 @@
       </c>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
       <c r="Q8" s="3" t="n"/>
       <c r="R8" s="3" t="n"/>
       <c r="S8" s="3" t="n"/>
       <c r="T8" s="3" t="n"/>
+      <c r="Z8" s="3" t="n"/>
+      <c r="AA8" s="3" t="n"/>
+      <c r="AB8" s="3" t="n"/>
+      <c r="AC8" s="3" t="n"/>
+      <c r="AD8" s="3" t="n"/>
+      <c r="AJ8" s="3" t="n"/>
+      <c r="AK8" s="3" t="n"/>
+      <c r="AL8" s="3" t="n"/>
+      <c r="AM8" s="3" t="n"/>
+      <c r="AN8" s="3" t="n"/>
+      <c r="AT8" s="3" t="n"/>
+      <c r="AU8" s="3" t="n"/>
+      <c r="AV8" s="3" t="n"/>
+      <c r="AW8" s="3" t="n"/>
+      <c r="AX8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -868,7 +984,7 @@
         <v>0.11</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -886,12 +1002,28 @@
       </c>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n"/>
       <c r="Q9" s="3" t="n"/>
       <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n"/>
+      <c r="Z9" s="3" t="n"/>
+      <c r="AA9" s="3" t="n"/>
+      <c r="AB9" s="3" t="n"/>
+      <c r="AC9" s="3" t="n"/>
+      <c r="AD9" s="3" t="n"/>
+      <c r="AJ9" s="3" t="n"/>
+      <c r="AK9" s="3" t="n"/>
+      <c r="AL9" s="3" t="n"/>
+      <c r="AM9" s="3" t="n"/>
+      <c r="AN9" s="3" t="n"/>
+      <c r="AT9" s="3" t="n"/>
+      <c r="AU9" s="3" t="n"/>
+      <c r="AV9" s="3" t="n"/>
+      <c r="AW9" s="3" t="n"/>
+      <c r="AX9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -900,7 +1032,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr">
@@ -919,12 +1051,28 @@
       </c>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="n"/>
       <c r="Q10" s="3" t="n"/>
       <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
+      <c r="Z10" s="3" t="n"/>
+      <c r="AA10" s="3" t="n"/>
+      <c r="AB10" s="3" t="n"/>
+      <c r="AC10" s="3" t="n"/>
+      <c r="AD10" s="3" t="n"/>
+      <c r="AJ10" s="3" t="n"/>
+      <c r="AK10" s="3" t="n"/>
+      <c r="AL10" s="3" t="n"/>
+      <c r="AM10" s="3" t="n"/>
+      <c r="AN10" s="3" t="n"/>
+      <c r="AT10" s="3" t="n"/>
+      <c r="AU10" s="3" t="n"/>
+      <c r="AV10" s="3" t="n"/>
+      <c r="AW10" s="3" t="n"/>
+      <c r="AX10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -933,7 +1081,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4.88</v>
+        <v>4.63</v>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
@@ -949,12 +1097,28 @@
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n"/>
       <c r="Q11" s="3" t="n"/>
       <c r="R11" s="3" t="n"/>
       <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="n"/>
+      <c r="Z11" s="3" t="n"/>
+      <c r="AA11" s="3" t="n"/>
+      <c r="AB11" s="3" t="n"/>
+      <c r="AC11" s="3" t="n"/>
+      <c r="AD11" s="3" t="n"/>
+      <c r="AJ11" s="3" t="n"/>
+      <c r="AK11" s="3" t="n"/>
+      <c r="AL11" s="3" t="n"/>
+      <c r="AM11" s="3" t="n"/>
+      <c r="AN11" s="3" t="n"/>
+      <c r="AT11" s="3" t="n"/>
+      <c r="AU11" s="3" t="n"/>
+      <c r="AV11" s="3" t="n"/>
+      <c r="AW11" s="3" t="n"/>
+      <c r="AX11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -963,10 +1127,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -981,12 +1145,28 @@
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="n"/>
       <c r="M12" s="3" t="n"/>
       <c r="Q12" s="3" t="n"/>
       <c r="R12" s="3" t="n"/>
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n"/>
+      <c r="Z12" s="3" t="n"/>
+      <c r="AA12" s="3" t="n"/>
+      <c r="AB12" s="3" t="n"/>
+      <c r="AC12" s="3" t="n"/>
+      <c r="AD12" s="3" t="n"/>
+      <c r="AJ12" s="3" t="n"/>
+      <c r="AK12" s="3" t="n"/>
+      <c r="AL12" s="3" t="n"/>
+      <c r="AM12" s="3" t="n"/>
+      <c r="AN12" s="3" t="n"/>
+      <c r="AT12" s="3" t="n"/>
+      <c r="AU12" s="3" t="n"/>
+      <c r="AV12" s="3" t="n"/>
+      <c r="AW12" s="3" t="n"/>
+      <c r="AX12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -995,10 +1175,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -1013,12 +1193,28 @@
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n"/>
       <c r="M13" s="3" t="n"/>
       <c r="Q13" s="3" t="n"/>
       <c r="R13" s="3" t="n"/>
       <c r="S13" s="3" t="n"/>
       <c r="T13" s="3" t="n"/>
+      <c r="Z13" s="3" t="n"/>
+      <c r="AA13" s="3" t="n"/>
+      <c r="AB13" s="3" t="n"/>
+      <c r="AC13" s="3" t="n"/>
+      <c r="AD13" s="3" t="n"/>
+      <c r="AJ13" s="3" t="n"/>
+      <c r="AK13" s="3" t="n"/>
+      <c r="AL13" s="3" t="n"/>
+      <c r="AM13" s="3" t="n"/>
+      <c r="AN13" s="3" t="n"/>
+      <c r="AT13" s="3" t="n"/>
+      <c r="AU13" s="3" t="n"/>
+      <c r="AV13" s="3" t="n"/>
+      <c r="AW13" s="3" t="n"/>
+      <c r="AX13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1027,7 +1223,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="inlineStr">
@@ -1043,12 +1239,28 @@
       <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="n"/>
       <c r="M14" s="3" t="n"/>
       <c r="Q14" s="3" t="n"/>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="n"/>
+      <c r="Z14" s="3" t="n"/>
+      <c r="AA14" s="3" t="n"/>
+      <c r="AB14" s="3" t="n"/>
+      <c r="AC14" s="3" t="n"/>
+      <c r="AD14" s="3" t="n"/>
+      <c r="AJ14" s="3" t="n"/>
+      <c r="AK14" s="3" t="n"/>
+      <c r="AL14" s="3" t="n"/>
+      <c r="AM14" s="3" t="n"/>
+      <c r="AN14" s="3" t="n"/>
+      <c r="AT14" s="3" t="n"/>
+      <c r="AU14" s="3" t="n"/>
+      <c r="AV14" s="3" t="n"/>
+      <c r="AW14" s="3" t="n"/>
+      <c r="AX14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1057,10 +1269,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
@@ -1075,12 +1287,28 @@
       <c r="H15" s="3" t="n"/>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="n"/>
       <c r="M15" s="3" t="n"/>
       <c r="Q15" s="3" t="n"/>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3" t="n"/>
       <c r="T15" s="3" t="n"/>
+      <c r="Z15" s="3" t="n"/>
+      <c r="AA15" s="3" t="n"/>
+      <c r="AB15" s="3" t="n"/>
+      <c r="AC15" s="3" t="n"/>
+      <c r="AD15" s="3" t="n"/>
+      <c r="AJ15" s="3" t="n"/>
+      <c r="AK15" s="3" t="n"/>
+      <c r="AL15" s="3" t="n"/>
+      <c r="AM15" s="3" t="n"/>
+      <c r="AN15" s="3" t="n"/>
+      <c r="AT15" s="3" t="n"/>
+      <c r="AU15" s="3" t="n"/>
+      <c r="AV15" s="3" t="n"/>
+      <c r="AW15" s="3" t="n"/>
+      <c r="AX15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1089,7 +1317,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0.15</v>
@@ -1107,12 +1335,28 @@
       <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n"/>
       <c r="Q16" s="3" t="n"/>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3" t="n"/>
       <c r="T16" s="3" t="n"/>
+      <c r="Z16" s="3" t="n"/>
+      <c r="AA16" s="3" t="n"/>
+      <c r="AB16" s="3" t="n"/>
+      <c r="AC16" s="3" t="n"/>
+      <c r="AD16" s="3" t="n"/>
+      <c r="AJ16" s="3" t="n"/>
+      <c r="AK16" s="3" t="n"/>
+      <c r="AL16" s="3" t="n"/>
+      <c r="AM16" s="3" t="n"/>
+      <c r="AN16" s="3" t="n"/>
+      <c r="AT16" s="3" t="n"/>
+      <c r="AU16" s="3" t="n"/>
+      <c r="AV16" s="3" t="n"/>
+      <c r="AW16" s="3" t="n"/>
+      <c r="AX16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1121,10 +1365,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -1139,12 +1383,28 @@
       <c r="H17" s="3" t="n"/>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n"/>
       <c r="M17" s="3" t="n"/>
       <c r="Q17" s="3" t="n"/>
       <c r="R17" s="3" t="n"/>
       <c r="S17" s="3" t="n"/>
       <c r="T17" s="3" t="n"/>
+      <c r="Z17" s="3" t="n"/>
+      <c r="AA17" s="3" t="n"/>
+      <c r="AB17" s="3" t="n"/>
+      <c r="AC17" s="3" t="n"/>
+      <c r="AD17" s="3" t="n"/>
+      <c r="AJ17" s="3" t="n"/>
+      <c r="AK17" s="3" t="n"/>
+      <c r="AL17" s="3" t="n"/>
+      <c r="AM17" s="3" t="n"/>
+      <c r="AN17" s="3" t="n"/>
+      <c r="AT17" s="3" t="n"/>
+      <c r="AU17" s="3" t="n"/>
+      <c r="AV17" s="3" t="n"/>
+      <c r="AW17" s="3" t="n"/>
+      <c r="AX17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1153,10 +1413,10 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -1171,12 +1431,28 @@
       <c r="H18" s="3" t="n"/>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3" t="n"/>
       <c r="Q18" s="3" t="n"/>
       <c r="R18" s="3" t="n"/>
       <c r="S18" s="3" t="n"/>
       <c r="T18" s="3" t="n"/>
+      <c r="Z18" s="3" t="n"/>
+      <c r="AA18" s="3" t="n"/>
+      <c r="AB18" s="3" t="n"/>
+      <c r="AC18" s="3" t="n"/>
+      <c r="AD18" s="3" t="n"/>
+      <c r="AJ18" s="3" t="n"/>
+      <c r="AK18" s="3" t="n"/>
+      <c r="AL18" s="3" t="n"/>
+      <c r="AM18" s="3" t="n"/>
+      <c r="AN18" s="3" t="n"/>
+      <c r="AT18" s="3" t="n"/>
+      <c r="AU18" s="3" t="n"/>
+      <c r="AV18" s="3" t="n"/>
+      <c r="AW18" s="3" t="n"/>
+      <c r="AX18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1185,7 +1461,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="inlineStr">
@@ -1201,12 +1477,28 @@
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
       <c r="L19" s="3" t="n"/>
       <c r="M19" s="3" t="n"/>
       <c r="Q19" s="3" t="n"/>
       <c r="R19" s="3" t="n"/>
       <c r="S19" s="3" t="n"/>
       <c r="T19" s="3" t="n"/>
+      <c r="Z19" s="3" t="n"/>
+      <c r="AA19" s="3" t="n"/>
+      <c r="AB19" s="3" t="n"/>
+      <c r="AC19" s="3" t="n"/>
+      <c r="AD19" s="3" t="n"/>
+      <c r="AJ19" s="3" t="n"/>
+      <c r="AK19" s="3" t="n"/>
+      <c r="AL19" s="3" t="n"/>
+      <c r="AM19" s="3" t="n"/>
+      <c r="AN19" s="3" t="n"/>
+      <c r="AT19" s="3" t="n"/>
+      <c r="AU19" s="3" t="n"/>
+      <c r="AV19" s="3" t="n"/>
+      <c r="AW19" s="3" t="n"/>
+      <c r="AX19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1215,7 +1507,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="inlineStr">
@@ -1231,12 +1523,28 @@
       <c r="H20" s="3" t="n"/>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="n"/>
       <c r="M20" s="3" t="n"/>
       <c r="Q20" s="3" t="n"/>
       <c r="R20" s="3" t="n"/>
       <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n"/>
+      <c r="Z20" s="3" t="n"/>
+      <c r="AA20" s="3" t="n"/>
+      <c r="AB20" s="3" t="n"/>
+      <c r="AC20" s="3" t="n"/>
+      <c r="AD20" s="3" t="n"/>
+      <c r="AJ20" s="3" t="n"/>
+      <c r="AK20" s="3" t="n"/>
+      <c r="AL20" s="3" t="n"/>
+      <c r="AM20" s="3" t="n"/>
+      <c r="AN20" s="3" t="n"/>
+      <c r="AT20" s="3" t="n"/>
+      <c r="AU20" s="3" t="n"/>
+      <c r="AV20" s="3" t="n"/>
+      <c r="AW20" s="3" t="n"/>
+      <c r="AX20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1245,7 +1553,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>14.02</v>
+        <v>14.26</v>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr">
@@ -1261,12 +1569,28 @@
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="n"/>
       <c r="M21" s="3" t="n"/>
       <c r="Q21" s="3" t="n"/>
       <c r="R21" s="3" t="n"/>
       <c r="S21" s="3" t="n"/>
       <c r="T21" s="3" t="n"/>
+      <c r="Z21" s="3" t="n"/>
+      <c r="AA21" s="3" t="n"/>
+      <c r="AB21" s="3" t="n"/>
+      <c r="AC21" s="3" t="n"/>
+      <c r="AD21" s="3" t="n"/>
+      <c r="AJ21" s="3" t="n"/>
+      <c r="AK21" s="3" t="n"/>
+      <c r="AL21" s="3" t="n"/>
+      <c r="AM21" s="3" t="n"/>
+      <c r="AN21" s="3" t="n"/>
+      <c r="AT21" s="3" t="n"/>
+      <c r="AU21" s="3" t="n"/>
+      <c r="AV21" s="3" t="n"/>
+      <c r="AW21" s="3" t="n"/>
+      <c r="AX21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1275,7 +1599,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>71.38</v>
+        <v>70.86</v>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="inlineStr">
@@ -1291,12 +1615,28 @@
       <c r="H22" s="3" t="n"/>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
       <c r="L22" s="3" t="n"/>
       <c r="M22" s="3" t="n"/>
       <c r="Q22" s="3" t="n"/>
       <c r="R22" s="3" t="n"/>
       <c r="S22" s="3" t="n"/>
       <c r="T22" s="3" t="n"/>
+      <c r="Z22" s="3" t="n"/>
+      <c r="AA22" s="3" t="n"/>
+      <c r="AB22" s="3" t="n"/>
+      <c r="AC22" s="3" t="n"/>
+      <c r="AD22" s="3" t="n"/>
+      <c r="AJ22" s="3" t="n"/>
+      <c r="AK22" s="3" t="n"/>
+      <c r="AL22" s="3" t="n"/>
+      <c r="AM22" s="3" t="n"/>
+      <c r="AN22" s="3" t="n"/>
+      <c r="AT22" s="3" t="n"/>
+      <c r="AU22" s="3" t="n"/>
+      <c r="AV22" s="3" t="n"/>
+      <c r="AW22" s="3" t="n"/>
+      <c r="AX22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1305,10 +1645,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
@@ -1323,12 +1663,28 @@
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n"/>
       <c r="M23" s="3" t="n"/>
       <c r="Q23" s="3" t="n"/>
       <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n"/>
+      <c r="Z23" s="3" t="n"/>
+      <c r="AA23" s="3" t="n"/>
+      <c r="AB23" s="3" t="n"/>
+      <c r="AC23" s="3" t="n"/>
+      <c r="AD23" s="3" t="n"/>
+      <c r="AJ23" s="3" t="n"/>
+      <c r="AK23" s="3" t="n"/>
+      <c r="AL23" s="3" t="n"/>
+      <c r="AM23" s="3" t="n"/>
+      <c r="AN23" s="3" t="n"/>
+      <c r="AT23" s="3" t="n"/>
+      <c r="AU23" s="3" t="n"/>
+      <c r="AV23" s="3" t="n"/>
+      <c r="AW23" s="3" t="n"/>
+      <c r="AX23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1337,7 +1693,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>36.58</v>
+        <v>36.42</v>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
       <c r="D24" s="3" t="inlineStr">
@@ -1353,12 +1709,28 @@
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n"/>
       <c r="M24" s="3" t="n"/>
       <c r="Q24" s="3" t="n"/>
       <c r="R24" s="3" t="n"/>
       <c r="S24" s="3" t="n"/>
       <c r="T24" s="3" t="n"/>
+      <c r="Z24" s="3" t="n"/>
+      <c r="AA24" s="3" t="n"/>
+      <c r="AB24" s="3" t="n"/>
+      <c r="AC24" s="3" t="n"/>
+      <c r="AD24" s="3" t="n"/>
+      <c r="AJ24" s="3" t="n"/>
+      <c r="AK24" s="3" t="n"/>
+      <c r="AL24" s="3" t="n"/>
+      <c r="AM24" s="3" t="n"/>
+      <c r="AN24" s="3" t="n"/>
+      <c r="AT24" s="3" t="n"/>
+      <c r="AU24" s="3" t="n"/>
+      <c r="AV24" s="3" t="n"/>
+      <c r="AW24" s="3" t="n"/>
+      <c r="AX24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1367,10 +1739,10 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1385,12 +1757,28 @@
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n"/>
       <c r="M25" s="3" t="n"/>
       <c r="Q25" s="3" t="n"/>
       <c r="R25" s="3" t="n"/>
       <c r="S25" s="3" t="n"/>
       <c r="T25" s="3" t="n"/>
+      <c r="Z25" s="3" t="n"/>
+      <c r="AA25" s="3" t="n"/>
+      <c r="AB25" s="3" t="n"/>
+      <c r="AC25" s="3" t="n"/>
+      <c r="AD25" s="3" t="n"/>
+      <c r="AJ25" s="3" t="n"/>
+      <c r="AK25" s="3" t="n"/>
+      <c r="AL25" s="3" t="n"/>
+      <c r="AM25" s="3" t="n"/>
+      <c r="AN25" s="3" t="n"/>
+      <c r="AT25" s="3" t="n"/>
+      <c r="AU25" s="3" t="n"/>
+      <c r="AV25" s="3" t="n"/>
+      <c r="AW25" s="3" t="n"/>
+      <c r="AX25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1399,10 +1787,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1417,12 +1805,28 @@
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="n"/>
       <c r="M26" s="3" t="n"/>
       <c r="Q26" s="3" t="n"/>
       <c r="R26" s="3" t="n"/>
       <c r="S26" s="3" t="n"/>
       <c r="T26" s="3" t="n"/>
+      <c r="Z26" s="3" t="n"/>
+      <c r="AA26" s="3" t="n"/>
+      <c r="AB26" s="3" t="n"/>
+      <c r="AC26" s="3" t="n"/>
+      <c r="AD26" s="3" t="n"/>
+      <c r="AJ26" s="3" t="n"/>
+      <c r="AK26" s="3" t="n"/>
+      <c r="AL26" s="3" t="n"/>
+      <c r="AM26" s="3" t="n"/>
+      <c r="AN26" s="3" t="n"/>
+      <c r="AT26" s="3" t="n"/>
+      <c r="AU26" s="3" t="n"/>
+      <c r="AV26" s="3" t="n"/>
+      <c r="AW26" s="3" t="n"/>
+      <c r="AX26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1431,7 +1835,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>9.82</v>
+        <v>9.58</v>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="inlineStr">
@@ -1447,12 +1851,28 @@
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="n"/>
       <c r="M27" s="3" t="n"/>
       <c r="Q27" s="3" t="n"/>
       <c r="R27" s="3" t="n"/>
       <c r="S27" s="3" t="n"/>
       <c r="T27" s="3" t="n"/>
+      <c r="Z27" s="3" t="n"/>
+      <c r="AA27" s="3" t="n"/>
+      <c r="AB27" s="3" t="n"/>
+      <c r="AC27" s="3" t="n"/>
+      <c r="AD27" s="3" t="n"/>
+      <c r="AJ27" s="3" t="n"/>
+      <c r="AK27" s="3" t="n"/>
+      <c r="AL27" s="3" t="n"/>
+      <c r="AM27" s="3" t="n"/>
+      <c r="AN27" s="3" t="n"/>
+      <c r="AT27" s="3" t="n"/>
+      <c r="AU27" s="3" t="n"/>
+      <c r="AV27" s="3" t="n"/>
+      <c r="AW27" s="3" t="n"/>
+      <c r="AX27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1461,10 +1881,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -1479,12 +1899,28 @@
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
       <c r="L28" s="3" t="n"/>
       <c r="M28" s="3" t="n"/>
       <c r="Q28" s="3" t="n"/>
       <c r="R28" s="3" t="n"/>
       <c r="S28" s="3" t="n"/>
       <c r="T28" s="3" t="n"/>
+      <c r="Z28" s="3" t="n"/>
+      <c r="AA28" s="3" t="n"/>
+      <c r="AB28" s="3" t="n"/>
+      <c r="AC28" s="3" t="n"/>
+      <c r="AD28" s="3" t="n"/>
+      <c r="AJ28" s="3" t="n"/>
+      <c r="AK28" s="3" t="n"/>
+      <c r="AL28" s="3" t="n"/>
+      <c r="AM28" s="3" t="n"/>
+      <c r="AN28" s="3" t="n"/>
+      <c r="AT28" s="3" t="n"/>
+      <c r="AU28" s="3" t="n"/>
+      <c r="AV28" s="3" t="n"/>
+      <c r="AW28" s="3" t="n"/>
+      <c r="AX28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1493,7 +1929,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="3" t="inlineStr">
@@ -1509,12 +1945,28 @@
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
       <c r="L29" s="3" t="n"/>
       <c r="M29" s="3" t="n"/>
       <c r="Q29" s="3" t="n"/>
       <c r="R29" s="3" t="n"/>
       <c r="S29" s="3" t="n"/>
       <c r="T29" s="3" t="n"/>
+      <c r="Z29" s="3" t="n"/>
+      <c r="AA29" s="3" t="n"/>
+      <c r="AB29" s="3" t="n"/>
+      <c r="AC29" s="3" t="n"/>
+      <c r="AD29" s="3" t="n"/>
+      <c r="AJ29" s="3" t="n"/>
+      <c r="AK29" s="3" t="n"/>
+      <c r="AL29" s="3" t="n"/>
+      <c r="AM29" s="3" t="n"/>
+      <c r="AN29" s="3" t="n"/>
+      <c r="AT29" s="3" t="n"/>
+      <c r="AU29" s="3" t="n"/>
+      <c r="AV29" s="3" t="n"/>
+      <c r="AW29" s="3" t="n"/>
+      <c r="AX29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1523,7 +1975,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>30.35</v>
+        <v>28.77</v>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="3" t="inlineStr">
@@ -1539,12 +1991,28 @@
       <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
       <c r="L30" s="3" t="n"/>
       <c r="M30" s="3" t="n"/>
       <c r="Q30" s="3" t="n"/>
       <c r="R30" s="3" t="n"/>
       <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="n"/>
+      <c r="Z30" s="3" t="n"/>
+      <c r="AA30" s="3" t="n"/>
+      <c r="AB30" s="3" t="n"/>
+      <c r="AC30" s="3" t="n"/>
+      <c r="AD30" s="3" t="n"/>
+      <c r="AJ30" s="3" t="n"/>
+      <c r="AK30" s="3" t="n"/>
+      <c r="AL30" s="3" t="n"/>
+      <c r="AM30" s="3" t="n"/>
+      <c r="AN30" s="3" t="n"/>
+      <c r="AT30" s="3" t="n"/>
+      <c r="AU30" s="3" t="n"/>
+      <c r="AV30" s="3" t="n"/>
+      <c r="AW30" s="3" t="n"/>
+      <c r="AX30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1553,7 +2021,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>212.94</v>
+        <v>206.73</v>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="3" t="inlineStr">
@@ -1569,12 +2037,28 @@
       <c r="H31" s="3" t="n"/>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="n"/>
       <c r="M31" s="3" t="n"/>
       <c r="Q31" s="3" t="n"/>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3" t="n"/>
       <c r="T31" s="3" t="n"/>
+      <c r="Z31" s="3" t="n"/>
+      <c r="AA31" s="3" t="n"/>
+      <c r="AB31" s="3" t="n"/>
+      <c r="AC31" s="3" t="n"/>
+      <c r="AD31" s="3" t="n"/>
+      <c r="AJ31" s="3" t="n"/>
+      <c r="AK31" s="3" t="n"/>
+      <c r="AL31" s="3" t="n"/>
+      <c r="AM31" s="3" t="n"/>
+      <c r="AN31" s="3" t="n"/>
+      <c r="AT31" s="3" t="n"/>
+      <c r="AU31" s="3" t="n"/>
+      <c r="AV31" s="3" t="n"/>
+      <c r="AW31" s="3" t="n"/>
+      <c r="AX31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1583,7 +2067,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>0.18</v>
@@ -1601,12 +2085,28 @@
       <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n"/>
       <c r="M32" s="3" t="n"/>
       <c r="Q32" s="3" t="n"/>
       <c r="R32" s="3" t="n"/>
       <c r="S32" s="3" t="n"/>
       <c r="T32" s="3" t="n"/>
+      <c r="Z32" s="3" t="n"/>
+      <c r="AA32" s="3" t="n"/>
+      <c r="AB32" s="3" t="n"/>
+      <c r="AC32" s="3" t="n"/>
+      <c r="AD32" s="3" t="n"/>
+      <c r="AJ32" s="3" t="n"/>
+      <c r="AK32" s="3" t="n"/>
+      <c r="AL32" s="3" t="n"/>
+      <c r="AM32" s="3" t="n"/>
+      <c r="AN32" s="3" t="n"/>
+      <c r="AT32" s="3" t="n"/>
+      <c r="AU32" s="3" t="n"/>
+      <c r="AV32" s="3" t="n"/>
+      <c r="AW32" s="3" t="n"/>
+      <c r="AX32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1615,7 +2115,7 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>51.89</v>
+        <v>50.77</v>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="inlineStr">
@@ -1631,12 +2131,28 @@
       <c r="H33" s="3" t="n"/>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="n"/>
       <c r="M33" s="3" t="n"/>
       <c r="Q33" s="3" t="n"/>
       <c r="R33" s="3" t="n"/>
       <c r="S33" s="3" t="n"/>
       <c r="T33" s="3" t="n"/>
+      <c r="Z33" s="3" t="n"/>
+      <c r="AA33" s="3" t="n"/>
+      <c r="AB33" s="3" t="n"/>
+      <c r="AC33" s="3" t="n"/>
+      <c r="AD33" s="3" t="n"/>
+      <c r="AJ33" s="3" t="n"/>
+      <c r="AK33" s="3" t="n"/>
+      <c r="AL33" s="3" t="n"/>
+      <c r="AM33" s="3" t="n"/>
+      <c r="AN33" s="3" t="n"/>
+      <c r="AT33" s="3" t="n"/>
+      <c r="AU33" s="3" t="n"/>
+      <c r="AV33" s="3" t="n"/>
+      <c r="AW33" s="3" t="n"/>
+      <c r="AX33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1645,10 +2161,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1663,12 +2179,28 @@
       <c r="H34" s="3" t="n"/>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="n"/>
       <c r="M34" s="3" t="n"/>
       <c r="Q34" s="3" t="n"/>
       <c r="R34" s="3" t="n"/>
       <c r="S34" s="3" t="n"/>
       <c r="T34" s="3" t="n"/>
+      <c r="Z34" s="3" t="n"/>
+      <c r="AA34" s="3" t="n"/>
+      <c r="AB34" s="3" t="n"/>
+      <c r="AC34" s="3" t="n"/>
+      <c r="AD34" s="3" t="n"/>
+      <c r="AJ34" s="3" t="n"/>
+      <c r="AK34" s="3" t="n"/>
+      <c r="AL34" s="3" t="n"/>
+      <c r="AM34" s="3" t="n"/>
+      <c r="AN34" s="3" t="n"/>
+      <c r="AT34" s="3" t="n"/>
+      <c r="AU34" s="3" t="n"/>
+      <c r="AV34" s="3" t="n"/>
+      <c r="AW34" s="3" t="n"/>
+      <c r="AX34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1677,7 +2209,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>33.53</v>
+        <v>32.51</v>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="3" t="inlineStr">
@@ -1693,12 +2225,28 @@
       <c r="H35" s="3" t="n"/>
       <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
       <c r="L35" s="3" t="n"/>
       <c r="M35" s="3" t="n"/>
       <c r="Q35" s="3" t="n"/>
       <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="n"/>
       <c r="T35" s="3" t="n"/>
+      <c r="Z35" s="3" t="n"/>
+      <c r="AA35" s="3" t="n"/>
+      <c r="AB35" s="3" t="n"/>
+      <c r="AC35" s="3" t="n"/>
+      <c r="AD35" s="3" t="n"/>
+      <c r="AJ35" s="3" t="n"/>
+      <c r="AK35" s="3" t="n"/>
+      <c r="AL35" s="3" t="n"/>
+      <c r="AM35" s="3" t="n"/>
+      <c r="AN35" s="3" t="n"/>
+      <c r="AT35" s="3" t="n"/>
+      <c r="AU35" s="3" t="n"/>
+      <c r="AV35" s="3" t="n"/>
+      <c r="AW35" s="3" t="n"/>
+      <c r="AX35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1707,10 +2255,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
@@ -1725,12 +2273,28 @@
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="n"/>
       <c r="M36" s="3" t="n"/>
       <c r="Q36" s="3" t="n"/>
       <c r="R36" s="3" t="n"/>
       <c r="S36" s="3" t="n"/>
       <c r="T36" s="3" t="n"/>
+      <c r="Z36" s="3" t="n"/>
+      <c r="AA36" s="3" t="n"/>
+      <c r="AB36" s="3" t="n"/>
+      <c r="AC36" s="3" t="n"/>
+      <c r="AD36" s="3" t="n"/>
+      <c r="AJ36" s="3" t="n"/>
+      <c r="AK36" s="3" t="n"/>
+      <c r="AL36" s="3" t="n"/>
+      <c r="AM36" s="3" t="n"/>
+      <c r="AN36" s="3" t="n"/>
+      <c r="AT36" s="3" t="n"/>
+      <c r="AU36" s="3" t="n"/>
+      <c r="AV36" s="3" t="n"/>
+      <c r="AW36" s="3" t="n"/>
+      <c r="AX36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1742,7 +2306,7 @@
         <v>0.08</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -1757,12 +2321,28 @@
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n"/>
       <c r="M37" s="3" t="n"/>
       <c r="Q37" s="3" t="n"/>
       <c r="R37" s="3" t="n"/>
       <c r="S37" s="3" t="n"/>
       <c r="T37" s="3" t="n"/>
+      <c r="Z37" s="3" t="n"/>
+      <c r="AA37" s="3" t="n"/>
+      <c r="AB37" s="3" t="n"/>
+      <c r="AC37" s="3" t="n"/>
+      <c r="AD37" s="3" t="n"/>
+      <c r="AJ37" s="3" t="n"/>
+      <c r="AK37" s="3" t="n"/>
+      <c r="AL37" s="3" t="n"/>
+      <c r="AM37" s="3" t="n"/>
+      <c r="AN37" s="3" t="n"/>
+      <c r="AT37" s="3" t="n"/>
+      <c r="AU37" s="3" t="n"/>
+      <c r="AV37" s="3" t="n"/>
+      <c r="AW37" s="3" t="n"/>
+      <c r="AX37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1774,7 +2354,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -1789,12 +2369,28 @@
       <c r="H38" s="3" t="n"/>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="n"/>
       <c r="M38" s="3" t="n"/>
       <c r="Q38" s="3" t="n"/>
       <c r="R38" s="3" t="n"/>
       <c r="S38" s="3" t="n"/>
       <c r="T38" s="3" t="n"/>
+      <c r="Z38" s="3" t="n"/>
+      <c r="AA38" s="3" t="n"/>
+      <c r="AB38" s="3" t="n"/>
+      <c r="AC38" s="3" t="n"/>
+      <c r="AD38" s="3" t="n"/>
+      <c r="AJ38" s="3" t="n"/>
+      <c r="AK38" s="3" t="n"/>
+      <c r="AL38" s="3" t="n"/>
+      <c r="AM38" s="3" t="n"/>
+      <c r="AN38" s="3" t="n"/>
+      <c r="AT38" s="3" t="n"/>
+      <c r="AU38" s="3" t="n"/>
+      <c r="AV38" s="3" t="n"/>
+      <c r="AW38" s="3" t="n"/>
+      <c r="AX38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1803,10 +2399,10 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -1821,12 +2417,28 @@
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="n"/>
       <c r="M39" s="3" t="n"/>
       <c r="Q39" s="3" t="n"/>
       <c r="R39" s="3" t="n"/>
       <c r="S39" s="3" t="n"/>
       <c r="T39" s="3" t="n"/>
+      <c r="Z39" s="3" t="n"/>
+      <c r="AA39" s="3" t="n"/>
+      <c r="AB39" s="3" t="n"/>
+      <c r="AC39" s="3" t="n"/>
+      <c r="AD39" s="3" t="n"/>
+      <c r="AJ39" s="3" t="n"/>
+      <c r="AK39" s="3" t="n"/>
+      <c r="AL39" s="3" t="n"/>
+      <c r="AM39" s="3" t="n"/>
+      <c r="AN39" s="3" t="n"/>
+      <c r="AT39" s="3" t="n"/>
+      <c r="AU39" s="3" t="n"/>
+      <c r="AV39" s="3" t="n"/>
+      <c r="AW39" s="3" t="n"/>
+      <c r="AX39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1835,10 +2447,10 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -1853,12 +2465,28 @@
       <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="n"/>
       <c r="Q40" s="3" t="n"/>
       <c r="R40" s="3" t="n"/>
       <c r="S40" s="3" t="n"/>
       <c r="T40" s="3" t="n"/>
+      <c r="Z40" s="3" t="n"/>
+      <c r="AA40" s="3" t="n"/>
+      <c r="AB40" s="3" t="n"/>
+      <c r="AC40" s="3" t="n"/>
+      <c r="AD40" s="3" t="n"/>
+      <c r="AJ40" s="3" t="n"/>
+      <c r="AK40" s="3" t="n"/>
+      <c r="AL40" s="3" t="n"/>
+      <c r="AM40" s="3" t="n"/>
+      <c r="AN40" s="3" t="n"/>
+      <c r="AT40" s="3" t="n"/>
+      <c r="AU40" s="3" t="n"/>
+      <c r="AV40" s="3" t="n"/>
+      <c r="AW40" s="3" t="n"/>
+      <c r="AX40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1870,7 +2498,7 @@
         <v>0.09</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -1885,12 +2513,28 @@
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
       <c r="L41" s="3" t="n"/>
       <c r="M41" s="3" t="n"/>
       <c r="Q41" s="3" t="n"/>
       <c r="R41" s="3" t="n"/>
       <c r="S41" s="3" t="n"/>
       <c r="T41" s="3" t="n"/>
+      <c r="Z41" s="3" t="n"/>
+      <c r="AA41" s="3" t="n"/>
+      <c r="AB41" s="3" t="n"/>
+      <c r="AC41" s="3" t="n"/>
+      <c r="AD41" s="3" t="n"/>
+      <c r="AJ41" s="3" t="n"/>
+      <c r="AK41" s="3" t="n"/>
+      <c r="AL41" s="3" t="n"/>
+      <c r="AM41" s="3" t="n"/>
+      <c r="AN41" s="3" t="n"/>
+      <c r="AT41" s="3" t="n"/>
+      <c r="AU41" s="3" t="n"/>
+      <c r="AV41" s="3" t="n"/>
+      <c r="AW41" s="3" t="n"/>
+      <c r="AX41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -1899,7 +2543,7 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>3.58</v>
+        <v>3.27</v>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
       <c r="D42" s="3" t="inlineStr">
@@ -1915,12 +2559,28 @@
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="n"/>
       <c r="L42" s="3" t="n"/>
       <c r="M42" s="3" t="n"/>
       <c r="Q42" s="3" t="n"/>
       <c r="R42" s="3" t="n"/>
       <c r="S42" s="3" t="n"/>
       <c r="T42" s="3" t="n"/>
+      <c r="Z42" s="3" t="n"/>
+      <c r="AA42" s="3" t="n"/>
+      <c r="AB42" s="3" t="n"/>
+      <c r="AC42" s="3" t="n"/>
+      <c r="AD42" s="3" t="n"/>
+      <c r="AJ42" s="3" t="n"/>
+      <c r="AK42" s="3" t="n"/>
+      <c r="AL42" s="3" t="n"/>
+      <c r="AM42" s="3" t="n"/>
+      <c r="AN42" s="3" t="n"/>
+      <c r="AT42" s="3" t="n"/>
+      <c r="AU42" s="3" t="n"/>
+      <c r="AV42" s="3" t="n"/>
+      <c r="AW42" s="3" t="n"/>
+      <c r="AX42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1929,10 +2589,10 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -1947,12 +2607,28 @@
       <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
       <c r="L43" s="3" t="n"/>
       <c r="M43" s="3" t="n"/>
       <c r="Q43" s="3" t="n"/>
       <c r="R43" s="3" t="n"/>
       <c r="S43" s="3" t="n"/>
       <c r="T43" s="3" t="n"/>
+      <c r="Z43" s="3" t="n"/>
+      <c r="AA43" s="3" t="n"/>
+      <c r="AB43" s="3" t="n"/>
+      <c r="AC43" s="3" t="n"/>
+      <c r="AD43" s="3" t="n"/>
+      <c r="AJ43" s="3" t="n"/>
+      <c r="AK43" s="3" t="n"/>
+      <c r="AL43" s="3" t="n"/>
+      <c r="AM43" s="3" t="n"/>
+      <c r="AN43" s="3" t="n"/>
+      <c r="AT43" s="3" t="n"/>
+      <c r="AU43" s="3" t="n"/>
+      <c r="AV43" s="3" t="n"/>
+      <c r="AW43" s="3" t="n"/>
+      <c r="AX43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1961,10 +2637,10 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -1979,12 +2655,28 @@
       <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="n"/>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
       <c r="Q44" s="3" t="n"/>
       <c r="R44" s="3" t="n"/>
       <c r="S44" s="3" t="n"/>
       <c r="T44" s="3" t="n"/>
+      <c r="Z44" s="3" t="n"/>
+      <c r="AA44" s="3" t="n"/>
+      <c r="AB44" s="3" t="n"/>
+      <c r="AC44" s="3" t="n"/>
+      <c r="AD44" s="3" t="n"/>
+      <c r="AJ44" s="3" t="n"/>
+      <c r="AK44" s="3" t="n"/>
+      <c r="AL44" s="3" t="n"/>
+      <c r="AM44" s="3" t="n"/>
+      <c r="AN44" s="3" t="n"/>
+      <c r="AT44" s="3" t="n"/>
+      <c r="AU44" s="3" t="n"/>
+      <c r="AV44" s="3" t="n"/>
+      <c r="AW44" s="3" t="n"/>
+      <c r="AX44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1993,10 +2685,10 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -2011,12 +2703,28 @@
       <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="n"/>
       <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="n"/>
       <c r="L45" s="3" t="n"/>
       <c r="M45" s="3" t="n"/>
       <c r="Q45" s="3" t="n"/>
       <c r="R45" s="3" t="n"/>
       <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="n"/>
+      <c r="Z45" s="3" t="n"/>
+      <c r="AA45" s="3" t="n"/>
+      <c r="AB45" s="3" t="n"/>
+      <c r="AC45" s="3" t="n"/>
+      <c r="AD45" s="3" t="n"/>
+      <c r="AJ45" s="3" t="n"/>
+      <c r="AK45" s="3" t="n"/>
+      <c r="AL45" s="3" t="n"/>
+      <c r="AM45" s="3" t="n"/>
+      <c r="AN45" s="3" t="n"/>
+      <c r="AT45" s="3" t="n"/>
+      <c r="AU45" s="3" t="n"/>
+      <c r="AV45" s="3" t="n"/>
+      <c r="AW45" s="3" t="n"/>
+      <c r="AX45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -2025,7 +2733,7 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="3" t="inlineStr">
@@ -2041,12 +2749,28 @@
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="n"/>
       <c r="M46" s="3" t="n"/>
       <c r="Q46" s="3" t="n"/>
       <c r="R46" s="3" t="n"/>
       <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n"/>
+      <c r="Z46" s="3" t="n"/>
+      <c r="AA46" s="3" t="n"/>
+      <c r="AB46" s="3" t="n"/>
+      <c r="AC46" s="3" t="n"/>
+      <c r="AD46" s="3" t="n"/>
+      <c r="AJ46" s="3" t="n"/>
+      <c r="AK46" s="3" t="n"/>
+      <c r="AL46" s="3" t="n"/>
+      <c r="AM46" s="3" t="n"/>
+      <c r="AN46" s="3" t="n"/>
+      <c r="AT46" s="3" t="n"/>
+      <c r="AU46" s="3" t="n"/>
+      <c r="AV46" s="3" t="n"/>
+      <c r="AW46" s="3" t="n"/>
+      <c r="AX46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -2055,10 +2779,10 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -2073,12 +2797,28 @@
       <c r="H47" s="3" t="n"/>
       <c r="I47" s="3" t="n"/>
       <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
       <c r="L47" s="3" t="n"/>
       <c r="M47" s="3" t="n"/>
       <c r="Q47" s="3" t="n"/>
       <c r="R47" s="3" t="n"/>
       <c r="S47" s="3" t="n"/>
       <c r="T47" s="3" t="n"/>
+      <c r="Z47" s="3" t="n"/>
+      <c r="AA47" s="3" t="n"/>
+      <c r="AB47" s="3" t="n"/>
+      <c r="AC47" s="3" t="n"/>
+      <c r="AD47" s="3" t="n"/>
+      <c r="AJ47" s="3" t="n"/>
+      <c r="AK47" s="3" t="n"/>
+      <c r="AL47" s="3" t="n"/>
+      <c r="AM47" s="3" t="n"/>
+      <c r="AN47" s="3" t="n"/>
+      <c r="AT47" s="3" t="n"/>
+      <c r="AU47" s="3" t="n"/>
+      <c r="AV47" s="3" t="n"/>
+      <c r="AW47" s="3" t="n"/>
+      <c r="AX47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2087,10 +2827,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -2105,12 +2845,28 @@
       <c r="H48" s="3" t="n"/>
       <c r="I48" s="3" t="n"/>
       <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="n"/>
       <c r="L48" s="3" t="n"/>
       <c r="M48" s="3" t="n"/>
       <c r="Q48" s="3" t="n"/>
       <c r="R48" s="3" t="n"/>
       <c r="S48" s="3" t="n"/>
       <c r="T48" s="3" t="n"/>
+      <c r="Z48" s="3" t="n"/>
+      <c r="AA48" s="3" t="n"/>
+      <c r="AB48" s="3" t="n"/>
+      <c r="AC48" s="3" t="n"/>
+      <c r="AD48" s="3" t="n"/>
+      <c r="AJ48" s="3" t="n"/>
+      <c r="AK48" s="3" t="n"/>
+      <c r="AL48" s="3" t="n"/>
+      <c r="AM48" s="3" t="n"/>
+      <c r="AN48" s="3" t="n"/>
+      <c r="AT48" s="3" t="n"/>
+      <c r="AU48" s="3" t="n"/>
+      <c r="AV48" s="3" t="n"/>
+      <c r="AW48" s="3" t="n"/>
+      <c r="AX48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -2119,10 +2875,10 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -2137,12 +2893,28 @@
       <c r="H49" s="3" t="n"/>
       <c r="I49" s="3" t="n"/>
       <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="n"/>
       <c r="L49" s="3" t="n"/>
       <c r="M49" s="3" t="n"/>
       <c r="Q49" s="3" t="n"/>
       <c r="R49" s="3" t="n"/>
       <c r="S49" s="3" t="n"/>
       <c r="T49" s="3" t="n"/>
+      <c r="Z49" s="3" t="n"/>
+      <c r="AA49" s="3" t="n"/>
+      <c r="AB49" s="3" t="n"/>
+      <c r="AC49" s="3" t="n"/>
+      <c r="AD49" s="3" t="n"/>
+      <c r="AJ49" s="3" t="n"/>
+      <c r="AK49" s="3" t="n"/>
+      <c r="AL49" s="3" t="n"/>
+      <c r="AM49" s="3" t="n"/>
+      <c r="AN49" s="3" t="n"/>
+      <c r="AT49" s="3" t="n"/>
+      <c r="AU49" s="3" t="n"/>
+      <c r="AV49" s="3" t="n"/>
+      <c r="AW49" s="3" t="n"/>
+      <c r="AX49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -2151,7 +2923,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>24.61</v>
+        <v>24.56</v>
       </c>
       <c r="C50" s="3" t="inlineStr"/>
       <c r="D50" s="3" t="inlineStr">
@@ -2167,12 +2939,28 @@
       <c r="H50" s="3" t="n"/>
       <c r="I50" s="3" t="n"/>
       <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="n"/>
       <c r="L50" s="3" t="n"/>
       <c r="M50" s="3" t="n"/>
       <c r="Q50" s="3" t="n"/>
       <c r="R50" s="3" t="n"/>
       <c r="S50" s="3" t="n"/>
       <c r="T50" s="3" t="n"/>
+      <c r="Z50" s="3" t="n"/>
+      <c r="AA50" s="3" t="n"/>
+      <c r="AB50" s="3" t="n"/>
+      <c r="AC50" s="3" t="n"/>
+      <c r="AD50" s="3" t="n"/>
+      <c r="AJ50" s="3" t="n"/>
+      <c r="AK50" s="3" t="n"/>
+      <c r="AL50" s="3" t="n"/>
+      <c r="AM50" s="3" t="n"/>
+      <c r="AN50" s="3" t="n"/>
+      <c r="AT50" s="3" t="n"/>
+      <c r="AU50" s="3" t="n"/>
+      <c r="AV50" s="3" t="n"/>
+      <c r="AW50" s="3" t="n"/>
+      <c r="AX50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -2181,10 +2969,10 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -2199,12 +2987,28 @@
       <c r="H51" s="3" t="n"/>
       <c r="I51" s="3" t="n"/>
       <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="n"/>
       <c r="L51" s="3" t="n"/>
       <c r="M51" s="3" t="n"/>
       <c r="Q51" s="3" t="n"/>
       <c r="R51" s="3" t="n"/>
       <c r="S51" s="3" t="n"/>
       <c r="T51" s="3" t="n"/>
+      <c r="Z51" s="3" t="n"/>
+      <c r="AA51" s="3" t="n"/>
+      <c r="AB51" s="3" t="n"/>
+      <c r="AC51" s="3" t="n"/>
+      <c r="AD51" s="3" t="n"/>
+      <c r="AJ51" s="3" t="n"/>
+      <c r="AK51" s="3" t="n"/>
+      <c r="AL51" s="3" t="n"/>
+      <c r="AM51" s="3" t="n"/>
+      <c r="AN51" s="3" t="n"/>
+      <c r="AT51" s="3" t="n"/>
+      <c r="AU51" s="3" t="n"/>
+      <c r="AV51" s="3" t="n"/>
+      <c r="AW51" s="3" t="n"/>
+      <c r="AX51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -2216,7 +3020,7 @@
         <v>0.11</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
@@ -2231,12 +3035,28 @@
       <c r="H52" s="3" t="n"/>
       <c r="I52" s="3" t="n"/>
       <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="n"/>
       <c r="L52" s="3" t="n"/>
       <c r="M52" s="3" t="n"/>
       <c r="Q52" s="3" t="n"/>
       <c r="R52" s="3" t="n"/>
       <c r="S52" s="3" t="n"/>
       <c r="T52" s="3" t="n"/>
+      <c r="Z52" s="3" t="n"/>
+      <c r="AA52" s="3" t="n"/>
+      <c r="AB52" s="3" t="n"/>
+      <c r="AC52" s="3" t="n"/>
+      <c r="AD52" s="3" t="n"/>
+      <c r="AJ52" s="3" t="n"/>
+      <c r="AK52" s="3" t="n"/>
+      <c r="AL52" s="3" t="n"/>
+      <c r="AM52" s="3" t="n"/>
+      <c r="AN52" s="3" t="n"/>
+      <c r="AT52" s="3" t="n"/>
+      <c r="AU52" s="3" t="n"/>
+      <c r="AV52" s="3" t="n"/>
+      <c r="AW52" s="3" t="n"/>
+      <c r="AX52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -2263,12 +3083,28 @@
       <c r="H53" s="3" t="n"/>
       <c r="I53" s="3" t="n"/>
       <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="n"/>
       <c r="L53" s="3" t="n"/>
       <c r="M53" s="3" t="n"/>
       <c r="Q53" s="3" t="n"/>
       <c r="R53" s="3" t="n"/>
       <c r="S53" s="3" t="n"/>
       <c r="T53" s="3" t="n"/>
+      <c r="Z53" s="3" t="n"/>
+      <c r="AA53" s="3" t="n"/>
+      <c r="AB53" s="3" t="n"/>
+      <c r="AC53" s="3" t="n"/>
+      <c r="AD53" s="3" t="n"/>
+      <c r="AJ53" s="3" t="n"/>
+      <c r="AK53" s="3" t="n"/>
+      <c r="AL53" s="3" t="n"/>
+      <c r="AM53" s="3" t="n"/>
+      <c r="AN53" s="3" t="n"/>
+      <c r="AT53" s="3" t="n"/>
+      <c r="AU53" s="3" t="n"/>
+      <c r="AV53" s="3" t="n"/>
+      <c r="AW53" s="3" t="n"/>
+      <c r="AX53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -2280,7 +3116,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -2295,12 +3131,28 @@
       <c r="H54" s="3" t="n"/>
       <c r="I54" s="3" t="n"/>
       <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="n"/>
       <c r="L54" s="3" t="n"/>
       <c r="M54" s="3" t="n"/>
       <c r="Q54" s="3" t="n"/>
       <c r="R54" s="3" t="n"/>
       <c r="S54" s="3" t="n"/>
       <c r="T54" s="3" t="n"/>
+      <c r="Z54" s="3" t="n"/>
+      <c r="AA54" s="3" t="n"/>
+      <c r="AB54" s="3" t="n"/>
+      <c r="AC54" s="3" t="n"/>
+      <c r="AD54" s="3" t="n"/>
+      <c r="AJ54" s="3" t="n"/>
+      <c r="AK54" s="3" t="n"/>
+      <c r="AL54" s="3" t="n"/>
+      <c r="AM54" s="3" t="n"/>
+      <c r="AN54" s="3" t="n"/>
+      <c r="AT54" s="3" t="n"/>
+      <c r="AU54" s="3" t="n"/>
+      <c r="AV54" s="3" t="n"/>
+      <c r="AW54" s="3" t="n"/>
+      <c r="AX54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -2309,7 +3161,7 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="C55" s="3" t="n">
         <v>0.22</v>
@@ -2327,12 +3179,28 @@
       <c r="H55" s="3" t="n"/>
       <c r="I55" s="3" t="n"/>
       <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="n"/>
       <c r="L55" s="3" t="n"/>
       <c r="M55" s="3" t="n"/>
       <c r="Q55" s="3" t="n"/>
       <c r="R55" s="3" t="n"/>
       <c r="S55" s="3" t="n"/>
       <c r="T55" s="3" t="n"/>
+      <c r="Z55" s="3" t="n"/>
+      <c r="AA55" s="3" t="n"/>
+      <c r="AB55" s="3" t="n"/>
+      <c r="AC55" s="3" t="n"/>
+      <c r="AD55" s="3" t="n"/>
+      <c r="AJ55" s="3" t="n"/>
+      <c r="AK55" s="3" t="n"/>
+      <c r="AL55" s="3" t="n"/>
+      <c r="AM55" s="3" t="n"/>
+      <c r="AN55" s="3" t="n"/>
+      <c r="AT55" s="3" t="n"/>
+      <c r="AU55" s="3" t="n"/>
+      <c r="AV55" s="3" t="n"/>
+      <c r="AW55" s="3" t="n"/>
+      <c r="AX55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -2341,10 +3209,10 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
@@ -2359,12 +3227,28 @@
       <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
       <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="n"/>
       <c r="L56" s="3" t="n"/>
       <c r="M56" s="3" t="n"/>
       <c r="Q56" s="3" t="n"/>
       <c r="R56" s="3" t="n"/>
       <c r="S56" s="3" t="n"/>
       <c r="T56" s="3" t="n"/>
+      <c r="Z56" s="3" t="n"/>
+      <c r="AA56" s="3" t="n"/>
+      <c r="AB56" s="3" t="n"/>
+      <c r="AC56" s="3" t="n"/>
+      <c r="AD56" s="3" t="n"/>
+      <c r="AJ56" s="3" t="n"/>
+      <c r="AK56" s="3" t="n"/>
+      <c r="AL56" s="3" t="n"/>
+      <c r="AM56" s="3" t="n"/>
+      <c r="AN56" s="3" t="n"/>
+      <c r="AT56" s="3" t="n"/>
+      <c r="AU56" s="3" t="n"/>
+      <c r="AV56" s="3" t="n"/>
+      <c r="AW56" s="3" t="n"/>
+      <c r="AX56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -2376,7 +3260,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
@@ -2391,12 +3275,28 @@
       <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="n"/>
       <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="n"/>
       <c r="L57" s="3" t="n"/>
       <c r="M57" s="3" t="n"/>
       <c r="Q57" s="3" t="n"/>
       <c r="R57" s="3" t="n"/>
       <c r="S57" s="3" t="n"/>
       <c r="T57" s="3" t="n"/>
+      <c r="Z57" s="3" t="n"/>
+      <c r="AA57" s="3" t="n"/>
+      <c r="AB57" s="3" t="n"/>
+      <c r="AC57" s="3" t="n"/>
+      <c r="AD57" s="3" t="n"/>
+      <c r="AJ57" s="3" t="n"/>
+      <c r="AK57" s="3" t="n"/>
+      <c r="AL57" s="3" t="n"/>
+      <c r="AM57" s="3" t="n"/>
+      <c r="AN57" s="3" t="n"/>
+      <c r="AT57" s="3" t="n"/>
+      <c r="AU57" s="3" t="n"/>
+      <c r="AV57" s="3" t="n"/>
+      <c r="AW57" s="3" t="n"/>
+      <c r="AX57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -2408,7 +3308,7 @@
         <v>0.11</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
@@ -2423,12 +3323,28 @@
       <c r="H58" s="3" t="n"/>
       <c r="I58" s="3" t="n"/>
       <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="n"/>
       <c r="L58" s="3" t="n"/>
       <c r="M58" s="3" t="n"/>
       <c r="Q58" s="3" t="n"/>
       <c r="R58" s="3" t="n"/>
       <c r="S58" s="3" t="n"/>
       <c r="T58" s="3" t="n"/>
+      <c r="Z58" s="3" t="n"/>
+      <c r="AA58" s="3" t="n"/>
+      <c r="AB58" s="3" t="n"/>
+      <c r="AC58" s="3" t="n"/>
+      <c r="AD58" s="3" t="n"/>
+      <c r="AJ58" s="3" t="n"/>
+      <c r="AK58" s="3" t="n"/>
+      <c r="AL58" s="3" t="n"/>
+      <c r="AM58" s="3" t="n"/>
+      <c r="AN58" s="3" t="n"/>
+      <c r="AT58" s="3" t="n"/>
+      <c r="AU58" s="3" t="n"/>
+      <c r="AV58" s="3" t="n"/>
+      <c r="AW58" s="3" t="n"/>
+      <c r="AX58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -2437,10 +3353,10 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
@@ -2455,12 +3371,28 @@
       <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="n"/>
       <c r="J59" s="3" t="n"/>
+      <c r="K59" s="3" t="n"/>
       <c r="L59" s="3" t="n"/>
       <c r="M59" s="3" t="n"/>
       <c r="Q59" s="3" t="n"/>
       <c r="R59" s="3" t="n"/>
       <c r="S59" s="3" t="n"/>
       <c r="T59" s="3" t="n"/>
+      <c r="Z59" s="3" t="n"/>
+      <c r="AA59" s="3" t="n"/>
+      <c r="AB59" s="3" t="n"/>
+      <c r="AC59" s="3" t="n"/>
+      <c r="AD59" s="3" t="n"/>
+      <c r="AJ59" s="3" t="n"/>
+      <c r="AK59" s="3" t="n"/>
+      <c r="AL59" s="3" t="n"/>
+      <c r="AM59" s="3" t="n"/>
+      <c r="AN59" s="3" t="n"/>
+      <c r="AT59" s="3" t="n"/>
+      <c r="AU59" s="3" t="n"/>
+      <c r="AV59" s="3" t="n"/>
+      <c r="AW59" s="3" t="n"/>
+      <c r="AX59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -2472,7 +3404,7 @@
         <v>0.12</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
@@ -2487,12 +3419,28 @@
       <c r="H60" s="3" t="n"/>
       <c r="I60" s="3" t="n"/>
       <c r="J60" s="3" t="n"/>
+      <c r="K60" s="3" t="n"/>
       <c r="L60" s="3" t="n"/>
       <c r="M60" s="3" t="n"/>
       <c r="Q60" s="3" t="n"/>
       <c r="R60" s="3" t="n"/>
       <c r="S60" s="3" t="n"/>
       <c r="T60" s="3" t="n"/>
+      <c r="Z60" s="3" t="n"/>
+      <c r="AA60" s="3" t="n"/>
+      <c r="AB60" s="3" t="n"/>
+      <c r="AC60" s="3" t="n"/>
+      <c r="AD60" s="3" t="n"/>
+      <c r="AJ60" s="3" t="n"/>
+      <c r="AK60" s="3" t="n"/>
+      <c r="AL60" s="3" t="n"/>
+      <c r="AM60" s="3" t="n"/>
+      <c r="AN60" s="3" t="n"/>
+      <c r="AT60" s="3" t="n"/>
+      <c r="AU60" s="3" t="n"/>
+      <c r="AV60" s="3" t="n"/>
+      <c r="AW60" s="3" t="n"/>
+      <c r="AX60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -2501,7 +3449,7 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>6.54</v>
+        <v>6.46</v>
       </c>
       <c r="C61" s="3" t="inlineStr"/>
       <c r="D61" s="3" t="inlineStr">
@@ -2517,12 +3465,28 @@
       <c r="H61" s="3" t="n"/>
       <c r="I61" s="3" t="n"/>
       <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="n"/>
       <c r="L61" s="3" t="n"/>
       <c r="M61" s="3" t="n"/>
       <c r="Q61" s="3" t="n"/>
       <c r="R61" s="3" t="n"/>
       <c r="S61" s="3" t="n"/>
       <c r="T61" s="3" t="n"/>
+      <c r="Z61" s="3" t="n"/>
+      <c r="AA61" s="3" t="n"/>
+      <c r="AB61" s="3" t="n"/>
+      <c r="AC61" s="3" t="n"/>
+      <c r="AD61" s="3" t="n"/>
+      <c r="AJ61" s="3" t="n"/>
+      <c r="AK61" s="3" t="n"/>
+      <c r="AL61" s="3" t="n"/>
+      <c r="AM61" s="3" t="n"/>
+      <c r="AN61" s="3" t="n"/>
+      <c r="AT61" s="3" t="n"/>
+      <c r="AU61" s="3" t="n"/>
+      <c r="AV61" s="3" t="n"/>
+      <c r="AW61" s="3" t="n"/>
+      <c r="AX61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -2531,7 +3495,7 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>14.18</v>
+        <v>14.31</v>
       </c>
       <c r="C62" s="3" t="inlineStr"/>
       <c r="D62" s="3" t="inlineStr">
@@ -2547,12 +3511,28 @@
       <c r="H62" s="3" t="n"/>
       <c r="I62" s="3" t="n"/>
       <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="n"/>
       <c r="L62" s="3" t="n"/>
       <c r="M62" s="3" t="n"/>
       <c r="Q62" s="3" t="n"/>
       <c r="R62" s="3" t="n"/>
       <c r="S62" s="3" t="n"/>
       <c r="T62" s="3" t="n"/>
+      <c r="Z62" s="3" t="n"/>
+      <c r="AA62" s="3" t="n"/>
+      <c r="AB62" s="3" t="n"/>
+      <c r="AC62" s="3" t="n"/>
+      <c r="AD62" s="3" t="n"/>
+      <c r="AJ62" s="3" t="n"/>
+      <c r="AK62" s="3" t="n"/>
+      <c r="AL62" s="3" t="n"/>
+      <c r="AM62" s="3" t="n"/>
+      <c r="AN62" s="3" t="n"/>
+      <c r="AT62" s="3" t="n"/>
+      <c r="AU62" s="3" t="n"/>
+      <c r="AV62" s="3" t="n"/>
+      <c r="AW62" s="3" t="n"/>
+      <c r="AX62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -2561,10 +3541,10 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
@@ -2579,12 +3559,28 @@
       <c r="H63" s="3" t="n"/>
       <c r="I63" s="3" t="n"/>
       <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="n"/>
       <c r="L63" s="3" t="n"/>
       <c r="M63" s="3" t="n"/>
       <c r="Q63" s="3" t="n"/>
       <c r="R63" s="3" t="n"/>
       <c r="S63" s="3" t="n"/>
       <c r="T63" s="3" t="n"/>
+      <c r="Z63" s="3" t="n"/>
+      <c r="AA63" s="3" t="n"/>
+      <c r="AB63" s="3" t="n"/>
+      <c r="AC63" s="3" t="n"/>
+      <c r="AD63" s="3" t="n"/>
+      <c r="AJ63" s="3" t="n"/>
+      <c r="AK63" s="3" t="n"/>
+      <c r="AL63" s="3" t="n"/>
+      <c r="AM63" s="3" t="n"/>
+      <c r="AN63" s="3" t="n"/>
+      <c r="AT63" s="3" t="n"/>
+      <c r="AU63" s="3" t="n"/>
+      <c r="AV63" s="3" t="n"/>
+      <c r="AW63" s="3" t="n"/>
+      <c r="AX63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -2593,10 +3589,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
@@ -2611,12 +3607,28 @@
       <c r="H64" s="3" t="n"/>
       <c r="I64" s="3" t="n"/>
       <c r="J64" s="3" t="n"/>
+      <c r="K64" s="3" t="n"/>
       <c r="L64" s="3" t="n"/>
       <c r="M64" s="3" t="n"/>
       <c r="Q64" s="3" t="n"/>
       <c r="R64" s="3" t="n"/>
       <c r="S64" s="3" t="n"/>
       <c r="T64" s="3" t="n"/>
+      <c r="Z64" s="3" t="n"/>
+      <c r="AA64" s="3" t="n"/>
+      <c r="AB64" s="3" t="n"/>
+      <c r="AC64" s="3" t="n"/>
+      <c r="AD64" s="3" t="n"/>
+      <c r="AJ64" s="3" t="n"/>
+      <c r="AK64" s="3" t="n"/>
+      <c r="AL64" s="3" t="n"/>
+      <c r="AM64" s="3" t="n"/>
+      <c r="AN64" s="3" t="n"/>
+      <c r="AT64" s="3" t="n"/>
+      <c r="AU64" s="3" t="n"/>
+      <c r="AV64" s="3" t="n"/>
+      <c r="AW64" s="3" t="n"/>
+      <c r="AX64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2625,7 +3637,7 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>0.14</v>
@@ -2643,12 +3655,28 @@
       <c r="H65" s="3" t="n"/>
       <c r="I65" s="3" t="n"/>
       <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="n"/>
       <c r="L65" s="3" t="n"/>
       <c r="M65" s="3" t="n"/>
       <c r="Q65" s="3" t="n"/>
       <c r="R65" s="3" t="n"/>
       <c r="S65" s="3" t="n"/>
       <c r="T65" s="3" t="n"/>
+      <c r="Z65" s="3" t="n"/>
+      <c r="AA65" s="3" t="n"/>
+      <c r="AB65" s="3" t="n"/>
+      <c r="AC65" s="3" t="n"/>
+      <c r="AD65" s="3" t="n"/>
+      <c r="AJ65" s="3" t="n"/>
+      <c r="AK65" s="3" t="n"/>
+      <c r="AL65" s="3" t="n"/>
+      <c r="AM65" s="3" t="n"/>
+      <c r="AN65" s="3" t="n"/>
+      <c r="AT65" s="3" t="n"/>
+      <c r="AU65" s="3" t="n"/>
+      <c r="AV65" s="3" t="n"/>
+      <c r="AW65" s="3" t="n"/>
+      <c r="AX65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -2660,7 +3688,7 @@
         <v>0.08</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
@@ -2675,12 +3703,28 @@
       <c r="H66" s="3" t="n"/>
       <c r="I66" s="3" t="n"/>
       <c r="J66" s="3" t="n"/>
+      <c r="K66" s="3" t="n"/>
       <c r="L66" s="3" t="n"/>
       <c r="M66" s="3" t="n"/>
       <c r="Q66" s="3" t="n"/>
       <c r="R66" s="3" t="n"/>
       <c r="S66" s="3" t="n"/>
       <c r="T66" s="3" t="n"/>
+      <c r="Z66" s="3" t="n"/>
+      <c r="AA66" s="3" t="n"/>
+      <c r="AB66" s="3" t="n"/>
+      <c r="AC66" s="3" t="n"/>
+      <c r="AD66" s="3" t="n"/>
+      <c r="AJ66" s="3" t="n"/>
+      <c r="AK66" s="3" t="n"/>
+      <c r="AL66" s="3" t="n"/>
+      <c r="AM66" s="3" t="n"/>
+      <c r="AN66" s="3" t="n"/>
+      <c r="AT66" s="3" t="n"/>
+      <c r="AU66" s="3" t="n"/>
+      <c r="AV66" s="3" t="n"/>
+      <c r="AW66" s="3" t="n"/>
+      <c r="AX66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2689,10 +3733,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -2707,12 +3751,28 @@
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="3" t="n"/>
       <c r="J67" s="3" t="n"/>
+      <c r="K67" s="3" t="n"/>
       <c r="L67" s="3" t="n"/>
       <c r="M67" s="3" t="n"/>
       <c r="Q67" s="3" t="n"/>
       <c r="R67" s="3" t="n"/>
       <c r="S67" s="3" t="n"/>
       <c r="T67" s="3" t="n"/>
+      <c r="Z67" s="3" t="n"/>
+      <c r="AA67" s="3" t="n"/>
+      <c r="AB67" s="3" t="n"/>
+      <c r="AC67" s="3" t="n"/>
+      <c r="AD67" s="3" t="n"/>
+      <c r="AJ67" s="3" t="n"/>
+      <c r="AK67" s="3" t="n"/>
+      <c r="AL67" s="3" t="n"/>
+      <c r="AM67" s="3" t="n"/>
+      <c r="AN67" s="3" t="n"/>
+      <c r="AT67" s="3" t="n"/>
+      <c r="AU67" s="3" t="n"/>
+      <c r="AV67" s="3" t="n"/>
+      <c r="AW67" s="3" t="n"/>
+      <c r="AX67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -2721,10 +3781,10 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
@@ -2739,12 +3799,28 @@
       <c r="H68" s="3" t="n"/>
       <c r="I68" s="3" t="n"/>
       <c r="J68" s="3" t="n"/>
+      <c r="K68" s="3" t="n"/>
       <c r="L68" s="3" t="n"/>
       <c r="M68" s="3" t="n"/>
       <c r="Q68" s="3" t="n"/>
       <c r="R68" s="3" t="n"/>
       <c r="S68" s="3" t="n"/>
       <c r="T68" s="3" t="n"/>
+      <c r="Z68" s="3" t="n"/>
+      <c r="AA68" s="3" t="n"/>
+      <c r="AB68" s="3" t="n"/>
+      <c r="AC68" s="3" t="n"/>
+      <c r="AD68" s="3" t="n"/>
+      <c r="AJ68" s="3" t="n"/>
+      <c r="AK68" s="3" t="n"/>
+      <c r="AL68" s="3" t="n"/>
+      <c r="AM68" s="3" t="n"/>
+      <c r="AN68" s="3" t="n"/>
+      <c r="AT68" s="3" t="n"/>
+      <c r="AU68" s="3" t="n"/>
+      <c r="AV68" s="3" t="n"/>
+      <c r="AW68" s="3" t="n"/>
+      <c r="AX68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -2753,10 +3829,10 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
@@ -2771,12 +3847,28 @@
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="3" t="n"/>
       <c r="J69" s="3" t="n"/>
+      <c r="K69" s="3" t="n"/>
       <c r="L69" s="3" t="n"/>
       <c r="M69" s="3" t="n"/>
       <c r="Q69" s="3" t="n"/>
       <c r="R69" s="3" t="n"/>
       <c r="S69" s="3" t="n"/>
       <c r="T69" s="3" t="n"/>
+      <c r="Z69" s="3" t="n"/>
+      <c r="AA69" s="3" t="n"/>
+      <c r="AB69" s="3" t="n"/>
+      <c r="AC69" s="3" t="n"/>
+      <c r="AD69" s="3" t="n"/>
+      <c r="AJ69" s="3" t="n"/>
+      <c r="AK69" s="3" t="n"/>
+      <c r="AL69" s="3" t="n"/>
+      <c r="AM69" s="3" t="n"/>
+      <c r="AN69" s="3" t="n"/>
+      <c r="AT69" s="3" t="n"/>
+      <c r="AU69" s="3" t="n"/>
+      <c r="AV69" s="3" t="n"/>
+      <c r="AW69" s="3" t="n"/>
+      <c r="AX69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -2788,7 +3880,7 @@
         <v>0.04</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
@@ -2803,12 +3895,28 @@
       <c r="H70" s="3" t="n"/>
       <c r="I70" s="3" t="n"/>
       <c r="J70" s="3" t="n"/>
+      <c r="K70" s="3" t="n"/>
       <c r="L70" s="3" t="n"/>
       <c r="M70" s="3" t="n"/>
       <c r="Q70" s="3" t="n"/>
       <c r="R70" s="3" t="n"/>
       <c r="S70" s="3" t="n"/>
       <c r="T70" s="3" t="n"/>
+      <c r="Z70" s="3" t="n"/>
+      <c r="AA70" s="3" t="n"/>
+      <c r="AB70" s="3" t="n"/>
+      <c r="AC70" s="3" t="n"/>
+      <c r="AD70" s="3" t="n"/>
+      <c r="AJ70" s="3" t="n"/>
+      <c r="AK70" s="3" t="n"/>
+      <c r="AL70" s="3" t="n"/>
+      <c r="AM70" s="3" t="n"/>
+      <c r="AN70" s="3" t="n"/>
+      <c r="AT70" s="3" t="n"/>
+      <c r="AU70" s="3" t="n"/>
+      <c r="AV70" s="3" t="n"/>
+      <c r="AW70" s="3" t="n"/>
+      <c r="AX70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -2820,7 +3928,7 @@
         <v>0.12</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
@@ -2835,12 +3943,28 @@
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="n"/>
       <c r="J71" s="3" t="n"/>
+      <c r="K71" s="3" t="n"/>
       <c r="L71" s="3" t="n"/>
       <c r="M71" s="3" t="n"/>
       <c r="Q71" s="3" t="n"/>
       <c r="R71" s="3" t="n"/>
       <c r="S71" s="3" t="n"/>
       <c r="T71" s="3" t="n"/>
+      <c r="Z71" s="3" t="n"/>
+      <c r="AA71" s="3" t="n"/>
+      <c r="AB71" s="3" t="n"/>
+      <c r="AC71" s="3" t="n"/>
+      <c r="AD71" s="3" t="n"/>
+      <c r="AJ71" s="3" t="n"/>
+      <c r="AK71" s="3" t="n"/>
+      <c r="AL71" s="3" t="n"/>
+      <c r="AM71" s="3" t="n"/>
+      <c r="AN71" s="3" t="n"/>
+      <c r="AT71" s="3" t="n"/>
+      <c r="AU71" s="3" t="n"/>
+      <c r="AV71" s="3" t="n"/>
+      <c r="AW71" s="3" t="n"/>
+      <c r="AX71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -2849,7 +3973,7 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>4.99</v>
+        <v>4.66</v>
       </c>
       <c r="C72" s="3" t="inlineStr"/>
       <c r="D72" s="3" t="inlineStr">
@@ -2865,12 +3989,28 @@
       <c r="H72" s="3" t="n"/>
       <c r="I72" s="3" t="n"/>
       <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="n"/>
       <c r="L72" s="3" t="n"/>
       <c r="M72" s="3" t="n"/>
       <c r="Q72" s="3" t="n"/>
       <c r="R72" s="3" t="n"/>
       <c r="S72" s="3" t="n"/>
       <c r="T72" s="3" t="n"/>
+      <c r="Z72" s="3" t="n"/>
+      <c r="AA72" s="3" t="n"/>
+      <c r="AB72" s="3" t="n"/>
+      <c r="AC72" s="3" t="n"/>
+      <c r="AD72" s="3" t="n"/>
+      <c r="AJ72" s="3" t="n"/>
+      <c r="AK72" s="3" t="n"/>
+      <c r="AL72" s="3" t="n"/>
+      <c r="AM72" s="3" t="n"/>
+      <c r="AN72" s="3" t="n"/>
+      <c r="AT72" s="3" t="n"/>
+      <c r="AU72" s="3" t="n"/>
+      <c r="AV72" s="3" t="n"/>
+      <c r="AW72" s="3" t="n"/>
+      <c r="AX72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -2879,7 +4019,7 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>12.78</v>
+        <v>13.6</v>
       </c>
       <c r="C73" s="3" t="inlineStr"/>
       <c r="D73" s="3" t="inlineStr">
@@ -2895,12 +4035,28 @@
       <c r="H73" s="3" t="n"/>
       <c r="I73" s="3" t="n"/>
       <c r="J73" s="3" t="n"/>
+      <c r="K73" s="3" t="n"/>
       <c r="L73" s="3" t="n"/>
       <c r="M73" s="3" t="n"/>
       <c r="Q73" s="3" t="n"/>
       <c r="R73" s="3" t="n"/>
       <c r="S73" s="3" t="n"/>
       <c r="T73" s="3" t="n"/>
+      <c r="Z73" s="3" t="n"/>
+      <c r="AA73" s="3" t="n"/>
+      <c r="AB73" s="3" t="n"/>
+      <c r="AC73" s="3" t="n"/>
+      <c r="AD73" s="3" t="n"/>
+      <c r="AJ73" s="3" t="n"/>
+      <c r="AK73" s="3" t="n"/>
+      <c r="AL73" s="3" t="n"/>
+      <c r="AM73" s="3" t="n"/>
+      <c r="AN73" s="3" t="n"/>
+      <c r="AT73" s="3" t="n"/>
+      <c r="AU73" s="3" t="n"/>
+      <c r="AV73" s="3" t="n"/>
+      <c r="AW73" s="3" t="n"/>
+      <c r="AX73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -2912,7 +4068,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
@@ -2927,12 +4083,28 @@
       <c r="H74" s="3" t="n"/>
       <c r="I74" s="3" t="n"/>
       <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="n"/>
       <c r="L74" s="3" t="n"/>
       <c r="M74" s="3" t="n"/>
       <c r="Q74" s="3" t="n"/>
       <c r="R74" s="3" t="n"/>
       <c r="S74" s="3" t="n"/>
       <c r="T74" s="3" t="n"/>
+      <c r="Z74" s="3" t="n"/>
+      <c r="AA74" s="3" t="n"/>
+      <c r="AB74" s="3" t="n"/>
+      <c r="AC74" s="3" t="n"/>
+      <c r="AD74" s="3" t="n"/>
+      <c r="AJ74" s="3" t="n"/>
+      <c r="AK74" s="3" t="n"/>
+      <c r="AL74" s="3" t="n"/>
+      <c r="AM74" s="3" t="n"/>
+      <c r="AN74" s="3" t="n"/>
+      <c r="AT74" s="3" t="n"/>
+      <c r="AU74" s="3" t="n"/>
+      <c r="AV74" s="3" t="n"/>
+      <c r="AW74" s="3" t="n"/>
+      <c r="AX74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2941,10 +4113,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
@@ -2959,12 +4131,28 @@
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="3" t="n"/>
       <c r="J75" s="3" t="n"/>
+      <c r="K75" s="3" t="n"/>
       <c r="L75" s="3" t="n"/>
       <c r="M75" s="3" t="n"/>
       <c r="Q75" s="3" t="n"/>
       <c r="R75" s="3" t="n"/>
       <c r="S75" s="3" t="n"/>
       <c r="T75" s="3" t="n"/>
+      <c r="Z75" s="3" t="n"/>
+      <c r="AA75" s="3" t="n"/>
+      <c r="AB75" s="3" t="n"/>
+      <c r="AC75" s="3" t="n"/>
+      <c r="AD75" s="3" t="n"/>
+      <c r="AJ75" s="3" t="n"/>
+      <c r="AK75" s="3" t="n"/>
+      <c r="AL75" s="3" t="n"/>
+      <c r="AM75" s="3" t="n"/>
+      <c r="AN75" s="3" t="n"/>
+      <c r="AT75" s="3" t="n"/>
+      <c r="AU75" s="3" t="n"/>
+      <c r="AV75" s="3" t="n"/>
+      <c r="AW75" s="3" t="n"/>
+      <c r="AX75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -2976,7 +4164,7 @@
         <v>0.05</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
@@ -2991,12 +4179,28 @@
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="3" t="n"/>
       <c r="J76" s="3" t="n"/>
+      <c r="K76" s="3" t="n"/>
       <c r="L76" s="3" t="n"/>
       <c r="M76" s="3" t="n"/>
       <c r="Q76" s="3" t="n"/>
       <c r="R76" s="3" t="n"/>
       <c r="S76" s="3" t="n"/>
       <c r="T76" s="3" t="n"/>
+      <c r="Z76" s="3" t="n"/>
+      <c r="AA76" s="3" t="n"/>
+      <c r="AB76" s="3" t="n"/>
+      <c r="AC76" s="3" t="n"/>
+      <c r="AD76" s="3" t="n"/>
+      <c r="AJ76" s="3" t="n"/>
+      <c r="AK76" s="3" t="n"/>
+      <c r="AL76" s="3" t="n"/>
+      <c r="AM76" s="3" t="n"/>
+      <c r="AN76" s="3" t="n"/>
+      <c r="AT76" s="3" t="n"/>
+      <c r="AU76" s="3" t="n"/>
+      <c r="AV76" s="3" t="n"/>
+      <c r="AW76" s="3" t="n"/>
+      <c r="AX76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -3005,10 +4209,10 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
@@ -3023,12 +4227,28 @@
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="3" t="n"/>
       <c r="J77" s="3" t="n"/>
+      <c r="K77" s="3" t="n"/>
       <c r="L77" s="3" t="n"/>
       <c r="M77" s="3" t="n"/>
       <c r="Q77" s="3" t="n"/>
       <c r="R77" s="3" t="n"/>
       <c r="S77" s="3" t="n"/>
       <c r="T77" s="3" t="n"/>
+      <c r="Z77" s="3" t="n"/>
+      <c r="AA77" s="3" t="n"/>
+      <c r="AB77" s="3" t="n"/>
+      <c r="AC77" s="3" t="n"/>
+      <c r="AD77" s="3" t="n"/>
+      <c r="AJ77" s="3" t="n"/>
+      <c r="AK77" s="3" t="n"/>
+      <c r="AL77" s="3" t="n"/>
+      <c r="AM77" s="3" t="n"/>
+      <c r="AN77" s="3" t="n"/>
+      <c r="AT77" s="3" t="n"/>
+      <c r="AU77" s="3" t="n"/>
+      <c r="AV77" s="3" t="n"/>
+      <c r="AW77" s="3" t="n"/>
+      <c r="AX77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -3037,7 +4257,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="C78" s="3" t="inlineStr"/>
       <c r="D78" s="3" t="inlineStr">
@@ -3053,12 +4273,28 @@
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="3" t="n"/>
       <c r="J78" s="3" t="n"/>
+      <c r="K78" s="3" t="n"/>
       <c r="L78" s="3" t="n"/>
       <c r="M78" s="3" t="n"/>
       <c r="Q78" s="3" t="n"/>
       <c r="R78" s="3" t="n"/>
       <c r="S78" s="3" t="n"/>
       <c r="T78" s="3" t="n"/>
+      <c r="Z78" s="3" t="n"/>
+      <c r="AA78" s="3" t="n"/>
+      <c r="AB78" s="3" t="n"/>
+      <c r="AC78" s="3" t="n"/>
+      <c r="AD78" s="3" t="n"/>
+      <c r="AJ78" s="3" t="n"/>
+      <c r="AK78" s="3" t="n"/>
+      <c r="AL78" s="3" t="n"/>
+      <c r="AM78" s="3" t="n"/>
+      <c r="AN78" s="3" t="n"/>
+      <c r="AT78" s="3" t="n"/>
+      <c r="AU78" s="3" t="n"/>
+      <c r="AV78" s="3" t="n"/>
+      <c r="AW78" s="3" t="n"/>
+      <c r="AX78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -3067,7 +4303,7 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>4.35</v>
+        <v>4.52</v>
       </c>
       <c r="C79" s="3" t="inlineStr"/>
       <c r="D79" s="3" t="inlineStr">
@@ -3083,12 +4319,28 @@
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="3" t="n"/>
       <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="n"/>
       <c r="L79" s="3" t="n"/>
       <c r="M79" s="3" t="n"/>
       <c r="Q79" s="3" t="n"/>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3" t="n"/>
       <c r="T79" s="3" t="n"/>
+      <c r="Z79" s="3" t="n"/>
+      <c r="AA79" s="3" t="n"/>
+      <c r="AB79" s="3" t="n"/>
+      <c r="AC79" s="3" t="n"/>
+      <c r="AD79" s="3" t="n"/>
+      <c r="AJ79" s="3" t="n"/>
+      <c r="AK79" s="3" t="n"/>
+      <c r="AL79" s="3" t="n"/>
+      <c r="AM79" s="3" t="n"/>
+      <c r="AN79" s="3" t="n"/>
+      <c r="AT79" s="3" t="n"/>
+      <c r="AU79" s="3" t="n"/>
+      <c r="AV79" s="3" t="n"/>
+      <c r="AW79" s="3" t="n"/>
+      <c r="AX79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -3097,10 +4349,10 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
@@ -3115,12 +4367,28 @@
       <c r="H80" s="3" t="n"/>
       <c r="I80" s="3" t="n"/>
       <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="n"/>
       <c r="L80" s="3" t="n"/>
       <c r="M80" s="3" t="n"/>
       <c r="Q80" s="3" t="n"/>
       <c r="R80" s="3" t="n"/>
       <c r="S80" s="3" t="n"/>
       <c r="T80" s="3" t="n"/>
+      <c r="Z80" s="3" t="n"/>
+      <c r="AA80" s="3" t="n"/>
+      <c r="AB80" s="3" t="n"/>
+      <c r="AC80" s="3" t="n"/>
+      <c r="AD80" s="3" t="n"/>
+      <c r="AJ80" s="3" t="n"/>
+      <c r="AK80" s="3" t="n"/>
+      <c r="AL80" s="3" t="n"/>
+      <c r="AM80" s="3" t="n"/>
+      <c r="AN80" s="3" t="n"/>
+      <c r="AT80" s="3" t="n"/>
+      <c r="AU80" s="3" t="n"/>
+      <c r="AV80" s="3" t="n"/>
+      <c r="AW80" s="3" t="n"/>
+      <c r="AX80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -3132,7 +4400,7 @@
         <v>0.06</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
@@ -3147,12 +4415,28 @@
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="3" t="n"/>
       <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="n"/>
       <c r="L81" s="3" t="n"/>
       <c r="M81" s="3" t="n"/>
       <c r="Q81" s="3" t="n"/>
       <c r="R81" s="3" t="n"/>
       <c r="S81" s="3" t="n"/>
       <c r="T81" s="3" t="n"/>
+      <c r="Z81" s="3" t="n"/>
+      <c r="AA81" s="3" t="n"/>
+      <c r="AB81" s="3" t="n"/>
+      <c r="AC81" s="3" t="n"/>
+      <c r="AD81" s="3" t="n"/>
+      <c r="AJ81" s="3" t="n"/>
+      <c r="AK81" s="3" t="n"/>
+      <c r="AL81" s="3" t="n"/>
+      <c r="AM81" s="3" t="n"/>
+      <c r="AN81" s="3" t="n"/>
+      <c r="AT81" s="3" t="n"/>
+      <c r="AU81" s="3" t="n"/>
+      <c r="AV81" s="3" t="n"/>
+      <c r="AW81" s="3" t="n"/>
+      <c r="AX81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -3161,10 +4445,10 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
@@ -3179,12 +4463,28 @@
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="3" t="n"/>
       <c r="J82" s="3" t="n"/>
+      <c r="K82" s="3" t="n"/>
       <c r="L82" s="3" t="n"/>
       <c r="M82" s="3" t="n"/>
       <c r="Q82" s="3" t="n"/>
       <c r="R82" s="3" t="n"/>
       <c r="S82" s="3" t="n"/>
       <c r="T82" s="3" t="n"/>
+      <c r="Z82" s="3" t="n"/>
+      <c r="AA82" s="3" t="n"/>
+      <c r="AB82" s="3" t="n"/>
+      <c r="AC82" s="3" t="n"/>
+      <c r="AD82" s="3" t="n"/>
+      <c r="AJ82" s="3" t="n"/>
+      <c r="AK82" s="3" t="n"/>
+      <c r="AL82" s="3" t="n"/>
+      <c r="AM82" s="3" t="n"/>
+      <c r="AN82" s="3" t="n"/>
+      <c r="AT82" s="3" t="n"/>
+      <c r="AU82" s="3" t="n"/>
+      <c r="AV82" s="3" t="n"/>
+      <c r="AW82" s="3" t="n"/>
+      <c r="AX82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -3211,12 +4511,28 @@
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="3" t="n"/>
       <c r="J83" s="3" t="n"/>
+      <c r="K83" s="3" t="n"/>
       <c r="L83" s="3" t="n"/>
       <c r="M83" s="3" t="n"/>
       <c r="Q83" s="3" t="n"/>
       <c r="R83" s="3" t="n"/>
       <c r="S83" s="3" t="n"/>
       <c r="T83" s="3" t="n"/>
+      <c r="Z83" s="3" t="n"/>
+      <c r="AA83" s="3" t="n"/>
+      <c r="AB83" s="3" t="n"/>
+      <c r="AC83" s="3" t="n"/>
+      <c r="AD83" s="3" t="n"/>
+      <c r="AJ83" s="3" t="n"/>
+      <c r="AK83" s="3" t="n"/>
+      <c r="AL83" s="3" t="n"/>
+      <c r="AM83" s="3" t="n"/>
+      <c r="AN83" s="3" t="n"/>
+      <c r="AT83" s="3" t="n"/>
+      <c r="AU83" s="3" t="n"/>
+      <c r="AV83" s="3" t="n"/>
+      <c r="AW83" s="3" t="n"/>
+      <c r="AX83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -3225,10 +4541,10 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
@@ -3243,12 +4559,28 @@
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="3" t="n"/>
       <c r="J84" s="3" t="n"/>
+      <c r="K84" s="3" t="n"/>
       <c r="L84" s="3" t="n"/>
       <c r="M84" s="3" t="n"/>
       <c r="Q84" s="3" t="n"/>
       <c r="R84" s="3" t="n"/>
       <c r="S84" s="3" t="n"/>
       <c r="T84" s="3" t="n"/>
+      <c r="Z84" s="3" t="n"/>
+      <c r="AA84" s="3" t="n"/>
+      <c r="AB84" s="3" t="n"/>
+      <c r="AC84" s="3" t="n"/>
+      <c r="AD84" s="3" t="n"/>
+      <c r="AJ84" s="3" t="n"/>
+      <c r="AK84" s="3" t="n"/>
+      <c r="AL84" s="3" t="n"/>
+      <c r="AM84" s="3" t="n"/>
+      <c r="AN84" s="3" t="n"/>
+      <c r="AT84" s="3" t="n"/>
+      <c r="AU84" s="3" t="n"/>
+      <c r="AV84" s="3" t="n"/>
+      <c r="AW84" s="3" t="n"/>
+      <c r="AX84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -3257,10 +4589,10 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
@@ -3275,12 +4607,28 @@
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="3" t="n"/>
       <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="n"/>
       <c r="L85" s="3" t="n"/>
       <c r="M85" s="3" t="n"/>
       <c r="Q85" s="3" t="n"/>
       <c r="R85" s="3" t="n"/>
       <c r="S85" s="3" t="n"/>
       <c r="T85" s="3" t="n"/>
+      <c r="Z85" s="3" t="n"/>
+      <c r="AA85" s="3" t="n"/>
+      <c r="AB85" s="3" t="n"/>
+      <c r="AC85" s="3" t="n"/>
+      <c r="AD85" s="3" t="n"/>
+      <c r="AJ85" s="3" t="n"/>
+      <c r="AK85" s="3" t="n"/>
+      <c r="AL85" s="3" t="n"/>
+      <c r="AM85" s="3" t="n"/>
+      <c r="AN85" s="3" t="n"/>
+      <c r="AT85" s="3" t="n"/>
+      <c r="AU85" s="3" t="n"/>
+      <c r="AV85" s="3" t="n"/>
+      <c r="AW85" s="3" t="n"/>
+      <c r="AX85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -3289,10 +4637,10 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
@@ -3307,12 +4655,28 @@
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="3" t="n"/>
       <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="n"/>
       <c r="L86" s="3" t="n"/>
       <c r="M86" s="3" t="n"/>
       <c r="Q86" s="3" t="n"/>
       <c r="R86" s="3" t="n"/>
       <c r="S86" s="3" t="n"/>
       <c r="T86" s="3" t="n"/>
+      <c r="Z86" s="3" t="n"/>
+      <c r="AA86" s="3" t="n"/>
+      <c r="AB86" s="3" t="n"/>
+      <c r="AC86" s="3" t="n"/>
+      <c r="AD86" s="3" t="n"/>
+      <c r="AJ86" s="3" t="n"/>
+      <c r="AK86" s="3" t="n"/>
+      <c r="AL86" s="3" t="n"/>
+      <c r="AM86" s="3" t="n"/>
+      <c r="AN86" s="3" t="n"/>
+      <c r="AT86" s="3" t="n"/>
+      <c r="AU86" s="3" t="n"/>
+      <c r="AV86" s="3" t="n"/>
+      <c r="AW86" s="3" t="n"/>
+      <c r="AX86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -3321,10 +4685,10 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
@@ -3339,12 +4703,28 @@
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="3" t="n"/>
       <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="n"/>
       <c r="L87" s="3" t="n"/>
       <c r="M87" s="3" t="n"/>
       <c r="Q87" s="3" t="n"/>
       <c r="R87" s="3" t="n"/>
       <c r="S87" s="3" t="n"/>
       <c r="T87" s="3" t="n"/>
+      <c r="Z87" s="3" t="n"/>
+      <c r="AA87" s="3" t="n"/>
+      <c r="AB87" s="3" t="n"/>
+      <c r="AC87" s="3" t="n"/>
+      <c r="AD87" s="3" t="n"/>
+      <c r="AJ87" s="3" t="n"/>
+      <c r="AK87" s="3" t="n"/>
+      <c r="AL87" s="3" t="n"/>
+      <c r="AM87" s="3" t="n"/>
+      <c r="AN87" s="3" t="n"/>
+      <c r="AT87" s="3" t="n"/>
+      <c r="AU87" s="3" t="n"/>
+      <c r="AV87" s="3" t="n"/>
+      <c r="AW87" s="3" t="n"/>
+      <c r="AX87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -3353,10 +4733,10 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
@@ -3371,12 +4751,28 @@
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="3" t="n"/>
       <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="n"/>
       <c r="L88" s="3" t="n"/>
       <c r="M88" s="3" t="n"/>
       <c r="Q88" s="3" t="n"/>
       <c r="R88" s="3" t="n"/>
       <c r="S88" s="3" t="n"/>
       <c r="T88" s="3" t="n"/>
+      <c r="Z88" s="3" t="n"/>
+      <c r="AA88" s="3" t="n"/>
+      <c r="AB88" s="3" t="n"/>
+      <c r="AC88" s="3" t="n"/>
+      <c r="AD88" s="3" t="n"/>
+      <c r="AJ88" s="3" t="n"/>
+      <c r="AK88" s="3" t="n"/>
+      <c r="AL88" s="3" t="n"/>
+      <c r="AM88" s="3" t="n"/>
+      <c r="AN88" s="3" t="n"/>
+      <c r="AT88" s="3" t="n"/>
+      <c r="AU88" s="3" t="n"/>
+      <c r="AV88" s="3" t="n"/>
+      <c r="AW88" s="3" t="n"/>
+      <c r="AX88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -3385,10 +4781,10 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
@@ -3403,12 +4799,28 @@
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="3" t="n"/>
       <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="n"/>
       <c r="L89" s="3" t="n"/>
       <c r="M89" s="3" t="n"/>
       <c r="Q89" s="3" t="n"/>
       <c r="R89" s="3" t="n"/>
       <c r="S89" s="3" t="n"/>
       <c r="T89" s="3" t="n"/>
+      <c r="Z89" s="3" t="n"/>
+      <c r="AA89" s="3" t="n"/>
+      <c r="AB89" s="3" t="n"/>
+      <c r="AC89" s="3" t="n"/>
+      <c r="AD89" s="3" t="n"/>
+      <c r="AJ89" s="3" t="n"/>
+      <c r="AK89" s="3" t="n"/>
+      <c r="AL89" s="3" t="n"/>
+      <c r="AM89" s="3" t="n"/>
+      <c r="AN89" s="3" t="n"/>
+      <c r="AT89" s="3" t="n"/>
+      <c r="AU89" s="3" t="n"/>
+      <c r="AV89" s="3" t="n"/>
+      <c r="AW89" s="3" t="n"/>
+      <c r="AX89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -3417,10 +4829,10 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
@@ -3435,12 +4847,28 @@
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="3" t="n"/>
       <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="n"/>
       <c r="L90" s="3" t="n"/>
       <c r="M90" s="3" t="n"/>
       <c r="Q90" s="3" t="n"/>
       <c r="R90" s="3" t="n"/>
       <c r="S90" s="3" t="n"/>
       <c r="T90" s="3" t="n"/>
+      <c r="Z90" s="3" t="n"/>
+      <c r="AA90" s="3" t="n"/>
+      <c r="AB90" s="3" t="n"/>
+      <c r="AC90" s="3" t="n"/>
+      <c r="AD90" s="3" t="n"/>
+      <c r="AJ90" s="3" t="n"/>
+      <c r="AK90" s="3" t="n"/>
+      <c r="AL90" s="3" t="n"/>
+      <c r="AM90" s="3" t="n"/>
+      <c r="AN90" s="3" t="n"/>
+      <c r="AT90" s="3" t="n"/>
+      <c r="AU90" s="3" t="n"/>
+      <c r="AV90" s="3" t="n"/>
+      <c r="AW90" s="3" t="n"/>
+      <c r="AX90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -3449,7 +4877,7 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>27.4</v>
+        <v>27.28</v>
       </c>
       <c r="C91" s="3" t="inlineStr"/>
       <c r="D91" s="3" t="inlineStr">
@@ -3465,12 +4893,28 @@
       <c r="H91" s="3" t="n"/>
       <c r="I91" s="3" t="n"/>
       <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="n"/>
       <c r="L91" s="3" t="n"/>
       <c r="M91" s="3" t="n"/>
       <c r="Q91" s="3" t="n"/>
       <c r="R91" s="3" t="n"/>
       <c r="S91" s="3" t="n"/>
       <c r="T91" s="3" t="n"/>
+      <c r="Z91" s="3" t="n"/>
+      <c r="AA91" s="3" t="n"/>
+      <c r="AB91" s="3" t="n"/>
+      <c r="AC91" s="3" t="n"/>
+      <c r="AD91" s="3" t="n"/>
+      <c r="AJ91" s="3" t="n"/>
+      <c r="AK91" s="3" t="n"/>
+      <c r="AL91" s="3" t="n"/>
+      <c r="AM91" s="3" t="n"/>
+      <c r="AN91" s="3" t="n"/>
+      <c r="AT91" s="3" t="n"/>
+      <c r="AU91" s="3" t="n"/>
+      <c r="AV91" s="3" t="n"/>
+      <c r="AW91" s="3" t="n"/>
+      <c r="AX91" s="3" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -3479,10 +4923,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
@@ -3497,12 +4941,28 @@
       <c r="H92" s="3" t="n"/>
       <c r="I92" s="3" t="n"/>
       <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="n"/>
       <c r="L92" s="3" t="n"/>
       <c r="M92" s="3" t="n"/>
       <c r="Q92" s="3" t="n"/>
       <c r="R92" s="3" t="n"/>
       <c r="S92" s="3" t="n"/>
       <c r="T92" s="3" t="n"/>
+      <c r="Z92" s="3" t="n"/>
+      <c r="AA92" s="3" t="n"/>
+      <c r="AB92" s="3" t="n"/>
+      <c r="AC92" s="3" t="n"/>
+      <c r="AD92" s="3" t="n"/>
+      <c r="AJ92" s="3" t="n"/>
+      <c r="AK92" s="3" t="n"/>
+      <c r="AL92" s="3" t="n"/>
+      <c r="AM92" s="3" t="n"/>
+      <c r="AN92" s="3" t="n"/>
+      <c r="AT92" s="3" t="n"/>
+      <c r="AU92" s="3" t="n"/>
+      <c r="AV92" s="3" t="n"/>
+      <c r="AW92" s="3" t="n"/>
+      <c r="AX92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -3511,10 +4971,10 @@
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
@@ -3529,12 +4989,28 @@
       <c r="H93" s="3" t="n"/>
       <c r="I93" s="3" t="n"/>
       <c r="J93" s="3" t="n"/>
+      <c r="K93" s="3" t="n"/>
       <c r="L93" s="3" t="n"/>
       <c r="M93" s="3" t="n"/>
       <c r="Q93" s="3" t="n"/>
       <c r="R93" s="3" t="n"/>
       <c r="S93" s="3" t="n"/>
       <c r="T93" s="3" t="n"/>
+      <c r="Z93" s="3" t="n"/>
+      <c r="AA93" s="3" t="n"/>
+      <c r="AB93" s="3" t="n"/>
+      <c r="AC93" s="3" t="n"/>
+      <c r="AD93" s="3" t="n"/>
+      <c r="AJ93" s="3" t="n"/>
+      <c r="AK93" s="3" t="n"/>
+      <c r="AL93" s="3" t="n"/>
+      <c r="AM93" s="3" t="n"/>
+      <c r="AN93" s="3" t="n"/>
+      <c r="AT93" s="3" t="n"/>
+      <c r="AU93" s="3" t="n"/>
+      <c r="AV93" s="3" t="n"/>
+      <c r="AW93" s="3" t="n"/>
+      <c r="AX93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -3543,7 +5019,7 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="C94" s="3" t="inlineStr"/>
       <c r="D94" s="3" t="inlineStr">
@@ -3559,12 +5035,28 @@
       <c r="H94" s="3" t="n"/>
       <c r="I94" s="3" t="n"/>
       <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="n"/>
       <c r="L94" s="3" t="n"/>
       <c r="M94" s="3" t="n"/>
       <c r="Q94" s="3" t="n"/>
       <c r="R94" s="3" t="n"/>
       <c r="S94" s="3" t="n"/>
       <c r="T94" s="3" t="n"/>
+      <c r="Z94" s="3" t="n"/>
+      <c r="AA94" s="3" t="n"/>
+      <c r="AB94" s="3" t="n"/>
+      <c r="AC94" s="3" t="n"/>
+      <c r="AD94" s="3" t="n"/>
+      <c r="AJ94" s="3" t="n"/>
+      <c r="AK94" s="3" t="n"/>
+      <c r="AL94" s="3" t="n"/>
+      <c r="AM94" s="3" t="n"/>
+      <c r="AN94" s="3" t="n"/>
+      <c r="AT94" s="3" t="n"/>
+      <c r="AU94" s="3" t="n"/>
+      <c r="AV94" s="3" t="n"/>
+      <c r="AW94" s="3" t="n"/>
+      <c r="AX94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -3573,7 +5065,7 @@
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>5.33</v>
+        <v>4.45</v>
       </c>
       <c r="C95" s="3" t="inlineStr"/>
       <c r="D95" s="3" t="inlineStr">
@@ -3589,12 +5081,28 @@
       <c r="H95" s="3" t="n"/>
       <c r="I95" s="3" t="n"/>
       <c r="J95" s="3" t="n"/>
+      <c r="K95" s="3" t="n"/>
       <c r="L95" s="3" t="n"/>
       <c r="M95" s="3" t="n"/>
       <c r="Q95" s="3" t="n"/>
       <c r="R95" s="3" t="n"/>
       <c r="S95" s="3" t="n"/>
       <c r="T95" s="3" t="n"/>
+      <c r="Z95" s="3" t="n"/>
+      <c r="AA95" s="3" t="n"/>
+      <c r="AB95" s="3" t="n"/>
+      <c r="AC95" s="3" t="n"/>
+      <c r="AD95" s="3" t="n"/>
+      <c r="AJ95" s="3" t="n"/>
+      <c r="AK95" s="3" t="n"/>
+      <c r="AL95" s="3" t="n"/>
+      <c r="AM95" s="3" t="n"/>
+      <c r="AN95" s="3" t="n"/>
+      <c r="AT95" s="3" t="n"/>
+      <c r="AU95" s="3" t="n"/>
+      <c r="AV95" s="3" t="n"/>
+      <c r="AW95" s="3" t="n"/>
+      <c r="AX95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -3603,10 +5111,10 @@
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
@@ -3621,12 +5129,28 @@
       <c r="H96" s="3" t="n"/>
       <c r="I96" s="3" t="n"/>
       <c r="J96" s="3" t="n"/>
+      <c r="K96" s="3" t="n"/>
       <c r="L96" s="3" t="n"/>
       <c r="M96" s="3" t="n"/>
       <c r="Q96" s="3" t="n"/>
       <c r="R96" s="3" t="n"/>
       <c r="S96" s="3" t="n"/>
       <c r="T96" s="3" t="n"/>
+      <c r="Z96" s="3" t="n"/>
+      <c r="AA96" s="3" t="n"/>
+      <c r="AB96" s="3" t="n"/>
+      <c r="AC96" s="3" t="n"/>
+      <c r="AD96" s="3" t="n"/>
+      <c r="AJ96" s="3" t="n"/>
+      <c r="AK96" s="3" t="n"/>
+      <c r="AL96" s="3" t="n"/>
+      <c r="AM96" s="3" t="n"/>
+      <c r="AN96" s="3" t="n"/>
+      <c r="AT96" s="3" t="n"/>
+      <c r="AU96" s="3" t="n"/>
+      <c r="AV96" s="3" t="n"/>
+      <c r="AW96" s="3" t="n"/>
+      <c r="AX96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -3635,10 +5159,10 @@
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
@@ -3653,12 +5177,28 @@
       <c r="H97" s="3" t="n"/>
       <c r="I97" s="3" t="n"/>
       <c r="J97" s="3" t="n"/>
+      <c r="K97" s="3" t="n"/>
       <c r="L97" s="3" t="n"/>
       <c r="M97" s="3" t="n"/>
       <c r="Q97" s="3" t="n"/>
       <c r="R97" s="3" t="n"/>
       <c r="S97" s="3" t="n"/>
       <c r="T97" s="3" t="n"/>
+      <c r="Z97" s="3" t="n"/>
+      <c r="AA97" s="3" t="n"/>
+      <c r="AB97" s="3" t="n"/>
+      <c r="AC97" s="3" t="n"/>
+      <c r="AD97" s="3" t="n"/>
+      <c r="AJ97" s="3" t="n"/>
+      <c r="AK97" s="3" t="n"/>
+      <c r="AL97" s="3" t="n"/>
+      <c r="AM97" s="3" t="n"/>
+      <c r="AN97" s="3" t="n"/>
+      <c r="AT97" s="3" t="n"/>
+      <c r="AU97" s="3" t="n"/>
+      <c r="AV97" s="3" t="n"/>
+      <c r="AW97" s="3" t="n"/>
+      <c r="AX97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -3667,10 +5207,10 @@
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
@@ -3685,12 +5225,28 @@
       <c r="H98" s="3" t="n"/>
       <c r="I98" s="3" t="n"/>
       <c r="J98" s="3" t="n"/>
+      <c r="K98" s="3" t="n"/>
       <c r="L98" s="3" t="n"/>
       <c r="M98" s="3" t="n"/>
       <c r="Q98" s="3" t="n"/>
       <c r="R98" s="3" t="n"/>
       <c r="S98" s="3" t="n"/>
       <c r="T98" s="3" t="n"/>
+      <c r="Z98" s="3" t="n"/>
+      <c r="AA98" s="3" t="n"/>
+      <c r="AB98" s="3" t="n"/>
+      <c r="AC98" s="3" t="n"/>
+      <c r="AD98" s="3" t="n"/>
+      <c r="AJ98" s="3" t="n"/>
+      <c r="AK98" s="3" t="n"/>
+      <c r="AL98" s="3" t="n"/>
+      <c r="AM98" s="3" t="n"/>
+      <c r="AN98" s="3" t="n"/>
+      <c r="AT98" s="3" t="n"/>
+      <c r="AU98" s="3" t="n"/>
+      <c r="AV98" s="3" t="n"/>
+      <c r="AW98" s="3" t="n"/>
+      <c r="AX98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -3702,7 +5258,7 @@
         <v>0.11</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
@@ -3717,12 +5273,28 @@
       <c r="H99" s="3" t="n"/>
       <c r="I99" s="3" t="n"/>
       <c r="J99" s="3" t="n"/>
+      <c r="K99" s="3" t="n"/>
       <c r="L99" s="3" t="n"/>
       <c r="M99" s="3" t="n"/>
       <c r="Q99" s="3" t="n"/>
       <c r="R99" s="3" t="n"/>
       <c r="S99" s="3" t="n"/>
       <c r="T99" s="3" t="n"/>
+      <c r="Z99" s="3" t="n"/>
+      <c r="AA99" s="3" t="n"/>
+      <c r="AB99" s="3" t="n"/>
+      <c r="AC99" s="3" t="n"/>
+      <c r="AD99" s="3" t="n"/>
+      <c r="AJ99" s="3" t="n"/>
+      <c r="AK99" s="3" t="n"/>
+      <c r="AL99" s="3" t="n"/>
+      <c r="AM99" s="3" t="n"/>
+      <c r="AN99" s="3" t="n"/>
+      <c r="AT99" s="3" t="n"/>
+      <c r="AU99" s="3" t="n"/>
+      <c r="AV99" s="3" t="n"/>
+      <c r="AW99" s="3" t="n"/>
+      <c r="AX99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -3731,7 +5303,7 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="C100" s="3" t="inlineStr"/>
       <c r="D100" s="3" t="inlineStr">
@@ -3747,12 +5319,28 @@
       <c r="H100" s="3" t="n"/>
       <c r="I100" s="3" t="n"/>
       <c r="J100" s="3" t="n"/>
+      <c r="K100" s="3" t="n"/>
       <c r="L100" s="3" t="n"/>
       <c r="M100" s="3" t="n"/>
       <c r="Q100" s="3" t="n"/>
       <c r="R100" s="3" t="n"/>
       <c r="S100" s="3" t="n"/>
       <c r="T100" s="3" t="n"/>
+      <c r="Z100" s="3" t="n"/>
+      <c r="AA100" s="3" t="n"/>
+      <c r="AB100" s="3" t="n"/>
+      <c r="AC100" s="3" t="n"/>
+      <c r="AD100" s="3" t="n"/>
+      <c r="AJ100" s="3" t="n"/>
+      <c r="AK100" s="3" t="n"/>
+      <c r="AL100" s="3" t="n"/>
+      <c r="AM100" s="3" t="n"/>
+      <c r="AN100" s="3" t="n"/>
+      <c r="AT100" s="3" t="n"/>
+      <c r="AU100" s="3" t="n"/>
+      <c r="AV100" s="3" t="n"/>
+      <c r="AW100" s="3" t="n"/>
+      <c r="AX100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -3761,7 +5349,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>5.17</v>
+        <v>5.08</v>
       </c>
       <c r="C101" s="3" t="inlineStr"/>
       <c r="D101" s="3" t="inlineStr">
@@ -3777,12 +5365,28 @@
       <c r="H101" s="3" t="n"/>
       <c r="I101" s="3" t="n"/>
       <c r="J101" s="3" t="n"/>
+      <c r="K101" s="3" t="n"/>
       <c r="L101" s="3" t="n"/>
       <c r="M101" s="3" t="n"/>
       <c r="Q101" s="3" t="n"/>
       <c r="R101" s="3" t="n"/>
       <c r="S101" s="3" t="n"/>
       <c r="T101" s="3" t="n"/>
+      <c r="Z101" s="3" t="n"/>
+      <c r="AA101" s="3" t="n"/>
+      <c r="AB101" s="3" t="n"/>
+      <c r="AC101" s="3" t="n"/>
+      <c r="AD101" s="3" t="n"/>
+      <c r="AJ101" s="3" t="n"/>
+      <c r="AK101" s="3" t="n"/>
+      <c r="AL101" s="3" t="n"/>
+      <c r="AM101" s="3" t="n"/>
+      <c r="AN101" s="3" t="n"/>
+      <c r="AT101" s="3" t="n"/>
+      <c r="AU101" s="3" t="n"/>
+      <c r="AV101" s="3" t="n"/>
+      <c r="AW101" s="3" t="n"/>
+      <c r="AX101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -3791,10 +5395,10 @@
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
@@ -3809,12 +5413,28 @@
       <c r="H102" s="3" t="n"/>
       <c r="I102" s="3" t="n"/>
       <c r="J102" s="3" t="n"/>
+      <c r="K102" s="3" t="n"/>
       <c r="L102" s="3" t="n"/>
       <c r="M102" s="3" t="n"/>
       <c r="Q102" s="3" t="n"/>
       <c r="R102" s="3" t="n"/>
       <c r="S102" s="3" t="n"/>
       <c r="T102" s="3" t="n"/>
+      <c r="Z102" s="3" t="n"/>
+      <c r="AA102" s="3" t="n"/>
+      <c r="AB102" s="3" t="n"/>
+      <c r="AC102" s="3" t="n"/>
+      <c r="AD102" s="3" t="n"/>
+      <c r="AJ102" s="3" t="n"/>
+      <c r="AK102" s="3" t="n"/>
+      <c r="AL102" s="3" t="n"/>
+      <c r="AM102" s="3" t="n"/>
+      <c r="AN102" s="3" t="n"/>
+      <c r="AT102" s="3" t="n"/>
+      <c r="AU102" s="3" t="n"/>
+      <c r="AV102" s="3" t="n"/>
+      <c r="AW102" s="3" t="n"/>
+      <c r="AX102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -3823,10 +5443,10 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
@@ -3841,12 +5461,28 @@
       <c r="H103" s="3" t="n"/>
       <c r="I103" s="3" t="n"/>
       <c r="J103" s="3" t="n"/>
+      <c r="K103" s="3" t="n"/>
       <c r="L103" s="3" t="n"/>
       <c r="M103" s="3" t="n"/>
       <c r="Q103" s="3" t="n"/>
       <c r="R103" s="3" t="n"/>
       <c r="S103" s="3" t="n"/>
       <c r="T103" s="3" t="n"/>
+      <c r="Z103" s="3" t="n"/>
+      <c r="AA103" s="3" t="n"/>
+      <c r="AB103" s="3" t="n"/>
+      <c r="AC103" s="3" t="n"/>
+      <c r="AD103" s="3" t="n"/>
+      <c r="AJ103" s="3" t="n"/>
+      <c r="AK103" s="3" t="n"/>
+      <c r="AL103" s="3" t="n"/>
+      <c r="AM103" s="3" t="n"/>
+      <c r="AN103" s="3" t="n"/>
+      <c r="AT103" s="3" t="n"/>
+      <c r="AU103" s="3" t="n"/>
+      <c r="AV103" s="3" t="n"/>
+      <c r="AW103" s="3" t="n"/>
+      <c r="AX103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -3855,10 +5491,10 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
@@ -3873,12 +5509,28 @@
       <c r="H104" s="3" t="n"/>
       <c r="I104" s="3" t="n"/>
       <c r="J104" s="3" t="n"/>
+      <c r="K104" s="3" t="n"/>
       <c r="L104" s="3" t="n"/>
       <c r="M104" s="3" t="n"/>
       <c r="Q104" s="3" t="n"/>
       <c r="R104" s="3" t="n"/>
       <c r="S104" s="3" t="n"/>
       <c r="T104" s="3" t="n"/>
+      <c r="Z104" s="3" t="n"/>
+      <c r="AA104" s="3" t="n"/>
+      <c r="AB104" s="3" t="n"/>
+      <c r="AC104" s="3" t="n"/>
+      <c r="AD104" s="3" t="n"/>
+      <c r="AJ104" s="3" t="n"/>
+      <c r="AK104" s="3" t="n"/>
+      <c r="AL104" s="3" t="n"/>
+      <c r="AM104" s="3" t="n"/>
+      <c r="AN104" s="3" t="n"/>
+      <c r="AT104" s="3" t="n"/>
+      <c r="AU104" s="3" t="n"/>
+      <c r="AV104" s="3" t="n"/>
+      <c r="AW104" s="3" t="n"/>
+      <c r="AX104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -3887,10 +5539,10 @@
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C105" s="3" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
@@ -3905,12 +5557,28 @@
       <c r="H105" s="3" t="n"/>
       <c r="I105" s="3" t="n"/>
       <c r="J105" s="3" t="n"/>
+      <c r="K105" s="3" t="n"/>
       <c r="L105" s="3" t="n"/>
       <c r="M105" s="3" t="n"/>
       <c r="Q105" s="3" t="n"/>
       <c r="R105" s="3" t="n"/>
       <c r="S105" s="3" t="n"/>
       <c r="T105" s="3" t="n"/>
+      <c r="Z105" s="3" t="n"/>
+      <c r="AA105" s="3" t="n"/>
+      <c r="AB105" s="3" t="n"/>
+      <c r="AC105" s="3" t="n"/>
+      <c r="AD105" s="3" t="n"/>
+      <c r="AJ105" s="3" t="n"/>
+      <c r="AK105" s="3" t="n"/>
+      <c r="AL105" s="3" t="n"/>
+      <c r="AM105" s="3" t="n"/>
+      <c r="AN105" s="3" t="n"/>
+      <c r="AT105" s="3" t="n"/>
+      <c r="AU105" s="3" t="n"/>
+      <c r="AV105" s="3" t="n"/>
+      <c r="AW105" s="3" t="n"/>
+      <c r="AX105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
@@ -3937,12 +5605,28 @@
       <c r="H106" s="3" t="n"/>
       <c r="I106" s="3" t="n"/>
       <c r="J106" s="3" t="n"/>
+      <c r="K106" s="3" t="n"/>
       <c r="L106" s="3" t="n"/>
       <c r="M106" s="3" t="n"/>
       <c r="Q106" s="3" t="n"/>
       <c r="R106" s="3" t="n"/>
       <c r="S106" s="3" t="n"/>
       <c r="T106" s="3" t="n"/>
+      <c r="Z106" s="3" t="n"/>
+      <c r="AA106" s="3" t="n"/>
+      <c r="AB106" s="3" t="n"/>
+      <c r="AC106" s="3" t="n"/>
+      <c r="AD106" s="3" t="n"/>
+      <c r="AJ106" s="3" t="n"/>
+      <c r="AK106" s="3" t="n"/>
+      <c r="AL106" s="3" t="n"/>
+      <c r="AM106" s="3" t="n"/>
+      <c r="AN106" s="3" t="n"/>
+      <c r="AT106" s="3" t="n"/>
+      <c r="AU106" s="3" t="n"/>
+      <c r="AV106" s="3" t="n"/>
+      <c r="AW106" s="3" t="n"/>
+      <c r="AX106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -3951,10 +5635,10 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
@@ -3969,12 +5653,28 @@
       <c r="H107" s="3" t="n"/>
       <c r="I107" s="3" t="n"/>
       <c r="J107" s="3" t="n"/>
+      <c r="K107" s="3" t="n"/>
       <c r="L107" s="3" t="n"/>
       <c r="M107" s="3" t="n"/>
       <c r="Q107" s="3" t="n"/>
       <c r="R107" s="3" t="n"/>
       <c r="S107" s="3" t="n"/>
       <c r="T107" s="3" t="n"/>
+      <c r="Z107" s="3" t="n"/>
+      <c r="AA107" s="3" t="n"/>
+      <c r="AB107" s="3" t="n"/>
+      <c r="AC107" s="3" t="n"/>
+      <c r="AD107" s="3" t="n"/>
+      <c r="AJ107" s="3" t="n"/>
+      <c r="AK107" s="3" t="n"/>
+      <c r="AL107" s="3" t="n"/>
+      <c r="AM107" s="3" t="n"/>
+      <c r="AN107" s="3" t="n"/>
+      <c r="AT107" s="3" t="n"/>
+      <c r="AU107" s="3" t="n"/>
+      <c r="AV107" s="3" t="n"/>
+      <c r="AW107" s="3" t="n"/>
+      <c r="AX107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -3983,10 +5683,10 @@
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
@@ -4001,12 +5701,28 @@
       <c r="H108" s="3" t="n"/>
       <c r="I108" s="3" t="n"/>
       <c r="J108" s="3" t="n"/>
+      <c r="K108" s="3" t="n"/>
       <c r="L108" s="3" t="n"/>
       <c r="M108" s="3" t="n"/>
       <c r="Q108" s="3" t="n"/>
       <c r="R108" s="3" t="n"/>
       <c r="S108" s="3" t="n"/>
       <c r="T108" s="3" t="n"/>
+      <c r="Z108" s="3" t="n"/>
+      <c r="AA108" s="3" t="n"/>
+      <c r="AB108" s="3" t="n"/>
+      <c r="AC108" s="3" t="n"/>
+      <c r="AD108" s="3" t="n"/>
+      <c r="AJ108" s="3" t="n"/>
+      <c r="AK108" s="3" t="n"/>
+      <c r="AL108" s="3" t="n"/>
+      <c r="AM108" s="3" t="n"/>
+      <c r="AN108" s="3" t="n"/>
+      <c r="AT108" s="3" t="n"/>
+      <c r="AU108" s="3" t="n"/>
+      <c r="AV108" s="3" t="n"/>
+      <c r="AW108" s="3" t="n"/>
+      <c r="AX108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -4015,10 +5731,10 @@
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C109" s="3" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
@@ -4033,12 +5749,28 @@
       <c r="H109" s="3" t="n"/>
       <c r="I109" s="3" t="n"/>
       <c r="J109" s="3" t="n"/>
+      <c r="K109" s="3" t="n"/>
       <c r="L109" s="3" t="n"/>
       <c r="M109" s="3" t="n"/>
       <c r="Q109" s="3" t="n"/>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3" t="n"/>
       <c r="T109" s="3" t="n"/>
+      <c r="Z109" s="3" t="n"/>
+      <c r="AA109" s="3" t="n"/>
+      <c r="AB109" s="3" t="n"/>
+      <c r="AC109" s="3" t="n"/>
+      <c r="AD109" s="3" t="n"/>
+      <c r="AJ109" s="3" t="n"/>
+      <c r="AK109" s="3" t="n"/>
+      <c r="AL109" s="3" t="n"/>
+      <c r="AM109" s="3" t="n"/>
+      <c r="AN109" s="3" t="n"/>
+      <c r="AT109" s="3" t="n"/>
+      <c r="AU109" s="3" t="n"/>
+      <c r="AV109" s="3" t="n"/>
+      <c r="AW109" s="3" t="n"/>
+      <c r="AX109" s="3" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -4047,7 +5779,7 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>10.73</v>
+        <v>9.34</v>
       </c>
       <c r="C110" s="3" t="inlineStr"/>
       <c r="D110" s="3" t="inlineStr">
@@ -4063,12 +5795,28 @@
       <c r="H110" s="3" t="n"/>
       <c r="I110" s="3" t="n"/>
       <c r="J110" s="3" t="n"/>
+      <c r="K110" s="3" t="n"/>
       <c r="L110" s="3" t="n"/>
       <c r="M110" s="3" t="n"/>
       <c r="Q110" s="3" t="n"/>
       <c r="R110" s="3" t="n"/>
       <c r="S110" s="3" t="n"/>
       <c r="T110" s="3" t="n"/>
+      <c r="Z110" s="3" t="n"/>
+      <c r="AA110" s="3" t="n"/>
+      <c r="AB110" s="3" t="n"/>
+      <c r="AC110" s="3" t="n"/>
+      <c r="AD110" s="3" t="n"/>
+      <c r="AJ110" s="3" t="n"/>
+      <c r="AK110" s="3" t="n"/>
+      <c r="AL110" s="3" t="n"/>
+      <c r="AM110" s="3" t="n"/>
+      <c r="AN110" s="3" t="n"/>
+      <c r="AT110" s="3" t="n"/>
+      <c r="AU110" s="3" t="n"/>
+      <c r="AV110" s="3" t="n"/>
+      <c r="AW110" s="3" t="n"/>
+      <c r="AX110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -4077,7 +5825,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0.14</v>
@@ -4095,12 +5843,28 @@
       <c r="H111" s="3" t="n"/>
       <c r="I111" s="3" t="n"/>
       <c r="J111" s="3" t="n"/>
+      <c r="K111" s="3" t="n"/>
       <c r="L111" s="3" t="n"/>
       <c r="M111" s="3" t="n"/>
       <c r="Q111" s="3" t="n"/>
       <c r="R111" s="3" t="n"/>
       <c r="S111" s="3" t="n"/>
       <c r="T111" s="3" t="n"/>
+      <c r="Z111" s="3" t="n"/>
+      <c r="AA111" s="3" t="n"/>
+      <c r="AB111" s="3" t="n"/>
+      <c r="AC111" s="3" t="n"/>
+      <c r="AD111" s="3" t="n"/>
+      <c r="AJ111" s="3" t="n"/>
+      <c r="AK111" s="3" t="n"/>
+      <c r="AL111" s="3" t="n"/>
+      <c r="AM111" s="3" t="n"/>
+      <c r="AN111" s="3" t="n"/>
+      <c r="AT111" s="3" t="n"/>
+      <c r="AU111" s="3" t="n"/>
+      <c r="AV111" s="3" t="n"/>
+      <c r="AW111" s="3" t="n"/>
+      <c r="AX111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -4112,7 +5876,7 @@
         <v>0.06</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
@@ -4127,12 +5891,28 @@
       <c r="H112" s="3" t="n"/>
       <c r="I112" s="3" t="n"/>
       <c r="J112" s="3" t="n"/>
+      <c r="K112" s="3" t="n"/>
       <c r="L112" s="3" t="n"/>
       <c r="M112" s="3" t="n"/>
       <c r="Q112" s="3" t="n"/>
       <c r="R112" s="3" t="n"/>
       <c r="S112" s="3" t="n"/>
       <c r="T112" s="3" t="n"/>
+      <c r="Z112" s="3" t="n"/>
+      <c r="AA112" s="3" t="n"/>
+      <c r="AB112" s="3" t="n"/>
+      <c r="AC112" s="3" t="n"/>
+      <c r="AD112" s="3" t="n"/>
+      <c r="AJ112" s="3" t="n"/>
+      <c r="AK112" s="3" t="n"/>
+      <c r="AL112" s="3" t="n"/>
+      <c r="AM112" s="3" t="n"/>
+      <c r="AN112" s="3" t="n"/>
+      <c r="AT112" s="3" t="n"/>
+      <c r="AU112" s="3" t="n"/>
+      <c r="AV112" s="3" t="n"/>
+      <c r="AW112" s="3" t="n"/>
+      <c r="AX112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -4141,10 +5921,10 @@
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C113" s="3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
@@ -4159,12 +5939,28 @@
       <c r="H113" s="3" t="n"/>
       <c r="I113" s="3" t="n"/>
       <c r="J113" s="3" t="n"/>
+      <c r="K113" s="3" t="n"/>
       <c r="L113" s="3" t="n"/>
       <c r="M113" s="3" t="n"/>
       <c r="Q113" s="3" t="n"/>
       <c r="R113" s="3" t="n"/>
       <c r="S113" s="3" t="n"/>
       <c r="T113" s="3" t="n"/>
+      <c r="Z113" s="3" t="n"/>
+      <c r="AA113" s="3" t="n"/>
+      <c r="AB113" s="3" t="n"/>
+      <c r="AC113" s="3" t="n"/>
+      <c r="AD113" s="3" t="n"/>
+      <c r="AJ113" s="3" t="n"/>
+      <c r="AK113" s="3" t="n"/>
+      <c r="AL113" s="3" t="n"/>
+      <c r="AM113" s="3" t="n"/>
+      <c r="AN113" s="3" t="n"/>
+      <c r="AT113" s="3" t="n"/>
+      <c r="AU113" s="3" t="n"/>
+      <c r="AV113" s="3" t="n"/>
+      <c r="AW113" s="3" t="n"/>
+      <c r="AX113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -4173,10 +5969,10 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
@@ -4191,12 +5987,28 @@
       <c r="H114" s="3" t="n"/>
       <c r="I114" s="3" t="n"/>
       <c r="J114" s="3" t="n"/>
+      <c r="K114" s="3" t="n"/>
       <c r="L114" s="3" t="n"/>
       <c r="M114" s="3" t="n"/>
       <c r="Q114" s="3" t="n"/>
       <c r="R114" s="3" t="n"/>
       <c r="S114" s="3" t="n"/>
       <c r="T114" s="3" t="n"/>
+      <c r="Z114" s="3" t="n"/>
+      <c r="AA114" s="3" t="n"/>
+      <c r="AB114" s="3" t="n"/>
+      <c r="AC114" s="3" t="n"/>
+      <c r="AD114" s="3" t="n"/>
+      <c r="AJ114" s="3" t="n"/>
+      <c r="AK114" s="3" t="n"/>
+      <c r="AL114" s="3" t="n"/>
+      <c r="AM114" s="3" t="n"/>
+      <c r="AN114" s="3" t="n"/>
+      <c r="AT114" s="3" t="n"/>
+      <c r="AU114" s="3" t="n"/>
+      <c r="AV114" s="3" t="n"/>
+      <c r="AW114" s="3" t="n"/>
+      <c r="AX114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -4205,10 +6017,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
@@ -4223,12 +6035,28 @@
       <c r="H115" s="3" t="n"/>
       <c r="I115" s="3" t="n"/>
       <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="n"/>
       <c r="L115" s="3" t="n"/>
       <c r="M115" s="3" t="n"/>
       <c r="Q115" s="3" t="n"/>
       <c r="R115" s="3" t="n"/>
       <c r="S115" s="3" t="n"/>
       <c r="T115" s="3" t="n"/>
+      <c r="Z115" s="3" t="n"/>
+      <c r="AA115" s="3" t="n"/>
+      <c r="AB115" s="3" t="n"/>
+      <c r="AC115" s="3" t="n"/>
+      <c r="AD115" s="3" t="n"/>
+      <c r="AJ115" s="3" t="n"/>
+      <c r="AK115" s="3" t="n"/>
+      <c r="AL115" s="3" t="n"/>
+      <c r="AM115" s="3" t="n"/>
+      <c r="AN115" s="3" t="n"/>
+      <c r="AT115" s="3" t="n"/>
+      <c r="AU115" s="3" t="n"/>
+      <c r="AV115" s="3" t="n"/>
+      <c r="AW115" s="3" t="n"/>
+      <c r="AX115" s="3" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -4237,7 +6065,7 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0.13</v>
@@ -4255,12 +6083,28 @@
       <c r="H116" s="3" t="n"/>
       <c r="I116" s="3" t="n"/>
       <c r="J116" s="3" t="n"/>
+      <c r="K116" s="3" t="n"/>
       <c r="L116" s="3" t="n"/>
       <c r="M116" s="3" t="n"/>
       <c r="Q116" s="3" t="n"/>
       <c r="R116" s="3" t="n"/>
       <c r="S116" s="3" t="n"/>
       <c r="T116" s="3" t="n"/>
+      <c r="Z116" s="3" t="n"/>
+      <c r="AA116" s="3" t="n"/>
+      <c r="AB116" s="3" t="n"/>
+      <c r="AC116" s="3" t="n"/>
+      <c r="AD116" s="3" t="n"/>
+      <c r="AJ116" s="3" t="n"/>
+      <c r="AK116" s="3" t="n"/>
+      <c r="AL116" s="3" t="n"/>
+      <c r="AM116" s="3" t="n"/>
+      <c r="AN116" s="3" t="n"/>
+      <c r="AT116" s="3" t="n"/>
+      <c r="AU116" s="3" t="n"/>
+      <c r="AV116" s="3" t="n"/>
+      <c r="AW116" s="3" t="n"/>
+      <c r="AX116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -4269,10 +6113,10 @@
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="C117" s="3" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
@@ -4287,12 +6131,28 @@
       <c r="H117" s="3" t="n"/>
       <c r="I117" s="3" t="n"/>
       <c r="J117" s="3" t="n"/>
+      <c r="K117" s="3" t="n"/>
       <c r="L117" s="3" t="n"/>
       <c r="M117" s="3" t="n"/>
       <c r="Q117" s="3" t="n"/>
       <c r="R117" s="3" t="n"/>
       <c r="S117" s="3" t="n"/>
       <c r="T117" s="3" t="n"/>
+      <c r="Z117" s="3" t="n"/>
+      <c r="AA117" s="3" t="n"/>
+      <c r="AB117" s="3" t="n"/>
+      <c r="AC117" s="3" t="n"/>
+      <c r="AD117" s="3" t="n"/>
+      <c r="AJ117" s="3" t="n"/>
+      <c r="AK117" s="3" t="n"/>
+      <c r="AL117" s="3" t="n"/>
+      <c r="AM117" s="3" t="n"/>
+      <c r="AN117" s="3" t="n"/>
+      <c r="AT117" s="3" t="n"/>
+      <c r="AU117" s="3" t="n"/>
+      <c r="AV117" s="3" t="n"/>
+      <c r="AW117" s="3" t="n"/>
+      <c r="AX117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -4319,12 +6179,28 @@
       <c r="H118" s="3" t="n"/>
       <c r="I118" s="3" t="n"/>
       <c r="J118" s="3" t="n"/>
+      <c r="K118" s="3" t="n"/>
       <c r="L118" s="3" t="n"/>
       <c r="M118" s="3" t="n"/>
       <c r="Q118" s="3" t="n"/>
       <c r="R118" s="3" t="n"/>
       <c r="S118" s="3" t="n"/>
       <c r="T118" s="3" t="n"/>
+      <c r="Z118" s="3" t="n"/>
+      <c r="AA118" s="3" t="n"/>
+      <c r="AB118" s="3" t="n"/>
+      <c r="AC118" s="3" t="n"/>
+      <c r="AD118" s="3" t="n"/>
+      <c r="AJ118" s="3" t="n"/>
+      <c r="AK118" s="3" t="n"/>
+      <c r="AL118" s="3" t="n"/>
+      <c r="AM118" s="3" t="n"/>
+      <c r="AN118" s="3" t="n"/>
+      <c r="AT118" s="3" t="n"/>
+      <c r="AU118" s="3" t="n"/>
+      <c r="AV118" s="3" t="n"/>
+      <c r="AW118" s="3" t="n"/>
+      <c r="AX118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -4333,10 +6209,10 @@
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="C119" s="3" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
@@ -4351,12 +6227,28 @@
       <c r="H119" s="3" t="n"/>
       <c r="I119" s="3" t="n"/>
       <c r="J119" s="3" t="n"/>
+      <c r="K119" s="3" t="n"/>
       <c r="L119" s="3" t="n"/>
       <c r="M119" s="3" t="n"/>
       <c r="Q119" s="3" t="n"/>
       <c r="R119" s="3" t="n"/>
       <c r="S119" s="3" t="n"/>
       <c r="T119" s="3" t="n"/>
+      <c r="Z119" s="3" t="n"/>
+      <c r="AA119" s="3" t="n"/>
+      <c r="AB119" s="3" t="n"/>
+      <c r="AC119" s="3" t="n"/>
+      <c r="AD119" s="3" t="n"/>
+      <c r="AJ119" s="3" t="n"/>
+      <c r="AK119" s="3" t="n"/>
+      <c r="AL119" s="3" t="n"/>
+      <c r="AM119" s="3" t="n"/>
+      <c r="AN119" s="3" t="n"/>
+      <c r="AT119" s="3" t="n"/>
+      <c r="AU119" s="3" t="n"/>
+      <c r="AV119" s="3" t="n"/>
+      <c r="AW119" s="3" t="n"/>
+      <c r="AX119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -4365,7 +6257,7 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
       <c r="C120" s="3" t="inlineStr"/>
       <c r="D120" s="3" t="inlineStr">
@@ -4381,12 +6273,28 @@
       <c r="H120" s="3" t="n"/>
       <c r="I120" s="3" t="n"/>
       <c r="J120" s="3" t="n"/>
+      <c r="K120" s="3" t="n"/>
       <c r="L120" s="3" t="n"/>
       <c r="M120" s="3" t="n"/>
       <c r="Q120" s="3" t="n"/>
       <c r="R120" s="3" t="n"/>
       <c r="S120" s="3" t="n"/>
       <c r="T120" s="3" t="n"/>
+      <c r="Z120" s="3" t="n"/>
+      <c r="AA120" s="3" t="n"/>
+      <c r="AB120" s="3" t="n"/>
+      <c r="AC120" s="3" t="n"/>
+      <c r="AD120" s="3" t="n"/>
+      <c r="AJ120" s="3" t="n"/>
+      <c r="AK120" s="3" t="n"/>
+      <c r="AL120" s="3" t="n"/>
+      <c r="AM120" s="3" t="n"/>
+      <c r="AN120" s="3" t="n"/>
+      <c r="AT120" s="3" t="n"/>
+      <c r="AU120" s="3" t="n"/>
+      <c r="AV120" s="3" t="n"/>
+      <c r="AW120" s="3" t="n"/>
+      <c r="AX120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -4395,7 +6303,7 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>18.15</v>
+        <v>16.94</v>
       </c>
       <c r="C121" s="3" t="inlineStr"/>
       <c r="D121" s="3" t="inlineStr">
@@ -4411,12 +6319,28 @@
       <c r="H121" s="3" t="n"/>
       <c r="I121" s="3" t="n"/>
       <c r="J121" s="3" t="n"/>
+      <c r="K121" s="3" t="n"/>
       <c r="L121" s="3" t="n"/>
       <c r="M121" s="3" t="n"/>
       <c r="Q121" s="3" t="n"/>
       <c r="R121" s="3" t="n"/>
       <c r="S121" s="3" t="n"/>
       <c r="T121" s="3" t="n"/>
+      <c r="Z121" s="3" t="n"/>
+      <c r="AA121" s="3" t="n"/>
+      <c r="AB121" s="3" t="n"/>
+      <c r="AC121" s="3" t="n"/>
+      <c r="AD121" s="3" t="n"/>
+      <c r="AJ121" s="3" t="n"/>
+      <c r="AK121" s="3" t="n"/>
+      <c r="AL121" s="3" t="n"/>
+      <c r="AM121" s="3" t="n"/>
+      <c r="AN121" s="3" t="n"/>
+      <c r="AT121" s="3" t="n"/>
+      <c r="AU121" s="3" t="n"/>
+      <c r="AV121" s="3" t="n"/>
+      <c r="AW121" s="3" t="n"/>
+      <c r="AX121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -4425,7 +6349,7 @@
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>14.09</v>
+        <v>14.24</v>
       </c>
       <c r="C122" s="3" t="inlineStr"/>
       <c r="D122" s="3" t="inlineStr">
@@ -4441,12 +6365,28 @@
       <c r="H122" s="3" t="n"/>
       <c r="I122" s="3" t="n"/>
       <c r="J122" s="3" t="n"/>
+      <c r="K122" s="3" t="n"/>
       <c r="L122" s="3" t="n"/>
       <c r="M122" s="3" t="n"/>
       <c r="Q122" s="3" t="n"/>
       <c r="R122" s="3" t="n"/>
       <c r="S122" s="3" t="n"/>
       <c r="T122" s="3" t="n"/>
+      <c r="Z122" s="3" t="n"/>
+      <c r="AA122" s="3" t="n"/>
+      <c r="AB122" s="3" t="n"/>
+      <c r="AC122" s="3" t="n"/>
+      <c r="AD122" s="3" t="n"/>
+      <c r="AJ122" s="3" t="n"/>
+      <c r="AK122" s="3" t="n"/>
+      <c r="AL122" s="3" t="n"/>
+      <c r="AM122" s="3" t="n"/>
+      <c r="AN122" s="3" t="n"/>
+      <c r="AT122" s="3" t="n"/>
+      <c r="AU122" s="3" t="n"/>
+      <c r="AV122" s="3" t="n"/>
+      <c r="AW122" s="3" t="n"/>
+      <c r="AX122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -4455,7 +6395,7 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>8.98</v>
+        <v>8.65</v>
       </c>
       <c r="C123" s="3" t="inlineStr"/>
       <c r="D123" s="3" t="inlineStr">
@@ -4471,12 +6411,28 @@
       <c r="H123" s="3" t="n"/>
       <c r="I123" s="3" t="n"/>
       <c r="J123" s="3" t="n"/>
+      <c r="K123" s="3" t="n"/>
       <c r="L123" s="3" t="n"/>
       <c r="M123" s="3" t="n"/>
       <c r="Q123" s="3" t="n"/>
       <c r="R123" s="3" t="n"/>
       <c r="S123" s="3" t="n"/>
       <c r="T123" s="3" t="n"/>
+      <c r="Z123" s="3" t="n"/>
+      <c r="AA123" s="3" t="n"/>
+      <c r="AB123" s="3" t="n"/>
+      <c r="AC123" s="3" t="n"/>
+      <c r="AD123" s="3" t="n"/>
+      <c r="AJ123" s="3" t="n"/>
+      <c r="AK123" s="3" t="n"/>
+      <c r="AL123" s="3" t="n"/>
+      <c r="AM123" s="3" t="n"/>
+      <c r="AN123" s="3" t="n"/>
+      <c r="AT123" s="3" t="n"/>
+      <c r="AU123" s="3" t="n"/>
+      <c r="AV123" s="3" t="n"/>
+      <c r="AW123" s="3" t="n"/>
+      <c r="AX123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -4485,10 +6441,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
@@ -4503,12 +6459,28 @@
       <c r="H124" s="3" t="n"/>
       <c r="I124" s="3" t="n"/>
       <c r="J124" s="3" t="n"/>
+      <c r="K124" s="3" t="n"/>
       <c r="L124" s="3" t="n"/>
       <c r="M124" s="3" t="n"/>
       <c r="Q124" s="3" t="n"/>
       <c r="R124" s="3" t="n"/>
       <c r="S124" s="3" t="n"/>
       <c r="T124" s="3" t="n"/>
+      <c r="Z124" s="3" t="n"/>
+      <c r="AA124" s="3" t="n"/>
+      <c r="AB124" s="3" t="n"/>
+      <c r="AC124" s="3" t="n"/>
+      <c r="AD124" s="3" t="n"/>
+      <c r="AJ124" s="3" t="n"/>
+      <c r="AK124" s="3" t="n"/>
+      <c r="AL124" s="3" t="n"/>
+      <c r="AM124" s="3" t="n"/>
+      <c r="AN124" s="3" t="n"/>
+      <c r="AT124" s="3" t="n"/>
+      <c r="AU124" s="3" t="n"/>
+      <c r="AV124" s="3" t="n"/>
+      <c r="AW124" s="3" t="n"/>
+      <c r="AX124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -4517,10 +6489,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
@@ -4535,12 +6507,28 @@
       <c r="H125" s="3" t="n"/>
       <c r="I125" s="3" t="n"/>
       <c r="J125" s="3" t="n"/>
+      <c r="K125" s="3" t="n"/>
       <c r="L125" s="3" t="n"/>
       <c r="M125" s="3" t="n"/>
       <c r="Q125" s="3" t="n"/>
       <c r="R125" s="3" t="n"/>
       <c r="S125" s="3" t="n"/>
       <c r="T125" s="3" t="n"/>
+      <c r="Z125" s="3" t="n"/>
+      <c r="AA125" s="3" t="n"/>
+      <c r="AB125" s="3" t="n"/>
+      <c r="AC125" s="3" t="n"/>
+      <c r="AD125" s="3" t="n"/>
+      <c r="AJ125" s="3" t="n"/>
+      <c r="AK125" s="3" t="n"/>
+      <c r="AL125" s="3" t="n"/>
+      <c r="AM125" s="3" t="n"/>
+      <c r="AN125" s="3" t="n"/>
+      <c r="AT125" s="3" t="n"/>
+      <c r="AU125" s="3" t="n"/>
+      <c r="AV125" s="3" t="n"/>
+      <c r="AW125" s="3" t="n"/>
+      <c r="AX125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -4549,10 +6537,10 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
@@ -4567,12 +6555,28 @@
       <c r="H126" s="3" t="n"/>
       <c r="I126" s="3" t="n"/>
       <c r="J126" s="3" t="n"/>
+      <c r="K126" s="3" t="n"/>
       <c r="L126" s="3" t="n"/>
       <c r="M126" s="3" t="n"/>
       <c r="Q126" s="3" t="n"/>
       <c r="R126" s="3" t="n"/>
       <c r="S126" s="3" t="n"/>
       <c r="T126" s="3" t="n"/>
+      <c r="Z126" s="3" t="n"/>
+      <c r="AA126" s="3" t="n"/>
+      <c r="AB126" s="3" t="n"/>
+      <c r="AC126" s="3" t="n"/>
+      <c r="AD126" s="3" t="n"/>
+      <c r="AJ126" s="3" t="n"/>
+      <c r="AK126" s="3" t="n"/>
+      <c r="AL126" s="3" t="n"/>
+      <c r="AM126" s="3" t="n"/>
+      <c r="AN126" s="3" t="n"/>
+      <c r="AT126" s="3" t="n"/>
+      <c r="AU126" s="3" t="n"/>
+      <c r="AV126" s="3" t="n"/>
+      <c r="AW126" s="3" t="n"/>
+      <c r="AX126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -4581,7 +6585,7 @@
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>5.64</v>
+        <v>5.52</v>
       </c>
       <c r="C127" s="3" t="inlineStr"/>
       <c r="D127" s="3" t="inlineStr">
@@ -4597,12 +6601,28 @@
       <c r="H127" s="3" t="n"/>
       <c r="I127" s="3" t="n"/>
       <c r="J127" s="3" t="n"/>
+      <c r="K127" s="3" t="n"/>
       <c r="L127" s="3" t="n"/>
       <c r="M127" s="3" t="n"/>
       <c r="Q127" s="3" t="n"/>
       <c r="R127" s="3" t="n"/>
       <c r="S127" s="3" t="n"/>
       <c r="T127" s="3" t="n"/>
+      <c r="Z127" s="3" t="n"/>
+      <c r="AA127" s="3" t="n"/>
+      <c r="AB127" s="3" t="n"/>
+      <c r="AC127" s="3" t="n"/>
+      <c r="AD127" s="3" t="n"/>
+      <c r="AJ127" s="3" t="n"/>
+      <c r="AK127" s="3" t="n"/>
+      <c r="AL127" s="3" t="n"/>
+      <c r="AM127" s="3" t="n"/>
+      <c r="AN127" s="3" t="n"/>
+      <c r="AT127" s="3" t="n"/>
+      <c r="AU127" s="3" t="n"/>
+      <c r="AV127" s="3" t="n"/>
+      <c r="AW127" s="3" t="n"/>
+      <c r="AX127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -4614,7 +6634,7 @@
         <v>0.08</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
@@ -4629,12 +6649,28 @@
       <c r="H128" s="3" t="n"/>
       <c r="I128" s="3" t="n"/>
       <c r="J128" s="3" t="n"/>
+      <c r="K128" s="3" t="n"/>
       <c r="L128" s="3" t="n"/>
       <c r="M128" s="3" t="n"/>
       <c r="Q128" s="3" t="n"/>
       <c r="R128" s="3" t="n"/>
       <c r="S128" s="3" t="n"/>
       <c r="T128" s="3" t="n"/>
+      <c r="Z128" s="3" t="n"/>
+      <c r="AA128" s="3" t="n"/>
+      <c r="AB128" s="3" t="n"/>
+      <c r="AC128" s="3" t="n"/>
+      <c r="AD128" s="3" t="n"/>
+      <c r="AJ128" s="3" t="n"/>
+      <c r="AK128" s="3" t="n"/>
+      <c r="AL128" s="3" t="n"/>
+      <c r="AM128" s="3" t="n"/>
+      <c r="AN128" s="3" t="n"/>
+      <c r="AT128" s="3" t="n"/>
+      <c r="AU128" s="3" t="n"/>
+      <c r="AV128" s="3" t="n"/>
+      <c r="AW128" s="3" t="n"/>
+      <c r="AX128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -4643,10 +6679,10 @@
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="C129" s="3" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
@@ -4661,12 +6697,28 @@
       <c r="H129" s="3" t="n"/>
       <c r="I129" s="3" t="n"/>
       <c r="J129" s="3" t="n"/>
+      <c r="K129" s="3" t="n"/>
       <c r="L129" s="3" t="n"/>
       <c r="M129" s="3" t="n"/>
       <c r="Q129" s="3" t="n"/>
       <c r="R129" s="3" t="n"/>
       <c r="S129" s="3" t="n"/>
       <c r="T129" s="3" t="n"/>
+      <c r="Z129" s="3" t="n"/>
+      <c r="AA129" s="3" t="n"/>
+      <c r="AB129" s="3" t="n"/>
+      <c r="AC129" s="3" t="n"/>
+      <c r="AD129" s="3" t="n"/>
+      <c r="AJ129" s="3" t="n"/>
+      <c r="AK129" s="3" t="n"/>
+      <c r="AL129" s="3" t="n"/>
+      <c r="AM129" s="3" t="n"/>
+      <c r="AN129" s="3" t="n"/>
+      <c r="AT129" s="3" t="n"/>
+      <c r="AU129" s="3" t="n"/>
+      <c r="AV129" s="3" t="n"/>
+      <c r="AW129" s="3" t="n"/>
+      <c r="AX129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -4675,7 +6727,7 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>9.58</v>
+        <v>9.48</v>
       </c>
       <c r="C130" s="3" t="inlineStr"/>
       <c r="D130" s="3" t="inlineStr">
@@ -4691,12 +6743,28 @@
       <c r="H130" s="3" t="n"/>
       <c r="I130" s="3" t="n"/>
       <c r="J130" s="3" t="n"/>
+      <c r="K130" s="3" t="n"/>
       <c r="L130" s="3" t="n"/>
       <c r="M130" s="3" t="n"/>
       <c r="Q130" s="3" t="n"/>
       <c r="R130" s="3" t="n"/>
       <c r="S130" s="3" t="n"/>
       <c r="T130" s="3" t="n"/>
+      <c r="Z130" s="3" t="n"/>
+      <c r="AA130" s="3" t="n"/>
+      <c r="AB130" s="3" t="n"/>
+      <c r="AC130" s="3" t="n"/>
+      <c r="AD130" s="3" t="n"/>
+      <c r="AJ130" s="3" t="n"/>
+      <c r="AK130" s="3" t="n"/>
+      <c r="AL130" s="3" t="n"/>
+      <c r="AM130" s="3" t="n"/>
+      <c r="AN130" s="3" t="n"/>
+      <c r="AT130" s="3" t="n"/>
+      <c r="AU130" s="3" t="n"/>
+      <c r="AV130" s="3" t="n"/>
+      <c r="AW130" s="3" t="n"/>
+      <c r="AX130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -4708,7 +6776,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C131" s="3" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
@@ -4723,12 +6791,28 @@
       <c r="H131" s="3" t="n"/>
       <c r="I131" s="3" t="n"/>
       <c r="J131" s="3" t="n"/>
+      <c r="K131" s="3" t="n"/>
       <c r="L131" s="3" t="n"/>
       <c r="M131" s="3" t="n"/>
       <c r="Q131" s="3" t="n"/>
       <c r="R131" s="3" t="n"/>
       <c r="S131" s="3" t="n"/>
       <c r="T131" s="3" t="n"/>
+      <c r="Z131" s="3" t="n"/>
+      <c r="AA131" s="3" t="n"/>
+      <c r="AB131" s="3" t="n"/>
+      <c r="AC131" s="3" t="n"/>
+      <c r="AD131" s="3" t="n"/>
+      <c r="AJ131" s="3" t="n"/>
+      <c r="AK131" s="3" t="n"/>
+      <c r="AL131" s="3" t="n"/>
+      <c r="AM131" s="3" t="n"/>
+      <c r="AN131" s="3" t="n"/>
+      <c r="AT131" s="3" t="n"/>
+      <c r="AU131" s="3" t="n"/>
+      <c r="AV131" s="3" t="n"/>
+      <c r="AW131" s="3" t="n"/>
+      <c r="AX131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -4737,10 +6821,10 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="C132" s="3" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
@@ -4755,12 +6839,28 @@
       <c r="H132" s="3" t="n"/>
       <c r="I132" s="3" t="n"/>
       <c r="J132" s="3" t="n"/>
+      <c r="K132" s="3" t="n"/>
       <c r="L132" s="3" t="n"/>
       <c r="M132" s="3" t="n"/>
       <c r="Q132" s="3" t="n"/>
       <c r="R132" s="3" t="n"/>
       <c r="S132" s="3" t="n"/>
       <c r="T132" s="3" t="n"/>
+      <c r="Z132" s="3" t="n"/>
+      <c r="AA132" s="3" t="n"/>
+      <c r="AB132" s="3" t="n"/>
+      <c r="AC132" s="3" t="n"/>
+      <c r="AD132" s="3" t="n"/>
+      <c r="AJ132" s="3" t="n"/>
+      <c r="AK132" s="3" t="n"/>
+      <c r="AL132" s="3" t="n"/>
+      <c r="AM132" s="3" t="n"/>
+      <c r="AN132" s="3" t="n"/>
+      <c r="AT132" s="3" t="n"/>
+      <c r="AU132" s="3" t="n"/>
+      <c r="AV132" s="3" t="n"/>
+      <c r="AW132" s="3" t="n"/>
+      <c r="AX132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -4769,10 +6869,10 @@
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="C133" s="3" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
@@ -4787,12 +6887,28 @@
       <c r="H133" s="3" t="n"/>
       <c r="I133" s="3" t="n"/>
       <c r="J133" s="3" t="n"/>
+      <c r="K133" s="3" t="n"/>
       <c r="L133" s="3" t="n"/>
       <c r="M133" s="3" t="n"/>
       <c r="Q133" s="3" t="n"/>
       <c r="R133" s="3" t="n"/>
       <c r="S133" s="3" t="n"/>
       <c r="T133" s="3" t="n"/>
+      <c r="Z133" s="3" t="n"/>
+      <c r="AA133" s="3" t="n"/>
+      <c r="AB133" s="3" t="n"/>
+      <c r="AC133" s="3" t="n"/>
+      <c r="AD133" s="3" t="n"/>
+      <c r="AJ133" s="3" t="n"/>
+      <c r="AK133" s="3" t="n"/>
+      <c r="AL133" s="3" t="n"/>
+      <c r="AM133" s="3" t="n"/>
+      <c r="AN133" s="3" t="n"/>
+      <c r="AT133" s="3" t="n"/>
+      <c r="AU133" s="3" t="n"/>
+      <c r="AV133" s="3" t="n"/>
+      <c r="AW133" s="3" t="n"/>
+      <c r="AX133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -4801,10 +6917,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
@@ -4819,12 +6935,28 @@
       <c r="H134" s="3" t="n"/>
       <c r="I134" s="3" t="n"/>
       <c r="J134" s="3" t="n"/>
+      <c r="K134" s="3" t="n"/>
       <c r="L134" s="3" t="n"/>
       <c r="M134" s="3" t="n"/>
       <c r="Q134" s="3" t="n"/>
       <c r="R134" s="3" t="n"/>
       <c r="S134" s="3" t="n"/>
       <c r="T134" s="3" t="n"/>
+      <c r="Z134" s="3" t="n"/>
+      <c r="AA134" s="3" t="n"/>
+      <c r="AB134" s="3" t="n"/>
+      <c r="AC134" s="3" t="n"/>
+      <c r="AD134" s="3" t="n"/>
+      <c r="AJ134" s="3" t="n"/>
+      <c r="AK134" s="3" t="n"/>
+      <c r="AL134" s="3" t="n"/>
+      <c r="AM134" s="3" t="n"/>
+      <c r="AN134" s="3" t="n"/>
+      <c r="AT134" s="3" t="n"/>
+      <c r="AU134" s="3" t="n"/>
+      <c r="AV134" s="3" t="n"/>
+      <c r="AW134" s="3" t="n"/>
+      <c r="AX134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -4833,10 +6965,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
@@ -4851,12 +6983,28 @@
       <c r="H135" s="3" t="n"/>
       <c r="I135" s="3" t="n"/>
       <c r="J135" s="3" t="n"/>
+      <c r="K135" s="3" t="n"/>
       <c r="L135" s="3" t="n"/>
       <c r="M135" s="3" t="n"/>
       <c r="Q135" s="3" t="n"/>
       <c r="R135" s="3" t="n"/>
       <c r="S135" s="3" t="n"/>
       <c r="T135" s="3" t="n"/>
+      <c r="Z135" s="3" t="n"/>
+      <c r="AA135" s="3" t="n"/>
+      <c r="AB135" s="3" t="n"/>
+      <c r="AC135" s="3" t="n"/>
+      <c r="AD135" s="3" t="n"/>
+      <c r="AJ135" s="3" t="n"/>
+      <c r="AK135" s="3" t="n"/>
+      <c r="AL135" s="3" t="n"/>
+      <c r="AM135" s="3" t="n"/>
+      <c r="AN135" s="3" t="n"/>
+      <c r="AT135" s="3" t="n"/>
+      <c r="AU135" s="3" t="n"/>
+      <c r="AV135" s="3" t="n"/>
+      <c r="AW135" s="3" t="n"/>
+      <c r="AX135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -4865,7 +7013,7 @@
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="C136" s="3" t="inlineStr"/>
       <c r="D136" s="3" t="inlineStr">
@@ -4881,12 +7029,28 @@
       <c r="H136" s="3" t="n"/>
       <c r="I136" s="3" t="n"/>
       <c r="J136" s="3" t="n"/>
+      <c r="K136" s="3" t="n"/>
       <c r="L136" s="3" t="n"/>
       <c r="M136" s="3" t="n"/>
       <c r="Q136" s="3" t="n"/>
       <c r="R136" s="3" t="n"/>
       <c r="S136" s="3" t="n"/>
       <c r="T136" s="3" t="n"/>
+      <c r="Z136" s="3" t="n"/>
+      <c r="AA136" s="3" t="n"/>
+      <c r="AB136" s="3" t="n"/>
+      <c r="AC136" s="3" t="n"/>
+      <c r="AD136" s="3" t="n"/>
+      <c r="AJ136" s="3" t="n"/>
+      <c r="AK136" s="3" t="n"/>
+      <c r="AL136" s="3" t="n"/>
+      <c r="AM136" s="3" t="n"/>
+      <c r="AN136" s="3" t="n"/>
+      <c r="AT136" s="3" t="n"/>
+      <c r="AU136" s="3" t="n"/>
+      <c r="AV136" s="3" t="n"/>
+      <c r="AW136" s="3" t="n"/>
+      <c r="AX136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -4895,7 +7059,7 @@
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>6.89</v>
+        <v>6.79</v>
       </c>
       <c r="C137" s="3" t="inlineStr"/>
       <c r="D137" s="3" t="inlineStr">
@@ -4911,12 +7075,28 @@
       <c r="H137" s="3" t="n"/>
       <c r="I137" s="3" t="n"/>
       <c r="J137" s="3" t="n"/>
+      <c r="K137" s="3" t="n"/>
       <c r="L137" s="3" t="n"/>
       <c r="M137" s="3" t="n"/>
       <c r="Q137" s="3" t="n"/>
       <c r="R137" s="3" t="n"/>
       <c r="S137" s="3" t="n"/>
       <c r="T137" s="3" t="n"/>
+      <c r="Z137" s="3" t="n"/>
+      <c r="AA137" s="3" t="n"/>
+      <c r="AB137" s="3" t="n"/>
+      <c r="AC137" s="3" t="n"/>
+      <c r="AD137" s="3" t="n"/>
+      <c r="AJ137" s="3" t="n"/>
+      <c r="AK137" s="3" t="n"/>
+      <c r="AL137" s="3" t="n"/>
+      <c r="AM137" s="3" t="n"/>
+      <c r="AN137" s="3" t="n"/>
+      <c r="AT137" s="3" t="n"/>
+      <c r="AU137" s="3" t="n"/>
+      <c r="AV137" s="3" t="n"/>
+      <c r="AW137" s="3" t="n"/>
+      <c r="AX137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -4925,10 +7105,10 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C138" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
@@ -4943,12 +7123,28 @@
       <c r="H138" s="3" t="n"/>
       <c r="I138" s="3" t="n"/>
       <c r="J138" s="3" t="n"/>
+      <c r="K138" s="3" t="n"/>
       <c r="L138" s="3" t="n"/>
       <c r="M138" s="3" t="n"/>
       <c r="Q138" s="3" t="n"/>
       <c r="R138" s="3" t="n"/>
       <c r="S138" s="3" t="n"/>
       <c r="T138" s="3" t="n"/>
+      <c r="Z138" s="3" t="n"/>
+      <c r="AA138" s="3" t="n"/>
+      <c r="AB138" s="3" t="n"/>
+      <c r="AC138" s="3" t="n"/>
+      <c r="AD138" s="3" t="n"/>
+      <c r="AJ138" s="3" t="n"/>
+      <c r="AK138" s="3" t="n"/>
+      <c r="AL138" s="3" t="n"/>
+      <c r="AM138" s="3" t="n"/>
+      <c r="AN138" s="3" t="n"/>
+      <c r="AT138" s="3" t="n"/>
+      <c r="AU138" s="3" t="n"/>
+      <c r="AV138" s="3" t="n"/>
+      <c r="AW138" s="3" t="n"/>
+      <c r="AX138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -4957,10 +7153,10 @@
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="C139" s="3" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
@@ -4975,12 +7171,28 @@
       <c r="H139" s="3" t="n"/>
       <c r="I139" s="3" t="n"/>
       <c r="J139" s="3" t="n"/>
+      <c r="K139" s="3" t="n"/>
       <c r="L139" s="3" t="n"/>
       <c r="M139" s="3" t="n"/>
       <c r="Q139" s="3" t="n"/>
       <c r="R139" s="3" t="n"/>
       <c r="S139" s="3" t="n"/>
       <c r="T139" s="3" t="n"/>
+      <c r="Z139" s="3" t="n"/>
+      <c r="AA139" s="3" t="n"/>
+      <c r="AB139" s="3" t="n"/>
+      <c r="AC139" s="3" t="n"/>
+      <c r="AD139" s="3" t="n"/>
+      <c r="AJ139" s="3" t="n"/>
+      <c r="AK139" s="3" t="n"/>
+      <c r="AL139" s="3" t="n"/>
+      <c r="AM139" s="3" t="n"/>
+      <c r="AN139" s="3" t="n"/>
+      <c r="AT139" s="3" t="n"/>
+      <c r="AU139" s="3" t="n"/>
+      <c r="AV139" s="3" t="n"/>
+      <c r="AW139" s="3" t="n"/>
+      <c r="AX139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -4989,7 +7201,7 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>7.33</v>
+        <v>7.05</v>
       </c>
       <c r="C140" s="3" t="inlineStr"/>
       <c r="D140" s="3" t="inlineStr">
@@ -5005,12 +7217,28 @@
       <c r="H140" s="3" t="n"/>
       <c r="I140" s="3" t="n"/>
       <c r="J140" s="3" t="n"/>
+      <c r="K140" s="3" t="n"/>
       <c r="L140" s="3" t="n"/>
       <c r="M140" s="3" t="n"/>
       <c r="Q140" s="3" t="n"/>
       <c r="R140" s="3" t="n"/>
       <c r="S140" s="3" t="n"/>
       <c r="T140" s="3" t="n"/>
+      <c r="Z140" s="3" t="n"/>
+      <c r="AA140" s="3" t="n"/>
+      <c r="AB140" s="3" t="n"/>
+      <c r="AC140" s="3" t="n"/>
+      <c r="AD140" s="3" t="n"/>
+      <c r="AJ140" s="3" t="n"/>
+      <c r="AK140" s="3" t="n"/>
+      <c r="AL140" s="3" t="n"/>
+      <c r="AM140" s="3" t="n"/>
+      <c r="AN140" s="3" t="n"/>
+      <c r="AT140" s="3" t="n"/>
+      <c r="AU140" s="3" t="n"/>
+      <c r="AV140" s="3" t="n"/>
+      <c r="AW140" s="3" t="n"/>
+      <c r="AX140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -5019,10 +7247,10 @@
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="C141" s="3" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
@@ -5037,12 +7265,28 @@
       <c r="H141" s="3" t="n"/>
       <c r="I141" s="3" t="n"/>
       <c r="J141" s="3" t="n"/>
+      <c r="K141" s="3" t="n"/>
       <c r="L141" s="3" t="n"/>
       <c r="M141" s="3" t="n"/>
       <c r="Q141" s="3" t="n"/>
       <c r="R141" s="3" t="n"/>
       <c r="S141" s="3" t="n"/>
       <c r="T141" s="3" t="n"/>
+      <c r="Z141" s="3" t="n"/>
+      <c r="AA141" s="3" t="n"/>
+      <c r="AB141" s="3" t="n"/>
+      <c r="AC141" s="3" t="n"/>
+      <c r="AD141" s="3" t="n"/>
+      <c r="AJ141" s="3" t="n"/>
+      <c r="AK141" s="3" t="n"/>
+      <c r="AL141" s="3" t="n"/>
+      <c r="AM141" s="3" t="n"/>
+      <c r="AN141" s="3" t="n"/>
+      <c r="AT141" s="3" t="n"/>
+      <c r="AU141" s="3" t="n"/>
+      <c r="AV141" s="3" t="n"/>
+      <c r="AW141" s="3" t="n"/>
+      <c r="AX141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -5054,7 +7298,7 @@
         <v>0.08</v>
       </c>
       <c r="C142" s="3" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
@@ -5069,12 +7313,28 @@
       <c r="H142" s="3" t="n"/>
       <c r="I142" s="3" t="n"/>
       <c r="J142" s="3" t="n"/>
+      <c r="K142" s="3" t="n"/>
       <c r="L142" s="3" t="n"/>
       <c r="M142" s="3" t="n"/>
       <c r="Q142" s="3" t="n"/>
       <c r="R142" s="3" t="n"/>
       <c r="S142" s="3" t="n"/>
       <c r="T142" s="3" t="n"/>
+      <c r="Z142" s="3" t="n"/>
+      <c r="AA142" s="3" t="n"/>
+      <c r="AB142" s="3" t="n"/>
+      <c r="AC142" s="3" t="n"/>
+      <c r="AD142" s="3" t="n"/>
+      <c r="AJ142" s="3" t="n"/>
+      <c r="AK142" s="3" t="n"/>
+      <c r="AL142" s="3" t="n"/>
+      <c r="AM142" s="3" t="n"/>
+      <c r="AN142" s="3" t="n"/>
+      <c r="AT142" s="3" t="n"/>
+      <c r="AU142" s="3" t="n"/>
+      <c r="AV142" s="3" t="n"/>
+      <c r="AW142" s="3" t="n"/>
+      <c r="AX142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -5083,10 +7343,10 @@
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="C143" s="3" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
@@ -5101,12 +7361,28 @@
       <c r="H143" s="3" t="n"/>
       <c r="I143" s="3" t="n"/>
       <c r="J143" s="3" t="n"/>
+      <c r="K143" s="3" t="n"/>
       <c r="L143" s="3" t="n"/>
       <c r="M143" s="3" t="n"/>
       <c r="Q143" s="3" t="n"/>
       <c r="R143" s="3" t="n"/>
       <c r="S143" s="3" t="n"/>
       <c r="T143" s="3" t="n"/>
+      <c r="Z143" s="3" t="n"/>
+      <c r="AA143" s="3" t="n"/>
+      <c r="AB143" s="3" t="n"/>
+      <c r="AC143" s="3" t="n"/>
+      <c r="AD143" s="3" t="n"/>
+      <c r="AJ143" s="3" t="n"/>
+      <c r="AK143" s="3" t="n"/>
+      <c r="AL143" s="3" t="n"/>
+      <c r="AM143" s="3" t="n"/>
+      <c r="AN143" s="3" t="n"/>
+      <c r="AT143" s="3" t="n"/>
+      <c r="AU143" s="3" t="n"/>
+      <c r="AV143" s="3" t="n"/>
+      <c r="AW143" s="3" t="n"/>
+      <c r="AX143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -5115,10 +7391,10 @@
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C144" s="3" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
@@ -5133,12 +7409,28 @@
       <c r="H144" s="3" t="n"/>
       <c r="I144" s="3" t="n"/>
       <c r="J144" s="3" t="n"/>
+      <c r="K144" s="3" t="n"/>
       <c r="L144" s="3" t="n"/>
       <c r="M144" s="3" t="n"/>
       <c r="Q144" s="3" t="n"/>
       <c r="R144" s="3" t="n"/>
       <c r="S144" s="3" t="n"/>
       <c r="T144" s="3" t="n"/>
+      <c r="Z144" s="3" t="n"/>
+      <c r="AA144" s="3" t="n"/>
+      <c r="AB144" s="3" t="n"/>
+      <c r="AC144" s="3" t="n"/>
+      <c r="AD144" s="3" t="n"/>
+      <c r="AJ144" s="3" t="n"/>
+      <c r="AK144" s="3" t="n"/>
+      <c r="AL144" s="3" t="n"/>
+      <c r="AM144" s="3" t="n"/>
+      <c r="AN144" s="3" t="n"/>
+      <c r="AT144" s="3" t="n"/>
+      <c r="AU144" s="3" t="n"/>
+      <c r="AV144" s="3" t="n"/>
+      <c r="AW144" s="3" t="n"/>
+      <c r="AX144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -5150,7 +7442,7 @@
         <v>0.06</v>
       </c>
       <c r="C145" s="3" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
@@ -5165,12 +7457,28 @@
       <c r="H145" s="3" t="n"/>
       <c r="I145" s="3" t="n"/>
       <c r="J145" s="3" t="n"/>
+      <c r="K145" s="3" t="n"/>
       <c r="L145" s="3" t="n"/>
       <c r="M145" s="3" t="n"/>
       <c r="Q145" s="3" t="n"/>
       <c r="R145" s="3" t="n"/>
       <c r="S145" s="3" t="n"/>
       <c r="T145" s="3" t="n"/>
+      <c r="Z145" s="3" t="n"/>
+      <c r="AA145" s="3" t="n"/>
+      <c r="AB145" s="3" t="n"/>
+      <c r="AC145" s="3" t="n"/>
+      <c r="AD145" s="3" t="n"/>
+      <c r="AJ145" s="3" t="n"/>
+      <c r="AK145" s="3" t="n"/>
+      <c r="AL145" s="3" t="n"/>
+      <c r="AM145" s="3" t="n"/>
+      <c r="AN145" s="3" t="n"/>
+      <c r="AT145" s="3" t="n"/>
+      <c r="AU145" s="3" t="n"/>
+      <c r="AV145" s="3" t="n"/>
+      <c r="AW145" s="3" t="n"/>
+      <c r="AX145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -5182,7 +7490,7 @@
         <v>0.06</v>
       </c>
       <c r="C146" s="3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
@@ -5197,12 +7505,28 @@
       <c r="H146" s="3" t="n"/>
       <c r="I146" s="3" t="n"/>
       <c r="J146" s="3" t="n"/>
+      <c r="K146" s="3" t="n"/>
       <c r="L146" s="3" t="n"/>
       <c r="M146" s="3" t="n"/>
       <c r="Q146" s="3" t="n"/>
       <c r="R146" s="3" t="n"/>
       <c r="S146" s="3" t="n"/>
       <c r="T146" s="3" t="n"/>
+      <c r="Z146" s="3" t="n"/>
+      <c r="AA146" s="3" t="n"/>
+      <c r="AB146" s="3" t="n"/>
+      <c r="AC146" s="3" t="n"/>
+      <c r="AD146" s="3" t="n"/>
+      <c r="AJ146" s="3" t="n"/>
+      <c r="AK146" s="3" t="n"/>
+      <c r="AL146" s="3" t="n"/>
+      <c r="AM146" s="3" t="n"/>
+      <c r="AN146" s="3" t="n"/>
+      <c r="AT146" s="3" t="n"/>
+      <c r="AU146" s="3" t="n"/>
+      <c r="AV146" s="3" t="n"/>
+      <c r="AW146" s="3" t="n"/>
+      <c r="AX146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -5211,10 +7535,10 @@
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="C147" s="3" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
@@ -5229,12 +7553,28 @@
       <c r="H147" s="3" t="n"/>
       <c r="I147" s="3" t="n"/>
       <c r="J147" s="3" t="n"/>
+      <c r="K147" s="3" t="n"/>
       <c r="L147" s="3" t="n"/>
       <c r="M147" s="3" t="n"/>
       <c r="Q147" s="3" t="n"/>
       <c r="R147" s="3" t="n"/>
       <c r="S147" s="3" t="n"/>
       <c r="T147" s="3" t="n"/>
+      <c r="Z147" s="3" t="n"/>
+      <c r="AA147" s="3" t="n"/>
+      <c r="AB147" s="3" t="n"/>
+      <c r="AC147" s="3" t="n"/>
+      <c r="AD147" s="3" t="n"/>
+      <c r="AJ147" s="3" t="n"/>
+      <c r="AK147" s="3" t="n"/>
+      <c r="AL147" s="3" t="n"/>
+      <c r="AM147" s="3" t="n"/>
+      <c r="AN147" s="3" t="n"/>
+      <c r="AT147" s="3" t="n"/>
+      <c r="AU147" s="3" t="n"/>
+      <c r="AV147" s="3" t="n"/>
+      <c r="AW147" s="3" t="n"/>
+      <c r="AX147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
@@ -5243,10 +7583,10 @@
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="C148" s="3" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
@@ -5261,12 +7601,28 @@
       <c r="H148" s="3" t="n"/>
       <c r="I148" s="3" t="n"/>
       <c r="J148" s="3" t="n"/>
+      <c r="K148" s="3" t="n"/>
       <c r="L148" s="3" t="n"/>
       <c r="M148" s="3" t="n"/>
       <c r="Q148" s="3" t="n"/>
       <c r="R148" s="3" t="n"/>
       <c r="S148" s="3" t="n"/>
       <c r="T148" s="3" t="n"/>
+      <c r="Z148" s="3" t="n"/>
+      <c r="AA148" s="3" t="n"/>
+      <c r="AB148" s="3" t="n"/>
+      <c r="AC148" s="3" t="n"/>
+      <c r="AD148" s="3" t="n"/>
+      <c r="AJ148" s="3" t="n"/>
+      <c r="AK148" s="3" t="n"/>
+      <c r="AL148" s="3" t="n"/>
+      <c r="AM148" s="3" t="n"/>
+      <c r="AN148" s="3" t="n"/>
+      <c r="AT148" s="3" t="n"/>
+      <c r="AU148" s="3" t="n"/>
+      <c r="AV148" s="3" t="n"/>
+      <c r="AW148" s="3" t="n"/>
+      <c r="AX148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -5275,10 +7631,10 @@
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C149" s="3" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
@@ -5293,12 +7649,28 @@
       <c r="H149" s="3" t="n"/>
       <c r="I149" s="3" t="n"/>
       <c r="J149" s="3" t="n"/>
+      <c r="K149" s="3" t="n"/>
       <c r="L149" s="3" t="n"/>
       <c r="M149" s="3" t="n"/>
       <c r="Q149" s="3" t="n"/>
       <c r="R149" s="3" t="n"/>
       <c r="S149" s="3" t="n"/>
       <c r="T149" s="3" t="n"/>
+      <c r="Z149" s="3" t="n"/>
+      <c r="AA149" s="3" t="n"/>
+      <c r="AB149" s="3" t="n"/>
+      <c r="AC149" s="3" t="n"/>
+      <c r="AD149" s="3" t="n"/>
+      <c r="AJ149" s="3" t="n"/>
+      <c r="AK149" s="3" t="n"/>
+      <c r="AL149" s="3" t="n"/>
+      <c r="AM149" s="3" t="n"/>
+      <c r="AN149" s="3" t="n"/>
+      <c r="AT149" s="3" t="n"/>
+      <c r="AU149" s="3" t="n"/>
+      <c r="AV149" s="3" t="n"/>
+      <c r="AW149" s="3" t="n"/>
+      <c r="AX149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -5307,7 +7679,7 @@
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>28.35</v>
+        <v>27.51</v>
       </c>
       <c r="C150" s="3" t="inlineStr"/>
       <c r="D150" s="3" t="inlineStr">
@@ -5323,12 +7695,28 @@
       <c r="H150" s="3" t="n"/>
       <c r="I150" s="3" t="n"/>
       <c r="J150" s="3" t="n"/>
+      <c r="K150" s="3" t="n"/>
       <c r="L150" s="3" t="n"/>
       <c r="M150" s="3" t="n"/>
       <c r="Q150" s="3" t="n"/>
       <c r="R150" s="3" t="n"/>
       <c r="S150" s="3" t="n"/>
       <c r="T150" s="3" t="n"/>
+      <c r="Z150" s="3" t="n"/>
+      <c r="AA150" s="3" t="n"/>
+      <c r="AB150" s="3" t="n"/>
+      <c r="AC150" s="3" t="n"/>
+      <c r="AD150" s="3" t="n"/>
+      <c r="AJ150" s="3" t="n"/>
+      <c r="AK150" s="3" t="n"/>
+      <c r="AL150" s="3" t="n"/>
+      <c r="AM150" s="3" t="n"/>
+      <c r="AN150" s="3" t="n"/>
+      <c r="AT150" s="3" t="n"/>
+      <c r="AU150" s="3" t="n"/>
+      <c r="AV150" s="3" t="n"/>
+      <c r="AW150" s="3" t="n"/>
+      <c r="AX150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -5337,10 +7725,10 @@
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="C151" s="3" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
@@ -5355,12 +7743,28 @@
       <c r="H151" s="3" t="n"/>
       <c r="I151" s="3" t="n"/>
       <c r="J151" s="3" t="n"/>
+      <c r="K151" s="3" t="n"/>
       <c r="L151" s="3" t="n"/>
       <c r="M151" s="3" t="n"/>
       <c r="Q151" s="3" t="n"/>
       <c r="R151" s="3" t="n"/>
       <c r="S151" s="3" t="n"/>
       <c r="T151" s="3" t="n"/>
+      <c r="Z151" s="3" t="n"/>
+      <c r="AA151" s="3" t="n"/>
+      <c r="AB151" s="3" t="n"/>
+      <c r="AC151" s="3" t="n"/>
+      <c r="AD151" s="3" t="n"/>
+      <c r="AJ151" s="3" t="n"/>
+      <c r="AK151" s="3" t="n"/>
+      <c r="AL151" s="3" t="n"/>
+      <c r="AM151" s="3" t="n"/>
+      <c r="AN151" s="3" t="n"/>
+      <c r="AT151" s="3" t="n"/>
+      <c r="AU151" s="3" t="n"/>
+      <c r="AV151" s="3" t="n"/>
+      <c r="AW151" s="3" t="n"/>
+      <c r="AX151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -5369,10 +7773,10 @@
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C152" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
@@ -5387,12 +7791,28 @@
       <c r="H152" s="3" t="n"/>
       <c r="I152" s="3" t="n"/>
       <c r="J152" s="3" t="n"/>
+      <c r="K152" s="3" t="n"/>
       <c r="L152" s="3" t="n"/>
       <c r="M152" s="3" t="n"/>
       <c r="Q152" s="3" t="n"/>
       <c r="R152" s="3" t="n"/>
       <c r="S152" s="3" t="n"/>
       <c r="T152" s="3" t="n"/>
+      <c r="Z152" s="3" t="n"/>
+      <c r="AA152" s="3" t="n"/>
+      <c r="AB152" s="3" t="n"/>
+      <c r="AC152" s="3" t="n"/>
+      <c r="AD152" s="3" t="n"/>
+      <c r="AJ152" s="3" t="n"/>
+      <c r="AK152" s="3" t="n"/>
+      <c r="AL152" s="3" t="n"/>
+      <c r="AM152" s="3" t="n"/>
+      <c r="AN152" s="3" t="n"/>
+      <c r="AT152" s="3" t="n"/>
+      <c r="AU152" s="3" t="n"/>
+      <c r="AV152" s="3" t="n"/>
+      <c r="AW152" s="3" t="n"/>
+      <c r="AX152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -5404,7 +7824,7 @@
         <v>0.11</v>
       </c>
       <c r="C153" s="3" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
@@ -5419,12 +7839,28 @@
       <c r="H153" s="3" t="n"/>
       <c r="I153" s="3" t="n"/>
       <c r="J153" s="3" t="n"/>
+      <c r="K153" s="3" t="n"/>
       <c r="L153" s="3" t="n"/>
       <c r="M153" s="3" t="n"/>
       <c r="Q153" s="3" t="n"/>
       <c r="R153" s="3" t="n"/>
       <c r="S153" s="3" t="n"/>
       <c r="T153" s="3" t="n"/>
+      <c r="Z153" s="3" t="n"/>
+      <c r="AA153" s="3" t="n"/>
+      <c r="AB153" s="3" t="n"/>
+      <c r="AC153" s="3" t="n"/>
+      <c r="AD153" s="3" t="n"/>
+      <c r="AJ153" s="3" t="n"/>
+      <c r="AK153" s="3" t="n"/>
+      <c r="AL153" s="3" t="n"/>
+      <c r="AM153" s="3" t="n"/>
+      <c r="AN153" s="3" t="n"/>
+      <c r="AT153" s="3" t="n"/>
+      <c r="AU153" s="3" t="n"/>
+      <c r="AV153" s="3" t="n"/>
+      <c r="AW153" s="3" t="n"/>
+      <c r="AX153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
@@ -5433,7 +7869,7 @@
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>18.77</v>
+        <v>15.56</v>
       </c>
       <c r="C154" s="3" t="inlineStr"/>
       <c r="D154" s="3" t="inlineStr">
@@ -5449,12 +7885,28 @@
       <c r="H154" s="3" t="n"/>
       <c r="I154" s="3" t="n"/>
       <c r="J154" s="3" t="n"/>
+      <c r="K154" s="3" t="n"/>
       <c r="L154" s="3" t="n"/>
       <c r="M154" s="3" t="n"/>
       <c r="Q154" s="3" t="n"/>
       <c r="R154" s="3" t="n"/>
       <c r="S154" s="3" t="n"/>
       <c r="T154" s="3" t="n"/>
+      <c r="Z154" s="3" t="n"/>
+      <c r="AA154" s="3" t="n"/>
+      <c r="AB154" s="3" t="n"/>
+      <c r="AC154" s="3" t="n"/>
+      <c r="AD154" s="3" t="n"/>
+      <c r="AJ154" s="3" t="n"/>
+      <c r="AK154" s="3" t="n"/>
+      <c r="AL154" s="3" t="n"/>
+      <c r="AM154" s="3" t="n"/>
+      <c r="AN154" s="3" t="n"/>
+      <c r="AT154" s="3" t="n"/>
+      <c r="AU154" s="3" t="n"/>
+      <c r="AV154" s="3" t="n"/>
+      <c r="AW154" s="3" t="n"/>
+      <c r="AX154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
@@ -5463,10 +7915,10 @@
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C155" s="3" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
@@ -5481,12 +7933,28 @@
       <c r="H155" s="3" t="n"/>
       <c r="I155" s="3" t="n"/>
       <c r="J155" s="3" t="n"/>
+      <c r="K155" s="3" t="n"/>
       <c r="L155" s="3" t="n"/>
       <c r="M155" s="3" t="n"/>
       <c r="Q155" s="3" t="n"/>
       <c r="R155" s="3" t="n"/>
       <c r="S155" s="3" t="n"/>
       <c r="T155" s="3" t="n"/>
+      <c r="Z155" s="3" t="n"/>
+      <c r="AA155" s="3" t="n"/>
+      <c r="AB155" s="3" t="n"/>
+      <c r="AC155" s="3" t="n"/>
+      <c r="AD155" s="3" t="n"/>
+      <c r="AJ155" s="3" t="n"/>
+      <c r="AK155" s="3" t="n"/>
+      <c r="AL155" s="3" t="n"/>
+      <c r="AM155" s="3" t="n"/>
+      <c r="AN155" s="3" t="n"/>
+      <c r="AT155" s="3" t="n"/>
+      <c r="AU155" s="3" t="n"/>
+      <c r="AV155" s="3" t="n"/>
+      <c r="AW155" s="3" t="n"/>
+      <c r="AX155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -5495,10 +7963,10 @@
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="C156" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
@@ -5513,12 +7981,28 @@
       <c r="H156" s="3" t="n"/>
       <c r="I156" s="3" t="n"/>
       <c r="J156" s="3" t="n"/>
+      <c r="K156" s="3" t="n"/>
       <c r="L156" s="3" t="n"/>
       <c r="M156" s="3" t="n"/>
       <c r="Q156" s="3" t="n"/>
       <c r="R156" s="3" t="n"/>
       <c r="S156" s="3" t="n"/>
       <c r="T156" s="3" t="n"/>
+      <c r="Z156" s="3" t="n"/>
+      <c r="AA156" s="3" t="n"/>
+      <c r="AB156" s="3" t="n"/>
+      <c r="AC156" s="3" t="n"/>
+      <c r="AD156" s="3" t="n"/>
+      <c r="AJ156" s="3" t="n"/>
+      <c r="AK156" s="3" t="n"/>
+      <c r="AL156" s="3" t="n"/>
+      <c r="AM156" s="3" t="n"/>
+      <c r="AN156" s="3" t="n"/>
+      <c r="AT156" s="3" t="n"/>
+      <c r="AU156" s="3" t="n"/>
+      <c r="AV156" s="3" t="n"/>
+      <c r="AW156" s="3" t="n"/>
+      <c r="AX156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -5530,7 +8014,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C157" s="3" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
@@ -5545,12 +8029,28 @@
       <c r="H157" s="3" t="n"/>
       <c r="I157" s="3" t="n"/>
       <c r="J157" s="3" t="n"/>
+      <c r="K157" s="3" t="n"/>
       <c r="L157" s="3" t="n"/>
       <c r="M157" s="3" t="n"/>
       <c r="Q157" s="3" t="n"/>
       <c r="R157" s="3" t="n"/>
       <c r="S157" s="3" t="n"/>
       <c r="T157" s="3" t="n"/>
+      <c r="Z157" s="3" t="n"/>
+      <c r="AA157" s="3" t="n"/>
+      <c r="AB157" s="3" t="n"/>
+      <c r="AC157" s="3" t="n"/>
+      <c r="AD157" s="3" t="n"/>
+      <c r="AJ157" s="3" t="n"/>
+      <c r="AK157" s="3" t="n"/>
+      <c r="AL157" s="3" t="n"/>
+      <c r="AM157" s="3" t="n"/>
+      <c r="AN157" s="3" t="n"/>
+      <c r="AT157" s="3" t="n"/>
+      <c r="AU157" s="3" t="n"/>
+      <c r="AV157" s="3" t="n"/>
+      <c r="AW157" s="3" t="n"/>
+      <c r="AX157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -5559,10 +8059,10 @@
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C158" s="3" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
@@ -5577,12 +8077,28 @@
       <c r="H158" s="3" t="n"/>
       <c r="I158" s="3" t="n"/>
       <c r="J158" s="3" t="n"/>
+      <c r="K158" s="3" t="n"/>
       <c r="L158" s="3" t="n"/>
       <c r="M158" s="3" t="n"/>
       <c r="Q158" s="3" t="n"/>
       <c r="R158" s="3" t="n"/>
       <c r="S158" s="3" t="n"/>
       <c r="T158" s="3" t="n"/>
+      <c r="Z158" s="3" t="n"/>
+      <c r="AA158" s="3" t="n"/>
+      <c r="AB158" s="3" t="n"/>
+      <c r="AC158" s="3" t="n"/>
+      <c r="AD158" s="3" t="n"/>
+      <c r="AJ158" s="3" t="n"/>
+      <c r="AK158" s="3" t="n"/>
+      <c r="AL158" s="3" t="n"/>
+      <c r="AM158" s="3" t="n"/>
+      <c r="AN158" s="3" t="n"/>
+      <c r="AT158" s="3" t="n"/>
+      <c r="AU158" s="3" t="n"/>
+      <c r="AV158" s="3" t="n"/>
+      <c r="AW158" s="3" t="n"/>
+      <c r="AX158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -5591,10 +8107,10 @@
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="C159" s="3" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
@@ -5609,12 +8125,28 @@
       <c r="H159" s="3" t="n"/>
       <c r="I159" s="3" t="n"/>
       <c r="J159" s="3" t="n"/>
+      <c r="K159" s="3" t="n"/>
       <c r="L159" s="3" t="n"/>
       <c r="M159" s="3" t="n"/>
       <c r="Q159" s="3" t="n"/>
       <c r="R159" s="3" t="n"/>
       <c r="S159" s="3" t="n"/>
       <c r="T159" s="3" t="n"/>
+      <c r="Z159" s="3" t="n"/>
+      <c r="AA159" s="3" t="n"/>
+      <c r="AB159" s="3" t="n"/>
+      <c r="AC159" s="3" t="n"/>
+      <c r="AD159" s="3" t="n"/>
+      <c r="AJ159" s="3" t="n"/>
+      <c r="AK159" s="3" t="n"/>
+      <c r="AL159" s="3" t="n"/>
+      <c r="AM159" s="3" t="n"/>
+      <c r="AN159" s="3" t="n"/>
+      <c r="AT159" s="3" t="n"/>
+      <c r="AU159" s="3" t="n"/>
+      <c r="AV159" s="3" t="n"/>
+      <c r="AW159" s="3" t="n"/>
+      <c r="AX159" s="3" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -5623,10 +8155,10 @@
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="C160" s="3" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
@@ -5641,12 +8173,28 @@
       <c r="H160" s="3" t="n"/>
       <c r="I160" s="3" t="n"/>
       <c r="J160" s="3" t="n"/>
+      <c r="K160" s="3" t="n"/>
       <c r="L160" s="3" t="n"/>
       <c r="M160" s="3" t="n"/>
       <c r="Q160" s="3" t="n"/>
       <c r="R160" s="3" t="n"/>
       <c r="S160" s="3" t="n"/>
       <c r="T160" s="3" t="n"/>
+      <c r="Z160" s="3" t="n"/>
+      <c r="AA160" s="3" t="n"/>
+      <c r="AB160" s="3" t="n"/>
+      <c r="AC160" s="3" t="n"/>
+      <c r="AD160" s="3" t="n"/>
+      <c r="AJ160" s="3" t="n"/>
+      <c r="AK160" s="3" t="n"/>
+      <c r="AL160" s="3" t="n"/>
+      <c r="AM160" s="3" t="n"/>
+      <c r="AN160" s="3" t="n"/>
+      <c r="AT160" s="3" t="n"/>
+      <c r="AU160" s="3" t="n"/>
+      <c r="AV160" s="3" t="n"/>
+      <c r="AW160" s="3" t="n"/>
+      <c r="AX160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -5655,7 +8203,7 @@
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>19.5</v>
+        <v>20.68</v>
       </c>
       <c r="C161" s="3" t="inlineStr"/>
       <c r="D161" s="3" t="inlineStr">
@@ -5671,12 +8219,28 @@
       <c r="H161" s="3" t="n"/>
       <c r="I161" s="3" t="n"/>
       <c r="J161" s="3" t="n"/>
+      <c r="K161" s="3" t="n"/>
       <c r="L161" s="3" t="n"/>
       <c r="M161" s="3" t="n"/>
       <c r="Q161" s="3" t="n"/>
       <c r="R161" s="3" t="n"/>
       <c r="S161" s="3" t="n"/>
       <c r="T161" s="3" t="n"/>
+      <c r="Z161" s="3" t="n"/>
+      <c r="AA161" s="3" t="n"/>
+      <c r="AB161" s="3" t="n"/>
+      <c r="AC161" s="3" t="n"/>
+      <c r="AD161" s="3" t="n"/>
+      <c r="AJ161" s="3" t="n"/>
+      <c r="AK161" s="3" t="n"/>
+      <c r="AL161" s="3" t="n"/>
+      <c r="AM161" s="3" t="n"/>
+      <c r="AN161" s="3" t="n"/>
+      <c r="AT161" s="3" t="n"/>
+      <c r="AU161" s="3" t="n"/>
+      <c r="AV161" s="3" t="n"/>
+      <c r="AW161" s="3" t="n"/>
+      <c r="AX161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
@@ -5685,7 +8249,7 @@
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="C162" s="3" t="n">
         <v>0.92</v>
@@ -5703,12 +8267,28 @@
       <c r="H162" s="3" t="n"/>
       <c r="I162" s="3" t="n"/>
       <c r="J162" s="3" t="n"/>
+      <c r="K162" s="3" t="n"/>
       <c r="L162" s="3" t="n"/>
       <c r="M162" s="3" t="n"/>
       <c r="Q162" s="3" t="n"/>
       <c r="R162" s="3" t="n"/>
       <c r="S162" s="3" t="n"/>
       <c r="T162" s="3" t="n"/>
+      <c r="Z162" s="3" t="n"/>
+      <c r="AA162" s="3" t="n"/>
+      <c r="AB162" s="3" t="n"/>
+      <c r="AC162" s="3" t="n"/>
+      <c r="AD162" s="3" t="n"/>
+      <c r="AJ162" s="3" t="n"/>
+      <c r="AK162" s="3" t="n"/>
+      <c r="AL162" s="3" t="n"/>
+      <c r="AM162" s="3" t="n"/>
+      <c r="AN162" s="3" t="n"/>
+      <c r="AT162" s="3" t="n"/>
+      <c r="AU162" s="3" t="n"/>
+      <c r="AV162" s="3" t="n"/>
+      <c r="AW162" s="3" t="n"/>
+      <c r="AX162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -5717,10 +8297,10 @@
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C163" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
@@ -5735,12 +8315,28 @@
       <c r="H163" s="3" t="n"/>
       <c r="I163" s="3" t="n"/>
       <c r="J163" s="3" t="n"/>
+      <c r="K163" s="3" t="n"/>
       <c r="L163" s="3" t="n"/>
       <c r="M163" s="3" t="n"/>
       <c r="Q163" s="3" t="n"/>
       <c r="R163" s="3" t="n"/>
       <c r="S163" s="3" t="n"/>
       <c r="T163" s="3" t="n"/>
+      <c r="Z163" s="3" t="n"/>
+      <c r="AA163" s="3" t="n"/>
+      <c r="AB163" s="3" t="n"/>
+      <c r="AC163" s="3" t="n"/>
+      <c r="AD163" s="3" t="n"/>
+      <c r="AJ163" s="3" t="n"/>
+      <c r="AK163" s="3" t="n"/>
+      <c r="AL163" s="3" t="n"/>
+      <c r="AM163" s="3" t="n"/>
+      <c r="AN163" s="3" t="n"/>
+      <c r="AT163" s="3" t="n"/>
+      <c r="AU163" s="3" t="n"/>
+      <c r="AV163" s="3" t="n"/>
+      <c r="AW163" s="3" t="n"/>
+      <c r="AX163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -5749,10 +8345,10 @@
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C164" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
@@ -5767,12 +8363,28 @@
       <c r="H164" s="3" t="n"/>
       <c r="I164" s="3" t="n"/>
       <c r="J164" s="3" t="n"/>
+      <c r="K164" s="3" t="n"/>
       <c r="L164" s="3" t="n"/>
       <c r="M164" s="3" t="n"/>
       <c r="Q164" s="3" t="n"/>
       <c r="R164" s="3" t="n"/>
       <c r="S164" s="3" t="n"/>
       <c r="T164" s="3" t="n"/>
+      <c r="Z164" s="3" t="n"/>
+      <c r="AA164" s="3" t="n"/>
+      <c r="AB164" s="3" t="n"/>
+      <c r="AC164" s="3" t="n"/>
+      <c r="AD164" s="3" t="n"/>
+      <c r="AJ164" s="3" t="n"/>
+      <c r="AK164" s="3" t="n"/>
+      <c r="AL164" s="3" t="n"/>
+      <c r="AM164" s="3" t="n"/>
+      <c r="AN164" s="3" t="n"/>
+      <c r="AT164" s="3" t="n"/>
+      <c r="AU164" s="3" t="n"/>
+      <c r="AV164" s="3" t="n"/>
+      <c r="AW164" s="3" t="n"/>
+      <c r="AX164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -5781,10 +8393,10 @@
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="C165" s="3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
@@ -5799,12 +8411,28 @@
       <c r="H165" s="3" t="n"/>
       <c r="I165" s="3" t="n"/>
       <c r="J165" s="3" t="n"/>
+      <c r="K165" s="3" t="n"/>
       <c r="L165" s="3" t="n"/>
       <c r="M165" s="3" t="n"/>
       <c r="Q165" s="3" t="n"/>
       <c r="R165" s="3" t="n"/>
       <c r="S165" s="3" t="n"/>
       <c r="T165" s="3" t="n"/>
+      <c r="Z165" s="3" t="n"/>
+      <c r="AA165" s="3" t="n"/>
+      <c r="AB165" s="3" t="n"/>
+      <c r="AC165" s="3" t="n"/>
+      <c r="AD165" s="3" t="n"/>
+      <c r="AJ165" s="3" t="n"/>
+      <c r="AK165" s="3" t="n"/>
+      <c r="AL165" s="3" t="n"/>
+      <c r="AM165" s="3" t="n"/>
+      <c r="AN165" s="3" t="n"/>
+      <c r="AT165" s="3" t="n"/>
+      <c r="AU165" s="3" t="n"/>
+      <c r="AV165" s="3" t="n"/>
+      <c r="AW165" s="3" t="n"/>
+      <c r="AX165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -5813,10 +8441,10 @@
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="C166" s="3" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
@@ -5831,12 +8459,28 @@
       <c r="H166" s="3" t="n"/>
       <c r="I166" s="3" t="n"/>
       <c r="J166" s="3" t="n"/>
+      <c r="K166" s="3" t="n"/>
       <c r="L166" s="3" t="n"/>
       <c r="M166" s="3" t="n"/>
       <c r="Q166" s="3" t="n"/>
       <c r="R166" s="3" t="n"/>
       <c r="S166" s="3" t="n"/>
       <c r="T166" s="3" t="n"/>
+      <c r="Z166" s="3" t="n"/>
+      <c r="AA166" s="3" t="n"/>
+      <c r="AB166" s="3" t="n"/>
+      <c r="AC166" s="3" t="n"/>
+      <c r="AD166" s="3" t="n"/>
+      <c r="AJ166" s="3" t="n"/>
+      <c r="AK166" s="3" t="n"/>
+      <c r="AL166" s="3" t="n"/>
+      <c r="AM166" s="3" t="n"/>
+      <c r="AN166" s="3" t="n"/>
+      <c r="AT166" s="3" t="n"/>
+      <c r="AU166" s="3" t="n"/>
+      <c r="AV166" s="3" t="n"/>
+      <c r="AW166" s="3" t="n"/>
+      <c r="AX166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -5848,7 +8492,7 @@
         <v>0.06</v>
       </c>
       <c r="C167" s="3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
@@ -5863,12 +8507,28 @@
       <c r="H167" s="3" t="n"/>
       <c r="I167" s="3" t="n"/>
       <c r="J167" s="3" t="n"/>
+      <c r="K167" s="3" t="n"/>
       <c r="L167" s="3" t="n"/>
       <c r="M167" s="3" t="n"/>
       <c r="Q167" s="3" t="n"/>
       <c r="R167" s="3" t="n"/>
       <c r="S167" s="3" t="n"/>
       <c r="T167" s="3" t="n"/>
+      <c r="Z167" s="3" t="n"/>
+      <c r="AA167" s="3" t="n"/>
+      <c r="AB167" s="3" t="n"/>
+      <c r="AC167" s="3" t="n"/>
+      <c r="AD167" s="3" t="n"/>
+      <c r="AJ167" s="3" t="n"/>
+      <c r="AK167" s="3" t="n"/>
+      <c r="AL167" s="3" t="n"/>
+      <c r="AM167" s="3" t="n"/>
+      <c r="AN167" s="3" t="n"/>
+      <c r="AT167" s="3" t="n"/>
+      <c r="AU167" s="3" t="n"/>
+      <c r="AV167" s="3" t="n"/>
+      <c r="AW167" s="3" t="n"/>
+      <c r="AX167" s="3" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
@@ -5877,10 +8537,10 @@
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="C168" s="3" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
@@ -5895,12 +8555,28 @@
       <c r="H168" s="3" t="n"/>
       <c r="I168" s="3" t="n"/>
       <c r="J168" s="3" t="n"/>
+      <c r="K168" s="3" t="n"/>
       <c r="L168" s="3" t="n"/>
       <c r="M168" s="3" t="n"/>
       <c r="Q168" s="3" t="n"/>
       <c r="R168" s="3" t="n"/>
       <c r="S168" s="3" t="n"/>
       <c r="T168" s="3" t="n"/>
+      <c r="Z168" s="3" t="n"/>
+      <c r="AA168" s="3" t="n"/>
+      <c r="AB168" s="3" t="n"/>
+      <c r="AC168" s="3" t="n"/>
+      <c r="AD168" s="3" t="n"/>
+      <c r="AJ168" s="3" t="n"/>
+      <c r="AK168" s="3" t="n"/>
+      <c r="AL168" s="3" t="n"/>
+      <c r="AM168" s="3" t="n"/>
+      <c r="AN168" s="3" t="n"/>
+      <c r="AT168" s="3" t="n"/>
+      <c r="AU168" s="3" t="n"/>
+      <c r="AV168" s="3" t="n"/>
+      <c r="AW168" s="3" t="n"/>
+      <c r="AX168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
@@ -5909,10 +8585,10 @@
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="C169" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
@@ -5927,12 +8603,28 @@
       <c r="H169" s="3" t="n"/>
       <c r="I169" s="3" t="n"/>
       <c r="J169" s="3" t="n"/>
+      <c r="K169" s="3" t="n"/>
       <c r="L169" s="3" t="n"/>
       <c r="M169" s="3" t="n"/>
       <c r="Q169" s="3" t="n"/>
       <c r="R169" s="3" t="n"/>
       <c r="S169" s="3" t="n"/>
       <c r="T169" s="3" t="n"/>
+      <c r="Z169" s="3" t="n"/>
+      <c r="AA169" s="3" t="n"/>
+      <c r="AB169" s="3" t="n"/>
+      <c r="AC169" s="3" t="n"/>
+      <c r="AD169" s="3" t="n"/>
+      <c r="AJ169" s="3" t="n"/>
+      <c r="AK169" s="3" t="n"/>
+      <c r="AL169" s="3" t="n"/>
+      <c r="AM169" s="3" t="n"/>
+      <c r="AN169" s="3" t="n"/>
+      <c r="AT169" s="3" t="n"/>
+      <c r="AU169" s="3" t="n"/>
+      <c r="AV169" s="3" t="n"/>
+      <c r="AW169" s="3" t="n"/>
+      <c r="AX169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -5944,7 +8636,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C170" s="3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
@@ -5959,12 +8651,28 @@
       <c r="H170" s="3" t="n"/>
       <c r="I170" s="3" t="n"/>
       <c r="J170" s="3" t="n"/>
+      <c r="K170" s="3" t="n"/>
       <c r="L170" s="3" t="n"/>
       <c r="M170" s="3" t="n"/>
       <c r="Q170" s="3" t="n"/>
       <c r="R170" s="3" t="n"/>
       <c r="S170" s="3" t="n"/>
       <c r="T170" s="3" t="n"/>
+      <c r="Z170" s="3" t="n"/>
+      <c r="AA170" s="3" t="n"/>
+      <c r="AB170" s="3" t="n"/>
+      <c r="AC170" s="3" t="n"/>
+      <c r="AD170" s="3" t="n"/>
+      <c r="AJ170" s="3" t="n"/>
+      <c r="AK170" s="3" t="n"/>
+      <c r="AL170" s="3" t="n"/>
+      <c r="AM170" s="3" t="n"/>
+      <c r="AN170" s="3" t="n"/>
+      <c r="AT170" s="3" t="n"/>
+      <c r="AU170" s="3" t="n"/>
+      <c r="AV170" s="3" t="n"/>
+      <c r="AW170" s="3" t="n"/>
+      <c r="AX170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -5973,7 +8681,7 @@
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="C171" s="3" t="n">
         <v>2.44</v>
@@ -5991,12 +8699,28 @@
       <c r="H171" s="3" t="n"/>
       <c r="I171" s="3" t="n"/>
       <c r="J171" s="3" t="n"/>
+      <c r="K171" s="3" t="n"/>
       <c r="L171" s="3" t="n"/>
       <c r="M171" s="3" t="n"/>
       <c r="Q171" s="3" t="n"/>
       <c r="R171" s="3" t="n"/>
       <c r="S171" s="3" t="n"/>
       <c r="T171" s="3" t="n"/>
+      <c r="Z171" s="3" t="n"/>
+      <c r="AA171" s="3" t="n"/>
+      <c r="AB171" s="3" t="n"/>
+      <c r="AC171" s="3" t="n"/>
+      <c r="AD171" s="3" t="n"/>
+      <c r="AJ171" s="3" t="n"/>
+      <c r="AK171" s="3" t="n"/>
+      <c r="AL171" s="3" t="n"/>
+      <c r="AM171" s="3" t="n"/>
+      <c r="AN171" s="3" t="n"/>
+      <c r="AT171" s="3" t="n"/>
+      <c r="AU171" s="3" t="n"/>
+      <c r="AV171" s="3" t="n"/>
+      <c r="AW171" s="3" t="n"/>
+      <c r="AX171" s="3" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -6008,7 +8732,7 @@
         <v>0.06</v>
       </c>
       <c r="C172" s="3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
@@ -6023,12 +8747,28 @@
       <c r="H172" s="3" t="n"/>
       <c r="I172" s="3" t="n"/>
       <c r="J172" s="3" t="n"/>
+      <c r="K172" s="3" t="n"/>
       <c r="L172" s="3" t="n"/>
       <c r="M172" s="3" t="n"/>
       <c r="Q172" s="3" t="n"/>
       <c r="R172" s="3" t="n"/>
       <c r="S172" s="3" t="n"/>
       <c r="T172" s="3" t="n"/>
+      <c r="Z172" s="3" t="n"/>
+      <c r="AA172" s="3" t="n"/>
+      <c r="AB172" s="3" t="n"/>
+      <c r="AC172" s="3" t="n"/>
+      <c r="AD172" s="3" t="n"/>
+      <c r="AJ172" s="3" t="n"/>
+      <c r="AK172" s="3" t="n"/>
+      <c r="AL172" s="3" t="n"/>
+      <c r="AM172" s="3" t="n"/>
+      <c r="AN172" s="3" t="n"/>
+      <c r="AT172" s="3" t="n"/>
+      <c r="AU172" s="3" t="n"/>
+      <c r="AV172" s="3" t="n"/>
+      <c r="AW172" s="3" t="n"/>
+      <c r="AX172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -6040,7 +8780,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C173" s="3" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
@@ -6055,12 +8795,28 @@
       <c r="H173" s="3" t="n"/>
       <c r="I173" s="3" t="n"/>
       <c r="J173" s="3" t="n"/>
+      <c r="K173" s="3" t="n"/>
       <c r="L173" s="3" t="n"/>
       <c r="M173" s="3" t="n"/>
       <c r="Q173" s="3" t="n"/>
       <c r="R173" s="3" t="n"/>
       <c r="S173" s="3" t="n"/>
       <c r="T173" s="3" t="n"/>
+      <c r="Z173" s="3" t="n"/>
+      <c r="AA173" s="3" t="n"/>
+      <c r="AB173" s="3" t="n"/>
+      <c r="AC173" s="3" t="n"/>
+      <c r="AD173" s="3" t="n"/>
+      <c r="AJ173" s="3" t="n"/>
+      <c r="AK173" s="3" t="n"/>
+      <c r="AL173" s="3" t="n"/>
+      <c r="AM173" s="3" t="n"/>
+      <c r="AN173" s="3" t="n"/>
+      <c r="AT173" s="3" t="n"/>
+      <c r="AU173" s="3" t="n"/>
+      <c r="AV173" s="3" t="n"/>
+      <c r="AW173" s="3" t="n"/>
+      <c r="AX173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -6069,10 +8825,10 @@
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="C174" s="3" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
@@ -6087,12 +8843,28 @@
       <c r="H174" s="3" t="n"/>
       <c r="I174" s="3" t="n"/>
       <c r="J174" s="3" t="n"/>
+      <c r="K174" s="3" t="n"/>
       <c r="L174" s="3" t="n"/>
       <c r="M174" s="3" t="n"/>
       <c r="Q174" s="3" t="n"/>
       <c r="R174" s="3" t="n"/>
       <c r="S174" s="3" t="n"/>
       <c r="T174" s="3" t="n"/>
+      <c r="Z174" s="3" t="n"/>
+      <c r="AA174" s="3" t="n"/>
+      <c r="AB174" s="3" t="n"/>
+      <c r="AC174" s="3" t="n"/>
+      <c r="AD174" s="3" t="n"/>
+      <c r="AJ174" s="3" t="n"/>
+      <c r="AK174" s="3" t="n"/>
+      <c r="AL174" s="3" t="n"/>
+      <c r="AM174" s="3" t="n"/>
+      <c r="AN174" s="3" t="n"/>
+      <c r="AT174" s="3" t="n"/>
+      <c r="AU174" s="3" t="n"/>
+      <c r="AV174" s="3" t="n"/>
+      <c r="AW174" s="3" t="n"/>
+      <c r="AX174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -6119,12 +8891,28 @@
       <c r="H175" s="3" t="n"/>
       <c r="I175" s="3" t="n"/>
       <c r="J175" s="3" t="n"/>
+      <c r="K175" s="3" t="n"/>
       <c r="L175" s="3" t="n"/>
       <c r="M175" s="3" t="n"/>
       <c r="Q175" s="3" t="n"/>
       <c r="R175" s="3" t="n"/>
       <c r="S175" s="3" t="n"/>
       <c r="T175" s="3" t="n"/>
+      <c r="Z175" s="3" t="n"/>
+      <c r="AA175" s="3" t="n"/>
+      <c r="AB175" s="3" t="n"/>
+      <c r="AC175" s="3" t="n"/>
+      <c r="AD175" s="3" t="n"/>
+      <c r="AJ175" s="3" t="n"/>
+      <c r="AK175" s="3" t="n"/>
+      <c r="AL175" s="3" t="n"/>
+      <c r="AM175" s="3" t="n"/>
+      <c r="AN175" s="3" t="n"/>
+      <c r="AT175" s="3" t="n"/>
+      <c r="AU175" s="3" t="n"/>
+      <c r="AV175" s="3" t="n"/>
+      <c r="AW175" s="3" t="n"/>
+      <c r="AX175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
@@ -6133,10 +8921,10 @@
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C176" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
@@ -6151,12 +8939,28 @@
       <c r="H176" s="3" t="n"/>
       <c r="I176" s="3" t="n"/>
       <c r="J176" s="3" t="n"/>
+      <c r="K176" s="3" t="n"/>
       <c r="L176" s="3" t="n"/>
       <c r="M176" s="3" t="n"/>
       <c r="Q176" s="3" t="n"/>
       <c r="R176" s="3" t="n"/>
       <c r="S176" s="3" t="n"/>
       <c r="T176" s="3" t="n"/>
+      <c r="Z176" s="3" t="n"/>
+      <c r="AA176" s="3" t="n"/>
+      <c r="AB176" s="3" t="n"/>
+      <c r="AC176" s="3" t="n"/>
+      <c r="AD176" s="3" t="n"/>
+      <c r="AJ176" s="3" t="n"/>
+      <c r="AK176" s="3" t="n"/>
+      <c r="AL176" s="3" t="n"/>
+      <c r="AM176" s="3" t="n"/>
+      <c r="AN176" s="3" t="n"/>
+      <c r="AT176" s="3" t="n"/>
+      <c r="AU176" s="3" t="n"/>
+      <c r="AV176" s="3" t="n"/>
+      <c r="AW176" s="3" t="n"/>
+      <c r="AX176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -6168,7 +8972,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C177" s="3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
@@ -6183,12 +8987,28 @@
       <c r="H177" s="3" t="n"/>
       <c r="I177" s="3" t="n"/>
       <c r="J177" s="3" t="n"/>
+      <c r="K177" s="3" t="n"/>
       <c r="L177" s="3" t="n"/>
       <c r="M177" s="3" t="n"/>
       <c r="Q177" s="3" t="n"/>
       <c r="R177" s="3" t="n"/>
       <c r="S177" s="3" t="n"/>
       <c r="T177" s="3" t="n"/>
+      <c r="Z177" s="3" t="n"/>
+      <c r="AA177" s="3" t="n"/>
+      <c r="AB177" s="3" t="n"/>
+      <c r="AC177" s="3" t="n"/>
+      <c r="AD177" s="3" t="n"/>
+      <c r="AJ177" s="3" t="n"/>
+      <c r="AK177" s="3" t="n"/>
+      <c r="AL177" s="3" t="n"/>
+      <c r="AM177" s="3" t="n"/>
+      <c r="AN177" s="3" t="n"/>
+      <c r="AT177" s="3" t="n"/>
+      <c r="AU177" s="3" t="n"/>
+      <c r="AV177" s="3" t="n"/>
+      <c r="AW177" s="3" t="n"/>
+      <c r="AX177" s="3" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -6197,10 +9017,10 @@
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="C178" s="3" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
@@ -6215,12 +9035,28 @@
       <c r="H178" s="3" t="n"/>
       <c r="I178" s="3" t="n"/>
       <c r="J178" s="3" t="n"/>
+      <c r="K178" s="3" t="n"/>
       <c r="L178" s="3" t="n"/>
       <c r="M178" s="3" t="n"/>
       <c r="Q178" s="3" t="n"/>
       <c r="R178" s="3" t="n"/>
       <c r="S178" s="3" t="n"/>
       <c r="T178" s="3" t="n"/>
+      <c r="Z178" s="3" t="n"/>
+      <c r="AA178" s="3" t="n"/>
+      <c r="AB178" s="3" t="n"/>
+      <c r="AC178" s="3" t="n"/>
+      <c r="AD178" s="3" t="n"/>
+      <c r="AJ178" s="3" t="n"/>
+      <c r="AK178" s="3" t="n"/>
+      <c r="AL178" s="3" t="n"/>
+      <c r="AM178" s="3" t="n"/>
+      <c r="AN178" s="3" t="n"/>
+      <c r="AT178" s="3" t="n"/>
+      <c r="AU178" s="3" t="n"/>
+      <c r="AV178" s="3" t="n"/>
+      <c r="AW178" s="3" t="n"/>
+      <c r="AX178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -6232,7 +9068,7 @@
         <v>0.06</v>
       </c>
       <c r="C179" s="3" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
@@ -6247,12 +9083,28 @@
       <c r="H179" s="3" t="n"/>
       <c r="I179" s="3" t="n"/>
       <c r="J179" s="3" t="n"/>
+      <c r="K179" s="3" t="n"/>
       <c r="L179" s="3" t="n"/>
       <c r="M179" s="3" t="n"/>
       <c r="Q179" s="3" t="n"/>
       <c r="R179" s="3" t="n"/>
       <c r="S179" s="3" t="n"/>
       <c r="T179" s="3" t="n"/>
+      <c r="Z179" s="3" t="n"/>
+      <c r="AA179" s="3" t="n"/>
+      <c r="AB179" s="3" t="n"/>
+      <c r="AC179" s="3" t="n"/>
+      <c r="AD179" s="3" t="n"/>
+      <c r="AJ179" s="3" t="n"/>
+      <c r="AK179" s="3" t="n"/>
+      <c r="AL179" s="3" t="n"/>
+      <c r="AM179" s="3" t="n"/>
+      <c r="AN179" s="3" t="n"/>
+      <c r="AT179" s="3" t="n"/>
+      <c r="AU179" s="3" t="n"/>
+      <c r="AV179" s="3" t="n"/>
+      <c r="AW179" s="3" t="n"/>
+      <c r="AX179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -6261,10 +9113,10 @@
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C180" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
@@ -6279,12 +9131,28 @@
       <c r="H180" s="3" t="n"/>
       <c r="I180" s="3" t="n"/>
       <c r="J180" s="3" t="n"/>
+      <c r="K180" s="3" t="n"/>
       <c r="L180" s="3" t="n"/>
       <c r="M180" s="3" t="n"/>
       <c r="Q180" s="3" t="n"/>
       <c r="R180" s="3" t="n"/>
       <c r="S180" s="3" t="n"/>
       <c r="T180" s="3" t="n"/>
+      <c r="Z180" s="3" t="n"/>
+      <c r="AA180" s="3" t="n"/>
+      <c r="AB180" s="3" t="n"/>
+      <c r="AC180" s="3" t="n"/>
+      <c r="AD180" s="3" t="n"/>
+      <c r="AJ180" s="3" t="n"/>
+      <c r="AK180" s="3" t="n"/>
+      <c r="AL180" s="3" t="n"/>
+      <c r="AM180" s="3" t="n"/>
+      <c r="AN180" s="3" t="n"/>
+      <c r="AT180" s="3" t="n"/>
+      <c r="AU180" s="3" t="n"/>
+      <c r="AV180" s="3" t="n"/>
+      <c r="AW180" s="3" t="n"/>
+      <c r="AX180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -6293,7 +9161,7 @@
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>45.29</v>
+        <v>44.39</v>
       </c>
       <c r="C181" s="3" t="inlineStr"/>
       <c r="D181" s="3" t="inlineStr">
@@ -6309,12 +9177,28 @@
       <c r="H181" s="3" t="n"/>
       <c r="I181" s="3" t="n"/>
       <c r="J181" s="3" t="n"/>
+      <c r="K181" s="3" t="n"/>
       <c r="L181" s="3" t="n"/>
       <c r="M181" s="3" t="n"/>
       <c r="Q181" s="3" t="n"/>
       <c r="R181" s="3" t="n"/>
       <c r="S181" s="3" t="n"/>
       <c r="T181" s="3" t="n"/>
+      <c r="Z181" s="3" t="n"/>
+      <c r="AA181" s="3" t="n"/>
+      <c r="AB181" s="3" t="n"/>
+      <c r="AC181" s="3" t="n"/>
+      <c r="AD181" s="3" t="n"/>
+      <c r="AJ181" s="3" t="n"/>
+      <c r="AK181" s="3" t="n"/>
+      <c r="AL181" s="3" t="n"/>
+      <c r="AM181" s="3" t="n"/>
+      <c r="AN181" s="3" t="n"/>
+      <c r="AT181" s="3" t="n"/>
+      <c r="AU181" s="3" t="n"/>
+      <c r="AV181" s="3" t="n"/>
+      <c r="AW181" s="3" t="n"/>
+      <c r="AX181" s="3" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
@@ -6323,10 +9207,10 @@
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="C182" s="3" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
@@ -6341,12 +9225,28 @@
       <c r="H182" s="3" t="n"/>
       <c r="I182" s="3" t="n"/>
       <c r="J182" s="3" t="n"/>
+      <c r="K182" s="3" t="n"/>
       <c r="L182" s="3" t="n"/>
       <c r="M182" s="3" t="n"/>
       <c r="Q182" s="3" t="n"/>
       <c r="R182" s="3" t="n"/>
       <c r="S182" s="3" t="n"/>
       <c r="T182" s="3" t="n"/>
+      <c r="Z182" s="3" t="n"/>
+      <c r="AA182" s="3" t="n"/>
+      <c r="AB182" s="3" t="n"/>
+      <c r="AC182" s="3" t="n"/>
+      <c r="AD182" s="3" t="n"/>
+      <c r="AJ182" s="3" t="n"/>
+      <c r="AK182" s="3" t="n"/>
+      <c r="AL182" s="3" t="n"/>
+      <c r="AM182" s="3" t="n"/>
+      <c r="AN182" s="3" t="n"/>
+      <c r="AT182" s="3" t="n"/>
+      <c r="AU182" s="3" t="n"/>
+      <c r="AV182" s="3" t="n"/>
+      <c r="AW182" s="3" t="n"/>
+      <c r="AX182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -6355,10 +9255,10 @@
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="C183" s="3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
@@ -6373,12 +9273,28 @@
       <c r="H183" s="3" t="n"/>
       <c r="I183" s="3" t="n"/>
       <c r="J183" s="3" t="n"/>
+      <c r="K183" s="3" t="n"/>
       <c r="L183" s="3" t="n"/>
       <c r="M183" s="3" t="n"/>
       <c r="Q183" s="3" t="n"/>
       <c r="R183" s="3" t="n"/>
       <c r="S183" s="3" t="n"/>
       <c r="T183" s="3" t="n"/>
+      <c r="Z183" s="3" t="n"/>
+      <c r="AA183" s="3" t="n"/>
+      <c r="AB183" s="3" t="n"/>
+      <c r="AC183" s="3" t="n"/>
+      <c r="AD183" s="3" t="n"/>
+      <c r="AJ183" s="3" t="n"/>
+      <c r="AK183" s="3" t="n"/>
+      <c r="AL183" s="3" t="n"/>
+      <c r="AM183" s="3" t="n"/>
+      <c r="AN183" s="3" t="n"/>
+      <c r="AT183" s="3" t="n"/>
+      <c r="AU183" s="3" t="n"/>
+      <c r="AV183" s="3" t="n"/>
+      <c r="AW183" s="3" t="n"/>
+      <c r="AX183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -6387,7 +9303,7 @@
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="C184" s="3" t="inlineStr"/>
       <c r="D184" s="3" t="inlineStr">
@@ -6403,12 +9319,28 @@
       <c r="H184" s="3" t="n"/>
       <c r="I184" s="3" t="n"/>
       <c r="J184" s="3" t="n"/>
+      <c r="K184" s="3" t="n"/>
       <c r="L184" s="3" t="n"/>
       <c r="M184" s="3" t="n"/>
       <c r="Q184" s="3" t="n"/>
       <c r="R184" s="3" t="n"/>
       <c r="S184" s="3" t="n"/>
       <c r="T184" s="3" t="n"/>
+      <c r="Z184" s="3" t="n"/>
+      <c r="AA184" s="3" t="n"/>
+      <c r="AB184" s="3" t="n"/>
+      <c r="AC184" s="3" t="n"/>
+      <c r="AD184" s="3" t="n"/>
+      <c r="AJ184" s="3" t="n"/>
+      <c r="AK184" s="3" t="n"/>
+      <c r="AL184" s="3" t="n"/>
+      <c r="AM184" s="3" t="n"/>
+      <c r="AN184" s="3" t="n"/>
+      <c r="AT184" s="3" t="n"/>
+      <c r="AU184" s="3" t="n"/>
+      <c r="AV184" s="3" t="n"/>
+      <c r="AW184" s="3" t="n"/>
+      <c r="AX184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -6417,7 +9349,7 @@
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="C185" s="3" t="n">
         <v>0.17</v>
@@ -6435,12 +9367,28 @@
       <c r="H185" s="3" t="n"/>
       <c r="I185" s="3" t="n"/>
       <c r="J185" s="3" t="n"/>
+      <c r="K185" s="3" t="n"/>
       <c r="L185" s="3" t="n"/>
       <c r="M185" s="3" t="n"/>
       <c r="Q185" s="3" t="n"/>
       <c r="R185" s="3" t="n"/>
       <c r="S185" s="3" t="n"/>
       <c r="T185" s="3" t="n"/>
+      <c r="Z185" s="3" t="n"/>
+      <c r="AA185" s="3" t="n"/>
+      <c r="AB185" s="3" t="n"/>
+      <c r="AC185" s="3" t="n"/>
+      <c r="AD185" s="3" t="n"/>
+      <c r="AJ185" s="3" t="n"/>
+      <c r="AK185" s="3" t="n"/>
+      <c r="AL185" s="3" t="n"/>
+      <c r="AM185" s="3" t="n"/>
+      <c r="AN185" s="3" t="n"/>
+      <c r="AT185" s="3" t="n"/>
+      <c r="AU185" s="3" t="n"/>
+      <c r="AV185" s="3" t="n"/>
+      <c r="AW185" s="3" t="n"/>
+      <c r="AX185" s="3" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -6449,7 +9397,7 @@
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>6.74</v>
+        <v>6.71</v>
       </c>
       <c r="C186" s="3" t="inlineStr"/>
       <c r="D186" s="3" t="inlineStr">
@@ -6465,12 +9413,28 @@
       <c r="H186" s="3" t="n"/>
       <c r="I186" s="3" t="n"/>
       <c r="J186" s="3" t="n"/>
+      <c r="K186" s="3" t="n"/>
       <c r="L186" s="3" t="n"/>
       <c r="M186" s="3" t="n"/>
       <c r="Q186" s="3" t="n"/>
       <c r="R186" s="3" t="n"/>
       <c r="S186" s="3" t="n"/>
       <c r="T186" s="3" t="n"/>
+      <c r="Z186" s="3" t="n"/>
+      <c r="AA186" s="3" t="n"/>
+      <c r="AB186" s="3" t="n"/>
+      <c r="AC186" s="3" t="n"/>
+      <c r="AD186" s="3" t="n"/>
+      <c r="AJ186" s="3" t="n"/>
+      <c r="AK186" s="3" t="n"/>
+      <c r="AL186" s="3" t="n"/>
+      <c r="AM186" s="3" t="n"/>
+      <c r="AN186" s="3" t="n"/>
+      <c r="AT186" s="3" t="n"/>
+      <c r="AU186" s="3" t="n"/>
+      <c r="AV186" s="3" t="n"/>
+      <c r="AW186" s="3" t="n"/>
+      <c r="AX186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -6479,10 +9443,10 @@
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C187" s="3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
@@ -6497,12 +9461,28 @@
       <c r="H187" s="3" t="n"/>
       <c r="I187" s="3" t="n"/>
       <c r="J187" s="3" t="n"/>
+      <c r="K187" s="3" t="n"/>
       <c r="L187" s="3" t="n"/>
       <c r="M187" s="3" t="n"/>
       <c r="Q187" s="3" t="n"/>
       <c r="R187" s="3" t="n"/>
       <c r="S187" s="3" t="n"/>
       <c r="T187" s="3" t="n"/>
+      <c r="Z187" s="3" t="n"/>
+      <c r="AA187" s="3" t="n"/>
+      <c r="AB187" s="3" t="n"/>
+      <c r="AC187" s="3" t="n"/>
+      <c r="AD187" s="3" t="n"/>
+      <c r="AJ187" s="3" t="n"/>
+      <c r="AK187" s="3" t="n"/>
+      <c r="AL187" s="3" t="n"/>
+      <c r="AM187" s="3" t="n"/>
+      <c r="AN187" s="3" t="n"/>
+      <c r="AT187" s="3" t="n"/>
+      <c r="AU187" s="3" t="n"/>
+      <c r="AV187" s="3" t="n"/>
+      <c r="AW187" s="3" t="n"/>
+      <c r="AX187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -6514,7 +9494,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C188" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
@@ -6529,12 +9509,28 @@
       <c r="H188" s="3" t="n"/>
       <c r="I188" s="3" t="n"/>
       <c r="J188" s="3" t="n"/>
+      <c r="K188" s="3" t="n"/>
       <c r="L188" s="3" t="n"/>
       <c r="M188" s="3" t="n"/>
       <c r="Q188" s="3" t="n"/>
       <c r="R188" s="3" t="n"/>
       <c r="S188" s="3" t="n"/>
       <c r="T188" s="3" t="n"/>
+      <c r="Z188" s="3" t="n"/>
+      <c r="AA188" s="3" t="n"/>
+      <c r="AB188" s="3" t="n"/>
+      <c r="AC188" s="3" t="n"/>
+      <c r="AD188" s="3" t="n"/>
+      <c r="AJ188" s="3" t="n"/>
+      <c r="AK188" s="3" t="n"/>
+      <c r="AL188" s="3" t="n"/>
+      <c r="AM188" s="3" t="n"/>
+      <c r="AN188" s="3" t="n"/>
+      <c r="AT188" s="3" t="n"/>
+      <c r="AU188" s="3" t="n"/>
+      <c r="AV188" s="3" t="n"/>
+      <c r="AW188" s="3" t="n"/>
+      <c r="AX188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -6561,12 +9557,28 @@
       <c r="H189" s="3" t="n"/>
       <c r="I189" s="3" t="n"/>
       <c r="J189" s="3" t="n"/>
+      <c r="K189" s="3" t="n"/>
       <c r="L189" s="3" t="n"/>
       <c r="M189" s="3" t="n"/>
       <c r="Q189" s="3" t="n"/>
       <c r="R189" s="3" t="n"/>
       <c r="S189" s="3" t="n"/>
       <c r="T189" s="3" t="n"/>
+      <c r="Z189" s="3" t="n"/>
+      <c r="AA189" s="3" t="n"/>
+      <c r="AB189" s="3" t="n"/>
+      <c r="AC189" s="3" t="n"/>
+      <c r="AD189" s="3" t="n"/>
+      <c r="AJ189" s="3" t="n"/>
+      <c r="AK189" s="3" t="n"/>
+      <c r="AL189" s="3" t="n"/>
+      <c r="AM189" s="3" t="n"/>
+      <c r="AN189" s="3" t="n"/>
+      <c r="AT189" s="3" t="n"/>
+      <c r="AU189" s="3" t="n"/>
+      <c r="AV189" s="3" t="n"/>
+      <c r="AW189" s="3" t="n"/>
+      <c r="AX189" s="3" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
@@ -6578,7 +9590,7 @@
         <v>0.24</v>
       </c>
       <c r="C190" s="3" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
@@ -6593,12 +9605,28 @@
       <c r="H190" s="3" t="n"/>
       <c r="I190" s="3" t="n"/>
       <c r="J190" s="3" t="n"/>
+      <c r="K190" s="3" t="n"/>
       <c r="L190" s="3" t="n"/>
       <c r="M190" s="3" t="n"/>
       <c r="Q190" s="3" t="n"/>
       <c r="R190" s="3" t="n"/>
       <c r="S190" s="3" t="n"/>
       <c r="T190" s="3" t="n"/>
+      <c r="Z190" s="3" t="n"/>
+      <c r="AA190" s="3" t="n"/>
+      <c r="AB190" s="3" t="n"/>
+      <c r="AC190" s="3" t="n"/>
+      <c r="AD190" s="3" t="n"/>
+      <c r="AJ190" s="3" t="n"/>
+      <c r="AK190" s="3" t="n"/>
+      <c r="AL190" s="3" t="n"/>
+      <c r="AM190" s="3" t="n"/>
+      <c r="AN190" s="3" t="n"/>
+      <c r="AT190" s="3" t="n"/>
+      <c r="AU190" s="3" t="n"/>
+      <c r="AV190" s="3" t="n"/>
+      <c r="AW190" s="3" t="n"/>
+      <c r="AX190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -6607,10 +9635,10 @@
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C191" s="3" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
@@ -6625,12 +9653,28 @@
       <c r="H191" s="3" t="n"/>
       <c r="I191" s="3" t="n"/>
       <c r="J191" s="3" t="n"/>
+      <c r="K191" s="3" t="n"/>
       <c r="L191" s="3" t="n"/>
       <c r="M191" s="3" t="n"/>
       <c r="Q191" s="3" t="n"/>
       <c r="R191" s="3" t="n"/>
       <c r="S191" s="3" t="n"/>
       <c r="T191" s="3" t="n"/>
+      <c r="Z191" s="3" t="n"/>
+      <c r="AA191" s="3" t="n"/>
+      <c r="AB191" s="3" t="n"/>
+      <c r="AC191" s="3" t="n"/>
+      <c r="AD191" s="3" t="n"/>
+      <c r="AJ191" s="3" t="n"/>
+      <c r="AK191" s="3" t="n"/>
+      <c r="AL191" s="3" t="n"/>
+      <c r="AM191" s="3" t="n"/>
+      <c r="AN191" s="3" t="n"/>
+      <c r="AT191" s="3" t="n"/>
+      <c r="AU191" s="3" t="n"/>
+      <c r="AV191" s="3" t="n"/>
+      <c r="AW191" s="3" t="n"/>
+      <c r="AX191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -6639,10 +9683,10 @@
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C192" s="3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
@@ -6657,12 +9701,28 @@
       <c r="H192" s="3" t="n"/>
       <c r="I192" s="3" t="n"/>
       <c r="J192" s="3" t="n"/>
+      <c r="K192" s="3" t="n"/>
       <c r="L192" s="3" t="n"/>
       <c r="M192" s="3" t="n"/>
       <c r="Q192" s="3" t="n"/>
       <c r="R192" s="3" t="n"/>
       <c r="S192" s="3" t="n"/>
       <c r="T192" s="3" t="n"/>
+      <c r="Z192" s="3" t="n"/>
+      <c r="AA192" s="3" t="n"/>
+      <c r="AB192" s="3" t="n"/>
+      <c r="AC192" s="3" t="n"/>
+      <c r="AD192" s="3" t="n"/>
+      <c r="AJ192" s="3" t="n"/>
+      <c r="AK192" s="3" t="n"/>
+      <c r="AL192" s="3" t="n"/>
+      <c r="AM192" s="3" t="n"/>
+      <c r="AN192" s="3" t="n"/>
+      <c r="AT192" s="3" t="n"/>
+      <c r="AU192" s="3" t="n"/>
+      <c r="AV192" s="3" t="n"/>
+      <c r="AW192" s="3" t="n"/>
+      <c r="AX192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -6687,12 +9747,28 @@
       <c r="H193" s="3" t="n"/>
       <c r="I193" s="3" t="n"/>
       <c r="J193" s="3" t="n"/>
+      <c r="K193" s="3" t="n"/>
       <c r="L193" s="3" t="n"/>
       <c r="M193" s="3" t="n"/>
       <c r="Q193" s="3" t="n"/>
       <c r="R193" s="3" t="n"/>
       <c r="S193" s="3" t="n"/>
       <c r="T193" s="3" t="n"/>
+      <c r="Z193" s="3" t="n"/>
+      <c r="AA193" s="3" t="n"/>
+      <c r="AB193" s="3" t="n"/>
+      <c r="AC193" s="3" t="n"/>
+      <c r="AD193" s="3" t="n"/>
+      <c r="AJ193" s="3" t="n"/>
+      <c r="AK193" s="3" t="n"/>
+      <c r="AL193" s="3" t="n"/>
+      <c r="AM193" s="3" t="n"/>
+      <c r="AN193" s="3" t="n"/>
+      <c r="AT193" s="3" t="n"/>
+      <c r="AU193" s="3" t="n"/>
+      <c r="AV193" s="3" t="n"/>
+      <c r="AW193" s="3" t="n"/>
+      <c r="AX193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -6701,7 +9777,7 @@
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>10.92</v>
+        <v>10.74</v>
       </c>
       <c r="C194" s="3" t="inlineStr"/>
       <c r="D194" s="3" t="inlineStr">
@@ -6717,12 +9793,28 @@
       <c r="H194" s="3" t="n"/>
       <c r="I194" s="3" t="n"/>
       <c r="J194" s="3" t="n"/>
+      <c r="K194" s="3" t="n"/>
       <c r="L194" s="3" t="n"/>
       <c r="M194" s="3" t="n"/>
       <c r="Q194" s="3" t="n"/>
       <c r="R194" s="3" t="n"/>
       <c r="S194" s="3" t="n"/>
       <c r="T194" s="3" t="n"/>
+      <c r="Z194" s="3" t="n"/>
+      <c r="AA194" s="3" t="n"/>
+      <c r="AB194" s="3" t="n"/>
+      <c r="AC194" s="3" t="n"/>
+      <c r="AD194" s="3" t="n"/>
+      <c r="AJ194" s="3" t="n"/>
+      <c r="AK194" s="3" t="n"/>
+      <c r="AL194" s="3" t="n"/>
+      <c r="AM194" s="3" t="n"/>
+      <c r="AN194" s="3" t="n"/>
+      <c r="AT194" s="3" t="n"/>
+      <c r="AU194" s="3" t="n"/>
+      <c r="AV194" s="3" t="n"/>
+      <c r="AW194" s="3" t="n"/>
+      <c r="AX194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -6731,7 +9823,7 @@
         </is>
       </c>
       <c r="B195" s="3" t="n">
-        <v>66.29000000000001</v>
+        <v>68.61</v>
       </c>
       <c r="C195" s="3" t="inlineStr"/>
       <c r="D195" s="3" t="inlineStr">
@@ -6747,12 +9839,28 @@
       <c r="H195" s="3" t="n"/>
       <c r="I195" s="3" t="n"/>
       <c r="J195" s="3" t="n"/>
+      <c r="K195" s="3" t="n"/>
       <c r="L195" s="3" t="n"/>
       <c r="M195" s="3" t="n"/>
       <c r="Q195" s="3" t="n"/>
       <c r="R195" s="3" t="n"/>
       <c r="S195" s="3" t="n"/>
       <c r="T195" s="3" t="n"/>
+      <c r="Z195" s="3" t="n"/>
+      <c r="AA195" s="3" t="n"/>
+      <c r="AB195" s="3" t="n"/>
+      <c r="AC195" s="3" t="n"/>
+      <c r="AD195" s="3" t="n"/>
+      <c r="AJ195" s="3" t="n"/>
+      <c r="AK195" s="3" t="n"/>
+      <c r="AL195" s="3" t="n"/>
+      <c r="AM195" s="3" t="n"/>
+      <c r="AN195" s="3" t="n"/>
+      <c r="AT195" s="3" t="n"/>
+      <c r="AU195" s="3" t="n"/>
+      <c r="AV195" s="3" t="n"/>
+      <c r="AW195" s="3" t="n"/>
+      <c r="AX195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
@@ -6764,7 +9872,7 @@
         <v>0.06</v>
       </c>
       <c r="C196" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
@@ -6779,12 +9887,28 @@
       <c r="H196" s="3" t="n"/>
       <c r="I196" s="3" t="n"/>
       <c r="J196" s="3" t="n"/>
+      <c r="K196" s="3" t="n"/>
       <c r="L196" s="3" t="n"/>
       <c r="M196" s="3" t="n"/>
       <c r="Q196" s="3" t="n"/>
       <c r="R196" s="3" t="n"/>
       <c r="S196" s="3" t="n"/>
       <c r="T196" s="3" t="n"/>
+      <c r="Z196" s="3" t="n"/>
+      <c r="AA196" s="3" t="n"/>
+      <c r="AB196" s="3" t="n"/>
+      <c r="AC196" s="3" t="n"/>
+      <c r="AD196" s="3" t="n"/>
+      <c r="AJ196" s="3" t="n"/>
+      <c r="AK196" s="3" t="n"/>
+      <c r="AL196" s="3" t="n"/>
+      <c r="AM196" s="3" t="n"/>
+      <c r="AN196" s="3" t="n"/>
+      <c r="AT196" s="3" t="n"/>
+      <c r="AU196" s="3" t="n"/>
+      <c r="AV196" s="3" t="n"/>
+      <c r="AW196" s="3" t="n"/>
+      <c r="AX196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -6793,10 +9917,10 @@
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="C197" s="3" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
@@ -6811,12 +9935,28 @@
       <c r="H197" s="3" t="n"/>
       <c r="I197" s="3" t="n"/>
       <c r="J197" s="3" t="n"/>
+      <c r="K197" s="3" t="n"/>
       <c r="L197" s="3" t="n"/>
       <c r="M197" s="3" t="n"/>
       <c r="Q197" s="3" t="n"/>
       <c r="R197" s="3" t="n"/>
       <c r="S197" s="3" t="n"/>
       <c r="T197" s="3" t="n"/>
+      <c r="Z197" s="3" t="n"/>
+      <c r="AA197" s="3" t="n"/>
+      <c r="AB197" s="3" t="n"/>
+      <c r="AC197" s="3" t="n"/>
+      <c r="AD197" s="3" t="n"/>
+      <c r="AJ197" s="3" t="n"/>
+      <c r="AK197" s="3" t="n"/>
+      <c r="AL197" s="3" t="n"/>
+      <c r="AM197" s="3" t="n"/>
+      <c r="AN197" s="3" t="n"/>
+      <c r="AT197" s="3" t="n"/>
+      <c r="AU197" s="3" t="n"/>
+      <c r="AV197" s="3" t="n"/>
+      <c r="AW197" s="3" t="n"/>
+      <c r="AX197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -6825,10 +9965,10 @@
         </is>
       </c>
       <c r="B198" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="C198" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
@@ -6843,12 +9983,28 @@
       <c r="H198" s="3" t="n"/>
       <c r="I198" s="3" t="n"/>
       <c r="J198" s="3" t="n"/>
+      <c r="K198" s="3" t="n"/>
       <c r="L198" s="3" t="n"/>
       <c r="M198" s="3" t="n"/>
       <c r="Q198" s="3" t="n"/>
       <c r="R198" s="3" t="n"/>
       <c r="S198" s="3" t="n"/>
       <c r="T198" s="3" t="n"/>
+      <c r="Z198" s="3" t="n"/>
+      <c r="AA198" s="3" t="n"/>
+      <c r="AB198" s="3" t="n"/>
+      <c r="AC198" s="3" t="n"/>
+      <c r="AD198" s="3" t="n"/>
+      <c r="AJ198" s="3" t="n"/>
+      <c r="AK198" s="3" t="n"/>
+      <c r="AL198" s="3" t="n"/>
+      <c r="AM198" s="3" t="n"/>
+      <c r="AN198" s="3" t="n"/>
+      <c r="AT198" s="3" t="n"/>
+      <c r="AU198" s="3" t="n"/>
+      <c r="AV198" s="3" t="n"/>
+      <c r="AW198" s="3" t="n"/>
+      <c r="AX198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -6857,10 +10013,10 @@
         </is>
       </c>
       <c r="B199" s="3" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C199" s="3" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
@@ -6875,12 +10031,28 @@
       <c r="H199" s="3" t="n"/>
       <c r="I199" s="3" t="n"/>
       <c r="J199" s="3" t="n"/>
+      <c r="K199" s="3" t="n"/>
       <c r="L199" s="3" t="n"/>
       <c r="M199" s="3" t="n"/>
       <c r="Q199" s="3" t="n"/>
       <c r="R199" s="3" t="n"/>
       <c r="S199" s="3" t="n"/>
       <c r="T199" s="3" t="n"/>
+      <c r="Z199" s="3" t="n"/>
+      <c r="AA199" s="3" t="n"/>
+      <c r="AB199" s="3" t="n"/>
+      <c r="AC199" s="3" t="n"/>
+      <c r="AD199" s="3" t="n"/>
+      <c r="AJ199" s="3" t="n"/>
+      <c r="AK199" s="3" t="n"/>
+      <c r="AL199" s="3" t="n"/>
+      <c r="AM199" s="3" t="n"/>
+      <c r="AN199" s="3" t="n"/>
+      <c r="AT199" s="3" t="n"/>
+      <c r="AU199" s="3" t="n"/>
+      <c r="AV199" s="3" t="n"/>
+      <c r="AW199" s="3" t="n"/>
+      <c r="AX199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -6889,10 +10061,10 @@
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="C200" s="3" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
@@ -6907,12 +10079,28 @@
       <c r="H200" s="3" t="n"/>
       <c r="I200" s="3" t="n"/>
       <c r="J200" s="3" t="n"/>
+      <c r="K200" s="3" t="n"/>
       <c r="L200" s="3" t="n"/>
       <c r="M200" s="3" t="n"/>
       <c r="Q200" s="3" t="n"/>
       <c r="R200" s="3" t="n"/>
       <c r="S200" s="3" t="n"/>
       <c r="T200" s="3" t="n"/>
+      <c r="Z200" s="3" t="n"/>
+      <c r="AA200" s="3" t="n"/>
+      <c r="AB200" s="3" t="n"/>
+      <c r="AC200" s="3" t="n"/>
+      <c r="AD200" s="3" t="n"/>
+      <c r="AJ200" s="3" t="n"/>
+      <c r="AK200" s="3" t="n"/>
+      <c r="AL200" s="3" t="n"/>
+      <c r="AM200" s="3" t="n"/>
+      <c r="AN200" s="3" t="n"/>
+      <c r="AT200" s="3" t="n"/>
+      <c r="AU200" s="3" t="n"/>
+      <c r="AV200" s="3" t="n"/>
+      <c r="AW200" s="3" t="n"/>
+      <c r="AX200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -6921,7 +10109,7 @@
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>28.22</v>
+        <v>26.2</v>
       </c>
       <c r="C201" s="3" t="inlineStr"/>
       <c r="D201" s="3" t="inlineStr">
@@ -6937,12 +10125,28 @@
       <c r="H201" s="3" t="n"/>
       <c r="I201" s="3" t="n"/>
       <c r="J201" s="3" t="n"/>
+      <c r="K201" s="3" t="n"/>
       <c r="L201" s="3" t="n"/>
       <c r="M201" s="3" t="n"/>
       <c r="Q201" s="3" t="n"/>
       <c r="R201" s="3" t="n"/>
       <c r="S201" s="3" t="n"/>
       <c r="T201" s="3" t="n"/>
+      <c r="Z201" s="3" t="n"/>
+      <c r="AA201" s="3" t="n"/>
+      <c r="AB201" s="3" t="n"/>
+      <c r="AC201" s="3" t="n"/>
+      <c r="AD201" s="3" t="n"/>
+      <c r="AJ201" s="3" t="n"/>
+      <c r="AK201" s="3" t="n"/>
+      <c r="AL201" s="3" t="n"/>
+      <c r="AM201" s="3" t="n"/>
+      <c r="AN201" s="3" t="n"/>
+      <c r="AT201" s="3" t="n"/>
+      <c r="AU201" s="3" t="n"/>
+      <c r="AV201" s="3" t="n"/>
+      <c r="AW201" s="3" t="n"/>
+      <c r="AX201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -6951,7 +10155,7 @@
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C202" s="3" t="n">
         <v>0.12</v>
@@ -6969,12 +10173,28 @@
       <c r="H202" s="3" t="n"/>
       <c r="I202" s="3" t="n"/>
       <c r="J202" s="3" t="n"/>
+      <c r="K202" s="3" t="n"/>
       <c r="L202" s="3" t="n"/>
       <c r="M202" s="3" t="n"/>
       <c r="Q202" s="3" t="n"/>
       <c r="R202" s="3" t="n"/>
       <c r="S202" s="3" t="n"/>
       <c r="T202" s="3" t="n"/>
+      <c r="Z202" s="3" t="n"/>
+      <c r="AA202" s="3" t="n"/>
+      <c r="AB202" s="3" t="n"/>
+      <c r="AC202" s="3" t="n"/>
+      <c r="AD202" s="3" t="n"/>
+      <c r="AJ202" s="3" t="n"/>
+      <c r="AK202" s="3" t="n"/>
+      <c r="AL202" s="3" t="n"/>
+      <c r="AM202" s="3" t="n"/>
+      <c r="AN202" s="3" t="n"/>
+      <c r="AT202" s="3" t="n"/>
+      <c r="AU202" s="3" t="n"/>
+      <c r="AV202" s="3" t="n"/>
+      <c r="AW202" s="3" t="n"/>
+      <c r="AX202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
@@ -6983,10 +10203,10 @@
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="C203" s="3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
@@ -7001,12 +10221,28 @@
       <c r="H203" s="3" t="n"/>
       <c r="I203" s="3" t="n"/>
       <c r="J203" s="3" t="n"/>
+      <c r="K203" s="3" t="n"/>
       <c r="L203" s="3" t="n"/>
       <c r="M203" s="3" t="n"/>
       <c r="Q203" s="3" t="n"/>
       <c r="R203" s="3" t="n"/>
       <c r="S203" s="3" t="n"/>
       <c r="T203" s="3" t="n"/>
+      <c r="Z203" s="3" t="n"/>
+      <c r="AA203" s="3" t="n"/>
+      <c r="AB203" s="3" t="n"/>
+      <c r="AC203" s="3" t="n"/>
+      <c r="AD203" s="3" t="n"/>
+      <c r="AJ203" s="3" t="n"/>
+      <c r="AK203" s="3" t="n"/>
+      <c r="AL203" s="3" t="n"/>
+      <c r="AM203" s="3" t="n"/>
+      <c r="AN203" s="3" t="n"/>
+      <c r="AT203" s="3" t="n"/>
+      <c r="AU203" s="3" t="n"/>
+      <c r="AV203" s="3" t="n"/>
+      <c r="AW203" s="3" t="n"/>
+      <c r="AX203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
@@ -7018,7 +10254,7 @@
         <v>0.16</v>
       </c>
       <c r="C204" s="3" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
@@ -7033,12 +10269,28 @@
       <c r="H204" s="3" t="n"/>
       <c r="I204" s="3" t="n"/>
       <c r="J204" s="3" t="n"/>
+      <c r="K204" s="3" t="n"/>
       <c r="L204" s="3" t="n"/>
       <c r="M204" s="3" t="n"/>
       <c r="Q204" s="3" t="n"/>
       <c r="R204" s="3" t="n"/>
       <c r="S204" s="3" t="n"/>
       <c r="T204" s="3" t="n"/>
+      <c r="Z204" s="3" t="n"/>
+      <c r="AA204" s="3" t="n"/>
+      <c r="AB204" s="3" t="n"/>
+      <c r="AC204" s="3" t="n"/>
+      <c r="AD204" s="3" t="n"/>
+      <c r="AJ204" s="3" t="n"/>
+      <c r="AK204" s="3" t="n"/>
+      <c r="AL204" s="3" t="n"/>
+      <c r="AM204" s="3" t="n"/>
+      <c r="AN204" s="3" t="n"/>
+      <c r="AT204" s="3" t="n"/>
+      <c r="AU204" s="3" t="n"/>
+      <c r="AV204" s="3" t="n"/>
+      <c r="AW204" s="3" t="n"/>
+      <c r="AX204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -7047,7 +10299,7 @@
         </is>
       </c>
       <c r="B205" s="3" t="n">
-        <v>0.78</v>
+        <v>0.58</v>
       </c>
       <c r="C205" s="3" t="inlineStr"/>
       <c r="D205" s="3" t="inlineStr">
@@ -7063,12 +10315,28 @@
       <c r="H205" s="3" t="n"/>
       <c r="I205" s="3" t="n"/>
       <c r="J205" s="3" t="n"/>
+      <c r="K205" s="3" t="n"/>
       <c r="L205" s="3" t="n"/>
       <c r="M205" s="3" t="n"/>
       <c r="Q205" s="3" t="n"/>
       <c r="R205" s="3" t="n"/>
       <c r="S205" s="3" t="n"/>
       <c r="T205" s="3" t="n"/>
+      <c r="Z205" s="3" t="n"/>
+      <c r="AA205" s="3" t="n"/>
+      <c r="AB205" s="3" t="n"/>
+      <c r="AC205" s="3" t="n"/>
+      <c r="AD205" s="3" t="n"/>
+      <c r="AJ205" s="3" t="n"/>
+      <c r="AK205" s="3" t="n"/>
+      <c r="AL205" s="3" t="n"/>
+      <c r="AM205" s="3" t="n"/>
+      <c r="AN205" s="3" t="n"/>
+      <c r="AT205" s="3" t="n"/>
+      <c r="AU205" s="3" t="n"/>
+      <c r="AV205" s="3" t="n"/>
+      <c r="AW205" s="3" t="n"/>
+      <c r="AX205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -7077,7 +10345,7 @@
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>7.18</v>
+        <v>6.3</v>
       </c>
       <c r="C206" s="3" t="inlineStr"/>
       <c r="D206" s="3" t="inlineStr">
@@ -7093,12 +10361,28 @@
       <c r="H206" s="3" t="n"/>
       <c r="I206" s="3" t="n"/>
       <c r="J206" s="3" t="n"/>
+      <c r="K206" s="3" t="n"/>
       <c r="L206" s="3" t="n"/>
       <c r="M206" s="3" t="n"/>
       <c r="Q206" s="3" t="n"/>
       <c r="R206" s="3" t="n"/>
       <c r="S206" s="3" t="n"/>
       <c r="T206" s="3" t="n"/>
+      <c r="Z206" s="3" t="n"/>
+      <c r="AA206" s="3" t="n"/>
+      <c r="AB206" s="3" t="n"/>
+      <c r="AC206" s="3" t="n"/>
+      <c r="AD206" s="3" t="n"/>
+      <c r="AJ206" s="3" t="n"/>
+      <c r="AK206" s="3" t="n"/>
+      <c r="AL206" s="3" t="n"/>
+      <c r="AM206" s="3" t="n"/>
+      <c r="AN206" s="3" t="n"/>
+      <c r="AT206" s="3" t="n"/>
+      <c r="AU206" s="3" t="n"/>
+      <c r="AV206" s="3" t="n"/>
+      <c r="AW206" s="3" t="n"/>
+      <c r="AX206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -7107,7 +10391,7 @@
         </is>
       </c>
       <c r="B207" s="3" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="C207" s="3" t="inlineStr"/>
       <c r="D207" s="3" t="inlineStr">
@@ -7123,12 +10407,28 @@
       <c r="H207" s="3" t="n"/>
       <c r="I207" s="3" t="n"/>
       <c r="J207" s="3" t="n"/>
+      <c r="K207" s="3" t="n"/>
       <c r="L207" s="3" t="n"/>
       <c r="M207" s="3" t="n"/>
       <c r="Q207" s="3" t="n"/>
       <c r="R207" s="3" t="n"/>
       <c r="S207" s="3" t="n"/>
       <c r="T207" s="3" t="n"/>
+      <c r="Z207" s="3" t="n"/>
+      <c r="AA207" s="3" t="n"/>
+      <c r="AB207" s="3" t="n"/>
+      <c r="AC207" s="3" t="n"/>
+      <c r="AD207" s="3" t="n"/>
+      <c r="AJ207" s="3" t="n"/>
+      <c r="AK207" s="3" t="n"/>
+      <c r="AL207" s="3" t="n"/>
+      <c r="AM207" s="3" t="n"/>
+      <c r="AN207" s="3" t="n"/>
+      <c r="AT207" s="3" t="n"/>
+      <c r="AU207" s="3" t="n"/>
+      <c r="AV207" s="3" t="n"/>
+      <c r="AW207" s="3" t="n"/>
+      <c r="AX207" s="3" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -7153,12 +10453,28 @@
       <c r="H208" s="3" t="n"/>
       <c r="I208" s="3" t="n"/>
       <c r="J208" s="3" t="n"/>
+      <c r="K208" s="3" t="n"/>
       <c r="L208" s="3" t="n"/>
       <c r="M208" s="3" t="n"/>
       <c r="Q208" s="3" t="n"/>
       <c r="R208" s="3" t="n"/>
       <c r="S208" s="3" t="n"/>
       <c r="T208" s="3" t="n"/>
+      <c r="Z208" s="3" t="n"/>
+      <c r="AA208" s="3" t="n"/>
+      <c r="AB208" s="3" t="n"/>
+      <c r="AC208" s="3" t="n"/>
+      <c r="AD208" s="3" t="n"/>
+      <c r="AJ208" s="3" t="n"/>
+      <c r="AK208" s="3" t="n"/>
+      <c r="AL208" s="3" t="n"/>
+      <c r="AM208" s="3" t="n"/>
+      <c r="AN208" s="3" t="n"/>
+      <c r="AT208" s="3" t="n"/>
+      <c r="AU208" s="3" t="n"/>
+      <c r="AV208" s="3" t="n"/>
+      <c r="AW208" s="3" t="n"/>
+      <c r="AX208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -7167,7 +10483,7 @@
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>54.16</v>
+        <v>53.48</v>
       </c>
       <c r="C209" s="3" t="inlineStr"/>
       <c r="D209" s="3" t="inlineStr">
@@ -7183,12 +10499,28 @@
       <c r="H209" s="3" t="n"/>
       <c r="I209" s="3" t="n"/>
       <c r="J209" s="3" t="n"/>
+      <c r="K209" s="3" t="n"/>
       <c r="L209" s="3" t="n"/>
       <c r="M209" s="3" t="n"/>
       <c r="Q209" s="3" t="n"/>
       <c r="R209" s="3" t="n"/>
       <c r="S209" s="3" t="n"/>
       <c r="T209" s="3" t="n"/>
+      <c r="Z209" s="3" t="n"/>
+      <c r="AA209" s="3" t="n"/>
+      <c r="AB209" s="3" t="n"/>
+      <c r="AC209" s="3" t="n"/>
+      <c r="AD209" s="3" t="n"/>
+      <c r="AJ209" s="3" t="n"/>
+      <c r="AK209" s="3" t="n"/>
+      <c r="AL209" s="3" t="n"/>
+      <c r="AM209" s="3" t="n"/>
+      <c r="AN209" s="3" t="n"/>
+      <c r="AT209" s="3" t="n"/>
+      <c r="AU209" s="3" t="n"/>
+      <c r="AV209" s="3" t="n"/>
+      <c r="AW209" s="3" t="n"/>
+      <c r="AX209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
@@ -7200,7 +10532,7 @@
         <v>0.06</v>
       </c>
       <c r="C210" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
@@ -7215,228 +10547,94 @@
       <c r="H210" s="3" t="n"/>
       <c r="I210" s="3" t="n"/>
       <c r="J210" s="3" t="n"/>
+      <c r="K210" s="3" t="n"/>
       <c r="L210" s="3" t="n"/>
       <c r="M210" s="3" t="n"/>
       <c r="Q210" s="3" t="n"/>
       <c r="R210" s="3" t="n"/>
       <c r="S210" s="3" t="n"/>
       <c r="T210" s="3" t="n"/>
+      <c r="Z210" s="3" t="n"/>
+      <c r="AA210" s="3" t="n"/>
+      <c r="AB210" s="3" t="n"/>
+      <c r="AC210" s="3" t="n"/>
+      <c r="AD210" s="3" t="n"/>
+      <c r="AJ210" s="3" t="n"/>
+      <c r="AK210" s="3" t="n"/>
+      <c r="AL210" s="3" t="n"/>
+      <c r="AM210" s="3" t="n"/>
+      <c r="AN210" s="3" t="n"/>
+      <c r="AT210" s="3" t="n"/>
+      <c r="AU210" s="3" t="n"/>
+      <c r="AV210" s="3" t="n"/>
+      <c r="AW210" s="3" t="n"/>
+      <c r="AX210" s="3" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="3" t="inlineStr">
-        <is>
-          <t>Weezing</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="C211" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="D211" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E211" s="3" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="F211" s="3">
-        <f>IF(B211="common", 4, IF(B211="uncommon", 3, IF(B211="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="A211" s="3" t="n"/>
+      <c r="B211" s="3" t="n"/>
+      <c r="C211" s="3" t="n"/>
+      <c r="D211" s="3" t="n"/>
+      <c r="E211" s="3" t="n"/>
+      <c r="F211" s="3" t="n"/>
     </row>
     <row r="212">
-      <c r="A212" s="3" t="inlineStr">
-        <is>
-          <t>Pack Prices:</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="inlineStr">
-        <is>
-          <t>double rare</t>
-        </is>
-      </c>
-      <c r="C212" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="D212" s="3" t="n">
-        <v>0.6899999999999999</v>
-      </c>
+      <c r="A212" s="3" t="n"/>
+      <c r="B212" s="3" t="n"/>
+      <c r="C212" s="3" t="n"/>
+      <c r="D212" s="3" t="n"/>
       <c r="E212" s="3" t="n"/>
-      <c r="F212" s="3" t="inlineStr">
-        <is>
-          <t>10.75</t>
-        </is>
-      </c>
-      <c r="G212" s="3" t="inlineStr">
-        <is>
-          <t>224.85</t>
-        </is>
-      </c>
-      <c r="H212" s="3" t="inlineStr">
-        <is>
-          <t>Unavailable</t>
-        </is>
-      </c>
-      <c r="I212" s="3" t="inlineStr">
-        <is>
-          <t>261.66</t>
-        </is>
-      </c>
-      <c r="J212" s="3" t="inlineStr">
-        <is>
-          <t>224.85</t>
-        </is>
-      </c>
-      <c r="L212" s="3" t="inlineStr">
-        <is>
-          <t>Unavailable</t>
-        </is>
-      </c>
-      <c r="M212" s="3" t="inlineStr">
-        <is>
-          <t>261.66</t>
-        </is>
-      </c>
-      <c r="Q212" s="3" t="inlineStr">
-        <is>
-          <t>10.76</t>
-        </is>
-      </c>
-      <c r="R212" s="3" t="inlineStr">
-        <is>
-          <t>224.84</t>
-        </is>
-      </c>
-      <c r="S212" s="3" t="inlineStr">
-        <is>
-          <t>Unavailable</t>
-        </is>
-      </c>
-      <c r="T212" s="3" t="inlineStr">
-        <is>
-          <t>261.66</t>
-        </is>
-      </c>
+      <c r="F212" s="3" t="n"/>
+      <c r="G212" s="3" t="n"/>
+      <c r="H212" s="3" t="n"/>
+      <c r="I212" s="3" t="n"/>
+      <c r="J212" s="3" t="n"/>
+      <c r="L212" s="3" t="n"/>
+      <c r="M212" s="3" t="n"/>
+      <c r="Q212" s="3" t="n"/>
+      <c r="R212" s="3" t="n"/>
+      <c r="S212" s="3" t="n"/>
+      <c r="T212" s="3" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="3" t="inlineStr">
-        <is>
-          <t>Wigglytuff ex - 187/165</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="inlineStr">
-        <is>
-          <t>ultra rare</t>
-        </is>
-      </c>
-      <c r="C213" s="3" t="n">
-        <v>248</v>
-      </c>
-      <c r="D213" s="3" t="n">
-        <v>6.97</v>
-      </c>
+      <c r="A213" s="3" t="n"/>
+      <c r="B213" s="3" t="n"/>
+      <c r="C213" s="3" t="n"/>
+      <c r="D213" s="3" t="n"/>
       <c r="E213" s="3" t="n"/>
-      <c r="F213" s="3">
-        <f>IF(B213="common", 4, IF(B213="uncommon", 3, IF(B213="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F213" s="3" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="3" t="inlineStr">
-        <is>
-          <t>Zapdos ex - 145/165</t>
-        </is>
-      </c>
-      <c r="B214" s="3" t="inlineStr">
-        <is>
-          <t>double rare</t>
-        </is>
-      </c>
-      <c r="C214" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="D214" s="3" t="n">
-        <v>0.79</v>
-      </c>
+      <c r="A214" s="3" t="n"/>
+      <c r="B214" s="3" t="n"/>
+      <c r="C214" s="3" t="n"/>
+      <c r="D214" s="3" t="n"/>
       <c r="E214" s="3" t="n"/>
-      <c r="F214" s="3">
-        <f>IF(B214="common", 4, IF(B214="uncommon", 3, IF(B214="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F214" s="3" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="3" t="inlineStr">
-        <is>
-          <t>Zapdos ex - 192/165</t>
-        </is>
-      </c>
-      <c r="B215" s="3" t="inlineStr">
-        <is>
-          <t>ultra rare</t>
-        </is>
-      </c>
-      <c r="C215" s="3" t="n">
-        <v>248</v>
-      </c>
-      <c r="D215" s="3" t="n">
-        <v>8.029999999999999</v>
-      </c>
+      <c r="A215" s="3" t="n"/>
+      <c r="B215" s="3" t="n"/>
+      <c r="C215" s="3" t="n"/>
+      <c r="D215" s="3" t="n"/>
       <c r="E215" s="3" t="n"/>
-      <c r="F215" s="3">
-        <f>IF(B215="common", 4, IF(B215="uncommon", 3, IF(B215="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F215" s="3" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="3" t="inlineStr">
-        <is>
-          <t>Zapdos ex - 202/165</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="inlineStr">
-        <is>
-          <t>special illustration rare</t>
-        </is>
-      </c>
-      <c r="C216" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="D216" s="3" t="n">
-        <v>50.83</v>
-      </c>
+      <c r="A216" s="3" t="n"/>
+      <c r="B216" s="3" t="n"/>
+      <c r="C216" s="3" t="n"/>
+      <c r="D216" s="3" t="n"/>
       <c r="E216" s="3" t="n"/>
-      <c r="F216" s="3">
-        <f>IF(B216="common", 4, IF(B216="uncommon", 3, IF(B216="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="F216" s="3" t="n"/>
     </row>
     <row r="217">
-      <c r="A217" s="3" t="inlineStr">
-        <is>
-          <t>Zubat</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="C217" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="D217" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E217" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F217" s="3">
-        <f>IF(B217="common", 4, IF(B217="uncommon", 3, IF(B217="rare", 1.74127216869152, 1)))</f>
-        <v/>
-      </c>
+      <c r="A217" s="3" t="n"/>
+      <c r="B217" s="3" t="n"/>
+      <c r="C217" s="3" t="n"/>
+      <c r="D217" s="3" t="n"/>
+      <c r="E217" s="3" t="n"/>
+      <c r="F217" s="3" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="n"/>
@@ -14020,7 +17218,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>0.4469565217391304</v>
+        <v>0.4017391304347826</v>
       </c>
     </row>
     <row r="3">
@@ -14030,7 +17228,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>0.4954545454545455</v>
+        <v>0.4472727272727273</v>
       </c>
     </row>
     <row r="4">
@@ -14040,7 +17238,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>0.2148360177404295</v>
+        <v>0.213703314659197</v>
       </c>
     </row>
     <row r="5">
@@ -14050,7 +17248,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>5.413358438813602</v>
+        <v>5.400100549360059</v>
       </c>
     </row>
     <row r="6">
@@ -14090,7 +17288,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1.936063829787234</v>
+        <v>1.88063829787234</v>
       </c>
     </row>
     <row r="10">
@@ -14100,7 +17298,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>2.105955555555556</v>
+        <v>2.089422222222222</v>
       </c>
     </row>
     <row r="11">
@@ -14110,7 +17308,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.3091111111111111</v>
+        <v>0.3071111111111112</v>
       </c>
     </row>
     <row r="12">
@@ -14120,7 +17318,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1379220779220779</v>
       </c>
     </row>
     <row r="13">
@@ -14130,7 +17328,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>0.5658467741935483</v>
+        <v>0.5426612903225806</v>
       </c>
     </row>
     <row r="14">
@@ -14160,7 +17358,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>5.053340907011087</v>
+        <v>4.957754999450333</v>
       </c>
     </row>
     <row r="17">
@@ -14170,7 +17368,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>11.62394643075879</v>
+        <v>11.4205707211771</v>
       </c>
     </row>
     <row r="18">
@@ -14180,7 +17378,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>0.7339464307587917</v>
+        <v>1.070570721177099</v>
       </c>
     </row>
     <row r="19">
@@ -14190,7 +17388,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1.067396366460862</v>
+        <v>1.103436784654792</v>
       </c>
     </row>
     <row r="20">
@@ -14200,7 +17398,7 @@
         </is>
       </c>
       <c r="B20" s="14" t="n">
-        <v>0.06739636646086233</v>
+        <v>0.1034367846547921</v>
       </c>
     </row>
     <row r="21">

--- a/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
+++ b/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
@@ -659,10 +659,10 @@
         <v>46</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="F2" s="3">
         <f>IF(B2:B210="common", 4, IF(B2:B210="uncommon", 3, IF(B2:B210="rare", 0.792892156862745, 1)))</f>
@@ -677,20 +677,20 @@
         <v/>
       </c>
       <c r="I2" s="3" t="n">
-        <v>9.43</v>
+        <v>9.56</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>64.86</v>
+        <v>66.05</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>228.78</v>
+        <v>231.7</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>5.77</v>
+        <v>5.84</v>
       </c>
       <c r="M2" s="3" t="n"/>
       <c r="N2" s="3" t="n">
-        <v>370</v>
+        <v>373.07</v>
       </c>
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
@@ -728,10 +728,10 @@
         <v>21</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="F3" s="3">
         <f>IF(B3:B211="common", 4, IF(B3:B211="uncommon", 3, IF(B3:B211="rare", 0.792892156862745, 1)))</f>
@@ -784,7 +784,7 @@
         <v>90</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3">
@@ -838,7 +838,7 @@
         <v>248</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7.42</v>
+        <v>7.37</v>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3">
@@ -847,7 +847,7 @@
       </c>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3">
-        <f>1.88541666666666* SUMPRODUCT((E2:E217&lt;&gt;"") * (#REF!&lt;&gt;"") * (#REF! / E2:E217))</f>
+        <f>1.88541666666666 * SUMPRODUCT((C2:C210&lt;&gt;"") * (E2:E210&lt;&gt;"") * (E2:E210 / C2:C210))</f>
         <v/>
       </c>
       <c r="I5" s="3" t="n"/>
@@ -892,7 +892,7 @@
         <v>225</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>38.64</v>
+        <v>37.41</v>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3">
@@ -901,7 +901,7 @@
       </c>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3">
-        <f>SUMPRODUCT((#REF!="Illustration Rare") *#REF! * F2:F217 / E2:E217)</f>
+        <f>SUMPRODUCT((B2:B210="Illustration Rare") *D2:D210 * F2:F210 / C2:C210)</f>
         <v/>
       </c>
       <c r="I6" s="3" t="n"/>
@@ -946,7 +946,7 @@
         <v>46</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.51</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3">
-        <f>SUMPRODUCT((#REF!="Special Illustration Rare") *#REF! * F2:F217 / E2:E217)</f>
+        <f>SUMPRODUCT((B2:B210="Special Illustration Rare") *D2:D210 * F2:F210 / C2:C210)</f>
         <v/>
       </c>
       <c r="I7" s="3" t="n"/>
@@ -1002,10 +1002,10 @@
         <v>46</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="F8" s="3">
         <f>IF(B8:B216="common", 4, IF(B8:B216="uncommon", 3, IF(B8:B216="rare", 0.792892156862745, 1)))</f>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3">
-        <f>SUMPRODUCT((#REF!="Double Rare") *#REF! * F2:F217 / E2:E217)</f>
+        <f>SUMPRODUCT((B2:B210="Double Rare") *D2:D210 * F2:F210 / C2:C210)</f>
         <v/>
       </c>
       <c r="I8" s="3" t="n"/>
@@ -1058,10 +1058,10 @@
         <v>46</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="F9" s="3">
         <f>IF(B9:B217="common", 4, IF(B9:B217="uncommon", 3, IF(B9:B217="rare", 0.792892156862745, 1)))</f>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3">
-        <f>SUMPRODUCT((#REF!="Hyper Rare") *#REF! * F2:F217 / E2:E217)</f>
+        <f>SUMPRODUCT((B2:B210="Hyper Rare") *D2:D210 * F2:F210 / C2:C210)</f>
         <v/>
       </c>
       <c r="I9" s="3" t="n"/>
@@ -1114,7 +1114,7 @@
         <v>90</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="3">
-        <f>SUMPRODUCT((#REF!="Ultra Rare") *#REF! * F2:F217 / E2:E217)</f>
+        <f>SUMPRODUCT((B2:B210="Ultra Rare") *D2:D210 * F2:F210 / C2:C210)</f>
         <v/>
       </c>
       <c r="I10" s="3" t="n"/>
@@ -1168,7 +1168,7 @@
         <v>248</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.24</v>
+        <v>5.63</v>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3">
@@ -1219,10 +1219,10 @@
         <v>33</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F12" s="3">
         <f>IF(B12:B220="common", 4, IF(B12:B220="uncommon", 3, IF(B12:B220="rare", 0.792892156862745, 1)))</f>
@@ -1275,7 +1275,7 @@
         <v>0.2</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="F13" s="3">
         <f>IF(B13:B221="common", 4, IF(B13:B221="uncommon", 3, IF(B13:B221="rare", 0.792892156862745, 1)))</f>
@@ -1325,7 +1325,7 @@
         <v>154</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.15</v>
+        <v>4.21</v>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3">
@@ -1376,10 +1376,10 @@
         <v>21</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="F15" s="3">
         <f>IF(B15:B223="common", 4, IF(B15:B223="uncommon", 3, IF(B15:B223="rare", 0.792892156862745, 1)))</f>
@@ -1429,10 +1429,10 @@
         <v>46</v>
       </c>
       <c r="D16" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>0.1</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0.11</v>
       </c>
       <c r="F16" s="3">
         <f>IF(B16:B224="common", 4, IF(B16:B224="uncommon", 3, IF(B16:B224="rare", 0.792892156862745, 1)))</f>
@@ -1485,7 +1485,7 @@
         <v>0.08</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="F17" s="3">
         <f>IF(B17:B225="common", 4, IF(B17:B225="uncommon", 3, IF(B17:B225="rare", 0.792892156862745, 1)))</f>
@@ -1535,10 +1535,10 @@
         <v>33</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="F18" s="3">
         <f>IF(B18:B226="common", 4, IF(B18:B226="uncommon", 3, IF(B18:B226="rare", 0.792892156862745, 1)))</f>
@@ -1588,7 +1588,7 @@
         <v>248</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3.11</v>
+        <v>3.27</v>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3">
@@ -1639,7 +1639,7 @@
         <v>90</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="E20" s="3" t="inlineStr"/>
       <c r="F20" s="3">
@@ -1690,7 +1690,7 @@
         <v>248</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>13.55</v>
+        <v>14</v>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3">
@@ -1741,7 +1741,7 @@
         <v>225</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>70.56</v>
+        <v>68.63</v>
       </c>
       <c r="E22" s="3" t="inlineStr"/>
       <c r="F22" s="3">
@@ -1792,10 +1792,10 @@
         <v>46</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="F23" s="3">
         <f>IF(B23:B231="common", 4, IF(B23:B231="uncommon", 3, IF(B23:B231="rare", 0.792892156862745, 1)))</f>
@@ -1845,7 +1845,7 @@
         <v>188</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>38.45</v>
+        <v>37.15</v>
       </c>
       <c r="E24" s="3" t="inlineStr"/>
       <c r="F24" s="3">
@@ -1896,10 +1896,10 @@
         <v>33</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F25" s="3">
         <f>IF(B25:B233="common", 4, IF(B25:B233="uncommon", 3, IF(B25:B233="rare", 0.792892156862745, 1)))</f>
@@ -1952,7 +1952,7 @@
         <v>0.05</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="F26" s="3">
         <f>IF(B26:B234="common", 4, IF(B26:B234="uncommon", 3, IF(B26:B234="rare", 0.792892156862745, 1)))</f>
@@ -2002,7 +2002,7 @@
         <v>188</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>7.92</v>
+        <v>7.82</v>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3">
@@ -2056,7 +2056,7 @@
         <v>0.16</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.73</v>
+        <v>0.85</v>
       </c>
       <c r="F28" s="3">
         <f>IF(B28:B236="common", 4, IF(B28:B236="uncommon", 3, IF(B28:B236="rare", 0.792892156862745, 1)))</f>
@@ -2106,7 +2106,7 @@
         <v>90</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.74</v>
+        <v>4.11</v>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3">
@@ -2157,7 +2157,7 @@
         <v>248</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>29.35</v>
+        <v>27.19</v>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3">
@@ -2208,7 +2208,7 @@
         <v>225</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>206.34</v>
+        <v>208.72</v>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3">
@@ -2259,10 +2259,10 @@
         <v>46</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="F32" s="3">
         <f>IF(B32:B240="common", 4, IF(B32:B240="uncommon", 3, IF(B32:B240="rare", 0.792892156862745, 1)))</f>
@@ -2312,7 +2312,7 @@
         <v>188</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>47.04</v>
+        <v>46.03</v>
       </c>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3">
@@ -2363,10 +2363,10 @@
         <v>33</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="F34" s="3">
         <f>IF(B34:B242="common", 4, IF(B34:B242="uncommon", 3, IF(B34:B242="rare", 0.792892156862745, 1)))</f>
@@ -2416,7 +2416,7 @@
         <v>188</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>32.31</v>
+        <v>33.1</v>
       </c>
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3">
@@ -2467,10 +2467,10 @@
         <v>33</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F36" s="3">
         <f>IF(B36:B244="common", 4, IF(B36:B244="uncommon", 3, IF(B36:B244="rare", 0.792892156862745, 1)))</f>
@@ -2520,7 +2520,7 @@
         <v>46</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>0.12</v>
@@ -2573,10 +2573,10 @@
         <v>33</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="F38" s="3">
         <f>IF(B38:B246="common", 4, IF(B38:B246="uncommon", 3, IF(B38:B246="rare", 0.792892156862745, 1)))</f>
@@ -2626,10 +2626,10 @@
         <v>46</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="F39" s="3">
         <f>IF(B39:B247="common", 4, IF(B39:B247="uncommon", 3, IF(B39:B247="rare", 0.792892156862745, 1)))</f>
@@ -2679,10 +2679,10 @@
         <v>33</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="F40" s="3">
         <f>IF(B40:B248="common", 4, IF(B40:B248="uncommon", 3, IF(B40:B248="rare", 0.792892156862745, 1)))</f>
@@ -2732,10 +2732,10 @@
         <v>33</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="F41" s="3">
         <f>IF(B41:B249="common", 4, IF(B41:B249="uncommon", 3, IF(B41:B249="rare", 0.792892156862745, 1)))</f>
@@ -2785,7 +2785,7 @@
         <v>248</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="E42" s="3" t="inlineStr"/>
       <c r="F42" s="3">
@@ -2836,10 +2836,10 @@
         <v>33</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F43" s="3">
         <f>IF(B43:B251="common", 4, IF(B43:B251="uncommon", 3, IF(B43:B251="rare", 0.792892156862745, 1)))</f>
@@ -2889,7 +2889,7 @@
         <v>46</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>0.11</v>
@@ -2942,10 +2942,10 @@
         <v>21</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="F45" s="3">
         <f>IF(B45:B253="common", 4, IF(B45:B253="uncommon", 3, IF(B45:B253="rare", 0.792892156862745, 1)))</f>
@@ -2995,7 +2995,7 @@
         <v>21</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="E46" s="3" t="inlineStr"/>
       <c r="F46" s="3">
@@ -3046,10 +3046,10 @@
         <v>21</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="F47" s="3">
         <f>IF(B47:B255="common", 4, IF(B47:B255="uncommon", 3, IF(B47:B255="rare", 0.792892156862745, 1)))</f>
@@ -3099,7 +3099,7 @@
         <v>46</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.15</v>
@@ -3152,10 +3152,10 @@
         <v>33</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="F49" s="3">
         <f>IF(B49:B257="common", 4, IF(B49:B257="uncommon", 3, IF(B49:B257="rare", 0.792892156862745, 1)))</f>
@@ -3205,7 +3205,7 @@
         <v>188</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>23.25</v>
+        <v>23.41</v>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="3">
@@ -3256,10 +3256,10 @@
         <v>21</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="F51" s="3">
         <f>IF(B51:B259="common", 4, IF(B51:B259="uncommon", 3, IF(B51:B259="rare", 0.792892156862745, 1)))</f>
@@ -3309,10 +3309,10 @@
         <v>46</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F52" s="3">
         <f>IF(B52:B260="common", 4, IF(B52:B260="uncommon", 3, IF(B52:B260="rare", 0.792892156862745, 1)))</f>
@@ -3365,7 +3365,7 @@
         <v>0.06</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="F53" s="3">
         <f>IF(B53:B261="common", 4, IF(B53:B261="uncommon", 3, IF(B53:B261="rare", 0.792892156862745, 1)))</f>
@@ -3415,7 +3415,7 @@
         <v>33</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>0.11</v>
@@ -3468,10 +3468,10 @@
         <v>46</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="F55" s="3">
         <f>IF(B55:B263="common", 4, IF(B55:B263="uncommon", 3, IF(B55:B263="rare", 0.792892156862745, 1)))</f>
@@ -3577,7 +3577,7 @@
         <v>0.06</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="F57" s="3">
         <f>IF(B57:B265="common", 4, IF(B57:B265="uncommon", 3, IF(B57:B265="rare", 0.792892156862745, 1)))</f>
@@ -3627,10 +3627,10 @@
         <v>21</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="F58" s="3">
         <f>IF(B58:B266="common", 4, IF(B58:B266="uncommon", 3, IF(B58:B266="rare", 0.792892156862745, 1)))</f>
@@ -3680,10 +3680,10 @@
         <v>33</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="F59" s="3">
         <f>IF(B59:B267="common", 4, IF(B59:B267="uncommon", 3, IF(B59:B267="rare", 0.792892156862745, 1)))</f>
@@ -3733,10 +3733,10 @@
         <v>33</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="F60" s="3">
         <f>IF(B60:B268="common", 4, IF(B60:B268="uncommon", 3, IF(B60:B268="rare", 0.792892156862745, 1)))</f>
@@ -3786,7 +3786,7 @@
         <v>248</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3">
@@ -3837,7 +3837,7 @@
         <v>225</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>14.43</v>
+        <v>13.96</v>
       </c>
       <c r="E62" s="3" t="inlineStr"/>
       <c r="F62" s="3">
@@ -3891,7 +3891,7 @@
         <v>0.06</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F63" s="3">
         <f>IF(B63:B271="common", 4, IF(B63:B271="uncommon", 3, IF(B63:B271="rare", 0.792892156862745, 1)))</f>
@@ -3944,7 +3944,7 @@
         <v>0.08</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="F64" s="3">
         <f>IF(B64:B272="common", 4, IF(B64:B272="uncommon", 3, IF(B64:B272="rare", 0.792892156862745, 1)))</f>
@@ -4050,7 +4050,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F66" s="3">
         <f>IF(B66:B274="common", 4, IF(B66:B274="uncommon", 3, IF(B66:B274="rare", 0.792892156862745, 1)))</f>
@@ -4100,10 +4100,10 @@
         <v>21</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="F67" s="3">
         <f>IF(B67:B275="common", 4, IF(B67:B275="uncommon", 3, IF(B67:B275="rare", 0.792892156862745, 1)))</f>
@@ -4153,7 +4153,7 @@
         <v>46</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E68" s="3" t="n">
         <v>0.13</v>
@@ -4206,10 +4206,10 @@
         <v>21</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="F69" s="3">
         <f>IF(B69:B277="common", 4, IF(B69:B277="uncommon", 3, IF(B69:B277="rare", 0.792892156862745, 1)))</f>
@@ -4259,10 +4259,10 @@
         <v>46</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="F70" s="3">
         <f>IF(B70:B278="common", 4, IF(B70:B278="uncommon", 3, IF(B70:B278="rare", 0.792892156862745, 1)))</f>
@@ -4315,7 +4315,7 @@
         <v>0.11</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="F71" s="3">
         <f>IF(B71:B279="common", 4, IF(B71:B279="uncommon", 3, IF(B71:B279="rare", 0.792892156862745, 1)))</f>
@@ -4365,7 +4365,7 @@
         <v>248</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>5.05</v>
+        <v>5.21</v>
       </c>
       <c r="E72" s="3" t="inlineStr"/>
       <c r="F72" s="3">
@@ -4416,7 +4416,7 @@
         <v>225</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>13.53</v>
+        <v>13.36</v>
       </c>
       <c r="E73" s="3" t="inlineStr"/>
       <c r="F73" s="3">
@@ -4467,7 +4467,7 @@
         <v>33</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>0.14</v>
@@ -4576,7 +4576,7 @@
         <v>0.06</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F76" s="3">
         <f>IF(B76:B284="common", 4, IF(B76:B284="uncommon", 3, IF(B76:B284="rare", 0.792892156862745, 1)))</f>
@@ -4626,10 +4626,10 @@
         <v>33</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F77" s="3">
         <f>IF(B77:B285="common", 4, IF(B77:B285="uncommon", 3, IF(B77:B285="rare", 0.792892156862745, 1)))</f>
@@ -4679,7 +4679,7 @@
         <v>90</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="E78" s="3" t="inlineStr"/>
       <c r="F78" s="3">
@@ -4730,7 +4730,7 @@
         <v>248</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>5.63</v>
+        <v>5.37</v>
       </c>
       <c r="E79" s="3" t="inlineStr"/>
       <c r="F79" s="3">
@@ -4781,10 +4781,10 @@
         <v>33</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="F80" s="3">
         <f>IF(B80:B288="common", 4, IF(B80:B288="uncommon", 3, IF(B80:B288="rare", 0.792892156862745, 1)))</f>
@@ -4834,10 +4834,10 @@
         <v>33</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="F81" s="3">
         <f>IF(B81:B289="common", 4, IF(B81:B289="uncommon", 3, IF(B81:B289="rare", 0.792892156862745, 1)))</f>
@@ -4890,7 +4890,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F82" s="3">
         <f>IF(B82:B290="common", 4, IF(B82:B290="uncommon", 3, IF(B82:B290="rare", 0.792892156862745, 1)))</f>
@@ -4940,10 +4940,10 @@
         <v>46</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="F83" s="3">
         <f>IF(B83:B291="common", 4, IF(B83:B291="uncommon", 3, IF(B83:B291="rare", 0.792892156862745, 1)))</f>
@@ -4993,10 +4993,10 @@
         <v>21</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F84" s="3">
         <f>IF(B84:B292="common", 4, IF(B84:B292="uncommon", 3, IF(B84:B292="rare", 0.792892156862745, 1)))</f>
@@ -5046,10 +5046,10 @@
         <v>33</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="F85" s="3">
         <f>IF(B85:B293="common", 4, IF(B85:B293="uncommon", 3, IF(B85:B293="rare", 0.792892156862745, 1)))</f>
@@ -5099,10 +5099,10 @@
         <v>33</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="F86" s="3">
         <f>IF(B86:B294="common", 4, IF(B86:B294="uncommon", 3, IF(B86:B294="rare", 0.792892156862745, 1)))</f>
@@ -5155,7 +5155,7 @@
         <v>0.12</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="F87" s="3">
         <f>IF(B87:B295="common", 4, IF(B87:B295="uncommon", 3, IF(B87:B295="rare", 0.792892156862745, 1)))</f>
@@ -5258,10 +5258,10 @@
         <v>33</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="F89" s="3">
         <f>IF(B89:B297="common", 4, IF(B89:B297="uncommon", 3, IF(B89:B297="rare", 0.792892156862745, 1)))</f>
@@ -5311,10 +5311,10 @@
         <v>33</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="F90" s="3">
         <f>IF(B90:B298="common", 4, IF(B90:B298="uncommon", 3, IF(B90:B298="rare", 0.792892156862745, 1)))</f>
@@ -5364,7 +5364,7 @@
         <v>188</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>27.62</v>
+        <v>27.64</v>
       </c>
       <c r="E91" s="3" t="inlineStr"/>
       <c r="F91" s="3">
@@ -5418,7 +5418,7 @@
         <v>0.08</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F92" s="3">
         <f>IF(B92:B300="common", 4, IF(B92:B300="uncommon", 3, IF(B92:B300="rare", 0.792892156862745, 1)))</f>
@@ -5468,10 +5468,10 @@
         <v>21</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="F93" s="3">
         <f>IF(B93:B301="common", 4, IF(B93:B301="uncommon", 3, IF(B93:B301="rare", 0.792892156862745, 1)))</f>
@@ -5521,7 +5521,7 @@
         <v>90</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.95</v>
+        <v>1.17</v>
       </c>
       <c r="E94" s="3" t="inlineStr"/>
       <c r="F94" s="3">
@@ -5572,7 +5572,7 @@
         <v>248</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>5.14</v>
+        <v>4.93</v>
       </c>
       <c r="E95" s="3" t="inlineStr"/>
       <c r="F95" s="3">
@@ -5623,10 +5623,10 @@
         <v>33</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="F96" s="3">
         <f>IF(B96:B304="common", 4, IF(B96:B304="uncommon", 3, IF(B96:B304="rare", 0.792892156862745, 1)))</f>
@@ -5676,10 +5676,10 @@
         <v>21</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F97" s="3">
         <f>IF(B97:B305="common", 4, IF(B97:B305="uncommon", 3, IF(B97:B305="rare", 0.792892156862745, 1)))</f>
@@ -5729,7 +5729,7 @@
         <v>33</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E98" s="3" t="n">
         <v>0.19</v>
@@ -5785,7 +5785,7 @@
         <v>0.09</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="F99" s="3">
         <f>IF(B99:B307="common", 4, IF(B99:B307="uncommon", 3, IF(B99:B307="rare", 0.792892156862745, 1)))</f>
@@ -5835,7 +5835,7 @@
         <v>90</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E100" s="3" t="inlineStr"/>
       <c r="F100" s="3">
@@ -5886,7 +5886,7 @@
         <v>248</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>4.71</v>
+        <v>4.44</v>
       </c>
       <c r="E101" s="3" t="inlineStr"/>
       <c r="F101" s="3">
@@ -5937,10 +5937,10 @@
         <v>33</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="F102" s="3">
         <f>IF(B102:B310="common", 4, IF(B102:B310="uncommon", 3, IF(B102:B310="rare", 0.792892156862745, 1)))</f>
@@ -5990,10 +5990,10 @@
         <v>46</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F103" s="3">
         <f>IF(B103:B311="common", 4, IF(B103:B311="uncommon", 3, IF(B103:B311="rare", 0.792892156862745, 1)))</f>
@@ -6043,7 +6043,7 @@
         <v>46</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E104" s="3" t="n">
         <v>0.12</v>
@@ -6099,7 +6099,7 @@
         <v>0.1</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="F105" s="3">
         <f>IF(B105:B313="common", 4, IF(B105:B313="uncommon", 3, IF(B105:B313="rare", 0.792892156862745, 1)))</f>
@@ -6149,10 +6149,10 @@
         <v>33</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="F106" s="3">
         <f>IF(B106:B314="common", 4, IF(B106:B314="uncommon", 3, IF(B106:B314="rare", 0.792892156862745, 1)))</f>
@@ -6205,7 +6205,7 @@
         <v>0.08</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F107" s="3">
         <f>IF(B107:B315="common", 4, IF(B107:B315="uncommon", 3, IF(B107:B315="rare", 0.792892156862745, 1)))</f>
@@ -6255,10 +6255,10 @@
         <v>21</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="F108" s="3">
         <f>IF(B108:B316="common", 4, IF(B108:B316="uncommon", 3, IF(B108:B316="rare", 0.792892156862745, 1)))</f>
@@ -6311,7 +6311,7 @@
         <v>0.09</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F109" s="3">
         <f>IF(B109:B317="common", 4, IF(B109:B317="uncommon", 3, IF(B109:B317="rare", 0.792892156862745, 1)))</f>
@@ -6361,7 +6361,7 @@
         <v>188</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>9.529999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="E110" s="3" t="inlineStr"/>
       <c r="F110" s="3">
@@ -6412,10 +6412,10 @@
         <v>46</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F111" s="3">
         <f>IF(B111:B319="common", 4, IF(B111:B319="uncommon", 3, IF(B111:B319="rare", 0.792892156862745, 1)))</f>
@@ -6465,10 +6465,10 @@
         <v>46</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F112" s="3">
         <f>IF(B112:B320="common", 4, IF(B112:B320="uncommon", 3, IF(B112:B320="rare", 0.792892156862745, 1)))</f>
@@ -6518,10 +6518,10 @@
         <v>46</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="F113" s="3">
         <f>IF(B113:B321="common", 4, IF(B113:B321="uncommon", 3, IF(B113:B321="rare", 0.792892156862745, 1)))</f>
@@ -6627,7 +6627,7 @@
         <v>0.1</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F115" s="3">
         <f>IF(B115:B323="common", 4, IF(B115:B323="uncommon", 3, IF(B115:B323="rare", 0.792892156862745, 1)))</f>
@@ -6677,7 +6677,7 @@
         <v>46</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0.11</v>
@@ -6730,10 +6730,10 @@
         <v>21</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="F117" s="3">
         <f>IF(B117:B325="common", 4, IF(B117:B325="uncommon", 3, IF(B117:B325="rare", 0.792892156862745, 1)))</f>
@@ -6783,10 +6783,10 @@
         <v>46</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F118" s="3">
         <f>IF(B118:B326="common", 4, IF(B118:B326="uncommon", 3, IF(B118:B326="rare", 0.792892156862745, 1)))</f>
@@ -6836,10 +6836,10 @@
         <v>46</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="F119" s="3">
         <f>IF(B119:B327="common", 4, IF(B119:B327="uncommon", 3, IF(B119:B327="rare", 0.792892156862745, 1)))</f>
@@ -6889,7 +6889,7 @@
         <v>90</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>7.15</v>
+        <v>8.68</v>
       </c>
       <c r="E120" s="3" t="inlineStr"/>
       <c r="F120" s="3">
@@ -6940,7 +6940,7 @@
         <v>248</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>18.07</v>
+        <v>19.31</v>
       </c>
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3">
@@ -6991,7 +6991,7 @@
         <v>154</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>13.23</v>
+        <v>12.75</v>
       </c>
       <c r="E122" s="3" t="inlineStr"/>
       <c r="F122" s="3">
@@ -7042,7 +7042,7 @@
         <v>90</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>8.94</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E123" s="3" t="inlineStr"/>
       <c r="F123" s="3">
@@ -7093,10 +7093,10 @@
         <v>21</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="F124" s="3">
         <f>IF(B124:B332="common", 4, IF(B124:B332="uncommon", 3, IF(B124:B332="rare", 0.792892156862745, 1)))</f>
@@ -7149,7 +7149,7 @@
         <v>0.2</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F125" s="3">
         <f>IF(B125:B333="common", 4, IF(B125:B333="uncommon", 3, IF(B125:B333="rare", 0.792892156862745, 1)))</f>
@@ -7202,7 +7202,7 @@
         <v>0.16</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="F126" s="3">
         <f>IF(B126:B334="common", 4, IF(B126:B334="uncommon", 3, IF(B126:B334="rare", 0.792892156862745, 1)))</f>
@@ -7252,7 +7252,7 @@
         <v>188</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>6.22</v>
+        <v>5.86</v>
       </c>
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3">
@@ -7303,10 +7303,10 @@
         <v>33</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="F128" s="3">
         <f>IF(B128:B336="common", 4, IF(B128:B336="uncommon", 3, IF(B128:B336="rare", 0.792892156862745, 1)))</f>
@@ -7356,10 +7356,10 @@
         <v>21</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
       <c r="F129" s="3">
         <f>IF(B129:B337="common", 4, IF(B129:B337="uncommon", 3, IF(B129:B337="rare", 0.792892156862745, 1)))</f>
@@ -7409,7 +7409,7 @@
         <v>188</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>9.56</v>
+        <v>9.27</v>
       </c>
       <c r="E130" s="3" t="inlineStr"/>
       <c r="F130" s="3">
@@ -7460,10 +7460,10 @@
         <v>33</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="F131" s="3">
         <f>IF(B131:B339="common", 4, IF(B131:B339="uncommon", 3, IF(B131:B339="rare", 0.792892156862745, 1)))</f>
@@ -7516,7 +7516,7 @@
         <v>0.13</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="F132" s="3">
         <f>IF(B132:B340="common", 4, IF(B132:B340="uncommon", 3, IF(B132:B340="rare", 0.792892156862745, 1)))</f>
@@ -7566,10 +7566,10 @@
         <v>46</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="F133" s="3">
         <f>IF(B133:B341="common", 4, IF(B133:B341="uncommon", 3, IF(B133:B341="rare", 0.792892156862745, 1)))</f>
@@ -7619,10 +7619,10 @@
         <v>33</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F134" s="3">
         <f>IF(B134:B342="common", 4, IF(B134:B342="uncommon", 3, IF(B134:B342="rare", 0.792892156862745, 1)))</f>
@@ -7725,7 +7725,7 @@
         <v>90</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="E136" s="3" t="inlineStr"/>
       <c r="F136" s="3">
@@ -7776,7 +7776,7 @@
         <v>248</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>8.52</v>
+        <v>7.61</v>
       </c>
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3">
@@ -7880,10 +7880,10 @@
         <v>33</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="F139" s="3">
         <f>IF(B139:B347="common", 4, IF(B139:B347="uncommon", 3, IF(B139:B347="rare", 0.792892156862745, 1)))</f>
@@ -7933,7 +7933,7 @@
         <v>188</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>5.57</v>
+        <v>5.48</v>
       </c>
       <c r="E140" s="3" t="inlineStr"/>
       <c r="F140" s="3">
@@ -7987,7 +7987,7 @@
         <v>0.13</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="F141" s="3">
         <f>IF(B141:B349="common", 4, IF(B141:B349="uncommon", 3, IF(B141:B349="rare", 0.792892156862745, 1)))</f>
@@ -8040,7 +8040,7 @@
         <v>0.08</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="F142" s="3">
         <f>IF(B142:B350="common", 4, IF(B142:B350="uncommon", 3, IF(B142:B350="rare", 0.792892156862745, 1)))</f>
@@ -8143,10 +8143,10 @@
         <v>33</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F144" s="3">
         <f>IF(B144:B352="common", 4, IF(B144:B352="uncommon", 3, IF(B144:B352="rare", 0.792892156862745, 1)))</f>
@@ -8199,7 +8199,7 @@
         <v>0.08</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F145" s="3">
         <f>IF(B145:B353="common", 4, IF(B145:B353="uncommon", 3, IF(B145:B353="rare", 0.792892156862745, 1)))</f>
@@ -8252,7 +8252,7 @@
         <v>0.09</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F146" s="3">
         <f>IF(B146:B354="common", 4, IF(B146:B354="uncommon", 3, IF(B146:B354="rare", 0.792892156862745, 1)))</f>
@@ -8302,10 +8302,10 @@
         <v>46</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="F147" s="3">
         <f>IF(B147:B355="common", 4, IF(B147:B355="uncommon", 3, IF(B147:B355="rare", 0.792892156862745, 1)))</f>
@@ -8358,7 +8358,7 @@
         <v>0.11</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="F148" s="3">
         <f>IF(B148:B356="common", 4, IF(B148:B356="uncommon", 3, IF(B148:B356="rare", 0.792892156862745, 1)))</f>
@@ -8408,10 +8408,10 @@
         <v>46</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="F149" s="3">
         <f>IF(B149:B357="common", 4, IF(B149:B357="uncommon", 3, IF(B149:B357="rare", 0.792892156862745, 1)))</f>
@@ -8461,7 +8461,7 @@
         <v>188</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>25.05</v>
+        <v>26.2</v>
       </c>
       <c r="E150" s="3" t="inlineStr"/>
       <c r="F150" s="3">
@@ -8512,10 +8512,10 @@
         <v>33</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="F151" s="3">
         <f>IF(B151:B359="common", 4, IF(B151:B359="uncommon", 3, IF(B151:B359="rare", 0.792892156862745, 1)))</f>
@@ -8565,10 +8565,10 @@
         <v>46</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="F152" s="3">
         <f>IF(B152:B360="common", 4, IF(B152:B360="uncommon", 3, IF(B152:B360="rare", 0.792892156862745, 1)))</f>
@@ -8618,10 +8618,10 @@
         <v>46</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="F153" s="3">
         <f>IF(B153:B361="common", 4, IF(B153:B361="uncommon", 3, IF(B153:B361="rare", 0.792892156862745, 1)))</f>
@@ -8671,7 +8671,7 @@
         <v>188</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>16.47</v>
+        <v>15.85</v>
       </c>
       <c r="E154" s="3" t="inlineStr"/>
       <c r="F154" s="3">
@@ -8775,7 +8775,7 @@
         <v>46</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E156" s="3" t="n">
         <v>0.11</v>
@@ -8831,7 +8831,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F157" s="3">
         <f>IF(B157:B365="common", 4, IF(B157:B365="uncommon", 3, IF(B157:B365="rare", 0.792892156862745, 1)))</f>
@@ -8881,10 +8881,10 @@
         <v>33</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F158" s="3">
         <f>IF(B158:B366="common", 4, IF(B158:B366="uncommon", 3, IF(B158:B366="rare", 0.792892156862745, 1)))</f>
@@ -8937,7 +8937,7 @@
         <v>0.12</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="F159" s="3">
         <f>IF(B159:B367="common", 4, IF(B159:B367="uncommon", 3, IF(B159:B367="rare", 0.792892156862745, 1)))</f>
@@ -8987,10 +8987,10 @@
         <v>46</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="F160" s="3">
         <f>IF(B160:B368="common", 4, IF(B160:B368="uncommon", 3, IF(B160:B368="rare", 0.792892156862745, 1)))</f>
@@ -9040,7 +9040,7 @@
         <v>188</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>17.87</v>
+        <v>17.69</v>
       </c>
       <c r="E161" s="3" t="inlineStr"/>
       <c r="F161" s="3">
@@ -9091,10 +9091,10 @@
         <v>21</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="F162" s="3">
         <f>IF(B162:B370="common", 4, IF(B162:B370="uncommon", 3, IF(B162:B370="rare", 0.792892156862745, 1)))</f>
@@ -9144,10 +9144,10 @@
         <v>33</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="F163" s="3">
         <f>IF(B163:B371="common", 4, IF(B163:B371="uncommon", 3, IF(B163:B371="rare", 0.792892156862745, 1)))</f>
@@ -9197,7 +9197,7 @@
         <v>33</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E164" s="3" t="n">
         <v>0.14</v>
@@ -9253,7 +9253,7 @@
         <v>0.05</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="F165" s="3">
         <f>IF(B165:B373="common", 4, IF(B165:B373="uncommon", 3, IF(B165:B373="rare", 0.792892156862745, 1)))</f>
@@ -9303,7 +9303,7 @@
         <v>33</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E166" s="3" t="n">
         <v>0.12</v>
@@ -9359,7 +9359,7 @@
         <v>0.06</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F167" s="3">
         <f>IF(B167:B375="common", 4, IF(B167:B375="uncommon", 3, IF(B167:B375="rare", 0.792892156862745, 1)))</f>
@@ -9409,10 +9409,10 @@
         <v>33</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="F168" s="3">
         <f>IF(B168:B376="common", 4, IF(B168:B376="uncommon", 3, IF(B168:B376="rare", 0.792892156862745, 1)))</f>
@@ -9462,7 +9462,7 @@
         <v>46</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E169" s="3" t="n">
         <v>0.15</v>
@@ -9518,7 +9518,7 @@
         <v>0.06</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F170" s="3">
         <f>IF(B170:B378="common", 4, IF(B170:B378="uncommon", 3, IF(B170:B378="rare", 0.792892156862745, 1)))</f>
@@ -9568,10 +9568,10 @@
         <v>33</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="F171" s="3">
         <f>IF(B171:B379="common", 4, IF(B171:B379="uncommon", 3, IF(B171:B379="rare", 0.792892156862745, 1)))</f>
@@ -9621,10 +9621,10 @@
         <v>33</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="F172" s="3">
         <f>IF(B172:B380="common", 4, IF(B172:B380="uncommon", 3, IF(B172:B380="rare", 0.792892156862745, 1)))</f>
@@ -9674,7 +9674,7 @@
         <v>33</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E173" s="3" t="n">
         <v>0.85</v>
@@ -9727,7 +9727,7 @@
         <v>46</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E174" s="3" t="n">
         <v>0.13</v>
@@ -9783,7 +9783,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="F175" s="3">
         <f>IF(B175:B383="common", 4, IF(B175:B383="uncommon", 3, IF(B175:B383="rare", 0.792892156862745, 1)))</f>
@@ -9836,7 +9836,7 @@
         <v>0.09</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="F176" s="3">
         <f>IF(B176:B384="common", 4, IF(B176:B384="uncommon", 3, IF(B176:B384="rare", 0.792892156862745, 1)))</f>
@@ -9886,10 +9886,10 @@
         <v>46</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F177" s="3">
         <f>IF(B177:B385="common", 4, IF(B177:B385="uncommon", 3, IF(B177:B385="rare", 0.792892156862745, 1)))</f>
@@ -9939,10 +9939,10 @@
         <v>33</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="F178" s="3">
         <f>IF(B178:B386="common", 4, IF(B178:B386="uncommon", 3, IF(B178:B386="rare", 0.792892156862745, 1)))</f>
@@ -9995,7 +9995,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="F179" s="3">
         <f>IF(B179:B387="common", 4, IF(B179:B387="uncommon", 3, IF(B179:B387="rare", 0.792892156862745, 1)))</f>
@@ -10045,7 +10045,7 @@
         <v>46</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E180" s="3" t="n">
         <v>0.22</v>
@@ -10098,7 +10098,7 @@
         <v>188</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>41.55</v>
+        <v>42.27</v>
       </c>
       <c r="E181" s="3" t="inlineStr"/>
       <c r="F181" s="3">
@@ -10149,10 +10149,10 @@
         <v>21</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="F182" s="3">
         <f>IF(B182:B390="common", 4, IF(B182:B390="uncommon", 3, IF(B182:B390="rare", 0.792892156862745, 1)))</f>
@@ -10205,7 +10205,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F183" s="3">
         <f>IF(B183:B391="common", 4, IF(B183:B391="uncommon", 3, IF(B183:B391="rare", 0.792892156862745, 1)))</f>
@@ -10255,7 +10255,7 @@
         <v>154</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="E184" s="3" t="inlineStr"/>
       <c r="F184" s="3">
@@ -10306,10 +10306,10 @@
         <v>46</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F185" s="3">
         <f>IF(B185:B393="common", 4, IF(B185:B393="uncommon", 3, IF(B185:B393="rare", 0.792892156862745, 1)))</f>
@@ -10359,7 +10359,7 @@
         <v>188</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>6.49</v>
+        <v>6.11</v>
       </c>
       <c r="E186" s="3" t="inlineStr"/>
       <c r="F186" s="3">
@@ -10410,10 +10410,10 @@
         <v>33</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="F187" s="3">
         <f>IF(B187:B395="common", 4, IF(B187:B395="uncommon", 3, IF(B187:B395="rare", 0.792892156862745, 1)))</f>
@@ -10463,7 +10463,7 @@
         <v>46</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E188" s="3" t="n">
         <v>0.11</v>
@@ -10519,7 +10519,7 @@
         <v>0.05</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F189" s="3">
         <f>IF(B189:B397="common", 4, IF(B189:B397="uncommon", 3, IF(B189:B397="rare", 0.792892156862745, 1)))</f>
@@ -10569,10 +10569,10 @@
         <v>21</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="F190" s="3">
         <f>IF(B190:B398="common", 4, IF(B190:B398="uncommon", 3, IF(B190:B398="rare", 0.792892156862745, 1)))</f>
@@ -10622,10 +10622,10 @@
         <v>33</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="F191" s="3">
         <f>IF(B191:B399="common", 4, IF(B191:B399="uncommon", 3, IF(B191:B399="rare", 0.792892156862745, 1)))</f>
@@ -10675,10 +10675,10 @@
         <v>46</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F192" s="3">
         <f>IF(B192:B400="common", 4, IF(B192:B400="uncommon", 3, IF(B192:B400="rare", 0.792892156862745, 1)))</f>
@@ -10728,7 +10728,7 @@
         <v>90</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="E193" s="3" t="inlineStr"/>
       <c r="F193" s="3">
@@ -10779,7 +10779,7 @@
         <v>248</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>9.75</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E194" s="3" t="inlineStr"/>
       <c r="F194" s="3">
@@ -10830,7 +10830,7 @@
         <v>225</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>62.3</v>
+        <v>59.53</v>
       </c>
       <c r="E195" s="3" t="inlineStr"/>
       <c r="F195" s="3">
@@ -10884,7 +10884,7 @@
         <v>0.08</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F196" s="3">
         <f>IF(B196:B404="common", 4, IF(B196:B404="uncommon", 3, IF(B196:B404="rare", 0.792892156862745, 1)))</f>
@@ -10934,10 +10934,10 @@
         <v>21</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="F197" s="3">
         <f>IF(B197:B405="common", 4, IF(B197:B405="uncommon", 3, IF(B197:B405="rare", 0.792892156862745, 1)))</f>
@@ -11040,10 +11040,10 @@
         <v>46</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F199" s="3">
         <f>IF(B199:B407="common", 4, IF(B199:B407="uncommon", 3, IF(B199:B407="rare", 0.792892156862745, 1)))</f>
@@ -11096,7 +11096,7 @@
         <v>0.1</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="F200" s="3">
         <f>IF(B200:B408="common", 4, IF(B200:B408="uncommon", 3, IF(B200:B408="rare", 0.792892156862745, 1)))</f>
@@ -11146,7 +11146,7 @@
         <v>188</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>25.92</v>
+        <v>25.79</v>
       </c>
       <c r="E201" s="3" t="inlineStr"/>
       <c r="F201" s="3">
@@ -11197,7 +11197,7 @@
         <v>46</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E202" s="3" t="n">
         <v>0.13</v>
@@ -11250,10 +11250,10 @@
         <v>46</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="F203" s="3">
         <f>IF(B203:B411="common", 4, IF(B203:B411="uncommon", 3, IF(B203:B411="rare", 0.792892156862745, 1)))</f>
@@ -11303,10 +11303,10 @@
         <v>21</v>
       </c>
       <c r="D204" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F204" s="3">
         <f>IF(B204:B412="common", 4, IF(B204:B412="uncommon", 3, IF(B204:B412="rare", 0.792892156862745, 1)))</f>
@@ -11356,7 +11356,7 @@
         <v>90</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="E205" s="3" t="inlineStr"/>
       <c r="F205" s="3">
@@ -11407,7 +11407,7 @@
         <v>248</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>6.73</v>
+        <v>6.57</v>
       </c>
       <c r="E206" s="3" t="inlineStr"/>
       <c r="F206" s="3">
@@ -11509,7 +11509,7 @@
         <v>248</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>8.390000000000001</v>
+        <v>7.56</v>
       </c>
       <c r="E208" s="3" t="inlineStr"/>
       <c r="F208" s="3">
@@ -11560,7 +11560,7 @@
         <v>225</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>50.6</v>
+        <v>47.94</v>
       </c>
       <c r="E209" s="3" t="inlineStr"/>
       <c r="F209" s="3">
@@ -18298,7 +18298,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>0.4417391304347826</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="3">
@@ -18308,7 +18308,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>0.4863636363636364</v>
+        <v>0.4936363636363635</v>
       </c>
     </row>
     <row r="4">
@@ -18318,7 +18318,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>0.1940697945845005</v>
+        <v>0.1970903361344538</v>
       </c>
     </row>
     <row r="5">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>4.939317917137211</v>
+        <v>5.123054663482653</v>
       </c>
     </row>
     <row r="6">
@@ -18368,7 +18368,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1.812872340425532</v>
+        <v>1.801808510638298</v>
       </c>
     </row>
     <row r="10">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>2.028444444444444</v>
+        <v>1.998</v>
       </c>
     </row>
     <row r="11">
@@ -18388,7 +18388,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>0.327</v>
+        <v>0.3487777777777778</v>
       </c>
     </row>
     <row r="12">
@@ -18398,7 +18398,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>0.1297402597402597</v>
+        <v>0.1273376623376623</v>
       </c>
     </row>
     <row r="13">
@@ -18408,7 +18408,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>0.5618548387096775</v>
+        <v>0.5482258064516129</v>
       </c>
     </row>
     <row r="14">
@@ -18438,7 +18438,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>4.859911883319915</v>
+        <v>4.824149757205351</v>
       </c>
     </row>
     <row r="17">
@@ -18448,7 +18448,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>10.92140236184004</v>
+        <v>11.07793112045882</v>
       </c>
     </row>
     <row r="18">
@@ -18458,7 +18458,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1.491402361840045</v>
+        <v>1.517931120458821</v>
       </c>
     </row>
     <row r="19">
@@ -18468,7 +18468,7 @@
         </is>
       </c>
       <c r="B19" s="14" t="n">
-        <v>1.158155075486749</v>
+        <v>1.158779405905734</v>
       </c>
     </row>
     <row r="20">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>0.1581550754867491</v>
+        <v>0.1587794059057344</v>
       </c>
     </row>
     <row r="21">

--- a/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
+++ b/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
@@ -659,10 +659,10 @@
         <v>46</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="F2" s="3">
         <f>IF(B2:B210="common", 4, IF(B2:B210="uncommon", 3, IF(B2:B210="rare", 0.792892156862745, 1)))</f>
@@ -677,20 +677,20 @@
         <v/>
       </c>
       <c r="I2" s="3" t="n">
-        <v>9.56</v>
+        <v>9.73</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>66.05</v>
+        <v>65.38</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>231.7</v>
+        <v>232.49</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>5.84</v>
+        <v>5.93</v>
       </c>
       <c r="M2" s="3" t="n"/>
       <c r="N2" s="3" t="n">
-        <v>373.07</v>
+        <v>372.1</v>
       </c>
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
@@ -728,10 +728,10 @@
         <v>21</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="F3" s="3">
         <f>IF(B3:B211="common", 4, IF(B3:B211="uncommon", 3, IF(B3:B211="rare", 0.792892156862745, 1)))</f>
@@ -784,7 +784,7 @@
         <v>90</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3">
@@ -838,7 +838,7 @@
         <v>248</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7.37</v>
+        <v>7.41</v>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3">
@@ -892,7 +892,7 @@
         <v>225</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>37.41</v>
+        <v>36.43</v>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3">
@@ -946,10 +946,10 @@
         <v>46</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="F7" s="3">
         <f>IF(B7:B215="common", 4, IF(B7:B215="uncommon", 3, IF(B7:B215="rare", 0.792892156862745, 1)))</f>
@@ -1002,10 +1002,10 @@
         <v>46</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="F8" s="3">
         <f>IF(B8:B216="common", 4, IF(B8:B216="uncommon", 3, IF(B8:B216="rare", 0.792892156862745, 1)))</f>
@@ -1058,10 +1058,10 @@
         <v>46</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="F9" s="3">
         <f>IF(B9:B217="common", 4, IF(B9:B217="uncommon", 3, IF(B9:B217="rare", 0.792892156862745, 1)))</f>
@@ -1114,7 +1114,7 @@
         <v>90</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.98</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3">
@@ -1168,7 +1168,7 @@
         <v>248</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.63</v>
+        <v>5.38</v>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3">
@@ -1219,10 +1219,10 @@
         <v>33</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F12" s="3">
         <f>IF(B12:B220="common", 4, IF(B12:B220="uncommon", 3, IF(B12:B220="rare", 0.792892156862745, 1)))</f>
@@ -1275,7 +1275,7 @@
         <v>0.2</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.92</v>
+        <v>1.1</v>
       </c>
       <c r="F13" s="3">
         <f>IF(B13:B221="common", 4, IF(B13:B221="uncommon", 3, IF(B13:B221="rare", 0.792892156862745, 1)))</f>
@@ -1325,7 +1325,7 @@
         <v>154</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.21</v>
+        <v>4.61</v>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3">
@@ -1376,10 +1376,10 @@
         <v>21</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="F15" s="3">
         <f>IF(B15:B223="common", 4, IF(B15:B223="uncommon", 3, IF(B15:B223="rare", 0.792892156862745, 1)))</f>
@@ -1432,7 +1432,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F16" s="3">
         <f>IF(B16:B224="common", 4, IF(B16:B224="uncommon", 3, IF(B16:B224="rare", 0.792892156862745, 1)))</f>
@@ -1482,10 +1482,10 @@
         <v>33</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="F17" s="3">
         <f>IF(B17:B225="common", 4, IF(B17:B225="uncommon", 3, IF(B17:B225="rare", 0.792892156862745, 1)))</f>
@@ -1538,7 +1538,7 @@
         <v>0.11</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="F18" s="3">
         <f>IF(B18:B226="common", 4, IF(B18:B226="uncommon", 3, IF(B18:B226="rare", 0.792892156862745, 1)))</f>
@@ -1588,7 +1588,7 @@
         <v>248</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3">
@@ -1639,7 +1639,7 @@
         <v>90</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.84</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E20" s="3" t="inlineStr"/>
       <c r="F20" s="3">
@@ -1690,7 +1690,7 @@
         <v>248</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14</v>
+        <v>13.25</v>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3">
@@ -1741,7 +1741,7 @@
         <v>225</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>68.63</v>
+        <v>65.98</v>
       </c>
       <c r="E22" s="3" t="inlineStr"/>
       <c r="F22" s="3">
@@ -1795,7 +1795,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="F23" s="3">
         <f>IF(B23:B231="common", 4, IF(B23:B231="uncommon", 3, IF(B23:B231="rare", 0.792892156862745, 1)))</f>
@@ -1845,7 +1845,7 @@
         <v>188</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>37.15</v>
+        <v>33.97</v>
       </c>
       <c r="E24" s="3" t="inlineStr"/>
       <c r="F24" s="3">
@@ -1896,10 +1896,10 @@
         <v>33</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="F25" s="3">
         <f>IF(B25:B233="common", 4, IF(B25:B233="uncommon", 3, IF(B25:B233="rare", 0.792892156862745, 1)))</f>
@@ -1949,10 +1949,10 @@
         <v>46</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="F26" s="3">
         <f>IF(B26:B234="common", 4, IF(B26:B234="uncommon", 3, IF(B26:B234="rare", 0.792892156862745, 1)))</f>
@@ -2002,7 +2002,7 @@
         <v>188</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>7.82</v>
+        <v>7.77</v>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3">
@@ -2053,10 +2053,10 @@
         <v>21</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="F28" s="3">
         <f>IF(B28:B236="common", 4, IF(B28:B236="uncommon", 3, IF(B28:B236="rare", 0.792892156862745, 1)))</f>
@@ -2106,7 +2106,7 @@
         <v>90</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.11</v>
+        <v>3.86</v>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3">
@@ -2157,7 +2157,7 @@
         <v>248</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>27.19</v>
+        <v>25.18</v>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3">
@@ -2208,7 +2208,7 @@
         <v>225</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>208.72</v>
+        <v>206.26</v>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3">
@@ -2259,10 +2259,10 @@
         <v>46</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="F32" s="3">
         <f>IF(B32:B240="common", 4, IF(B32:B240="uncommon", 3, IF(B32:B240="rare", 0.792892156862745, 1)))</f>
@@ -2312,7 +2312,7 @@
         <v>188</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>46.03</v>
+        <v>42.53</v>
       </c>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3">
@@ -2363,10 +2363,10 @@
         <v>33</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.33</v>
+        <v>0.21</v>
       </c>
       <c r="F34" s="3">
         <f>IF(B34:B242="common", 4, IF(B34:B242="uncommon", 3, IF(B34:B242="rare", 0.792892156862745, 1)))</f>
@@ -2416,7 +2416,7 @@
         <v>188</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>33.1</v>
+        <v>32.92</v>
       </c>
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3">
@@ -2470,7 +2470,7 @@
         <v>0.06</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="F36" s="3">
         <f>IF(B36:B244="common", 4, IF(B36:B244="uncommon", 3, IF(B36:B244="rare", 0.792892156862745, 1)))</f>
@@ -2523,7 +2523,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F37" s="3">
         <f>IF(B37:B245="common", 4, IF(B37:B245="uncommon", 3, IF(B37:B245="rare", 0.792892156862745, 1)))</f>
@@ -2576,7 +2576,7 @@
         <v>0.06</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="F38" s="3">
         <f>IF(B38:B246="common", 4, IF(B38:B246="uncommon", 3, IF(B38:B246="rare", 0.792892156862745, 1)))</f>
@@ -2629,7 +2629,7 @@
         <v>0.08</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="F39" s="3">
         <f>IF(B39:B247="common", 4, IF(B39:B247="uncommon", 3, IF(B39:B247="rare", 0.792892156862745, 1)))</f>
@@ -2679,10 +2679,10 @@
         <v>33</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="F40" s="3">
         <f>IF(B40:B248="common", 4, IF(B40:B248="uncommon", 3, IF(B40:B248="rare", 0.792892156862745, 1)))</f>
@@ -2735,7 +2735,7 @@
         <v>0.09</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="F41" s="3">
         <f>IF(B41:B249="common", 4, IF(B41:B249="uncommon", 3, IF(B41:B249="rare", 0.792892156862745, 1)))</f>
@@ -2785,7 +2785,7 @@
         <v>248</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>2.77</v>
+        <v>3.18</v>
       </c>
       <c r="E42" s="3" t="inlineStr"/>
       <c r="F42" s="3">
@@ -2839,7 +2839,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F43" s="3">
         <f>IF(B43:B251="common", 4, IF(B43:B251="uncommon", 3, IF(B43:B251="rare", 0.792892156862745, 1)))</f>
@@ -2892,7 +2892,7 @@
         <v>0.05</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="F44" s="3">
         <f>IF(B44:B252="common", 4, IF(B44:B252="uncommon", 3, IF(B44:B252="rare", 0.792892156862745, 1)))</f>
@@ -2945,7 +2945,7 @@
         <v>0.28</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="F45" s="3">
         <f>IF(B45:B253="common", 4, IF(B45:B253="uncommon", 3, IF(B45:B253="rare", 0.792892156862745, 1)))</f>
@@ -2995,7 +2995,7 @@
         <v>21</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="E46" s="3" t="inlineStr"/>
       <c r="F46" s="3">
@@ -3049,7 +3049,7 @@
         <v>0.13</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="F47" s="3">
         <f>IF(B47:B255="common", 4, IF(B47:B255="uncommon", 3, IF(B47:B255="rare", 0.792892156862745, 1)))</f>
@@ -3155,7 +3155,7 @@
         <v>0.13</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="F49" s="3">
         <f>IF(B49:B257="common", 4, IF(B49:B257="uncommon", 3, IF(B49:B257="rare", 0.792892156862745, 1)))</f>
@@ -3205,7 +3205,7 @@
         <v>188</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>23.41</v>
+        <v>20.09</v>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="3">
@@ -3256,10 +3256,10 @@
         <v>21</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="F51" s="3">
         <f>IF(B51:B259="common", 4, IF(B51:B259="uncommon", 3, IF(B51:B259="rare", 0.792892156862745, 1)))</f>
@@ -3312,7 +3312,7 @@
         <v>0.1</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="F52" s="3">
         <f>IF(B52:B260="common", 4, IF(B52:B260="uncommon", 3, IF(B52:B260="rare", 0.792892156862745, 1)))</f>
@@ -3362,10 +3362,10 @@
         <v>46</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F53" s="3">
         <f>IF(B53:B261="common", 4, IF(B53:B261="uncommon", 3, IF(B53:B261="rare", 0.792892156862745, 1)))</f>
@@ -3418,7 +3418,7 @@
         <v>0.06</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="F54" s="3">
         <f>IF(B54:B262="common", 4, IF(B54:B262="uncommon", 3, IF(B54:B262="rare", 0.792892156862745, 1)))</f>
@@ -3468,10 +3468,10 @@
         <v>46</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="F55" s="3">
         <f>IF(B55:B263="common", 4, IF(B55:B263="uncommon", 3, IF(B55:B263="rare", 0.792892156862745, 1)))</f>
@@ -3521,10 +3521,10 @@
         <v>46</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F56" s="3">
         <f>IF(B56:B264="common", 4, IF(B56:B264="uncommon", 3, IF(B56:B264="rare", 0.792892156862745, 1)))</f>
@@ -3577,7 +3577,7 @@
         <v>0.06</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.52</v>
+        <v>0.66</v>
       </c>
       <c r="F57" s="3">
         <f>IF(B57:B265="common", 4, IF(B57:B265="uncommon", 3, IF(B57:B265="rare", 0.792892156862745, 1)))</f>
@@ -3630,7 +3630,7 @@
         <v>0.14</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="F58" s="3">
         <f>IF(B58:B266="common", 4, IF(B58:B266="uncommon", 3, IF(B58:B266="rare", 0.792892156862745, 1)))</f>
@@ -3680,10 +3680,10 @@
         <v>33</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="F59" s="3">
         <f>IF(B59:B267="common", 4, IF(B59:B267="uncommon", 3, IF(B59:B267="rare", 0.792892156862745, 1)))</f>
@@ -3736,7 +3736,7 @@
         <v>0.09</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="F60" s="3">
         <f>IF(B60:B268="common", 4, IF(B60:B268="uncommon", 3, IF(B60:B268="rare", 0.792892156862745, 1)))</f>
@@ -3786,7 +3786,7 @@
         <v>248</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>4.95</v>
+        <v>5.88</v>
       </c>
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3">
@@ -3837,7 +3837,7 @@
         <v>225</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>13.96</v>
+        <v>13.84</v>
       </c>
       <c r="E62" s="3" t="inlineStr"/>
       <c r="F62" s="3">
@@ -3944,7 +3944,7 @@
         <v>0.08</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="F64" s="3">
         <f>IF(B64:B272="common", 4, IF(B64:B272="uncommon", 3, IF(B64:B272="rare", 0.792892156862745, 1)))</f>
@@ -3997,7 +3997,7 @@
         <v>0.05</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F65" s="3">
         <f>IF(B65:B273="common", 4, IF(B65:B273="uncommon", 3, IF(B65:B273="rare", 0.792892156862745, 1)))</f>
@@ -4047,10 +4047,10 @@
         <v>33</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F66" s="3">
         <f>IF(B66:B274="common", 4, IF(B66:B274="uncommon", 3, IF(B66:B274="rare", 0.792892156862745, 1)))</f>
@@ -4100,10 +4100,10 @@
         <v>21</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="F67" s="3">
         <f>IF(B67:B275="common", 4, IF(B67:B275="uncommon", 3, IF(B67:B275="rare", 0.792892156862745, 1)))</f>
@@ -4153,10 +4153,10 @@
         <v>46</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="F68" s="3">
         <f>IF(B68:B276="common", 4, IF(B68:B276="uncommon", 3, IF(B68:B276="rare", 0.792892156862745, 1)))</f>
@@ -4206,10 +4206,10 @@
         <v>21</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="F69" s="3">
         <f>IF(B69:B277="common", 4, IF(B69:B277="uncommon", 3, IF(B69:B277="rare", 0.792892156862745, 1)))</f>
@@ -4259,10 +4259,10 @@
         <v>46</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="F70" s="3">
         <f>IF(B70:B278="common", 4, IF(B70:B278="uncommon", 3, IF(B70:B278="rare", 0.792892156862745, 1)))</f>
@@ -4312,10 +4312,10 @@
         <v>33</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F71" s="3">
         <f>IF(B71:B279="common", 4, IF(B71:B279="uncommon", 3, IF(B71:B279="rare", 0.792892156862745, 1)))</f>
@@ -4365,7 +4365,7 @@
         <v>248</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>5.21</v>
+        <v>5.54</v>
       </c>
       <c r="E72" s="3" t="inlineStr"/>
       <c r="F72" s="3">
@@ -4416,7 +4416,7 @@
         <v>225</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>13.36</v>
+        <v>13.18</v>
       </c>
       <c r="E73" s="3" t="inlineStr"/>
       <c r="F73" s="3">
@@ -4467,10 +4467,10 @@
         <v>33</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="F74" s="3">
         <f>IF(B74:B282="common", 4, IF(B74:B282="uncommon", 3, IF(B74:B282="rare", 0.792892156862745, 1)))</f>
@@ -4520,10 +4520,10 @@
         <v>33</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="F75" s="3">
         <f>IF(B75:B283="common", 4, IF(B75:B283="uncommon", 3, IF(B75:B283="rare", 0.792892156862745, 1)))</f>
@@ -4573,10 +4573,10 @@
         <v>46</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="F76" s="3">
         <f>IF(B76:B284="common", 4, IF(B76:B284="uncommon", 3, IF(B76:B284="rare", 0.792892156862745, 1)))</f>
@@ -4679,7 +4679,7 @@
         <v>90</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.75</v>
+        <v>0.61</v>
       </c>
       <c r="E78" s="3" t="inlineStr"/>
       <c r="F78" s="3">
@@ -4784,7 +4784,7 @@
         <v>0.12</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="F80" s="3">
         <f>IF(B80:B288="common", 4, IF(B80:B288="uncommon", 3, IF(B80:B288="rare", 0.792892156862745, 1)))</f>
@@ -4837,7 +4837,7 @@
         <v>0.06</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="F81" s="3">
         <f>IF(B81:B289="common", 4, IF(B81:B289="uncommon", 3, IF(B81:B289="rare", 0.792892156862745, 1)))</f>
@@ -4890,7 +4890,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="F82" s="3">
         <f>IF(B82:B290="common", 4, IF(B82:B290="uncommon", 3, IF(B82:B290="rare", 0.792892156862745, 1)))</f>
@@ -4940,10 +4940,10 @@
         <v>46</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F83" s="3">
         <f>IF(B83:B291="common", 4, IF(B83:B291="uncommon", 3, IF(B83:B291="rare", 0.792892156862745, 1)))</f>
@@ -4993,10 +4993,10 @@
         <v>21</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="F84" s="3">
         <f>IF(B84:B292="common", 4, IF(B84:B292="uncommon", 3, IF(B84:B292="rare", 0.792892156862745, 1)))</f>
@@ -5046,10 +5046,10 @@
         <v>33</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="F85" s="3">
         <f>IF(B85:B293="common", 4, IF(B85:B293="uncommon", 3, IF(B85:B293="rare", 0.792892156862745, 1)))</f>
@@ -5102,7 +5102,7 @@
         <v>0.11</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="F86" s="3">
         <f>IF(B86:B294="common", 4, IF(B86:B294="uncommon", 3, IF(B86:B294="rare", 0.792892156862745, 1)))</f>
@@ -5155,7 +5155,7 @@
         <v>0.12</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="F87" s="3">
         <f>IF(B87:B295="common", 4, IF(B87:B295="uncommon", 3, IF(B87:B295="rare", 0.792892156862745, 1)))</f>
@@ -5205,10 +5205,10 @@
         <v>46</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="F88" s="3">
         <f>IF(B88:B296="common", 4, IF(B88:B296="uncommon", 3, IF(B88:B296="rare", 0.792892156862745, 1)))</f>
@@ -5258,10 +5258,10 @@
         <v>33</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="F89" s="3">
         <f>IF(B89:B297="common", 4, IF(B89:B297="uncommon", 3, IF(B89:B297="rare", 0.792892156862745, 1)))</f>
@@ -5314,7 +5314,7 @@
         <v>0.1</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="F90" s="3">
         <f>IF(B90:B298="common", 4, IF(B90:B298="uncommon", 3, IF(B90:B298="rare", 0.792892156862745, 1)))</f>
@@ -5364,7 +5364,7 @@
         <v>188</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>27.64</v>
+        <v>27.43</v>
       </c>
       <c r="E91" s="3" t="inlineStr"/>
       <c r="F91" s="3">
@@ -5418,7 +5418,7 @@
         <v>0.08</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="F92" s="3">
         <f>IF(B92:B300="common", 4, IF(B92:B300="uncommon", 3, IF(B92:B300="rare", 0.792892156862745, 1)))</f>
@@ -5468,10 +5468,10 @@
         <v>21</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="F93" s="3">
         <f>IF(B93:B301="common", 4, IF(B93:B301="uncommon", 3, IF(B93:B301="rare", 0.792892156862745, 1)))</f>
@@ -5521,7 +5521,7 @@
         <v>90</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="E94" s="3" t="inlineStr"/>
       <c r="F94" s="3">
@@ -5572,7 +5572,7 @@
         <v>248</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>4.93</v>
+        <v>4.34</v>
       </c>
       <c r="E95" s="3" t="inlineStr"/>
       <c r="F95" s="3">
@@ -5626,7 +5626,7 @@
         <v>0.08</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="F96" s="3">
         <f>IF(B96:B304="common", 4, IF(B96:B304="uncommon", 3, IF(B96:B304="rare", 0.792892156862745, 1)))</f>
@@ -5676,10 +5676,10 @@
         <v>21</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="F97" s="3">
         <f>IF(B97:B305="common", 4, IF(B97:B305="uncommon", 3, IF(B97:B305="rare", 0.792892156862745, 1)))</f>
@@ -5729,7 +5729,7 @@
         <v>33</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E98" s="3" t="n">
         <v>0.19</v>
@@ -5785,7 +5785,7 @@
         <v>0.09</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="F99" s="3">
         <f>IF(B99:B307="common", 4, IF(B99:B307="uncommon", 3, IF(B99:B307="rare", 0.792892156862745, 1)))</f>
@@ -5835,7 +5835,7 @@
         <v>90</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="E100" s="3" t="inlineStr"/>
       <c r="F100" s="3">
@@ -5886,7 +5886,7 @@
         <v>248</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>4.44</v>
+        <v>4.81</v>
       </c>
       <c r="E101" s="3" t="inlineStr"/>
       <c r="F101" s="3">
@@ -5937,10 +5937,10 @@
         <v>33</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="F102" s="3">
         <f>IF(B102:B310="common", 4, IF(B102:B310="uncommon", 3, IF(B102:B310="rare", 0.792892156862745, 1)))</f>
@@ -5993,7 +5993,7 @@
         <v>0.08</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="F103" s="3">
         <f>IF(B103:B311="common", 4, IF(B103:B311="uncommon", 3, IF(B103:B311="rare", 0.792892156862745, 1)))</f>
@@ -6043,10 +6043,10 @@
         <v>46</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="F104" s="3">
         <f>IF(B104:B312="common", 4, IF(B104:B312="uncommon", 3, IF(B104:B312="rare", 0.792892156862745, 1)))</f>
@@ -6096,10 +6096,10 @@
         <v>33</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="F105" s="3">
         <f>IF(B105:B313="common", 4, IF(B105:B313="uncommon", 3, IF(B105:B313="rare", 0.792892156862745, 1)))</f>
@@ -6149,10 +6149,10 @@
         <v>33</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="F106" s="3">
         <f>IF(B106:B314="common", 4, IF(B106:B314="uncommon", 3, IF(B106:B314="rare", 0.792892156862745, 1)))</f>
@@ -6202,10 +6202,10 @@
         <v>46</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="F107" s="3">
         <f>IF(B107:B315="common", 4, IF(B107:B315="uncommon", 3, IF(B107:B315="rare", 0.792892156862745, 1)))</f>
@@ -6255,10 +6255,10 @@
         <v>21</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F108" s="3">
         <f>IF(B108:B316="common", 4, IF(B108:B316="uncommon", 3, IF(B108:B316="rare", 0.792892156862745, 1)))</f>
@@ -6308,10 +6308,10 @@
         <v>33</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="F109" s="3">
         <f>IF(B109:B317="common", 4, IF(B109:B317="uncommon", 3, IF(B109:B317="rare", 0.792892156862745, 1)))</f>
@@ -6361,7 +6361,7 @@
         <v>188</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>9.07</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E110" s="3" t="inlineStr"/>
       <c r="F110" s="3">
@@ -6412,10 +6412,10 @@
         <v>46</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="F111" s="3">
         <f>IF(B111:B319="common", 4, IF(B111:B319="uncommon", 3, IF(B111:B319="rare", 0.792892156862745, 1)))</f>
@@ -6468,7 +6468,7 @@
         <v>0.09</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F112" s="3">
         <f>IF(B112:B320="common", 4, IF(B112:B320="uncommon", 3, IF(B112:B320="rare", 0.792892156862745, 1)))</f>
@@ -6518,10 +6518,10 @@
         <v>46</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="F113" s="3">
         <f>IF(B113:B321="common", 4, IF(B113:B321="uncommon", 3, IF(B113:B321="rare", 0.792892156862745, 1)))</f>
@@ -6571,10 +6571,10 @@
         <v>46</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="F114" s="3">
         <f>IF(B114:B322="common", 4, IF(B114:B322="uncommon", 3, IF(B114:B322="rare", 0.792892156862745, 1)))</f>
@@ -6624,10 +6624,10 @@
         <v>33</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F115" s="3">
         <f>IF(B115:B323="common", 4, IF(B115:B323="uncommon", 3, IF(B115:B323="rare", 0.792892156862745, 1)))</f>
@@ -6677,10 +6677,10 @@
         <v>46</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="F116" s="3">
         <f>IF(B116:B324="common", 4, IF(B116:B324="uncommon", 3, IF(B116:B324="rare", 0.792892156862745, 1)))</f>
@@ -6730,10 +6730,10 @@
         <v>21</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="F117" s="3">
         <f>IF(B117:B325="common", 4, IF(B117:B325="uncommon", 3, IF(B117:B325="rare", 0.792892156862745, 1)))</f>
@@ -6783,10 +6783,10 @@
         <v>46</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="F118" s="3">
         <f>IF(B118:B326="common", 4, IF(B118:B326="uncommon", 3, IF(B118:B326="rare", 0.792892156862745, 1)))</f>
@@ -6836,10 +6836,10 @@
         <v>46</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="F119" s="3">
         <f>IF(B119:B327="common", 4, IF(B119:B327="uncommon", 3, IF(B119:B327="rare", 0.792892156862745, 1)))</f>
@@ -6889,7 +6889,7 @@
         <v>90</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>8.68</v>
+        <v>6.41</v>
       </c>
       <c r="E120" s="3" t="inlineStr"/>
       <c r="F120" s="3">
@@ -6940,7 +6940,7 @@
         <v>248</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>19.31</v>
+        <v>18.51</v>
       </c>
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3">
@@ -6991,7 +6991,7 @@
         <v>154</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>12.75</v>
+        <v>12.65</v>
       </c>
       <c r="E122" s="3" t="inlineStr"/>
       <c r="F122" s="3">
@@ -7042,7 +7042,7 @@
         <v>90</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>9.609999999999999</v>
+        <v>10.27</v>
       </c>
       <c r="E123" s="3" t="inlineStr"/>
       <c r="F123" s="3">
@@ -7093,10 +7093,10 @@
         <v>21</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="F124" s="3">
         <f>IF(B124:B332="common", 4, IF(B124:B332="uncommon", 3, IF(B124:B332="rare", 0.792892156862745, 1)))</f>
@@ -7146,10 +7146,10 @@
         <v>21</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="F125" s="3">
         <f>IF(B125:B333="common", 4, IF(B125:B333="uncommon", 3, IF(B125:B333="rare", 0.792892156862745, 1)))</f>
@@ -7199,10 +7199,10 @@
         <v>21</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
       <c r="F126" s="3">
         <f>IF(B126:B334="common", 4, IF(B126:B334="uncommon", 3, IF(B126:B334="rare", 0.792892156862745, 1)))</f>
@@ -7252,7 +7252,7 @@
         <v>188</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>5.86</v>
+        <v>5.65</v>
       </c>
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3">
@@ -7303,10 +7303,10 @@
         <v>33</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F128" s="3">
         <f>IF(B128:B336="common", 4, IF(B128:B336="uncommon", 3, IF(B128:B336="rare", 0.792892156862745, 1)))</f>
@@ -7356,10 +7356,10 @@
         <v>21</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="F129" s="3">
         <f>IF(B129:B337="common", 4, IF(B129:B337="uncommon", 3, IF(B129:B337="rare", 0.792892156862745, 1)))</f>
@@ -7409,7 +7409,7 @@
         <v>188</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>9.27</v>
+        <v>9.49</v>
       </c>
       <c r="E130" s="3" t="inlineStr"/>
       <c r="F130" s="3">
@@ -7460,7 +7460,7 @@
         <v>33</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E131" s="3" t="n">
         <v>0.17</v>
@@ -7513,10 +7513,10 @@
         <v>46</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="F132" s="3">
         <f>IF(B132:B340="common", 4, IF(B132:B340="uncommon", 3, IF(B132:B340="rare", 0.792892156862745, 1)))</f>
@@ -7569,7 +7569,7 @@
         <v>0.1</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="F133" s="3">
         <f>IF(B133:B341="common", 4, IF(B133:B341="uncommon", 3, IF(B133:B341="rare", 0.792892156862745, 1)))</f>
@@ -7619,10 +7619,10 @@
         <v>33</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="F134" s="3">
         <f>IF(B134:B342="common", 4, IF(B134:B342="uncommon", 3, IF(B134:B342="rare", 0.792892156862745, 1)))</f>
@@ -7672,10 +7672,10 @@
         <v>33</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="F135" s="3">
         <f>IF(B135:B343="common", 4, IF(B135:B343="uncommon", 3, IF(B135:B343="rare", 0.792892156862745, 1)))</f>
@@ -7725,7 +7725,7 @@
         <v>90</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="E136" s="3" t="inlineStr"/>
       <c r="F136" s="3">
@@ -7776,7 +7776,7 @@
         <v>248</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>7.61</v>
+        <v>7.37</v>
       </c>
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3">
@@ -7827,10 +7827,10 @@
         <v>46</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="F138" s="3">
         <f>IF(B138:B346="common", 4, IF(B138:B346="uncommon", 3, IF(B138:B346="rare", 0.792892156862745, 1)))</f>
@@ -7883,7 +7883,7 @@
         <v>0.09</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="F139" s="3">
         <f>IF(B139:B347="common", 4, IF(B139:B347="uncommon", 3, IF(B139:B347="rare", 0.792892156862745, 1)))</f>
@@ -7933,7 +7933,7 @@
         <v>188</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>5.48</v>
+        <v>5.82</v>
       </c>
       <c r="E140" s="3" t="inlineStr"/>
       <c r="F140" s="3">
@@ -7984,10 +7984,10 @@
         <v>21</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="F141" s="3">
         <f>IF(B141:B349="common", 4, IF(B141:B349="uncommon", 3, IF(B141:B349="rare", 0.792892156862745, 1)))</f>
@@ -8037,10 +8037,10 @@
         <v>33</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="F142" s="3">
         <f>IF(B142:B350="common", 4, IF(B142:B350="uncommon", 3, IF(B142:B350="rare", 0.792892156862745, 1)))</f>
@@ -8143,10 +8143,10 @@
         <v>33</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="F144" s="3">
         <f>IF(B144:B352="common", 4, IF(B144:B352="uncommon", 3, IF(B144:B352="rare", 0.792892156862745, 1)))</f>
@@ -8196,10 +8196,10 @@
         <v>33</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="F145" s="3">
         <f>IF(B145:B353="common", 4, IF(B145:B353="uncommon", 3, IF(B145:B353="rare", 0.792892156862745, 1)))</f>
@@ -8252,7 +8252,7 @@
         <v>0.09</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="F146" s="3">
         <f>IF(B146:B354="common", 4, IF(B146:B354="uncommon", 3, IF(B146:B354="rare", 0.792892156862745, 1)))</f>
@@ -8305,7 +8305,7 @@
         <v>0.15</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="F147" s="3">
         <f>IF(B147:B355="common", 4, IF(B147:B355="uncommon", 3, IF(B147:B355="rare", 0.792892156862745, 1)))</f>
@@ -8355,10 +8355,10 @@
         <v>46</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="F148" s="3">
         <f>IF(B148:B356="common", 4, IF(B148:B356="uncommon", 3, IF(B148:B356="rare", 0.792892156862745, 1)))</f>
@@ -8408,10 +8408,10 @@
         <v>46</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="F149" s="3">
         <f>IF(B149:B357="common", 4, IF(B149:B357="uncommon", 3, IF(B149:B357="rare", 0.792892156862745, 1)))</f>
@@ -8461,7 +8461,7 @@
         <v>188</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>26.2</v>
+        <v>24.97</v>
       </c>
       <c r="E150" s="3" t="inlineStr"/>
       <c r="F150" s="3">
@@ -8512,10 +8512,10 @@
         <v>33</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="F151" s="3">
         <f>IF(B151:B359="common", 4, IF(B151:B359="uncommon", 3, IF(B151:B359="rare", 0.792892156862745, 1)))</f>
@@ -8568,7 +8568,7 @@
         <v>0.05</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F152" s="3">
         <f>IF(B152:B360="common", 4, IF(B152:B360="uncommon", 3, IF(B152:B360="rare", 0.792892156862745, 1)))</f>
@@ -8621,7 +8621,7 @@
         <v>0.13</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="F153" s="3">
         <f>IF(B153:B361="common", 4, IF(B153:B361="uncommon", 3, IF(B153:B361="rare", 0.792892156862745, 1)))</f>
@@ -8671,7 +8671,7 @@
         <v>188</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>15.85</v>
+        <v>17.04</v>
       </c>
       <c r="E154" s="3" t="inlineStr"/>
       <c r="F154" s="3">
@@ -8775,10 +8775,10 @@
         <v>46</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="F156" s="3">
         <f>IF(B156:B364="common", 4, IF(B156:B364="uncommon", 3, IF(B156:B364="rare", 0.792892156862745, 1)))</f>
@@ -8828,10 +8828,10 @@
         <v>46</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="F157" s="3">
         <f>IF(B157:B365="common", 4, IF(B157:B365="uncommon", 3, IF(B157:B365="rare", 0.792892156862745, 1)))</f>
@@ -8881,10 +8881,10 @@
         <v>33</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F158" s="3">
         <f>IF(B158:B366="common", 4, IF(B158:B366="uncommon", 3, IF(B158:B366="rare", 0.792892156862745, 1)))</f>
@@ -8937,7 +8937,7 @@
         <v>0.12</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="F159" s="3">
         <f>IF(B159:B367="common", 4, IF(B159:B367="uncommon", 3, IF(B159:B367="rare", 0.792892156862745, 1)))</f>
@@ -8990,7 +8990,7 @@
         <v>0.08</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F160" s="3">
         <f>IF(B160:B368="common", 4, IF(B160:B368="uncommon", 3, IF(B160:B368="rare", 0.792892156862745, 1)))</f>
@@ -9040,7 +9040,7 @@
         <v>188</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>17.69</v>
+        <v>18.79</v>
       </c>
       <c r="E161" s="3" t="inlineStr"/>
       <c r="F161" s="3">
@@ -9091,10 +9091,10 @@
         <v>21</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>0.89</v>
+        <v>1.19</v>
       </c>
       <c r="F162" s="3">
         <f>IF(B162:B370="common", 4, IF(B162:B370="uncommon", 3, IF(B162:B370="rare", 0.792892156862745, 1)))</f>
@@ -9147,7 +9147,7 @@
         <v>0.08</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="F163" s="3">
         <f>IF(B163:B371="common", 4, IF(B163:B371="uncommon", 3, IF(B163:B371="rare", 0.792892156862745, 1)))</f>
@@ -9200,7 +9200,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F164" s="3">
         <f>IF(B164:B372="common", 4, IF(B164:B372="uncommon", 3, IF(B164:B372="rare", 0.792892156862745, 1)))</f>
@@ -9253,7 +9253,7 @@
         <v>0.05</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="F165" s="3">
         <f>IF(B165:B373="common", 4, IF(B165:B373="uncommon", 3, IF(B165:B373="rare", 0.792892156862745, 1)))</f>
@@ -9303,10 +9303,10 @@
         <v>33</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="F166" s="3">
         <f>IF(B166:B374="common", 4, IF(B166:B374="uncommon", 3, IF(B166:B374="rare", 0.792892156862745, 1)))</f>
@@ -9356,7 +9356,7 @@
         <v>46</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E167" s="3" t="n">
         <v>0.13</v>
@@ -9409,10 +9409,10 @@
         <v>33</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="F168" s="3">
         <f>IF(B168:B376="common", 4, IF(B168:B376="uncommon", 3, IF(B168:B376="rare", 0.792892156862745, 1)))</f>
@@ -9465,7 +9465,7 @@
         <v>0.05</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="F169" s="3">
         <f>IF(B169:B377="common", 4, IF(B169:B377="uncommon", 3, IF(B169:B377="rare", 0.792892156862745, 1)))</f>
@@ -9515,10 +9515,10 @@
         <v>33</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="F170" s="3">
         <f>IF(B170:B378="common", 4, IF(B170:B378="uncommon", 3, IF(B170:B378="rare", 0.792892156862745, 1)))</f>
@@ -9571,7 +9571,7 @@
         <v>0.09</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="F171" s="3">
         <f>IF(B171:B379="common", 4, IF(B171:B379="uncommon", 3, IF(B171:B379="rare", 0.792892156862745, 1)))</f>
@@ -9624,7 +9624,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F172" s="3">
         <f>IF(B172:B380="common", 4, IF(B172:B380="uncommon", 3, IF(B172:B380="rare", 0.792892156862745, 1)))</f>
@@ -9677,7 +9677,7 @@
         <v>0.1</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="F173" s="3">
         <f>IF(B173:B381="common", 4, IF(B173:B381="uncommon", 3, IF(B173:B381="rare", 0.792892156862745, 1)))</f>
@@ -9730,7 +9730,7 @@
         <v>0.05</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="F174" s="3">
         <f>IF(B174:B382="common", 4, IF(B174:B382="uncommon", 3, IF(B174:B382="rare", 0.792892156862745, 1)))</f>
@@ -9783,7 +9783,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="F175" s="3">
         <f>IF(B175:B383="common", 4, IF(B175:B383="uncommon", 3, IF(B175:B383="rare", 0.792892156862745, 1)))</f>
@@ -9833,10 +9833,10 @@
         <v>33</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F176" s="3">
         <f>IF(B176:B384="common", 4, IF(B176:B384="uncommon", 3, IF(B176:B384="rare", 0.792892156862745, 1)))</f>
@@ -9939,10 +9939,10 @@
         <v>33</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="F178" s="3">
         <f>IF(B178:B386="common", 4, IF(B178:B386="uncommon", 3, IF(B178:B386="rare", 0.792892156862745, 1)))</f>
@@ -9992,10 +9992,10 @@
         <v>46</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="F179" s="3">
         <f>IF(B179:B387="common", 4, IF(B179:B387="uncommon", 3, IF(B179:B387="rare", 0.792892156862745, 1)))</f>
@@ -10045,10 +10045,10 @@
         <v>46</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="F180" s="3">
         <f>IF(B180:B388="common", 4, IF(B180:B388="uncommon", 3, IF(B180:B388="rare", 0.792892156862745, 1)))</f>
@@ -10098,7 +10098,7 @@
         <v>188</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>42.27</v>
+        <v>40</v>
       </c>
       <c r="E181" s="3" t="inlineStr"/>
       <c r="F181" s="3">
@@ -10149,10 +10149,10 @@
         <v>21</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F182" s="3">
         <f>IF(B182:B390="common", 4, IF(B182:B390="uncommon", 3, IF(B182:B390="rare", 0.792892156862745, 1)))</f>
@@ -10205,7 +10205,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="F183" s="3">
         <f>IF(B183:B391="common", 4, IF(B183:B391="uncommon", 3, IF(B183:B391="rare", 0.792892156862745, 1)))</f>
@@ -10255,7 +10255,7 @@
         <v>154</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="E184" s="3" t="inlineStr"/>
       <c r="F184" s="3">
@@ -10309,7 +10309,7 @@
         <v>0.05</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F185" s="3">
         <f>IF(B185:B393="common", 4, IF(B185:B393="uncommon", 3, IF(B185:B393="rare", 0.792892156862745, 1)))</f>
@@ -10359,7 +10359,7 @@
         <v>188</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>6.11</v>
+        <v>6.7</v>
       </c>
       <c r="E186" s="3" t="inlineStr"/>
       <c r="F186" s="3">
@@ -10410,7 +10410,7 @@
         <v>33</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E187" s="3" t="n">
         <v>0.87</v>
@@ -10463,7 +10463,7 @@
         <v>46</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E188" s="3" t="n">
         <v>0.11</v>
@@ -10516,10 +10516,10 @@
         <v>33</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="F189" s="3">
         <f>IF(B189:B397="common", 4, IF(B189:B397="uncommon", 3, IF(B189:B397="rare", 0.792892156862745, 1)))</f>
@@ -10569,10 +10569,10 @@
         <v>21</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="F190" s="3">
         <f>IF(B190:B398="common", 4, IF(B190:B398="uncommon", 3, IF(B190:B398="rare", 0.792892156862745, 1)))</f>
@@ -10622,7 +10622,7 @@
         <v>33</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E191" s="3" t="n">
         <v>0.17</v>
@@ -10728,7 +10728,7 @@
         <v>90</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>0.73</v>
+        <v>0.55</v>
       </c>
       <c r="E193" s="3" t="inlineStr"/>
       <c r="F193" s="3">
@@ -10779,7 +10779,7 @@
         <v>248</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>9.779999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="E194" s="3" t="inlineStr"/>
       <c r="F194" s="3">
@@ -10830,7 +10830,7 @@
         <v>225</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>59.53</v>
+        <v>57.96</v>
       </c>
       <c r="E195" s="3" t="inlineStr"/>
       <c r="F195" s="3">
@@ -10884,7 +10884,7 @@
         <v>0.08</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="F196" s="3">
         <f>IF(B196:B404="common", 4, IF(B196:B404="uncommon", 3, IF(B196:B404="rare", 0.792892156862745, 1)))</f>
@@ -10934,10 +10934,10 @@
         <v>21</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="F197" s="3">
         <f>IF(B197:B405="common", 4, IF(B197:B405="uncommon", 3, IF(B197:B405="rare", 0.792892156862745, 1)))</f>
@@ -10987,10 +10987,10 @@
         <v>46</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="F198" s="3">
         <f>IF(B198:B406="common", 4, IF(B198:B406="uncommon", 3, IF(B198:B406="rare", 0.792892156862745, 1)))</f>
@@ -11043,7 +11043,7 @@
         <v>0.05</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="F199" s="3">
         <f>IF(B199:B407="common", 4, IF(B199:B407="uncommon", 3, IF(B199:B407="rare", 0.792892156862745, 1)))</f>
@@ -11096,7 +11096,7 @@
         <v>0.1</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="F200" s="3">
         <f>IF(B200:B408="common", 4, IF(B200:B408="uncommon", 3, IF(B200:B408="rare", 0.792892156862745, 1)))</f>
@@ -11146,7 +11146,7 @@
         <v>188</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>25.79</v>
+        <v>24.22</v>
       </c>
       <c r="E201" s="3" t="inlineStr"/>
       <c r="F201" s="3">
@@ -11197,7 +11197,7 @@
         <v>46</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E202" s="3" t="n">
         <v>0.13</v>
@@ -11250,10 +11250,10 @@
         <v>46</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="F203" s="3">
         <f>IF(B203:B411="common", 4, IF(B203:B411="uncommon", 3, IF(B203:B411="rare", 0.792892156862745, 1)))</f>
@@ -11306,7 +11306,7 @@
         <v>0.13</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="F204" s="3">
         <f>IF(B204:B412="common", 4, IF(B204:B412="uncommon", 3, IF(B204:B412="rare", 0.792892156862745, 1)))</f>
@@ -11356,7 +11356,7 @@
         <v>90</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="E205" s="3" t="inlineStr"/>
       <c r="F205" s="3">
@@ -11407,7 +11407,7 @@
         <v>248</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>6.57</v>
+        <v>6.9</v>
       </c>
       <c r="E206" s="3" t="inlineStr"/>
       <c r="F206" s="3">
@@ -11458,7 +11458,7 @@
         <v>90</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>0.9</v>
+        <v>0.76</v>
       </c>
       <c r="E207" s="3" t="inlineStr"/>
       <c r="F207" s="3">
@@ -11509,7 +11509,7 @@
         <v>248</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>7.56</v>
+        <v>7.15</v>
       </c>
       <c r="E208" s="3" t="inlineStr"/>
       <c r="F208" s="3">
@@ -11560,7 +11560,7 @@
         <v>225</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>47.94</v>
+        <v>46.15</v>
       </c>
       <c r="E209" s="3" t="inlineStr"/>
       <c r="F209" s="3">
@@ -11611,10 +11611,10 @@
         <v>46</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F210" s="3">
         <f>IF(B210:B418="common", 4, IF(B210:B418="uncommon", 3, IF(B210:B418="rare", 0.792892156862745, 1)))</f>
@@ -18298,7 +18298,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>0.44</v>
+        <v>0.4304347826086957</v>
       </c>
     </row>
     <row r="3">
@@ -18308,7 +18308,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>0.4936363636363635</v>
+        <v>0.4881818181818181</v>
       </c>
     </row>
     <row r="4">
@@ -18318,7 +18318,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>0.1970903361344538</v>
+        <v>0.2016211484593838</v>
       </c>
     </row>
     <row r="5">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>5.123054663482653</v>
+        <v>5.329323789133571</v>
       </c>
     </row>
     <row r="6">
@@ -18368,7 +18368,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1.801808510638298</v>
+        <v>1.740372340425532</v>
       </c>
     </row>
     <row r="10">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1.998</v>
+        <v>1.954666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -18388,7 +18388,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>0.3487777777777778</v>
+        <v>0.3157777777777778</v>
       </c>
     </row>
     <row r="12">
@@ -18398,7 +18398,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>0.1273376623376623</v>
+        <v>0.1305844155844156</v>
       </c>
     </row>
     <row r="13">
@@ -18408,7 +18408,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>0.5482258064516129</v>
+        <v>0.5363709677419355</v>
       </c>
     </row>
     <row r="14">
@@ -18438,7 +18438,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>4.824149757205351</v>
+        <v>4.677772168196328</v>
       </c>
     </row>
     <row r="17">
@@ -18448,7 +18448,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>11.07793112045882</v>
+        <v>11.12733370657979</v>
       </c>
     </row>
     <row r="18">
@@ -18458,7 +18458,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1.517931120458821</v>
+        <v>1.397333706579793</v>
       </c>
     </row>
     <row r="19">
@@ -18468,7 +18468,7 @@
         </is>
       </c>
       <c r="B19" s="14" t="n">
-        <v>1.158779405905734</v>
+        <v>1.14361086398559</v>
       </c>
     </row>
     <row r="20">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>0.1587794059057344</v>
+        <v>0.1436108639855902</v>
       </c>
     </row>
     <row r="21">

--- a/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
+++ b/Expected Value and Cost Ratio Calculator Pokemon/excelDocs/scarletAndViolet151/pokemon_data.xlsx
@@ -662,7 +662,7 @@
         <v>0.06</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F2" s="3">
         <f>IF(B2:B210="common", 4, IF(B2:B210="uncommon", 3, IF(B2:B210="rare", 0.792892156862745, 1)))</f>
@@ -677,20 +677,20 @@
         <v/>
       </c>
       <c r="I2" s="3" t="n">
-        <v>9.73</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>65.38</v>
+        <v>65.62</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>232.49</v>
+        <v>232.98</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>5.93</v>
+        <v>6.19</v>
       </c>
       <c r="M2" s="3" t="n"/>
       <c r="N2" s="3" t="n">
-        <v>372.1</v>
+        <v>372.92</v>
       </c>
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
@@ -728,10 +728,10 @@
         <v>21</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="F3" s="3">
         <f>IF(B3:B211="common", 4, IF(B3:B211="uncommon", 3, IF(B3:B211="rare", 0.792892156862745, 1)))</f>
@@ -838,7 +838,7 @@
         <v>248</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7.41</v>
+        <v>7.01</v>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3">
@@ -892,7 +892,7 @@
         <v>225</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36.43</v>
+        <v>36.5</v>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3">
@@ -946,7 +946,7 @@
         <v>46</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.58</v>
@@ -1002,10 +1002,10 @@
         <v>46</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="F8" s="3">
         <f>IF(B8:B216="common", 4, IF(B8:B216="uncommon", 3, IF(B8:B216="rare", 0.792892156862745, 1)))</f>
@@ -1058,10 +1058,10 @@
         <v>46</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="F9" s="3">
         <f>IF(B9:B217="common", 4, IF(B9:B217="uncommon", 3, IF(B9:B217="rare", 0.792892156862745, 1)))</f>
@@ -1114,7 +1114,7 @@
         <v>90</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3">
@@ -1168,7 +1168,7 @@
         <v>248</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.38</v>
+        <v>4.77</v>
       </c>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3">
@@ -1222,7 +1222,7 @@
         <v>0.06</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="F12" s="3">
         <f>IF(B12:B220="common", 4, IF(B12:B220="uncommon", 3, IF(B12:B220="rare", 0.792892156862745, 1)))</f>
@@ -1272,10 +1272,10 @@
         <v>21</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1.1</v>
+        <v>0.96</v>
       </c>
       <c r="F13" s="3">
         <f>IF(B13:B221="common", 4, IF(B13:B221="uncommon", 3, IF(B13:B221="rare", 0.792892156862745, 1)))</f>
@@ -1325,7 +1325,7 @@
         <v>154</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.61</v>
+        <v>4.45</v>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3">
@@ -1376,10 +1376,10 @@
         <v>21</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F15" s="3">
         <f>IF(B15:B223="common", 4, IF(B15:B223="uncommon", 3, IF(B15:B223="rare", 0.792892156862745, 1)))</f>
@@ -1429,7 +1429,7 @@
         <v>46</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0.11</v>
@@ -1485,7 +1485,7 @@
         <v>0.09</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="F17" s="3">
         <f>IF(B17:B225="common", 4, IF(B17:B225="uncommon", 3, IF(B17:B225="rare", 0.792892156862745, 1)))</f>
@@ -1538,7 +1538,7 @@
         <v>0.11</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="F18" s="3">
         <f>IF(B18:B226="common", 4, IF(B18:B226="uncommon", 3, IF(B18:B226="rare", 0.792892156862745, 1)))</f>
@@ -1588,7 +1588,7 @@
         <v>248</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3">
@@ -1639,7 +1639,7 @@
         <v>90</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="E20" s="3" t="inlineStr"/>
       <c r="F20" s="3">
@@ -1690,7 +1690,7 @@
         <v>248</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>13.25</v>
+        <v>13.09</v>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3">
@@ -1741,7 +1741,7 @@
         <v>225</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>65.98</v>
+        <v>65.44</v>
       </c>
       <c r="E22" s="3" t="inlineStr"/>
       <c r="F22" s="3">
@@ -1792,10 +1792,10 @@
         <v>46</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="F23" s="3">
         <f>IF(B23:B231="common", 4, IF(B23:B231="uncommon", 3, IF(B23:B231="rare", 0.792892156862745, 1)))</f>
@@ -1845,7 +1845,7 @@
         <v>188</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>33.97</v>
+        <v>34.54</v>
       </c>
       <c r="E24" s="3" t="inlineStr"/>
       <c r="F24" s="3">
@@ -1896,7 +1896,7 @@
         <v>33</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>0.14</v>
@@ -1949,10 +1949,10 @@
         <v>46</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="F26" s="3">
         <f>IF(B26:B234="common", 4, IF(B26:B234="uncommon", 3, IF(B26:B234="rare", 0.792892156862745, 1)))</f>
@@ -2002,7 +2002,7 @@
         <v>188</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>7.77</v>
+        <v>7.19</v>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3">
@@ -2056,7 +2056,7 @@
         <v>0.18</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="F28" s="3">
         <f>IF(B28:B236="common", 4, IF(B28:B236="uncommon", 3, IF(B28:B236="rare", 0.792892156862745, 1)))</f>
@@ -2106,7 +2106,7 @@
         <v>90</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.86</v>
+        <v>4.25</v>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3">
@@ -2157,7 +2157,7 @@
         <v>248</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>25.18</v>
+        <v>26.9</v>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3">
@@ -2208,7 +2208,7 @@
         <v>225</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>206.26</v>
+        <v>198.4</v>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3">
@@ -2259,10 +2259,10 @@
         <v>46</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="F32" s="3">
         <f>IF(B32:B240="common", 4, IF(B32:B240="uncommon", 3, IF(B32:B240="rare", 0.792892156862745, 1)))</f>
@@ -2312,7 +2312,7 @@
         <v>188</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>42.53</v>
+        <v>42.66</v>
       </c>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3">
@@ -2363,10 +2363,10 @@
         <v>33</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F34" s="3">
         <f>IF(B34:B242="common", 4, IF(B34:B242="uncommon", 3, IF(B34:B242="rare", 0.792892156862745, 1)))</f>
@@ -2416,7 +2416,7 @@
         <v>188</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>32.92</v>
+        <v>32.18</v>
       </c>
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3">
@@ -2467,10 +2467,10 @@
         <v>33</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="F36" s="3">
         <f>IF(B36:B244="common", 4, IF(B36:B244="uncommon", 3, IF(B36:B244="rare", 0.792892156862745, 1)))</f>
@@ -2520,7 +2520,7 @@
         <v>46</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>0.13</v>
@@ -2573,7 +2573,7 @@
         <v>33</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>0.18</v>
@@ -2626,10 +2626,10 @@
         <v>46</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="F39" s="3">
         <f>IF(B39:B247="common", 4, IF(B39:B247="uncommon", 3, IF(B39:B247="rare", 0.792892156862745, 1)))</f>
@@ -2682,7 +2682,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="F40" s="3">
         <f>IF(B40:B248="common", 4, IF(B40:B248="uncommon", 3, IF(B40:B248="rare", 0.792892156862745, 1)))</f>
@@ -2735,7 +2735,7 @@
         <v>0.09</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="F41" s="3">
         <f>IF(B41:B249="common", 4, IF(B41:B249="uncommon", 3, IF(B41:B249="rare", 0.792892156862745, 1)))</f>
@@ -2785,7 +2785,7 @@
         <v>248</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="E42" s="3" t="inlineStr"/>
       <c r="F42" s="3">
@@ -2836,10 +2836,10 @@
         <v>33</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="F43" s="3">
         <f>IF(B43:B251="common", 4, IF(B43:B251="uncommon", 3, IF(B43:B251="rare", 0.792892156862745, 1)))</f>
@@ -2889,7 +2889,7 @@
         <v>46</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>0.14</v>
@@ -2942,10 +2942,10 @@
         <v>21</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="F45" s="3">
         <f>IF(B45:B253="common", 4, IF(B45:B253="uncommon", 3, IF(B45:B253="rare", 0.792892156862745, 1)))</f>
@@ -2995,7 +2995,7 @@
         <v>21</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="E46" s="3" t="inlineStr"/>
       <c r="F46" s="3">
@@ -3046,10 +3046,10 @@
         <v>21</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="F47" s="3">
         <f>IF(B47:B255="common", 4, IF(B47:B255="uncommon", 3, IF(B47:B255="rare", 0.792892156862745, 1)))</f>
@@ -3099,10 +3099,10 @@
         <v>46</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F48" s="3">
         <f>IF(B48:B256="common", 4, IF(B48:B256="uncommon", 3, IF(B48:B256="rare", 0.792892156862745, 1)))</f>
@@ -3152,10 +3152,10 @@
         <v>33</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="F49" s="3">
         <f>IF(B49:B257="common", 4, IF(B49:B257="uncommon", 3, IF(B49:B257="rare", 0.792892156862745, 1)))</f>
@@ -3205,7 +3205,7 @@
         <v>188</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>20.09</v>
+        <v>20.11</v>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="3">
@@ -3256,10 +3256,10 @@
         <v>21</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="F51" s="3">
         <f>IF(B51:B259="common", 4, IF(B51:B259="uncommon", 3, IF(B51:B259="rare", 0.792892156862745, 1)))</f>
@@ -3312,7 +3312,7 @@
         <v>0.1</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F52" s="3">
         <f>IF(B52:B260="common", 4, IF(B52:B260="uncommon", 3, IF(B52:B260="rare", 0.792892156862745, 1)))</f>
@@ -3362,10 +3362,10 @@
         <v>46</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F53" s="3">
         <f>IF(B53:B261="common", 4, IF(B53:B261="uncommon", 3, IF(B53:B261="rare", 0.792892156862745, 1)))</f>
@@ -3415,10 +3415,10 @@
         <v>33</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="F54" s="3">
         <f>IF(B54:B262="common", 4, IF(B54:B262="uncommon", 3, IF(B54:B262="rare", 0.792892156862745, 1)))</f>
@@ -3471,7 +3471,7 @@
         <v>0.12</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="F55" s="3">
         <f>IF(B55:B263="common", 4, IF(B55:B263="uncommon", 3, IF(B55:B263="rare", 0.792892156862745, 1)))</f>
@@ -3524,7 +3524,7 @@
         <v>0.06</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F56" s="3">
         <f>IF(B56:B264="common", 4, IF(B56:B264="uncommon", 3, IF(B56:B264="rare", 0.792892156862745, 1)))</f>
@@ -3627,10 +3627,10 @@
         <v>21</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="F58" s="3">
         <f>IF(B58:B266="common", 4, IF(B58:B266="uncommon", 3, IF(B58:B266="rare", 0.792892156862745, 1)))</f>
@@ -3680,10 +3680,10 @@
         <v>33</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="F59" s="3">
         <f>IF(B59:B267="common", 4, IF(B59:B267="uncommon", 3, IF(B59:B267="rare", 0.792892156862745, 1)))</f>
@@ -3786,7 +3786,7 @@
         <v>248</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3">
@@ -3837,7 +3837,7 @@
         <v>225</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>13.84</v>
+        <v>13.57</v>
       </c>
       <c r="E62" s="3" t="inlineStr"/>
       <c r="F62" s="3">
@@ -3888,10 +3888,10 @@
         <v>46</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F63" s="3">
         <f>IF(B63:B271="common", 4, IF(B63:B271="uncommon", 3, IF(B63:B271="rare", 0.792892156862745, 1)))</f>
@@ -3941,10 +3941,10 @@
         <v>33</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="F64" s="3">
         <f>IF(B64:B272="common", 4, IF(B64:B272="uncommon", 3, IF(B64:B272="rare", 0.792892156862745, 1)))</f>
@@ -3997,7 +3997,7 @@
         <v>0.05</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F65" s="3">
         <f>IF(B65:B273="common", 4, IF(B65:B273="uncommon", 3, IF(B65:B273="rare", 0.792892156862745, 1)))</f>
@@ -4047,10 +4047,10 @@
         <v>33</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="F66" s="3">
         <f>IF(B66:B274="common", 4, IF(B66:B274="uncommon", 3, IF(B66:B274="rare", 0.792892156862745, 1)))</f>
@@ -4100,10 +4100,10 @@
         <v>21</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="F67" s="3">
         <f>IF(B67:B275="common", 4, IF(B67:B275="uncommon", 3, IF(B67:B275="rare", 0.792892156862745, 1)))</f>
@@ -4156,7 +4156,7 @@
         <v>0.08</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="F68" s="3">
         <f>IF(B68:B276="common", 4, IF(B68:B276="uncommon", 3, IF(B68:B276="rare", 0.792892156862745, 1)))</f>
@@ -4206,10 +4206,10 @@
         <v>21</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="F69" s="3">
         <f>IF(B69:B277="common", 4, IF(B69:B277="uncommon", 3, IF(B69:B277="rare", 0.792892156862745, 1)))</f>
@@ -4259,10 +4259,10 @@
         <v>46</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="F70" s="3">
         <f>IF(B70:B278="common", 4, IF(B70:B278="uncommon", 3, IF(B70:B278="rare", 0.792892156862745, 1)))</f>
@@ -4312,10 +4312,10 @@
         <v>33</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="F71" s="3">
         <f>IF(B71:B279="common", 4, IF(B71:B279="uncommon", 3, IF(B71:B279="rare", 0.792892156862745, 1)))</f>
@@ -4365,7 +4365,7 @@
         <v>248</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>5.54</v>
+        <v>4.99</v>
       </c>
       <c r="E72" s="3" t="inlineStr"/>
       <c r="F72" s="3">
@@ -4416,7 +4416,7 @@
         <v>225</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>13.18</v>
+        <v>12.98</v>
       </c>
       <c r="E73" s="3" t="inlineStr"/>
       <c r="F73" s="3">
@@ -4467,10 +4467,10 @@
         <v>33</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="F74" s="3">
         <f>IF(B74:B282="common", 4, IF(B74:B282="uncommon", 3, IF(B74:B282="rare", 0.792892156862745, 1)))</f>
@@ -4626,7 +4626,7 @@
         <v>33</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E77" s="3" t="n">
         <v>0.16</v>
@@ -4679,7 +4679,7 @@
         <v>90</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="E78" s="3" t="inlineStr"/>
       <c r="F78" s="3">
@@ -4730,7 +4730,7 @@
         <v>248</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>5.37</v>
+        <v>5.26</v>
       </c>
       <c r="E79" s="3" t="inlineStr"/>
       <c r="F79" s="3">
@@ -4784,7 +4784,7 @@
         <v>0.12</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="F80" s="3">
         <f>IF(B80:B288="common", 4, IF(B80:B288="uncommon", 3, IF(B80:B288="rare", 0.792892156862745, 1)))</f>
@@ -4837,7 +4837,7 @@
         <v>0.06</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="F81" s="3">
         <f>IF(B81:B289="common", 4, IF(B81:B289="uncommon", 3, IF(B81:B289="rare", 0.792892156862745, 1)))</f>
@@ -4887,10 +4887,10 @@
         <v>46</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="F82" s="3">
         <f>IF(B82:B290="common", 4, IF(B82:B290="uncommon", 3, IF(B82:B290="rare", 0.792892156862745, 1)))</f>
@@ -4943,7 +4943,7 @@
         <v>0.05</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="F83" s="3">
         <f>IF(B83:B291="common", 4, IF(B83:B291="uncommon", 3, IF(B83:B291="rare", 0.792892156862745, 1)))</f>
@@ -4993,10 +4993,10 @@
         <v>21</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="F84" s="3">
         <f>IF(B84:B292="common", 4, IF(B84:B292="uncommon", 3, IF(B84:B292="rare", 0.792892156862745, 1)))</f>
@@ -5046,10 +5046,10 @@
         <v>33</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F85" s="3">
         <f>IF(B85:B293="common", 4, IF(B85:B293="uncommon", 3, IF(B85:B293="rare", 0.792892156862745, 1)))</f>
@@ -5102,7 +5102,7 @@
         <v>0.11</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="F86" s="3">
         <f>IF(B86:B294="common", 4, IF(B86:B294="uncommon", 3, IF(B86:B294="rare", 0.792892156862745, 1)))</f>
@@ -5152,10 +5152,10 @@
         <v>33</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="F87" s="3">
         <f>IF(B87:B295="common", 4, IF(B87:B295="uncommon", 3, IF(B87:B295="rare", 0.792892156862745, 1)))</f>
@@ -5205,7 +5205,7 @@
         <v>46</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E88" s="3" t="n">
         <v>0.14</v>
@@ -5258,10 +5258,10 @@
         <v>33</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="F89" s="3">
         <f>IF(B89:B297="common", 4, IF(B89:B297="uncommon", 3, IF(B89:B297="rare", 0.792892156862745, 1)))</f>
@@ -5314,7 +5314,7 @@
         <v>0.1</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="F90" s="3">
         <f>IF(B90:B298="common", 4, IF(B90:B298="uncommon", 3, IF(B90:B298="rare", 0.792892156862745, 1)))</f>
@@ -5364,7 +5364,7 @@
         <v>188</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>27.43</v>
+        <v>27.57</v>
       </c>
       <c r="E91" s="3" t="inlineStr"/>
       <c r="F91" s="3">
@@ -5415,10 +5415,10 @@
         <v>46</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="F92" s="3">
         <f>IF(B92:B300="common", 4, IF(B92:B300="uncommon", 3, IF(B92:B300="rare", 0.792892156862745, 1)))</f>
@@ -5468,10 +5468,10 @@
         <v>21</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="F93" s="3">
         <f>IF(B93:B301="common", 4, IF(B93:B301="uncommon", 3, IF(B93:B301="rare", 0.792892156862745, 1)))</f>
@@ -5521,7 +5521,7 @@
         <v>90</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>1.06</v>
+        <v>0.82</v>
       </c>
       <c r="E94" s="3" t="inlineStr"/>
       <c r="F94" s="3">
@@ -5572,7 +5572,7 @@
         <v>248</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>4.34</v>
+        <v>4.23</v>
       </c>
       <c r="E95" s="3" t="inlineStr"/>
       <c r="F95" s="3">
@@ -5626,7 +5626,7 @@
         <v>0.08</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="F96" s="3">
         <f>IF(B96:B304="common", 4, IF(B96:B304="uncommon", 3, IF(B96:B304="rare", 0.792892156862745, 1)))</f>
@@ -5676,10 +5676,10 @@
         <v>21</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>1.07</v>
+        <v>0.96</v>
       </c>
       <c r="F97" s="3">
         <f>IF(B97:B305="common", 4, IF(B97:B305="uncommon", 3, IF(B97:B305="rare", 0.792892156862745, 1)))</f>
@@ -5729,10 +5729,10 @@
         <v>33</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="F98" s="3">
         <f>IF(B98:B306="common", 4, IF(B98:B306="uncommon", 3, IF(B98:B306="rare", 0.792892156862745, 1)))</f>
@@ -5782,10 +5782,10 @@
         <v>46</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="F99" s="3">
         <f>IF(B99:B307="common", 4, IF(B99:B307="uncommon", 3, IF(B99:B307="rare", 0.792892156862745, 1)))</f>
@@ -5835,7 +5835,7 @@
         <v>90</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="E100" s="3" t="inlineStr"/>
       <c r="F100" s="3">
@@ -5886,7 +5886,7 @@
         <v>248</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>4.81</v>
+        <v>4.89</v>
       </c>
       <c r="E101" s="3" t="inlineStr"/>
       <c r="F101" s="3">
@@ -5937,10 +5937,10 @@
         <v>33</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="F102" s="3">
         <f>IF(B102:B310="common", 4, IF(B102:B310="uncommon", 3, IF(B102:B310="rare", 0.792892156862745, 1)))</f>
@@ -5990,10 +5990,10 @@
         <v>46</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F103" s="3">
         <f>IF(B103:B311="common", 4, IF(B103:B311="uncommon", 3, IF(B103:B311="rare", 0.792892156862745, 1)))</f>
@@ -6043,7 +6043,7 @@
         <v>46</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E104" s="3" t="n">
         <v>0.16</v>
@@ -6099,7 +6099,7 @@
         <v>0.09</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="F105" s="3">
         <f>IF(B105:B313="common", 4, IF(B105:B313="uncommon", 3, IF(B105:B313="rare", 0.792892156862745, 1)))</f>
@@ -6149,10 +6149,10 @@
         <v>33</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="F106" s="3">
         <f>IF(B106:B314="common", 4, IF(B106:B314="uncommon", 3, IF(B106:B314="rare", 0.792892156862745, 1)))</f>
@@ -6202,7 +6202,7 @@
         <v>46</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0.14</v>
@@ -6258,7 +6258,7 @@
         <v>0.18</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="F108" s="3">
         <f>IF(B108:B316="common", 4, IF(B108:B316="uncommon", 3, IF(B108:B316="rare", 0.792892156862745, 1)))</f>
@@ -6308,7 +6308,7 @@
         <v>33</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E109" s="3" t="n">
         <v>0.17</v>
@@ -6361,7 +6361,7 @@
         <v>188</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="E110" s="3" t="inlineStr"/>
       <c r="F110" s="3">
@@ -6415,7 +6415,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F111" s="3">
         <f>IF(B111:B319="common", 4, IF(B111:B319="uncommon", 3, IF(B111:B319="rare", 0.792892156862745, 1)))</f>
@@ -6465,10 +6465,10 @@
         <v>46</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="F112" s="3">
         <f>IF(B112:B320="common", 4, IF(B112:B320="uncommon", 3, IF(B112:B320="rare", 0.792892156862745, 1)))</f>
@@ -6518,10 +6518,10 @@
         <v>46</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>1.06</v>
+        <v>0.96</v>
       </c>
       <c r="F113" s="3">
         <f>IF(B113:B321="common", 4, IF(B113:B321="uncommon", 3, IF(B113:B321="rare", 0.792892156862745, 1)))</f>
@@ -6571,10 +6571,10 @@
         <v>46</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F114" s="3">
         <f>IF(B114:B322="common", 4, IF(B114:B322="uncommon", 3, IF(B114:B322="rare", 0.792892156862745, 1)))</f>
@@ -6627,7 +6627,7 @@
         <v>0.09</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="F115" s="3">
         <f>IF(B115:B323="common", 4, IF(B115:B323="uncommon", 3, IF(B115:B323="rare", 0.792892156862745, 1)))</f>
@@ -6677,7 +6677,7 @@
         <v>46</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0.12</v>
@@ -6730,10 +6730,10 @@
         <v>21</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="F117" s="3">
         <f>IF(B117:B325="common", 4, IF(B117:B325="uncommon", 3, IF(B117:B325="rare", 0.792892156862745, 1)))</f>
@@ -6786,7 +6786,7 @@
         <v>0.08</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F118" s="3">
         <f>IF(B118:B326="common", 4, IF(B118:B326="uncommon", 3, IF(B118:B326="rare", 0.792892156862745, 1)))</f>
@@ -6839,7 +6839,7 @@
         <v>0.1</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>2.18</v>
+        <v>2.61</v>
       </c>
       <c r="F119" s="3">
         <f>IF(B119:B327="common", 4, IF(B119:B327="uncommon", 3, IF(B119:B327="rare", 0.792892156862745, 1)))</f>
@@ -6889,7 +6889,7 @@
         <v>90</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>6.41</v>
+        <v>6.32</v>
       </c>
       <c r="E120" s="3" t="inlineStr"/>
       <c r="F120" s="3">
@@ -6940,7 +6940,7 @@
         <v>248</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>18.51</v>
+        <v>17.12</v>
       </c>
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3">
@@ -6991,7 +6991,7 @@
         <v>154</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>12.65</v>
+        <v>12</v>
       </c>
       <c r="E122" s="3" t="inlineStr"/>
       <c r="F122" s="3">
@@ -7042,7 +7042,7 @@
         <v>90</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>10.27</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E123" s="3" t="inlineStr"/>
       <c r="F123" s="3">
@@ -7093,10 +7093,10 @@
         <v>21</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="F124" s="3">
         <f>IF(B124:B332="common", 4, IF(B124:B332="uncommon", 3, IF(B124:B332="rare", 0.792892156862745, 1)))</f>
@@ -7149,7 +7149,7 @@
         <v>0.24</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="F125" s="3">
         <f>IF(B125:B333="common", 4, IF(B125:B333="uncommon", 3, IF(B125:B333="rare", 0.792892156862745, 1)))</f>
@@ -7199,10 +7199,10 @@
         <v>21</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F126" s="3">
         <f>IF(B126:B334="common", 4, IF(B126:B334="uncommon", 3, IF(B126:B334="rare", 0.792892156862745, 1)))</f>
@@ -7252,7 +7252,7 @@
         <v>188</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>5.65</v>
+        <v>5.29</v>
       </c>
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3">
@@ -7303,10 +7303,10 @@
         <v>33</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="F128" s="3">
         <f>IF(B128:B336="common", 4, IF(B128:B336="uncommon", 3, IF(B128:B336="rare", 0.792892156862745, 1)))</f>
@@ -7359,7 +7359,7 @@
         <v>0.16</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F129" s="3">
         <f>IF(B129:B337="common", 4, IF(B129:B337="uncommon", 3, IF(B129:B337="rare", 0.792892156862745, 1)))</f>
@@ -7409,7 +7409,7 @@
         <v>188</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>9.49</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="E130" s="3" t="inlineStr"/>
       <c r="F130" s="3">
@@ -7463,7 +7463,7 @@
         <v>0.09</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="F131" s="3">
         <f>IF(B131:B339="common", 4, IF(B131:B339="uncommon", 3, IF(B131:B339="rare", 0.792892156862745, 1)))</f>
@@ -7513,10 +7513,10 @@
         <v>46</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="F132" s="3">
         <f>IF(B132:B340="common", 4, IF(B132:B340="uncommon", 3, IF(B132:B340="rare", 0.792892156862745, 1)))</f>
@@ -7569,7 +7569,7 @@
         <v>0.1</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="F133" s="3">
         <f>IF(B133:B341="common", 4, IF(B133:B341="uncommon", 3, IF(B133:B341="rare", 0.792892156862745, 1)))</f>
@@ -7675,7 +7675,7 @@
         <v>0.05</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F135" s="3">
         <f>IF(B135:B343="common", 4, IF(B135:B343="uncommon", 3, IF(B135:B343="rare", 0.792892156862745, 1)))</f>
@@ -7725,7 +7725,7 @@
         <v>90</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="E136" s="3" t="inlineStr"/>
       <c r="F136" s="3">
@@ -7776,7 +7776,7 @@
         <v>248</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>7.37</v>
+        <v>7.43</v>
       </c>
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3">
@@ -7827,7 +7827,7 @@
         <v>46</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E138" s="3" t="n">
         <v>0.14</v>
@@ -7883,7 +7883,7 @@
         <v>0.09</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="F139" s="3">
         <f>IF(B139:B347="common", 4, IF(B139:B347="uncommon", 3, IF(B139:B347="rare", 0.792892156862745, 1)))</f>
@@ -7933,7 +7933,7 @@
         <v>188</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>5.82</v>
+        <v>5.73</v>
       </c>
       <c r="E140" s="3" t="inlineStr"/>
       <c r="F140" s="3">
@@ -7984,10 +7984,10 @@
         <v>21</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="F141" s="3">
         <f>IF(B141:B349="common", 4, IF(B141:B349="uncommon", 3, IF(B141:B349="rare", 0.792892156862745, 1)))</f>
@@ -8037,10 +8037,10 @@
         <v>33</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="F142" s="3">
         <f>IF(B142:B350="common", 4, IF(B142:B350="uncommon", 3, IF(B142:B350="rare", 0.792892156862745, 1)))</f>
@@ -8093,7 +8093,7 @@
         <v>0.05</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="F143" s="3">
         <f>IF(B143:B351="common", 4, IF(B143:B351="uncommon", 3, IF(B143:B351="rare", 0.792892156862745, 1)))</f>
@@ -8146,7 +8146,7 @@
         <v>0.06</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F144" s="3">
         <f>IF(B144:B352="common", 4, IF(B144:B352="uncommon", 3, IF(B144:B352="rare", 0.792892156862745, 1)))</f>
@@ -8196,10 +8196,10 @@
         <v>33</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F145" s="3">
         <f>IF(B145:B353="common", 4, IF(B145:B353="uncommon", 3, IF(B145:B353="rare", 0.792892156862745, 1)))</f>
@@ -8249,10 +8249,10 @@
         <v>33</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="F146" s="3">
         <f>IF(B146:B354="common", 4, IF(B146:B354="uncommon", 3, IF(B146:B354="rare", 0.792892156862745, 1)))</f>
@@ -8302,10 +8302,10 @@
         <v>46</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="F147" s="3">
         <f>IF(B147:B355="common", 4, IF(B147:B355="uncommon", 3, IF(B147:B355="rare", 0.792892156862745, 1)))</f>
@@ -8358,7 +8358,7 @@
         <v>0.1</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="F148" s="3">
         <f>IF(B148:B356="common", 4, IF(B148:B356="uncommon", 3, IF(B148:B356="rare", 0.792892156862745, 1)))</f>
@@ -8408,10 +8408,10 @@
         <v>46</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="F149" s="3">
         <f>IF(B149:B357="common", 4, IF(B149:B357="uncommon", 3, IF(B149:B357="rare", 0.792892156862745, 1)))</f>
@@ -8461,7 +8461,7 @@
         <v>188</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>24.97</v>
+        <v>24.78</v>
       </c>
       <c r="E150" s="3" t="inlineStr"/>
       <c r="F150" s="3">
@@ -8512,10 +8512,10 @@
         <v>33</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="F151" s="3">
         <f>IF(B151:B359="common", 4, IF(B151:B359="uncommon", 3, IF(B151:B359="rare", 0.792892156862745, 1)))</f>
@@ -8618,10 +8618,10 @@
         <v>46</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="F153" s="3">
         <f>IF(B153:B361="common", 4, IF(B153:B361="uncommon", 3, IF(B153:B361="rare", 0.792892156862745, 1)))</f>
@@ -8671,7 +8671,7 @@
         <v>188</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>17.04</v>
+        <v>16.93</v>
       </c>
       <c r="E154" s="3" t="inlineStr"/>
       <c r="F154" s="3">
@@ -8722,10 +8722,10 @@
         <v>33</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F155" s="3">
         <f>IF(B155:B363="common", 4, IF(B155:B363="uncommon", 3, IF(B155:B363="rare", 0.792892156862745, 1)))</f>
@@ -8778,7 +8778,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F156" s="3">
         <f>IF(B156:B364="common", 4, IF(B156:B364="uncommon", 3, IF(B156:B364="rare", 0.792892156862745, 1)))</f>
@@ -8831,7 +8831,7 @@
         <v>0.06</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F157" s="3">
         <f>IF(B157:B365="common", 4, IF(B157:B365="uncommon", 3, IF(B157:B365="rare", 0.792892156862745, 1)))</f>
@@ -8881,7 +8881,7 @@
         <v>33</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E158" s="3" t="n">
         <v>0.16</v>
@@ -8934,10 +8934,10 @@
         <v>33</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="F159" s="3">
         <f>IF(B159:B367="common", 4, IF(B159:B367="uncommon", 3, IF(B159:B367="rare", 0.792892156862745, 1)))</f>
@@ -8987,10 +8987,10 @@
         <v>46</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F160" s="3">
         <f>IF(B160:B368="common", 4, IF(B160:B368="uncommon", 3, IF(B160:B368="rare", 0.792892156862745, 1)))</f>
@@ -9040,7 +9040,7 @@
         <v>188</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>18.79</v>
+        <v>18.6</v>
       </c>
       <c r="E161" s="3" t="inlineStr"/>
       <c r="F161" s="3">
@@ -9091,10 +9091,10 @@
         <v>21</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="F162" s="3">
         <f>IF(B162:B370="common", 4, IF(B162:B370="uncommon", 3, IF(B162:B370="rare", 0.792892156862745, 1)))</f>
@@ -9144,10 +9144,10 @@
         <v>33</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F163" s="3">
         <f>IF(B163:B371="common", 4, IF(B163:B371="uncommon", 3, IF(B163:B371="rare", 0.792892156862745, 1)))</f>
@@ -9197,10 +9197,10 @@
         <v>33</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F164" s="3">
         <f>IF(B164:B372="common", 4, IF(B164:B372="uncommon", 3, IF(B164:B372="rare", 0.792892156862745, 1)))</f>
@@ -9253,7 +9253,7 @@
         <v>0.05</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="F165" s="3">
         <f>IF(B165:B373="common", 4, IF(B165:B373="uncommon", 3, IF(B165:B373="rare", 0.792892156862745, 1)))</f>
@@ -9303,10 +9303,10 @@
         <v>33</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="F166" s="3">
         <f>IF(B166:B374="common", 4, IF(B166:B374="uncommon", 3, IF(B166:B374="rare", 0.792892156862745, 1)))</f>
@@ -9356,10 +9356,10 @@
         <v>46</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F167" s="3">
         <f>IF(B167:B375="common", 4, IF(B167:B375="uncommon", 3, IF(B167:B375="rare", 0.792892156862745, 1)))</f>
@@ -9409,10 +9409,10 @@
         <v>33</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="F168" s="3">
         <f>IF(B168:B376="common", 4, IF(B168:B376="uncommon", 3, IF(B168:B376="rare", 0.792892156862745, 1)))</f>
@@ -9462,7 +9462,7 @@
         <v>46</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E169" s="3" t="n">
         <v>0.17</v>
@@ -9518,7 +9518,7 @@
         <v>0.05</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F170" s="3">
         <f>IF(B170:B378="common", 4, IF(B170:B378="uncommon", 3, IF(B170:B378="rare", 0.792892156862745, 1)))</f>
@@ -9568,10 +9568,10 @@
         <v>33</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="F171" s="3">
         <f>IF(B171:B379="common", 4, IF(B171:B379="uncommon", 3, IF(B171:B379="rare", 0.792892156862745, 1)))</f>
@@ -9621,10 +9621,10 @@
         <v>33</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="F172" s="3">
         <f>IF(B172:B380="common", 4, IF(B172:B380="uncommon", 3, IF(B172:B380="rare", 0.792892156862745, 1)))</f>
@@ -9674,10 +9674,10 @@
         <v>33</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="F173" s="3">
         <f>IF(B173:B381="common", 4, IF(B173:B381="uncommon", 3, IF(B173:B381="rare", 0.792892156862745, 1)))</f>
@@ -9780,10 +9780,10 @@
         <v>46</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="F175" s="3">
         <f>IF(B175:B383="common", 4, IF(B175:B383="uncommon", 3, IF(B175:B383="rare", 0.792892156862745, 1)))</f>
@@ -9833,10 +9833,10 @@
         <v>33</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F176" s="3">
         <f>IF(B176:B384="common", 4, IF(B176:B384="uncommon", 3, IF(B176:B384="rare", 0.792892156862745, 1)))</f>
@@ -9886,10 +9886,10 @@
         <v>46</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="F177" s="3">
         <f>IF(B177:B385="common", 4, IF(B177:B385="uncommon", 3, IF(B177:B385="rare", 0.792892156862745, 1)))</f>
@@ -9939,10 +9939,10 @@
         <v>33</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="F178" s="3">
         <f>IF(B178:B386="common", 4, IF(B178:B386="uncommon", 3, IF(B178:B386="rare", 0.792892156862745, 1)))</f>
@@ -9992,10 +9992,10 @@
         <v>46</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>0.83</v>
+        <v>1.07</v>
       </c>
       <c r="F179" s="3">
         <f>IF(B179:B387="common", 4, IF(B179:B387="uncommon", 3, IF(B179:B387="rare", 0.792892156862745, 1)))</f>
@@ -10045,7 +10045,7 @@
         <v>46</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E180" s="3" t="n">
         <v>0.18</v>
@@ -10098,7 +10098,7 @@
         <v>188</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>40</v>
+        <v>38.56</v>
       </c>
       <c r="E181" s="3" t="inlineStr"/>
       <c r="F181" s="3">
@@ -10152,7 +10152,7 @@
         <v>0.16</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="F182" s="3">
         <f>IF(B182:B390="common", 4, IF(B182:B390="uncommon", 3, IF(B182:B390="rare", 0.792892156862745, 1)))</f>
@@ -10202,10 +10202,10 @@
         <v>46</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="F183" s="3">
         <f>IF(B183:B391="common", 4, IF(B183:B391="uncommon", 3, IF(B183:B391="rare", 0.792892156862745, 1)))</f>
@@ -10255,7 +10255,7 @@
         <v>154</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>2.85</v>
+        <v>2.19</v>
       </c>
       <c r="E184" s="3" t="inlineStr"/>
       <c r="F184" s="3">
@@ -10306,10 +10306,10 @@
         <v>46</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="F185" s="3">
         <f>IF(B185:B393="common", 4, IF(B185:B393="uncommon", 3, IF(B185:B393="rare", 0.792892156862745, 1)))</f>
@@ -10359,7 +10359,7 @@
         <v>188</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>6.7</v>
+        <v>6.47</v>
       </c>
       <c r="E186" s="3" t="inlineStr"/>
       <c r="F186" s="3">
@@ -10413,7 +10413,7 @@
         <v>0.1</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="F187" s="3">
         <f>IF(B187:B395="common", 4, IF(B187:B395="uncommon", 3, IF(B187:B395="rare", 0.792892156862745, 1)))</f>
@@ -10466,7 +10466,7 @@
         <v>0.06</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="F188" s="3">
         <f>IF(B188:B396="common", 4, IF(B188:B396="uncommon", 3, IF(B188:B396="rare", 0.792892156862745, 1)))</f>
@@ -10516,10 +10516,10 @@
         <v>33</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="F189" s="3">
         <f>IF(B189:B397="common", 4, IF(B189:B397="uncommon", 3, IF(B189:B397="rare", 0.792892156862745, 1)))</f>
@@ -10569,10 +10569,10 @@
         <v>21</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="F190" s="3">
         <f>IF(B190:B398="common", 4, IF(B190:B398="uncommon", 3, IF(B190:B398="rare", 0.792892156862745, 1)))</f>
@@ -10622,10 +10622,10 @@
         <v>33</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="F191" s="3">
         <f>IF(B191:B399="common", 4, IF(B191:B399="uncommon", 3, IF(B191:B399="rare", 0.792892156862745, 1)))</f>
@@ -10675,10 +10675,10 @@
         <v>46</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="F192" s="3">
         <f>IF(B192:B400="common", 4, IF(B192:B400="uncommon", 3, IF(B192:B400="rare", 0.792892156862745, 1)))</f>
@@ -10728,7 +10728,7 @@
         <v>90</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>0.55</v>
+        <v>0.73</v>
       </c>
       <c r="E193" s="3" t="inlineStr"/>
       <c r="F193" s="3">
@@ -10779,7 +10779,7 @@
         <v>248</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>9.69</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="E194" s="3" t="inlineStr"/>
       <c r="F194" s="3">
@@ -10830,7 +10830,7 @@
         <v>225</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>57.96</v>
+        <v>57.55</v>
       </c>
       <c r="E195" s="3" t="inlineStr"/>
       <c r="F195" s="3">
@@ -10934,7 +10934,7 @@
         <v>21</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="E197" s="3" t="n">
         <v>0.77</v>
@@ -10990,7 +10990,7 @@
         <v>0.06</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F198" s="3">
         <f>IF(B198:B406="common", 4, IF(B198:B406="uncommon", 3, IF(B198:B406="rare", 0.792892156862745, 1)))</f>
@@ -11040,10 +11040,10 @@
         <v>46</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="F199" s="3">
         <f>IF(B199:B407="common", 4, IF(B199:B407="uncommon", 3, IF(B199:B407="rare", 0.792892156862745, 1)))</f>
@@ -11096,7 +11096,7 @@
         <v>0.1</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F200" s="3">
         <f>IF(B200:B408="common", 4, IF(B200:B408="uncommon", 3, IF(B200:B408="rare", 0.792892156862745, 1)))</f>
@@ -11146,7 +11146,7 @@
         <v>188</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>24.22</v>
+        <v>23.06</v>
       </c>
       <c r="E201" s="3" t="inlineStr"/>
       <c r="F201" s="3">
@@ -11250,10 +11250,10 @@
         <v>46</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="F203" s="3">
         <f>IF(B203:B411="common", 4, IF(B203:B411="uncommon", 3, IF(B203:B411="rare", 0.792892156862745, 1)))</f>
@@ -11306,7 +11306,7 @@
         <v>0.13</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="F204" s="3">
         <f>IF(B204:B412="common", 4, IF(B204:B412="uncommon", 3, IF(B204:B412="rare", 0.792892156862745, 1)))</f>
@@ -11356,7 +11356,7 @@
         <v>90</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="E205" s="3" t="inlineStr"/>
       <c r="F205" s="3">
@@ -11407,7 +11407,7 @@
         <v>248</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>6.9</v>
+        <v>6.27</v>
       </c>
       <c r="E206" s="3" t="inlineStr"/>
       <c r="F206" s="3">
@@ -11458,7 +11458,7 @@
         <v>90</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="E207" s="3" t="inlineStr"/>
       <c r="F207" s="3">
@@ -11509,7 +11509,7 @@
         <v>248</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>7.15</v>
+        <v>7.23</v>
       </c>
       <c r="E208" s="3" t="inlineStr"/>
       <c r="F208" s="3">
@@ -11560,7 +11560,7 @@
         <v>225</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>46.15</v>
+        <v>47.08</v>
       </c>
       <c r="E209" s="3" t="inlineStr"/>
       <c r="F209" s="3">
@@ -18298,7 +18298,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>0.4304347826086957</v>
+        <v>0.4008695652173913</v>
       </c>
     </row>
     <row r="3">
@@ -18308,7 +18308,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>0.4881818181818181</v>
+        <v>0.4536363636363635</v>
       </c>
     </row>
     <row r="4">
@@ -18318,7 +18318,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>0.2016211484593838</v>
+        <v>0.1925595238095238</v>
       </c>
     </row>
     <row r="5">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>5.329323789133571</v>
+        <v>5.212912706255096</v>
       </c>
     </row>
     <row r="6">
@@ -18368,7 +18368,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>1.740372340425532</v>
+        <v>1.716223404255319</v>
       </c>
     </row>
     <row r="10">
@@ -18378,7 +18378,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1.954666666666667</v>
+        <v>1.917866666666667</v>
       </c>
     </row>
     <row r="11">
@@ -18388,7 +18388,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>0.3157777777777778</v>
+        <v>0.3143333333333334</v>
       </c>
     </row>
     <row r="12">
@@ -18398,7 +18398,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>0.1305844155844156</v>
+        <v>0.121038961038961</v>
       </c>
     </row>
     <row r="13">
@@ -18408,7 +18408,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>0.5363709677419355</v>
+        <v>0.5255241935483871</v>
       </c>
     </row>
     <row r="14">
@@ -18438,7 +18438,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>4.677772168196328</v>
+        <v>4.594986558842668</v>
       </c>
     </row>
     <row r="17">
@@ -18448,7 +18448,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>11.12733370657979</v>
+        <v>10.85496471776104</v>
       </c>
     </row>
     <row r="18">
@@ -18458,7 +18458,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1.397333706579793</v>
+        <v>0.9649647177610419</v>
       </c>
     </row>
     <row r="19">
@@ -18468,7 +18468,7 @@
         </is>
       </c>
       <c r="B19" s="14" t="n">
-        <v>1.14361086398559</v>
+        <v>1.097569738904049</v>
       </c>
     </row>
     <row r="20">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="B20" s="15" t="n">
-        <v>0.1436108639855902</v>
+        <v>0.09756973890404863</v>
       </c>
     </row>
     <row r="21">
